--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\datacontract-github-dev\datacontract-cli\tests\fixtures\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmaresma\Repos\datacontract-cli\tests\fixtures\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D316ADF1-8766-4715-B007-DB5AD54C7BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA53D90-0BEE-43B6-ADE3-52491332DBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="345" windowWidth="27360" windowHeight="14340" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="280">
   <si>
     <t>Property</t>
   </si>
@@ -972,6 +972,15 @@
   </si>
   <si>
     <t>[25,75]</t>
+  </si>
+  <si>
+    <t>ScdType</t>
+  </si>
+  <si>
+    <t>isMasked</t>
+  </si>
+  <si>
+    <t>True</t>
   </si>
 </sst>
 </file>
@@ -1710,13 +1719,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="3"/>
+    <col min="2" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1725,7 +1734,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>46</v>
       </c>
@@ -1734,14 +1743,14 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>43</v>
       </c>
@@ -1754,7 +1763,7 @@
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>44</v>
       </c>
@@ -1767,7 +1776,7 @@
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>45</v>
       </c>
@@ -1780,7 +1789,7 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>47</v>
       </c>
@@ -1793,7 +1802,7 @@
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>48</v>
       </c>
@@ -1806,7 +1815,7 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -1817,7 +1826,7 @@
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -1828,7 +1837,7 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>34</v>
       </c>
@@ -1841,7 +1850,7 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>35</v>
       </c>
@@ -1854,7 +1863,7 @@
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>36</v>
       </c>
@@ -1867,7 +1876,7 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>137</v>
       </c>
@@ -1880,7 +1889,7 @@
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
         <v>138</v>
       </c>
@@ -1895,7 +1904,7 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
       <c r="B19" s="24" t="s">
         <v>146</v>
@@ -1908,7 +1917,7 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -1919,7 +1928,7 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>140</v>
       </c>
@@ -1934,7 +1943,7 @@
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" s="13" t="s">
         <v>149</v>
@@ -1947,7 +1956,7 @@
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="13" t="s">
         <v>141</v>
@@ -1960,7 +1969,7 @@
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="13" t="s">
         <v>162</v>
@@ -1973,7 +1982,7 @@
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -1984,7 +1993,7 @@
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>39</v>
       </c>
@@ -1999,7 +2008,7 @@
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>38</v>
       </c>
@@ -2014,7 +2023,7 @@
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>41</v>
       </c>
@@ -2029,7 +2038,7 @@
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2040,7 +2049,7 @@
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2051,7 +2060,7 @@
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2074,25 +2083,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95CB51A-C5C4-224E-AA94-69EA1F503FF6}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.1328125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="22" customWidth="1"/>
-    <col min="3" max="16384" width="10.796875" style="22"/>
+    <col min="1" max="1" width="26.140625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="22" customWidth="1"/>
+    <col min="3" max="16384" width="10.85546875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
-    <row r="4" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>90</v>
       </c>
@@ -2100,7 +2109,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>91</v>
       </c>
@@ -2108,7 +2117,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>92</v>
       </c>
@@ -2129,24 +2138,24 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29635FC6-19E5-6E43-84D3-3161FAC792B3}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="90" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="2"/>
+    <col min="3" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
@@ -2154,7 +2163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>49</v>
       </c>
@@ -2163,7 +2172,7 @@
         <v>fulfillment</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>237</v>
       </c>
@@ -2171,63 +2180,63 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
     </row>
@@ -2242,33 +2251,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ABE851-FB8B-2145-B7F8-5CF6722D55A6}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="45" style="2" customWidth="1"/>
-    <col min="4" max="4" width="1.796875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="1.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="2" customWidth="1"/>
     <col min="7" max="8" width="10" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="2"/>
+    <col min="9" max="9" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>21</v>
       </c>
@@ -2277,7 +2286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -2286,11 +2295,11 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
@@ -2299,7 +2308,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>8</v>
       </c>
@@ -2308,7 +2317,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>23</v>
       </c>
@@ -2317,7 +2326,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>24</v>
       </c>
@@ -2326,11 +2335,11 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>37</v>
       </c>
@@ -2340,11 +2349,11 @@
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>25</v>
       </c>
@@ -2352,7 +2361,7 @@
       <c r="C14" s="5"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
@@ -2360,7 +2369,7 @@
       <c r="C15" s="5"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
@@ -2369,17 +2378,17 @@
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="7"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
         <v>28</v>
@@ -2388,7 +2397,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
         <v>29</v>
@@ -2397,7 +2406,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
         <v>30</v>
@@ -2406,11 +2415,11 @@
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>12</v>
       </c>
@@ -2440,47 +2449,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AL49"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:AN49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.46484375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.1328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.7109375" style="2" customWidth="1"/>
     <col min="7" max="8" width="10" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="28.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="20" width="19" style="2" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="37" width="15.46484375" style="2" customWidth="1"/>
-    <col min="38" max="38" width="26.1328125" style="2" customWidth="1"/>
-    <col min="39" max="16384" width="8.796875" style="2"/>
+    <col min="21" max="21" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="37" width="15.42578125" style="2" customWidth="1"/>
+    <col min="38" max="38" width="26.140625" style="2" customWidth="1"/>
+    <col min="39" max="39" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:40" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
@@ -2491,7 +2502,7 @@
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
@@ -2502,7 +2513,7 @@
       <c r="D6" s="41"/>
       <c r="E6" s="41"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2513,7 +2524,7 @@
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -2524,7 +2535,7 @@
       <c r="D8" s="43"/>
       <c r="E8" s="44"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -2535,7 +2546,7 @@
       <c r="D9" s="43"/>
       <c r="E9" s="44"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>52</v>
       </c>
@@ -2546,7 +2557,7 @@
       <c r="D10" s="43"/>
       <c r="E10" s="44"/>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
@@ -2557,7 +2568,7 @@
       <c r="D11" s="41"/>
       <c r="E11" s="41"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="W12" s="19" t="s">
         <v>77</v>
       </c>
@@ -2575,8 +2586,12 @@
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
       <c r="AK12" s="21"/>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AN12" s="20"/>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>0</v>
       </c>
@@ -2691,8 +2706,14 @@
       <c r="AL13" s="10" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="14" spans="1:38" ht="47.25" x14ac:dyDescent="0.5">
+      <c r="AM13" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="AN13" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" ht="63" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>178</v>
       </c>
@@ -2763,8 +2784,12 @@
       <c r="AJ14" s="15"/>
       <c r="AK14" s="15"/>
       <c r="AL14" s="28"/>
-    </row>
-    <row r="15" spans="1:38" ht="47.25" x14ac:dyDescent="0.5">
+      <c r="AM14" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="15"/>
+    </row>
+    <row r="15" spans="1:40" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>189</v>
       </c>
@@ -2817,8 +2842,12 @@
       <c r="AJ15" s="15"/>
       <c r="AK15" s="15"/>
       <c r="AL15" s="28"/>
-    </row>
-    <row r="16" spans="1:38" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="AM15" s="15">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="15"/>
+    </row>
+    <row r="16" spans="1:40" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>193</v>
       </c>
@@ -2881,8 +2910,12 @@
       <c r="AJ16" s="15"/>
       <c r="AK16" s="15"/>
       <c r="AL16" s="28"/>
-    </row>
-    <row r="17" spans="1:38" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="AM16" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="15"/>
+    </row>
+    <row r="17" spans="1:40" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>199</v>
       </c>
@@ -2945,8 +2978,12 @@
       <c r="AJ17" s="15"/>
       <c r="AK17" s="15"/>
       <c r="AL17" s="28"/>
-    </row>
-    <row r="18" spans="1:38" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="AM17" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="15"/>
+    </row>
+    <row r="18" spans="1:40" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>203</v>
       </c>
@@ -3009,8 +3046,12 @@
       <c r="AJ18" s="15"/>
       <c r="AK18" s="15"/>
       <c r="AL18" s="28"/>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM18" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="15"/>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>208</v>
       </c>
@@ -3073,8 +3114,12 @@
       <c r="AJ19" s="15"/>
       <c r="AK19" s="15"/>
       <c r="AL19" s="28"/>
-    </row>
-    <row r="20" spans="1:38" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="AM19" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="15"/>
+    </row>
+    <row r="20" spans="1:40" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>211</v>
       </c>
@@ -3139,8 +3184,12 @@
       <c r="AJ20" s="15"/>
       <c r="AK20" s="15"/>
       <c r="AL20" s="28"/>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM20" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="15"/>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>218</v>
       </c>
@@ -3193,8 +3242,14 @@
       <c r="AJ21" s="15"/>
       <c r="AK21" s="15"/>
       <c r="AL21" s="28"/>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM21" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>222</v>
       </c>
@@ -3255,8 +3310,14 @@
       <c r="AJ22" s="15"/>
       <c r="AK22" s="15"/>
       <c r="AL22" s="28"/>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM22" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>226</v>
       </c>
@@ -3317,8 +3378,14 @@
       <c r="AJ23" s="15"/>
       <c r="AK23" s="15"/>
       <c r="AL23" s="28"/>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM23" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>230</v>
       </c>
@@ -3377,8 +3444,14 @@
       <c r="AJ24" s="15"/>
       <c r="AK24" s="15"/>
       <c r="AL24" s="28"/>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM24" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -3417,8 +3490,10 @@
       <c r="AJ25" s="15"/>
       <c r="AK25" s="15"/>
       <c r="AL25" s="28"/>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM25" s="15"/>
+      <c r="AN25" s="15"/>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -3457,8 +3532,10 @@
       <c r="AJ26" s="15"/>
       <c r="AK26" s="15"/>
       <c r="AL26" s="28"/>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM26" s="15"/>
+      <c r="AN26" s="15"/>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -3497,8 +3574,10 @@
       <c r="AJ27" s="15"/>
       <c r="AK27" s="15"/>
       <c r="AL27" s="28"/>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -3537,8 +3616,10 @@
       <c r="AJ28" s="15"/>
       <c r="AK28" s="15"/>
       <c r="AL28" s="28"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM28" s="15"/>
+      <c r="AN28" s="15"/>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -3577,8 +3658,10 @@
       <c r="AJ29" s="15"/>
       <c r="AK29" s="15"/>
       <c r="AL29" s="28"/>
-    </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM29" s="15"/>
+      <c r="AN29" s="15"/>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -3617,8 +3700,10 @@
       <c r="AJ30" s="15"/>
       <c r="AK30" s="15"/>
       <c r="AL30" s="28"/>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM30" s="15"/>
+      <c r="AN30" s="15"/>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -3657,8 +3742,10 @@
       <c r="AJ31" s="15"/>
       <c r="AK31" s="15"/>
       <c r="AL31" s="28"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM31" s="15"/>
+      <c r="AN31" s="15"/>
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -3697,8 +3784,10 @@
       <c r="AJ32" s="15"/>
       <c r="AK32" s="15"/>
       <c r="AL32" s="28"/>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM32" s="15"/>
+      <c r="AN32" s="15"/>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -3737,8 +3826,10 @@
       <c r="AJ33" s="15"/>
       <c r="AK33" s="15"/>
       <c r="AL33" s="28"/>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM33" s="15"/>
+      <c r="AN33" s="15"/>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -3777,8 +3868,10 @@
       <c r="AJ34" s="15"/>
       <c r="AK34" s="15"/>
       <c r="AL34" s="28"/>
-    </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM34" s="15"/>
+      <c r="AN34" s="15"/>
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -3817,8 +3910,10 @@
       <c r="AJ35" s="15"/>
       <c r="AK35" s="15"/>
       <c r="AL35" s="28"/>
-    </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM35" s="15"/>
+      <c r="AN35" s="15"/>
+    </row>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -3857,8 +3952,10 @@
       <c r="AJ36" s="15"/>
       <c r="AK36" s="15"/>
       <c r="AL36" s="28"/>
-    </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM36" s="15"/>
+      <c r="AN36" s="15"/>
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -3897,8 +3994,10 @@
       <c r="AJ37" s="15"/>
       <c r="AK37" s="15"/>
       <c r="AL37" s="28"/>
-    </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM37" s="15"/>
+      <c r="AN37" s="15"/>
+    </row>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -3937,8 +4036,10 @@
       <c r="AJ38" s="15"/>
       <c r="AK38" s="15"/>
       <c r="AL38" s="28"/>
-    </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM38" s="15"/>
+      <c r="AN38" s="15"/>
+    </row>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -3977,8 +4078,10 @@
       <c r="AJ39" s="15"/>
       <c r="AK39" s="15"/>
       <c r="AL39" s="28"/>
-    </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM39" s="15"/>
+      <c r="AN39" s="15"/>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -4017,8 +4120,10 @@
       <c r="AJ40" s="15"/>
       <c r="AK40" s="15"/>
       <c r="AL40" s="28"/>
-    </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM40" s="15"/>
+      <c r="AN40" s="15"/>
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -4057,8 +4162,10 @@
       <c r="AJ41" s="15"/>
       <c r="AK41" s="15"/>
       <c r="AL41" s="28"/>
-    </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM41" s="15"/>
+      <c r="AN41" s="15"/>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -4097,8 +4204,10 @@
       <c r="AJ42" s="15"/>
       <c r="AK42" s="15"/>
       <c r="AL42" s="28"/>
-    </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM42" s="15"/>
+      <c r="AN42" s="15"/>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -4137,8 +4246,10 @@
       <c r="AJ43" s="15"/>
       <c r="AK43" s="15"/>
       <c r="AL43" s="28"/>
-    </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM43" s="15"/>
+      <c r="AN43" s="15"/>
+    </row>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -4177,8 +4288,10 @@
       <c r="AJ44" s="15"/>
       <c r="AK44" s="15"/>
       <c r="AL44" s="28"/>
-    </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM44" s="15"/>
+      <c r="AN44" s="15"/>
+    </row>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -4217,8 +4330,10 @@
       <c r="AJ45" s="15"/>
       <c r="AK45" s="15"/>
       <c r="AL45" s="28"/>
-    </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM45" s="15"/>
+      <c r="AN45" s="15"/>
+    </row>
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -4257,8 +4372,10 @@
       <c r="AJ46" s="15"/>
       <c r="AK46" s="15"/>
       <c r="AL46" s="28"/>
-    </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM46" s="15"/>
+      <c r="AN46" s="15"/>
+    </row>
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -4297,8 +4414,10 @@
       <c r="AJ47" s="15"/>
       <c r="AK47" s="15"/>
       <c r="AL47" s="28"/>
-    </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM47" s="15"/>
+      <c r="AN47" s="15"/>
+    </row>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4337,8 +4456,10 @@
       <c r="AJ48" s="15"/>
       <c r="AK48" s="15"/>
       <c r="AL48" s="28"/>
-    </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.5">
+      <c r="AM48" s="15"/>
+      <c r="AN48" s="15"/>
+    </row>
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -4377,6 +4498,8 @@
       <c r="AJ49" s="15"/>
       <c r="AK49" s="15"/>
       <c r="AL49" s="28"/>
+      <c r="AM49" s="15"/>
+      <c r="AN49" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4420,41 +4543,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0F4C5A-BE41-6140-9B9B-80B8DB7D1AD7}">
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.46484375" style="30" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" style="30" customWidth="1"/>
     <col min="2" max="2" width="22" style="30" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="40.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="30" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="30" customWidth="1"/>
     <col min="7" max="7" width="19" style="30" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.796875" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.46484375" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.46484375" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.796875" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.796875" style="30" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="30"/>
+    <col min="9" max="9" width="22.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="30" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="29"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
         <v>151</v>
       </c>
       <c r="B2" s="31"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>17</v>
       </c>
@@ -4495,7 +4618,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
         <v>173</v>
       </c>
@@ -4522,7 +4645,7 @@
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
     </row>
-    <row r="6" spans="1:13" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
         <v>173</v>
       </c>
@@ -4545,7 +4668,7 @@
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>173</v>
       </c>
@@ -4572,7 +4695,7 @@
       <c r="L7" s="36"/>
       <c r="M7" s="36"/>
     </row>
-    <row r="8" spans="1:13" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>173</v>
       </c>
@@ -4599,7 +4722,7 @@
       <c r="L8" s="36"/>
       <c r="M8" s="36"/>
     </row>
-    <row r="9" spans="1:13" ht="47.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
         <v>173</v>
       </c>
@@ -4626,7 +4749,7 @@
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>173</v>
       </c>
@@ -4653,7 +4776,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>173</v>
       </c>
@@ -4680,7 +4803,7 @@
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="15"/>
@@ -4695,7 +4818,7 @@
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="15"/>
@@ -4710,7 +4833,7 @@
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="15"/>
@@ -4725,7 +4848,7 @@
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="15"/>
@@ -4740,7 +4863,7 @@
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="15"/>
@@ -4755,7 +4878,7 @@
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="15"/>
@@ -4770,7 +4893,7 @@
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="15"/>
@@ -4785,7 +4908,7 @@
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="15"/>
@@ -4800,7 +4923,7 @@
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="15"/>
@@ -4815,7 +4938,7 @@
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="15"/>
@@ -4872,25 +4995,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FB3633-F435-1B44-A99B-F400ACF77C57}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1328125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="6" width="23.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="59.7109375" style="2" customWidth="1"/>
+    <col min="4" max="6" width="23.7109375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>53</v>
       </c>
@@ -4910,7 +5033,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>239</v>
       </c>
@@ -4926,7 +5049,7 @@
       </c>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -4934,7 +5057,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -4942,7 +5065,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -4950,7 +5073,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -4958,7 +5081,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -4966,7 +5089,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -4974,7 +5097,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -4982,7 +5105,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -4990,7 +5113,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -4998,7 +5121,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5006,7 +5129,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -5014,7 +5137,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -5022,7 +5145,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -5030,7 +5153,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -5038,7 +5161,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -5046,7 +5169,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -5065,25 +5188,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1328125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="7" width="23.6640625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="59.7109375" style="2" customWidth="1"/>
+    <col min="4" max="7" width="23.7109375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>62</v>
       </c>
@@ -5106,7 +5229,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>243</v>
       </c>
@@ -5121,7 +5244,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>246</v>
       </c>
@@ -5138,7 +5261,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -5147,7 +5270,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -5156,7 +5279,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -5165,7 +5288,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -5174,7 +5297,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -5183,7 +5306,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -5192,7 +5315,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -5201,7 +5324,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5210,7 +5333,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5219,7 +5342,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -5228,7 +5351,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -5237,7 +5360,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -5246,7 +5369,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -5255,7 +5378,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -5264,7 +5387,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -5284,27 +5407,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B433535-9968-AF4C-822D-F1478F01E2E0}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.796875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>63</v>
       </c>
@@ -5321,119 +5444,119 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -5451,36 +5574,36 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C18618-CA09-244F-9E12-D5D128AED5CE}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="32.796875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="32.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="34.7109375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>101</v>
       </c>
       <c r="B4" s="26"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
@@ -5500,7 +5623,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>249</v>
       </c>
@@ -5516,7 +5639,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -5524,7 +5647,7 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -5532,7 +5655,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -5540,7 +5663,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -5548,7 +5671,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -5556,7 +5679,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -5564,7 +5687,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5572,7 +5695,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5580,7 +5703,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -5588,7 +5711,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -5596,7 +5719,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -5604,7 +5727,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -5612,7 +5735,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -5620,7 +5743,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -5628,7 +5751,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -5636,7 +5759,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -5656,30 +5779,30 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{246082EA-DAAB-1649-871C-B98419509DC8}">
   <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.1328125" style="2" customWidth="1"/>
-    <col min="3" max="6" width="36.1328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="2" customWidth="1"/>
+    <col min="3" max="6" width="36.140625" style="2" customWidth="1"/>
     <col min="7" max="22" width="15" style="2" customWidth="1"/>
-    <col min="23" max="30" width="32.796875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="34.6640625" style="2" customWidth="1"/>
-    <col min="32" max="16384" width="8.796875" style="2"/>
+    <col min="23" max="30" width="32.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="34.7109375" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>108</v>
       </c>
@@ -5691,7 +5814,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>109</v>
       </c>
@@ -5703,7 +5826,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -5713,11 +5836,11 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>18</v>
       </c>
@@ -5729,12 +5852,12 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="2" t="s">
         <v>117</v>
@@ -5744,7 +5867,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="2" t="s">
         <v>80</v>
@@ -5754,7 +5877,7 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="2" t="s">
         <v>114</v>
@@ -5764,15 +5887,15 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="2" t="s">
         <v>120</v>
@@ -5784,7 +5907,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="2" t="s">
         <v>113</v>
@@ -5796,15 +5919,15 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="2" t="s">
         <v>111</v>
@@ -5814,7 +5937,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="2" t="s">
         <v>17</v>
@@ -5824,7 +5947,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="2" t="s">
         <v>116</v>
@@ -5834,15 +5957,15 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="2" t="s">
         <v>110</v>
@@ -5852,7 +5975,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="2" t="s">
         <v>112</v>
@@ -5862,7 +5985,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="2" t="s">
         <v>117</v>
@@ -5872,7 +5995,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="2" t="s">
         <v>80</v>
@@ -5882,15 +6005,15 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="2" t="s">
         <v>116</v>
@@ -5900,7 +6023,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="2" t="s">
         <v>80</v>
@@ -5910,15 +6033,15 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="2" t="s">
         <v>116</v>
@@ -5928,7 +6051,7 @@
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="2" t="s">
         <v>119</v>
@@ -5938,7 +6061,7 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
       <c r="B38" s="2" t="s">
         <v>112</v>
@@ -5948,7 +6071,7 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="2" t="s">
         <v>17</v>
@@ -5958,15 +6081,15 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="2" t="s">
         <v>117</v>
@@ -5976,7 +6099,7 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
       <c r="B43" s="2" t="s">
         <v>115</v>
@@ -5986,7 +6109,7 @@
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="2" t="s">
         <v>80</v>
@@ -5996,7 +6119,7 @@
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="2" t="s">
         <v>114</v>
@@ -6006,15 +6129,15 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
       <c r="B48" s="2" t="s">
         <v>116</v>
@@ -6024,7 +6147,7 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="2" t="s">
         <v>119</v>
@@ -6034,7 +6157,7 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="2" t="s">
         <v>110</v>
@@ -6044,7 +6167,7 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
       <c r="B51" s="2" t="s">
         <v>112</v>
@@ -6054,7 +6177,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="2" t="s">
         <v>130</v>
@@ -6064,7 +6187,7 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
       <c r="B53" s="2" t="s">
         <v>17</v>
@@ -6074,15 +6197,15 @@
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7"/>
       <c r="B56" s="2" t="s">
         <v>116</v>
@@ -6092,7 +6215,7 @@
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7"/>
       <c r="B57" s="2" t="s">
         <v>119</v>
@@ -6102,7 +6225,7 @@
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7"/>
       <c r="B58" s="2" t="s">
         <v>112</v>
@@ -6112,7 +6235,7 @@
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7"/>
       <c r="B59" s="2" t="s">
         <v>17</v>
@@ -6122,15 +6245,15 @@
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7"/>
       <c r="B62" s="2" t="s">
         <v>110</v>
@@ -6140,7 +6263,7 @@
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
       <c r="B63" s="2" t="s">
         <v>111</v>
@@ -6150,7 +6273,7 @@
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7"/>
       <c r="B64" s="2" t="s">
         <v>112</v>
@@ -6160,7 +6283,7 @@
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7"/>
       <c r="B65" s="2" t="s">
         <v>113</v>
@@ -6170,7 +6293,7 @@
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7"/>
       <c r="B66" s="2" t="s">
         <v>114</v>
@@ -6180,7 +6303,7 @@
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7"/>
       <c r="B67" s="2" t="s">
         <v>115</v>
@@ -6190,7 +6313,7 @@
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7"/>
       <c r="B68" s="2" t="s">
         <v>80</v>
@@ -6200,7 +6323,7 @@
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="7"/>
       <c r="B69" s="2" t="s">
         <v>116</v>
@@ -6210,7 +6333,7 @@
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7"/>
       <c r="B70" s="2" t="s">
         <v>117</v>
@@ -6220,7 +6343,7 @@
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7"/>
       <c r="B71" s="2" t="s">
         <v>118</v>
@@ -6230,7 +6353,7 @@
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="2" t="s">
         <v>119</v>
@@ -6240,7 +6363,7 @@
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="2" t="s">
         <v>120</v>
@@ -6250,7 +6373,7 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="2" t="s">
         <v>121</v>
@@ -6260,7 +6383,7 @@
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7"/>
       <c r="B75" s="2" t="s">
         <v>122</v>
@@ -6270,7 +6393,7 @@
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="2" t="s">
         <v>17</v>
@@ -6280,7 +6403,7 @@
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="7"/>
       <c r="B77" s="2" t="s">
         <v>133</v>
@@ -6290,7 +6413,7 @@
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7"/>
       <c r="B78" s="2" t="s">
         <v>134</v>
@@ -6300,7 +6423,7 @@
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="2" t="s">
         <v>135</v>
@@ -6310,7 +6433,7 @@
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7"/>
       <c r="B80" s="2" t="s">
         <v>130</v>
@@ -6329,4 +6452,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{dfbd6cd6-3262-48dc-8011-f5abeb79275f}" enabled="1" method="Standard" siteId="{da67ef1b-ca59-4db2-9a8c-aa8d94617a16}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -3,21 +3,20 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1620" yWindow="345" windowWidth="27360" windowHeight="14340" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Schema shipments" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Support" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Team" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Roles" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SLA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Servers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Support" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Team" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Roles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SLA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Servers" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Pricing" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Custom Properties" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
@@ -37,31 +36,30 @@
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
     <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
-    <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
     <definedName name="servers.azure.delimiter">Servers!$C$14</definedName>
     <definedName name="servers.azure.format">Servers!$C$13</definedName>
     <definedName name="servers.azure.location">Servers!$C$12</definedName>
     <definedName name="servers.bigquery.dataset">Servers!$C$18</definedName>
     <definedName name="servers.bigquery.project">Servers!$C$17</definedName>
-    <definedName name="servers.custom.account">Servers!$C$67</definedName>
-    <definedName name="servers.custom.catalog">Servers!$C$68</definedName>
-    <definedName name="servers.custom.database">Servers!$C$69</definedName>
-    <definedName name="servers.custom.dataset">Servers!$C$70</definedName>
-    <definedName name="servers.custom.delimiter">Servers!$C$71</definedName>
-    <definedName name="servers.custom.endpointUrl">Servers!$C$72</definedName>
-    <definedName name="servers.custom.format">Servers!$C$73</definedName>
-    <definedName name="servers.custom.host">Servers!$C$74</definedName>
-    <definedName name="servers.custom.location">Servers!$C$75</definedName>
-    <definedName name="servers.custom.path">Servers!$C$76</definedName>
-    <definedName name="servers.custom.port">Servers!$C$77</definedName>
-    <definedName name="servers.custom.project">Servers!$C$78</definedName>
-    <definedName name="servers.custom.region">Servers!$C$79</definedName>
-    <definedName name="servers.custom.regionName">Servers!$C$80</definedName>
-    <definedName name="servers.custom.schema">Servers!$C$81</definedName>
-    <definedName name="servers.custom.serviceName">Servers!$C$82</definedName>
-    <definedName name="servers.custom.stagingDir">Servers!$C$83</definedName>
-    <definedName name="servers.custom.stream">Servers!$C$84</definedName>
-    <definedName name="servers.custom.warehouse">Servers!$C$85</definedName>
+    <definedName name="servers.custom.account">Servers!$C$62</definedName>
+    <definedName name="servers.custom.catalog">Servers!$C$63</definedName>
+    <definedName name="servers.custom.database">Servers!$C$64</definedName>
+    <definedName name="servers.custom.dataset">Servers!$C$65</definedName>
+    <definedName name="servers.custom.delimiter">Servers!$C$66</definedName>
+    <definedName name="servers.custom.endpointUrl">Servers!$C$67</definedName>
+    <definedName name="servers.custom.format">Servers!$C$68</definedName>
+    <definedName name="servers.custom.host">Servers!$C$69</definedName>
+    <definedName name="servers.custom.location">Servers!$C$70</definedName>
+    <definedName name="servers.custom.path">Servers!$C$71</definedName>
+    <definedName name="servers.custom.port">Servers!$C$72</definedName>
+    <definedName name="servers.custom.project">Servers!$C$73</definedName>
+    <definedName name="servers.custom.region">Servers!$C$74</definedName>
+    <definedName name="servers.custom.regionName">Servers!$C$75</definedName>
+    <definedName name="servers.custom.schema">Servers!$C$76</definedName>
+    <definedName name="servers.custom.serviceName">Servers!$C$77</definedName>
+    <definedName name="servers.custom.stagingDir">Servers!$C$78</definedName>
+    <definedName name="servers.custom.stream">Servers!$C$79</definedName>
+    <definedName name="servers.custom.warehouse">Servers!$C$80</definedName>
     <definedName name="servers.databricks.catalog">Servers!$C$21</definedName>
     <definedName name="servers.databricks.host">Servers!$C$23</definedName>
     <definedName name="servers.databricks.schema">Servers!$C$22</definedName>
@@ -73,9 +71,6 @@
     <definedName name="servers.glue.location">Servers!$C$28</definedName>
     <definedName name="servers.kafka.format">Servers!$C$33</definedName>
     <definedName name="servers.kafka.host">Servers!$C$32</definedName>
-    <definedName name="servers.oracle.host">Servers!$C$62</definedName>
-    <definedName name="servers.oracle.port">Servers!$C$63</definedName>
-    <definedName name="servers.oracle.servicename">Servers!$C$64</definedName>
     <definedName name="servers.postgres.database">Servers!$C$38</definedName>
     <definedName name="servers.postgres.host">Servers!$C$36</definedName>
     <definedName name="servers.postgres.port">Servers!$C$37</definedName>
@@ -111,17 +106,17 @@
     <definedName name="schema.physicalType" localSheetId="2">'Schema shipments'!$B$6</definedName>
     <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$13:$L$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema shipments'!$B$11</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$A$4:$E$1000</definedName>
-    <definedName name="slaProperties" localSheetId="8">SLA!$A$6:$F$1002</definedName>
+    <definedName name="roles" localSheetId="6">Roles!$A$4:$E$1000</definedName>
+    <definedName name="slaProperties" localSheetId="7">SLA!$A$6:$F$1002</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -169,6 +164,25 @@
     </font>
     <font>
       <name val="Aptos Mono"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Mono"/>
+      <family val="3"/>
       <color theme="1"/>
       <sz val="12"/>
     </font>
@@ -334,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -419,6 +433,21 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -444,14 +473,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F4F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -762,10 +784,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="8.83203125" customWidth="1" style="3" min="2" max="16384"/>
+    <col width="8.85546875" customWidth="1" style="3" min="2" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -779,7 +801,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Use this Excel template to edit data contracts.</t>
@@ -790,14 +812,14 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Data Contract</t>
@@ -812,7 +834,7 @@
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="13" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">A data contract is a document that defines the structure, format, semantics, quality, and terms of use </t>
@@ -827,7 +849,7 @@
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="13" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">for exchanging data between a data provider and their consumers. </t>
@@ -842,7 +864,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="13" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>A data contract is usually defined in YAML, but you can use this Excel document for easier collaboration</t>
@@ -857,7 +879,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="13" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>with your stakeholders.</t>
@@ -872,7 +894,7 @@
       <c r="H11" s="13" t="n"/>
       <c r="I11" s="13" t="n"/>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="13" t="n"/>
       <c r="B12" s="13" t="n"/>
       <c r="C12" s="13" t="n"/>
@@ -883,7 +905,7 @@
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="13" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="13" t="n"/>
@@ -894,7 +916,7 @@
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="13" t="n"/>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Instructions</t>
@@ -909,7 +931,7 @@
       <c r="H14" s="13" t="n"/>
       <c r="I14" s="13" t="n"/>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>1. Fill in the 'Fundamentals' sheet with basic contract information</t>
@@ -924,7 +946,7 @@
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="13" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
           <t>2. For every table create a Sheet called "Schema &lt;tablename&gt;"</t>
@@ -939,7 +961,7 @@
       <c r="H16" s="13" t="n"/>
       <c r="I16" s="13" t="n"/>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">3. After completing the template, </t>
@@ -954,7 +976,7 @@
       <c r="H17" s="13" t="n"/>
       <c r="I17" s="13" t="n"/>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>a)</t>
@@ -973,7 +995,7 @@
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="13" t="n"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="23" t="n"/>
       <c r="B19" s="24" t="inlineStr">
         <is>
@@ -988,7 +1010,7 @@
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="13" t="n"/>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="13" t="n"/>
@@ -999,7 +1021,7 @@
       <c r="H20" s="13" t="n"/>
       <c r="I20" s="13" t="n"/>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
           <t>b)</t>
@@ -1007,7 +1029,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Or, if you use Entropy Data, import the Excel directly.</t>
+          <t>Or, if you use Data Mesh Manager, import the Excel directly.</t>
         </is>
       </c>
       <c r="C21" s="13" t="n"/>
@@ -1018,7 +1040,7 @@
       <c r="H21" s="13" t="n"/>
       <c r="I21" s="13" t="n"/>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="25" t="n"/>
       <c r="B22" s="13" t="inlineStr">
         <is>
@@ -1033,11 +1055,11 @@
       <c r="H22" s="13" t="n"/>
       <c r="I22" s="13" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Open Entropy Data → Go to Data Contracts → Click Add Data Contract → Import from Excel</t>
+          <t>Open Data Mesh Manager → Go to Data Contracts → Click Add Data Contract → Import from Excel</t>
         </is>
       </c>
       <c r="C23" s="13" t="n"/>
@@ -1048,9 +1070,13 @@
       <c r="H23" s="13" t="n"/>
       <c r="I23" s="13" t="n"/>
     </row>
-    <row r="24" ht="16" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="13" t="n"/>
-      <c r="B24" s="13" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>http://localhost:8080/demo203502625092/datacontracts/import/excel</t>
+        </is>
+      </c>
       <c r="C24" s="13" t="n"/>
       <c r="D24" s="13" t="n"/>
       <c r="E24" s="13" t="n"/>
@@ -1059,7 +1085,7 @@
       <c r="H24" s="13" t="n"/>
       <c r="I24" s="13" t="n"/>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
@@ -1070,7 +1096,7 @@
       <c r="H25" s="13" t="n"/>
       <c r="I25" s="13" t="n"/>
     </row>
-    <row r="26" ht="16" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Authors:</t>
@@ -1089,7 +1115,7 @@
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="n"/>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Version:</t>
@@ -1097,7 +1123,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -1108,7 +1134,7 @@
       <c r="H27" s="13" t="n"/>
       <c r="I27" s="13" t="n"/>
     </row>
-    <row r="28" ht="16" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>License:</t>
@@ -1127,7 +1153,7 @@
       <c r="H28" s="13" t="n"/>
       <c r="I28" s="13" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="13" t="n"/>
       <c r="C29" s="13" t="n"/>
@@ -1138,7 +1164,7 @@
       <c r="H29" s="13" t="n"/>
       <c r="I29" s="13" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="13" t="n"/>
       <c r="C30" s="13" t="n"/>
@@ -1149,7 +1175,7 @@
       <c r="H30" s="13" t="n"/>
       <c r="I30" s="13" t="n"/>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="13" t="n"/>
       <c r="C31" s="13" t="n"/>
@@ -1161,6 +1187,9 @@
       <c r="I31" s="13" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1171,866 +1200,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col width="6.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="33.1640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="36.1640625" customWidth="1" style="2" min="3" max="6"/>
-    <col width="15" customWidth="1" style="2" min="7" max="22"/>
-    <col width="32.83203125" customWidth="1" style="2" min="23" max="30"/>
-    <col width="34.6640625" customWidth="1" style="2" min="31" max="31"/>
-    <col width="8.83203125" customWidth="1" style="2" min="32" max="16384"/>
+    <col width="26.140625" customWidth="1" style="22" min="1" max="1"/>
+    <col width="22.28515625" customWidth="1" style="22" min="2" max="2"/>
+    <col width="10.85546875" customWidth="1" style="22" min="3" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="24" customFormat="1" customHeight="1" s="2">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure and Servers</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-    </row>
-    <row r="2">
+          <t>Pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The servers element describes where the data protected by this data contract is physically located. </t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="34" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="D4" s="36" t="n"/>
-      <c r="E4" s="36" t="n"/>
-      <c r="F4" s="36" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B6" s="34" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="n"/>
-      <c r="B7" s="34" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>bigquery</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="n"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="34" t="n"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="34" t="n"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>BigQuery</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="n"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>acme_shipments_prod</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="n"/>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>shipments_v1</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t>Databricks Server</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="34" t="n"/>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="n"/>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="n"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="34" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>Amazon Glue</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="34" t="n"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="34" t="n"/>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="36" t="n"/>
-      <c r="E27" s="36" t="n"/>
-      <c r="F27" s="36" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="n"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="34" t="n"/>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="n"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="34" t="n"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="36" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="34" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="34" t="n"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="34" t="n"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="36" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="34" t="n"/>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="34" t="n"/>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="36" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="34" t="n"/>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
-      <c r="F42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="34" t="n"/>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Endpoint URL</t>
-        </is>
-      </c>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="n"/>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C44" s="36" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
-      <c r="F44" s="36" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="34" t="n"/>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
-      <c r="F45" s="36" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="34" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="34" t="n"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="34" t="n"/>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="34" t="n"/>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C50" s="36" t="n"/>
-      <c r="D50" s="36" t="n"/>
-      <c r="E50" s="36" t="n"/>
-      <c r="F50" s="36" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="34" t="n"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="n"/>
-      <c r="F51" s="36" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="34" t="n"/>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C52" s="36" t="n"/>
-      <c r="D52" s="36" t="n"/>
-      <c r="E52" s="36" t="n"/>
-      <c r="F52" s="36" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="34" t="n"/>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="36" t="n"/>
-      <c r="E53" s="36" t="n"/>
-      <c r="F53" s="36" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="34" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>SQL Server</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="n"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-      <c r="F56" s="36" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="n"/>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="n"/>
-      <c r="F57" s="36" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="34" t="n"/>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="34" t="n"/>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="36" t="n"/>
-      <c r="E59" s="36" t="n"/>
-      <c r="F59" s="36" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="34" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="34" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="34" t="n"/>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C62" s="36" t="n"/>
-      <c r="D62" s="36" t="n"/>
-      <c r="E62" s="36" t="n"/>
-      <c r="F62" s="36" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="34" t="n"/>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C63" s="36" t="n"/>
-      <c r="D63" s="36" t="n"/>
-      <c r="E63" s="36" t="n"/>
-      <c r="F63" s="36" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="34" t="n"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>ServiceName</t>
-        </is>
-      </c>
-      <c r="C64" s="36" t="n"/>
-      <c r="D64" s="36" t="n"/>
-      <c r="E64" s="36" t="n"/>
-      <c r="F64" s="36" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="34" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="34" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="34" t="n"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C67" s="36" t="n"/>
-      <c r="D67" s="36" t="n"/>
-      <c r="E67" s="36" t="n"/>
-      <c r="F67" s="36" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="n"/>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="n"/>
-      <c r="D68" s="36" t="n"/>
-      <c r="E68" s="36" t="n"/>
-      <c r="F68" s="36" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="34" t="n"/>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C69" s="36" t="n"/>
-      <c r="D69" s="36" t="n"/>
-      <c r="E69" s="36" t="n"/>
-      <c r="F69" s="36" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="34" t="n"/>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
-      <c r="F70" s="36" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="34" t="n"/>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C71" s="36" t="n"/>
-      <c r="D71" s="36" t="n"/>
-      <c r="E71" s="36" t="n"/>
-      <c r="F71" s="36" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="34" t="n"/>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Endpoint URL</t>
-        </is>
-      </c>
-      <c r="C72" s="36" t="n"/>
-      <c r="D72" s="36" t="n"/>
-      <c r="E72" s="36" t="n"/>
-      <c r="F72" s="36" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="34" t="n"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C73" s="36" t="n"/>
-      <c r="D73" s="36" t="n"/>
-      <c r="E73" s="36" t="n"/>
-      <c r="F73" s="36" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="34" t="n"/>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C74" s="36" t="n"/>
-      <c r="D74" s="36" t="n"/>
-      <c r="E74" s="36" t="n"/>
-      <c r="F74" s="36" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="34" t="n"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C75" s="36" t="n"/>
-      <c r="D75" s="36" t="n"/>
-      <c r="E75" s="36" t="n"/>
-      <c r="F75" s="36" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="34" t="n"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="C76" s="36" t="n"/>
-      <c r="D76" s="36" t="n"/>
-      <c r="E76" s="36" t="n"/>
-      <c r="F76" s="36" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="34" t="n"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C77" s="36" t="n"/>
-      <c r="D77" s="36" t="n"/>
-      <c r="E77" s="36" t="n"/>
-      <c r="F77" s="36" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="34" t="n"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C78" s="36" t="n"/>
-      <c r="D78" s="36" t="n"/>
-      <c r="E78" s="36" t="n"/>
-      <c r="F78" s="36" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="34" t="n"/>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C79" s="36" t="n"/>
-      <c r="D79" s="36" t="n"/>
-      <c r="E79" s="36" t="n"/>
-      <c r="F79" s="36" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="34" t="n"/>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Region Name</t>
-        </is>
-      </c>
-      <c r="C80" s="36" t="n"/>
-      <c r="D80" s="36" t="n"/>
-      <c r="E80" s="36" t="n"/>
-      <c r="F80" s="36" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="34" t="n"/>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C81" s="36" t="n"/>
-      <c r="D81" s="36" t="n"/>
-      <c r="E81" s="36" t="n"/>
-      <c r="F81" s="36" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="34" t="n"/>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Service Name</t>
-        </is>
-      </c>
-      <c r="C82" s="36" t="n"/>
-      <c r="D82" s="36" t="n"/>
-      <c r="E82" s="36" t="n"/>
-      <c r="F82" s="36" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="34" t="n"/>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Staging Directory</t>
-        </is>
-      </c>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="36" t="n"/>
-      <c r="E83" s="36" t="n"/>
-      <c r="F83" s="36" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="34" t="n"/>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="C84" s="36" t="n"/>
-      <c r="D84" s="36" t="n"/>
-      <c r="E84" s="36" t="n"/>
-      <c r="F84" s="36" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="34" t="n"/>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C85" s="36" t="n"/>
-      <c r="D85" s="36" t="n"/>
-      <c r="E85" s="36" t="n"/>
-      <c r="F85" s="36" t="n"/>
+          <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2"/>
+    <row r="4" ht="15.75" customFormat="1" customHeight="1" s="2">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>Price Amount</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customFormat="1" customHeight="1" s="2">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>Price Currency</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customFormat="1" customHeight="1" s="2">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Price Unit</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Per 1000 requests</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C4:F7 C9:F45 C48:F53 C56:F59 C62:F64 C67:F85 G4:AE43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="C8:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"api,athena,azure,bigquery,clickhouse,databricks,db2,denodo,dremio,duckdb,glue,cloudsql,informix,kafka,kinesis,mysql,local,oracle,postgresql,presto,pubsub,redshift,s3,sftp,snowflake,sqlserver,synapse,trino,vertica,custom"</formula1>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation sqref="F4:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2043,86 +1276,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="26.1640625" customWidth="1" style="22" min="1" max="1"/>
-    <col width="22.33203125" customWidth="1" style="22" min="2" max="2"/>
-    <col width="10.83203125" customWidth="1" style="22" min="3" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customFormat="1" customHeight="1" s="2"/>
-    <row r="4" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>Price Amount</t>
-        </is>
-      </c>
-      <c r="B4" s="36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="34" t="inlineStr">
-        <is>
-          <t>Price Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="36" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="34" t="inlineStr">
-        <is>
-          <t>Price Unit</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>Per 1000 requests</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="F4:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
     <col width="90" customWidth="1" style="2" min="2" max="2"/>
-    <col width="8.83203125" customWidth="1" style="2" min="3" max="16384"/>
+    <col width="8.85546875" customWidth="1" style="2" min="3" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2152,87 +1311,87 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="B5" s="36">
-        <f>IF(owner &lt;&gt; "", owner, "")</f>
+      <c r="B5" s="41">
+        <f>IF(owner&lt;&gt;"",owner,"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>additionalField</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>We added an addition field - b</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
+      <c r="A7" s="41" t="n"/>
+      <c r="B7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
+      <c r="A8" s="41" t="n"/>
+      <c r="B8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
+      <c r="A9" s="41" t="n"/>
+      <c r="B9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
+      <c r="A14" s="41" t="n"/>
+      <c r="B14" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="41" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="41" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2249,20 +1408,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="2.83203125" customWidth="1" style="2" min="1" max="1"/>
-    <col width="19.6640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="2.85546875" customWidth="1" style="2" min="1" max="1"/>
+    <col width="19.7109375" customWidth="1" style="2" min="2" max="2"/>
     <col width="45" customWidth="1" style="2" min="3" max="3"/>
-    <col width="1.83203125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="28.1640625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14.33203125" customWidth="1" style="2" min="6" max="6"/>
+    <col width="1.85546875" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="14.28515625" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
-    <col width="14.1640625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.33203125" customWidth="1" style="2" min="10" max="11"/>
-    <col width="23.5" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="24.1640625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
-    <col width="8.83203125" customWidth="1" style="2" min="14" max="16384"/>
+    <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.28515625" customWidth="1" style="2" min="10" max="11"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+    <col width="24.140625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
+    <col width="8.85546875" customWidth="1" style="2" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2280,99 +1439,99 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="B4" s="39" t="n"/>
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>DataContract</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>apiVersion</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>v3.0.0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="n"/>
-      <c r="B6" s="34" t="n"/>
+      <c r="A6" s="39" t="n"/>
+      <c r="B6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n"/>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="B7" s="39" t="n"/>
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>fulfillment_shipments_v1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n"/>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="B9" s="39" t="n"/>
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>1.0.2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="34" t="n"/>
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>fulfillment</t>
         </is>
@@ -2380,105 +1539,105 @@
       <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="n"/>
-      <c r="B13" s="34" t="n"/>
+      <c r="A13" s="39" t="n"/>
+      <c r="B13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="36" t="n"/>
+      <c r="B14" s="39" t="n"/>
+      <c r="C14" s="41" t="n"/>
       <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Data Product</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="36" t="n"/>
+      <c r="B15" s="39" t="n"/>
+      <c r="C15" s="41" t="n"/>
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Tenant</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>company-A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="n"/>
-      <c r="B17" s="34" t="n"/>
+      <c r="A17" s="39" t="n"/>
+      <c r="B17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n"/>
+      <c r="B18" s="39" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="n"/>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="A19" s="39" t="n"/>
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>This data can be used for analytical purposes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="n"/>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="A20" s="39" t="n"/>
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>Limitations</t>
         </is>
       </c>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Not suitable for real-time use cases</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="n"/>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="A21" s="39" t="n"/>
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Use this to analyze shipments</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="n"/>
-      <c r="B22" s="34" t="n"/>
+      <c r="A22" s="39" t="n"/>
+      <c r="B22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B23" s="34" t="n"/>
-      <c r="C23" s="36" t="inlineStr">
+      <c r="B23" s="39" t="n"/>
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>datalocation:EU</t>
         </is>
@@ -2509,29 +1668,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:AN49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="34.83203125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="34.85546875" customWidth="1" style="2" min="1" max="1"/>
     <col width="24" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="12.5" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="17.5" customWidth="1" style="2" min="4" max="4"/>
-    <col width="28.1640625" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="35.6640625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="17.42578125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="35.7109375" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
-    <col width="14.1640625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.33203125" customWidth="1" style="2" min="10" max="10"/>
-    <col width="28.1640625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
-    <col width="28.6640625" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="28.6640625" customWidth="1" style="2" min="13" max="13"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
+    <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.28515625" customWidth="1" style="2" min="10" max="10"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="28.7109375" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+    <col width="28.7109375" customWidth="1" style="2" min="13" max="13"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
     <col width="19" bestFit="1" customWidth="1" style="2" min="15" max="15"/>
     <col width="19" customWidth="1" style="2" min="16" max="20"/>
-    <col width="21.6640625" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
-    <col width="27.33203125" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
-    <col width="15.5" customWidth="1" style="2" min="23" max="37"/>
-    <col width="26.1640625" customWidth="1" style="2" min="38" max="38"/>
-    <col width="8.83203125" customWidth="1" style="2" min="39" max="16384"/>
+    <col width="21.7109375" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
+    <col width="27.28515625" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
+    <col width="15.42578125" customWidth="1" style="2" min="23" max="37"/>
+    <col width="26.140625" customWidth="1" style="2" min="38" max="38"/>
+    <col width="10.140625" bestFit="1" customWidth="1" style="2" min="39" max="39"/>
+    <col width="11.140625" bestFit="1" customWidth="1" style="2" min="40" max="40"/>
+    <col width="8.85546875" customWidth="1" style="2" min="41" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2556,109 +1717,109 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="42" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="47" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="42" t="n"/>
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n"/>
+      <c r="E6" s="47" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>This table contains shipment data, including details about shipment IDs, associated orders, delivery dates, carriers, tracking numbers, statuses, and additional shipment information in JSON format.</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="42" t="n"/>
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="46" t="n"/>
+      <c r="E7" s="47" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="42" t="n"/>
+      <c r="C8" s="46" t="n"/>
+      <c r="D8" s="46" t="n"/>
+      <c r="E8" s="47" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Physical Name</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>shipments_v1</t>
         </is>
       </c>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="42" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="47" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Data Granularity</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>Not Aggregated</t>
         </is>
       </c>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="42" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="47" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>pii</t>
         </is>
       </c>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="42" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
+      <c r="E11" s="47" t="n"/>
     </row>
     <row r="12">
       <c r="W12" s="19" t="inlineStr">
@@ -2680,6 +1841,12 @@
       <c r="AI12" s="20" t="n"/>
       <c r="AJ12" s="20" t="n"/>
       <c r="AK12" s="21" t="n"/>
+      <c r="AM12" s="19" t="inlineStr">
+        <is>
+          <t>Custom Properties</t>
+        </is>
+      </c>
+      <c r="AN12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2872,8 +2039,18 @@
           <t>Comments (internal)</t>
         </is>
       </c>
-    </row>
-    <row r="14">
+      <c r="AM13" s="10" t="inlineStr">
+        <is>
+          <t>ScdType</t>
+        </is>
+      </c>
+      <c r="AN13" s="10" t="inlineStr">
+        <is>
+          <t>isMasked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="63" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>shipment_id</t>
@@ -2944,7 +2121,7 @@
       </c>
       <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
-      <c r="S14" s="15" t="inlineStr"/>
+      <c r="S14" s="15" t="n"/>
       <c r="T14" s="15" t="n"/>
       <c r="U14" s="15" t="n"/>
       <c r="V14" s="15" t="b">
@@ -2966,8 +2143,12 @@
       <c r="AJ14" s="15" t="n"/>
       <c r="AK14" s="15" t="n"/>
       <c r="AL14" s="28" t="n"/>
-    </row>
-    <row r="15">
+      <c r="AM14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="47.25" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
           <t>order_id</t>
@@ -2980,12 +2161,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr"/>
+      <c r="E15" s="16" t="n"/>
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="inlineStr"/>
+      <c r="J15" s="15" t="n"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>http://localhost:8080/demo203502625092/definitions/sales/order_id</t>
@@ -3010,7 +2191,7 @@
       </c>
       <c r="Q15" s="15" t="n"/>
       <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="inlineStr"/>
+      <c r="S15" s="15" t="n"/>
       <c r="T15" s="15" t="n"/>
       <c r="U15" s="15" t="n"/>
       <c r="V15" s="15" t="n"/>
@@ -3030,8 +2211,12 @@
       <c r="AJ15" s="15" t="n"/>
       <c r="AK15" s="15" t="n"/>
       <c r="AL15" s="28" t="n"/>
-    </row>
-    <row r="16">
+      <c r="AM15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="31.5" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
           <t>delivery_date</t>
@@ -3073,7 +2258,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr"/>
+      <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -3086,7 +2271,7 @@
       </c>
       <c r="Q16" s="15" t="n"/>
       <c r="R16" s="15" t="n"/>
-      <c r="S16" s="15" t="inlineStr"/>
+      <c r="S16" s="15" t="n"/>
       <c r="T16" s="15" t="n"/>
       <c r="U16" s="15" t="n"/>
       <c r="V16" s="15" t="b">
@@ -3108,8 +2293,12 @@
       <c r="AJ16" s="15" t="n"/>
       <c r="AK16" s="15" t="n"/>
       <c r="AL16" s="28" t="n"/>
-    </row>
-    <row r="17">
+      <c r="AM16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="31.5" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
           <t>carrier</t>
@@ -3151,7 +2340,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr"/>
+      <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
@@ -3164,7 +2353,7 @@
       </c>
       <c r="Q17" s="15" t="n"/>
       <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="inlineStr"/>
+      <c r="S17" s="15" t="n"/>
       <c r="T17" s="15" t="n"/>
       <c r="U17" s="15" t="n"/>
       <c r="V17" s="15" t="b">
@@ -3186,8 +2375,12 @@
       <c r="AJ17" s="15" t="n"/>
       <c r="AK17" s="15" t="n"/>
       <c r="AL17" s="28" t="n"/>
-    </row>
-    <row r="18">
+      <c r="AM17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="31.5" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
         <is>
           <t>tracking_number</t>
@@ -3229,7 +2422,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr"/>
+      <c r="J18" s="15" t="n"/>
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -3242,7 +2435,7 @@
       </c>
       <c r="Q18" s="15" t="n"/>
       <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="inlineStr"/>
+      <c r="S18" s="15" t="n"/>
       <c r="T18" s="15" t="n"/>
       <c r="U18" s="15" t="n"/>
       <c r="V18" s="15" t="b">
@@ -3264,6 +2457,10 @@
       <c r="AJ18" s="15" t="n"/>
       <c r="AK18" s="15" t="n"/>
       <c r="AL18" s="28" t="n"/>
+      <c r="AM18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
@@ -3307,7 +2504,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr"/>
+      <c r="J19" s="15" t="n"/>
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
@@ -3320,7 +2517,7 @@
       </c>
       <c r="Q19" s="15" t="n"/>
       <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="inlineStr"/>
+      <c r="S19" s="15" t="n"/>
       <c r="T19" s="15" t="n"/>
       <c r="U19" s="15" t="n"/>
       <c r="V19" s="15" t="b">
@@ -3342,8 +2539,12 @@
       <c r="AJ19" s="15" t="n"/>
       <c r="AK19" s="15" t="n"/>
       <c r="AL19" s="28" t="n"/>
-    </row>
-    <row r="20">
+      <c r="AM19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="31.5" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>inline_object_definition</t>
@@ -3385,7 +2586,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr"/>
+      <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
@@ -3396,11 +2597,13 @@
       <c r="P20" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="Q20" s="15" t="n">
-        <v>-1</v>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="inlineStr"/>
+      <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n"/>
       <c r="U20" s="15" t="n"/>
       <c r="V20" s="15" t="b">
@@ -3422,6 +2625,10 @@
       <c r="AJ20" s="15" t="n"/>
       <c r="AK20" s="15" t="n"/>
       <c r="AL20" s="28" t="n"/>
+      <c r="AM20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
@@ -3444,7 +2651,7 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr"/>
+      <c r="E21" s="16" t="n"/>
       <c r="F21" s="15" t="inlineStr">
         <is>
           <t>Shipping address details.</t>
@@ -3459,7 +2666,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr"/>
+      <c r="J21" s="15" t="n"/>
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
@@ -3468,7 +2675,7 @@
       <c r="P21" s="15" t="n"/>
       <c r="Q21" s="15" t="n"/>
       <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="inlineStr"/>
+      <c r="S21" s="15" t="n"/>
       <c r="T21" s="15" t="n"/>
       <c r="U21" s="15" t="n"/>
       <c r="V21" s="15" t="n"/>
@@ -3488,6 +2695,14 @@
       <c r="AJ21" s="15" t="n"/>
       <c r="AK21" s="15" t="n"/>
       <c r="AL21" s="28" t="n"/>
+      <c r="AM21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -3531,7 +2746,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr"/>
+      <c r="J22" s="15" t="n"/>
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
@@ -3544,7 +2759,7 @@
       </c>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="inlineStr"/>
+      <c r="S22" s="15" t="n"/>
       <c r="T22" s="15" t="n"/>
       <c r="U22" s="15" t="n"/>
       <c r="V22" s="15" t="n"/>
@@ -3564,6 +2779,14 @@
       <c r="AJ22" s="15" t="n"/>
       <c r="AK22" s="15" t="n"/>
       <c r="AL22" s="28" t="n"/>
+      <c r="AM22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
@@ -3607,7 +2830,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr"/>
+      <c r="J23" s="15" t="n"/>
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
@@ -3620,7 +2843,7 @@
       </c>
       <c r="Q23" s="15" t="n"/>
       <c r="R23" s="15" t="n"/>
-      <c r="S23" s="15" t="inlineStr"/>
+      <c r="S23" s="15" t="n"/>
       <c r="T23" s="15" t="n"/>
       <c r="U23" s="15" t="n"/>
       <c r="V23" s="15" t="n"/>
@@ -3640,6 +2863,14 @@
       <c r="AJ23" s="15" t="n"/>
       <c r="AK23" s="15" t="n"/>
       <c r="AL23" s="28" t="n"/>
+      <c r="AM23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -3681,7 +2912,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr"/>
+      <c r="J24" s="15" t="n"/>
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
@@ -3694,7 +2925,7 @@
       </c>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="inlineStr"/>
+      <c r="S24" s="15" t="n"/>
       <c r="T24" s="15" t="n"/>
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="15" t="n"/>
@@ -3714,6 +2945,14 @@
       <c r="AJ24" s="15" t="n"/>
       <c r="AK24" s="15" t="n"/>
       <c r="AL24" s="28" t="n"/>
+      <c r="AM24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
@@ -3754,6 +2993,8 @@
       <c r="AJ25" s="15" t="n"/>
       <c r="AK25" s="15" t="n"/>
       <c r="AL25" s="28" t="n"/>
+      <c r="AM25" s="15" t="n"/>
+      <c r="AN25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n"/>
@@ -3794,6 +3035,8 @@
       <c r="AJ26" s="15" t="n"/>
       <c r="AK26" s="15" t="n"/>
       <c r="AL26" s="28" t="n"/>
+      <c r="AM26" s="15" t="n"/>
+      <c r="AN26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
@@ -3834,6 +3077,8 @@
       <c r="AJ27" s="15" t="n"/>
       <c r="AK27" s="15" t="n"/>
       <c r="AL27" s="28" t="n"/>
+      <c r="AM27" s="15" t="n"/>
+      <c r="AN27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n"/>
@@ -3874,6 +3119,8 @@
       <c r="AJ28" s="15" t="n"/>
       <c r="AK28" s="15" t="n"/>
       <c r="AL28" s="28" t="n"/>
+      <c r="AM28" s="15" t="n"/>
+      <c r="AN28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
@@ -3914,6 +3161,8 @@
       <c r="AJ29" s="15" t="n"/>
       <c r="AK29" s="15" t="n"/>
       <c r="AL29" s="28" t="n"/>
+      <c r="AM29" s="15" t="n"/>
+      <c r="AN29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n"/>
@@ -3954,6 +3203,8 @@
       <c r="AJ30" s="15" t="n"/>
       <c r="AK30" s="15" t="n"/>
       <c r="AL30" s="28" t="n"/>
+      <c r="AM30" s="15" t="n"/>
+      <c r="AN30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
@@ -3994,6 +3245,8 @@
       <c r="AJ31" s="15" t="n"/>
       <c r="AK31" s="15" t="n"/>
       <c r="AL31" s="28" t="n"/>
+      <c r="AM31" s="15" t="n"/>
+      <c r="AN31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n"/>
@@ -4034,6 +3287,8 @@
       <c r="AJ32" s="15" t="n"/>
       <c r="AK32" s="15" t="n"/>
       <c r="AL32" s="28" t="n"/>
+      <c r="AM32" s="15" t="n"/>
+      <c r="AN32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
@@ -4074,6 +3329,8 @@
       <c r="AJ33" s="15" t="n"/>
       <c r="AK33" s="15" t="n"/>
       <c r="AL33" s="28" t="n"/>
+      <c r="AM33" s="15" t="n"/>
+      <c r="AN33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n"/>
@@ -4114,6 +3371,8 @@
       <c r="AJ34" s="15" t="n"/>
       <c r="AK34" s="15" t="n"/>
       <c r="AL34" s="28" t="n"/>
+      <c r="AM34" s="15" t="n"/>
+      <c r="AN34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>
@@ -4154,6 +3413,8 @@
       <c r="AJ35" s="15" t="n"/>
       <c r="AK35" s="15" t="n"/>
       <c r="AL35" s="28" t="n"/>
+      <c r="AM35" s="15" t="n"/>
+      <c r="AN35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n"/>
@@ -4194,6 +3455,8 @@
       <c r="AJ36" s="15" t="n"/>
       <c r="AK36" s="15" t="n"/>
       <c r="AL36" s="28" t="n"/>
+      <c r="AM36" s="15" t="n"/>
+      <c r="AN36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n"/>
@@ -4234,6 +3497,8 @@
       <c r="AJ37" s="15" t="n"/>
       <c r="AK37" s="15" t="n"/>
       <c r="AL37" s="28" t="n"/>
+      <c r="AM37" s="15" t="n"/>
+      <c r="AN37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n"/>
@@ -4274,6 +3539,8 @@
       <c r="AJ38" s="15" t="n"/>
       <c r="AK38" s="15" t="n"/>
       <c r="AL38" s="28" t="n"/>
+      <c r="AM38" s="15" t="n"/>
+      <c r="AN38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n"/>
@@ -4314,6 +3581,8 @@
       <c r="AJ39" s="15" t="n"/>
       <c r="AK39" s="15" t="n"/>
       <c r="AL39" s="28" t="n"/>
+      <c r="AM39" s="15" t="n"/>
+      <c r="AN39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n"/>
@@ -4354,6 +3623,8 @@
       <c r="AJ40" s="15" t="n"/>
       <c r="AK40" s="15" t="n"/>
       <c r="AL40" s="28" t="n"/>
+      <c r="AM40" s="15" t="n"/>
+      <c r="AN40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n"/>
@@ -4394,6 +3665,8 @@
       <c r="AJ41" s="15" t="n"/>
       <c r="AK41" s="15" t="n"/>
       <c r="AL41" s="28" t="n"/>
+      <c r="AM41" s="15" t="n"/>
+      <c r="AN41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n"/>
@@ -4434,6 +3707,8 @@
       <c r="AJ42" s="15" t="n"/>
       <c r="AK42" s="15" t="n"/>
       <c r="AL42" s="28" t="n"/>
+      <c r="AM42" s="15" t="n"/>
+      <c r="AN42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n"/>
@@ -4474,6 +3749,8 @@
       <c r="AJ43" s="15" t="n"/>
       <c r="AK43" s="15" t="n"/>
       <c r="AL43" s="28" t="n"/>
+      <c r="AM43" s="15" t="n"/>
+      <c r="AN43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n"/>
@@ -4514,6 +3791,8 @@
       <c r="AJ44" s="15" t="n"/>
       <c r="AK44" s="15" t="n"/>
       <c r="AL44" s="28" t="n"/>
+      <c r="AM44" s="15" t="n"/>
+      <c r="AN44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
@@ -4554,6 +3833,8 @@
       <c r="AJ45" s="15" t="n"/>
       <c r="AK45" s="15" t="n"/>
       <c r="AL45" s="28" t="n"/>
+      <c r="AM45" s="15" t="n"/>
+      <c r="AN45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n"/>
@@ -4594,6 +3875,8 @@
       <c r="AJ46" s="15" t="n"/>
       <c r="AK46" s="15" t="n"/>
       <c r="AL46" s="28" t="n"/>
+      <c r="AM46" s="15" t="n"/>
+      <c r="AN46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n"/>
@@ -4634,6 +3917,8 @@
       <c r="AJ47" s="15" t="n"/>
       <c r="AK47" s="15" t="n"/>
       <c r="AL47" s="28" t="n"/>
+      <c r="AM47" s="15" t="n"/>
+      <c r="AN47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n"/>
@@ -4674,6 +3959,8 @@
       <c r="AJ48" s="15" t="n"/>
       <c r="AK48" s="15" t="n"/>
       <c r="AL48" s="28" t="n"/>
+      <c r="AM48" s="15" t="n"/>
+      <c r="AN48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n"/>
@@ -4714,6 +4001,8 @@
       <c r="AJ49" s="15" t="n"/>
       <c r="AK49" s="15" t="n"/>
       <c r="AL49" s="28" t="n"/>
+      <c r="AM49" s="15" t="n"/>
+      <c r="AN49" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4725,6 +4014,31 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
+  <dataValidations count="11">
+    <dataValidation sqref="H14:H49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Unique" prompt="A value must be unique within the dataset" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C14:C49" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"string,number,integer,boolean,array,object,timestamp,date,time"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14:B49 J14:J49 M14:U49 W14:AL49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="G14:G49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" type="list">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Schema Name" prompt="The name of the schema (e.g., table) must match the Sheet name &quot;Schema &lt;schema_name&gt;&quot;"/>
+    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number."/>
+    <dataValidation sqref="L14:L49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" type="list">
+      <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I14:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"confidential,restricted,public"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K14:K49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_"/>
+    <dataValidation sqref="V14:V49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AL13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML."/>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4735,240 +4049,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="8.33203125" customWidth="1" style="30" min="1" max="1"/>
-    <col width="13" customWidth="1" style="30" min="2" max="2"/>
-    <col width="48.5" customWidth="1" style="30" min="3" max="3"/>
-    <col width="42.83203125" customWidth="1" style="30" min="4" max="4"/>
-    <col width="25.83203125" customWidth="1" style="30" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="30" min="6" max="16384"/>
+    <col width="17.42578125" customWidth="1" style="30" min="1" max="1"/>
+    <col width="22" customWidth="1" style="30" min="2" max="2"/>
+    <col width="14.28515625" customWidth="1" style="30" min="3" max="3"/>
+    <col width="40.7109375" bestFit="1" customWidth="1" style="30" min="4" max="4"/>
+    <col width="18.28515625" customWidth="1" style="30" min="5" max="5"/>
+    <col width="28.28515625" customWidth="1" style="30" min="6" max="6"/>
+    <col width="19" bestFit="1" customWidth="1" style="30" min="7" max="7"/>
+    <col width="16" bestFit="1" customWidth="1" style="30" min="8" max="8"/>
+    <col width="22.85546875" bestFit="1" customWidth="1" style="30" min="9" max="9"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="30" min="10" max="10"/>
+    <col width="15.42578125" bestFit="1" customWidth="1" style="30" min="11" max="11"/>
+    <col width="17.85546875" bestFit="1" customWidth="1" style="30" min="12" max="12"/>
+    <col width="17.85546875" customWidth="1" style="30" min="13" max="13"/>
+    <col width="8.85546875" customWidth="1" style="30" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="29" t="inlineStr">
         <is>
-          <t>Relationships</t>
-        </is>
-      </c>
-      <c r="B1" s="29" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>Define relationships between schemas by mapping properties from one schema to another (e.g., foreign keys).</t>
-        </is>
-      </c>
-      <c r="B2" s="31" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>Use schema.property dot syntax (e.g., orders.customer_id). Comma-separated for composite keys. Level: 'schema' or 'property'.</t>
-        </is>
-      </c>
-      <c r="B3" s="31" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C4" s="33" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="D4" s="33" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n"/>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n"/>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>C5="sql"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="8">
-    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Description" prompt="A human-readable description of the relationship. Explain the business context or purpose of how the source and target are related."/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Type" prompt="Type of the relationship column(s)."/>
-    <dataValidation sqref="A4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="From" prompt="Source property or schema of the relationship. Use schema.property dot notation (e.g., orders.customer_id). For composite keys at schema level, use comma-separated values (e.g., orders.order_id, orders.line_id)."/>
-    <dataValidation sqref="C22:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="A5:A100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Level" prompt="Select if the relationship shall be defined on schema or property level. Use schema level for composite keys." type="list">
-      <formula1>"schema,property"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B5:B100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Type" prompt="Type of the relationship column(s)." type="list">
-      <formula1>"foreignKey,references,mapsTo"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="To" prompt="Target property or schema the source maps to. Use schema.property dot notation (e.g., customers.id). For composite keys at schema level, use comma-separated values matching the order of the 'From' fields."/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="17.5" customWidth="1" style="30" min="1" max="1"/>
-    <col width="22" customWidth="1" style="30" min="2" max="2"/>
-    <col width="14.33203125" customWidth="1" style="30" min="3" max="3"/>
-    <col width="32.6640625" customWidth="1" style="30" min="4" max="4"/>
-    <col width="18.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col width="28.33203125" customWidth="1" style="30" min="6" max="6"/>
-    <col width="19" bestFit="1" customWidth="1" style="30" min="7" max="7"/>
-    <col width="16" bestFit="1" customWidth="1" style="30" min="8" max="8"/>
-    <col width="22.83203125" bestFit="1" customWidth="1" style="30" min="9" max="9"/>
-    <col width="23.5" bestFit="1" customWidth="1" style="30" min="10" max="10"/>
-    <col width="15.5" bestFit="1" customWidth="1" style="30" min="11" max="11"/>
-    <col width="17.83203125" bestFit="1" customWidth="1" style="30" min="12" max="12"/>
-    <col width="17.83203125" customWidth="1" style="30" min="13" max="13"/>
-    <col width="8.83203125" customWidth="1" style="30" min="14" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
           <t>Quality</t>
         </is>
       </c>
@@ -4987,7 +4089,7 @@
       <c r="B3" s="31" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
@@ -5053,25 +4155,25 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>sql</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>testscenario for mustBeGreaterOrEqualTo</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM shipments</t>
         </is>
@@ -5081,10 +4183,8 @@
           <t>mustBeGreaterOrEqualTo</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H5" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
@@ -5092,46 +4192,38 @@
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBe (integer)</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="27" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>mustBe</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>inline_object_definition</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>{field} must contain the field "destination"</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="31.5" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
@@ -5143,15 +4235,15 @@
           <t>sql</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBe (float)</t>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>testscenario for mustBe (integer)</t>
         </is>
       </c>
       <c r="E7" s="15" t="n"/>
-      <c r="F7" s="27" t="inlineStr">
-        <is>
-          <t>SELECT AVG(duration) FROM shipments</t>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM shipments</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -5159,18 +4251,16 @@
           <t>mustBe</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="15" t="n"/>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
-    </row>
-    <row r="8">
+      <c r="H7" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="36" t="n"/>
+      <c r="L7" s="36" t="n"/>
+      <c r="M7" s="36" t="n"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
@@ -5182,65 +4272,63 @@
           <t>sql</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>testscenario for mustBe (float)</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>SELECT AVG(duration) FROM shipments</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>mustBe</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="36" t="n"/>
+    </row>
+    <row r="9" ht="47.25" customHeight="1">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>testscenario for mustBeLessThan (integer)</t>
         </is>
       </c>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="27" t="inlineStr">
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM shipments where carries='active'</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>mustBeLessThan</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="15" t="n"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeLessThan (float)</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>SELECT AVG(duration) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>mustBeLessOrEqualTo</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
+      <c r="H9" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
@@ -5248,37 +4336,37 @@
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="10" ht="31.5" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>sql</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeBetween</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>SELECT AVG(*) FROM shipments</t>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>testscenario for mustBeLessThan (float)</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>SELECT AVG(duration) FROM shipments</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>mustBeBetween</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>[25.0, 75.0]</t>
+          <t>mustBeLessOrEqualTo</t>
+        </is>
+      </c>
+      <c r="H10" s="36" t="inlineStr">
+        <is>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I10" s="15" t="n"/>
@@ -5287,31 +4375,39 @@
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="11" ht="31.5" customHeight="1">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>inline_object_definition</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>{field} must contain the field "destination"</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>testscenario for mustBeBetween</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>SELECT AVG(*) FROM shipments</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>mustBeBetween</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>[25,75]</t>
+        </is>
+      </c>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
@@ -5322,7 +4418,7 @@
       <c r="A12" s="17" t="n"/>
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
+      <c r="D12" s="17" t="n"/>
       <c r="E12" s="15" t="n"/>
       <c r="F12" s="27" t="n"/>
       <c r="G12" s="15" t="n"/>
@@ -5337,7 +4433,7 @@
       <c r="A13" s="17" t="n"/>
       <c r="B13" s="17" t="n"/>
       <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
+      <c r="D13" s="17" t="n"/>
       <c r="E13" s="15" t="n"/>
       <c r="F13" s="27" t="n"/>
       <c r="G13" s="15" t="n"/>
@@ -5352,7 +4448,7 @@
       <c r="A14" s="17" t="n"/>
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
+      <c r="D14" s="17" t="n"/>
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="27" t="n"/>
       <c r="G14" s="15" t="n"/>
@@ -5367,7 +4463,7 @@
       <c r="A15" s="17" t="n"/>
       <c r="B15" s="17" t="n"/>
       <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
+      <c r="D15" s="17" t="n"/>
       <c r="E15" s="15" t="n"/>
       <c r="F15" s="27" t="n"/>
       <c r="G15" s="15" t="n"/>
@@ -5382,7 +4478,7 @@
       <c r="A16" s="17" t="n"/>
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
+      <c r="D16" s="17" t="n"/>
       <c r="E16" s="15" t="n"/>
       <c r="F16" s="27" t="n"/>
       <c r="G16" s="15" t="n"/>
@@ -5397,7 +4493,7 @@
       <c r="A17" s="17" t="n"/>
       <c r="B17" s="17" t="n"/>
       <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
+      <c r="D17" s="17" t="n"/>
       <c r="E17" s="15" t="n"/>
       <c r="F17" s="27" t="n"/>
       <c r="G17" s="15" t="n"/>
@@ -5412,7 +4508,7 @@
       <c r="A18" s="17" t="n"/>
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
+      <c r="D18" s="17" t="n"/>
       <c r="E18" s="15" t="n"/>
       <c r="F18" s="27" t="n"/>
       <c r="G18" s="15" t="n"/>
@@ -5427,7 +4523,7 @@
       <c r="A19" s="17" t="n"/>
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
+      <c r="D19" s="17" t="n"/>
       <c r="E19" s="15" t="n"/>
       <c r="F19" s="27" t="n"/>
       <c r="G19" s="15" t="n"/>
@@ -5442,7 +4538,7 @@
       <c r="A20" s="17" t="n"/>
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
+      <c r="D20" s="17" t="n"/>
       <c r="E20" s="15" t="n"/>
       <c r="F20" s="27" t="n"/>
       <c r="G20" s="15" t="n"/>
@@ -5457,7 +4553,7 @@
       <c r="A21" s="17" t="n"/>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
+      <c r="D21" s="17" t="n"/>
       <c r="E21" s="15" t="n"/>
       <c r="F21" s="27" t="n"/>
       <c r="G21" s="15" t="n"/>
@@ -5486,6 +4582,10 @@
     <dataValidation sqref="K5:K21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Severity" prompt="The severity of the data quality rule, such as error or warning."/>
     <dataValidation sqref="J5:J21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Implementation" prompt="The data quality check in the engine's specific format."/>
     <dataValidation sqref="I5:I21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Engine" prompt="Required for custom DQ rule: name of the third-party engine being used. Any value is authorized here but common values are soda, greatExpectations, montecarlo, etc."/>
+    <dataValidation sqref="A4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Schema" prompt="The schema name must match the name of the schema (table, ...) in the previous sheets."/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_"/>
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)"/>
+    <dataValidation sqref="D5:D21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description"/>
     <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Threshold Value" prompt="The acutal value for the treshold operator._x000a_For mustBeBetween adn mustNotBeBetween, use [lowerBoundry, upperBoundy] syntax, e.g. [0, 100]."/>
     <dataValidation sqref="G5:G21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Operator" prompt="The comparation operator specifies the condition to validate the rule._x000a_Use it together with the threshold value, e.g. mustBe 0, or mustBeBetween [0,100]_x000a_This is applicable for quality type sql and some library rules." type="list">
       <formula1>"mustBe, mustNotBe, mustBeGreaterThan, mustBeGreaterOrEqualTo, mustBeLessThan, mustBeLessOrEqualTo, mustBeBetween, mustNotBeBetween"</formula1>
@@ -5497,13 +4597,231 @@
     <dataValidation sqref="C5:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"text,library,sql,custom"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description"/>
-    <dataValidation sqref="A4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Schema" prompt="The schema name must match the name of the schema (table, ...) in the previous sheets."/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_"/>
-    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <cols>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.7109375" customWidth="1" style="2" min="4" max="6"/>
+    <col width="8.85546875" customWidth="1" style="2" min="7" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Support and Communication Channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Support and communication channels help consumers find help regarding their use of the data contract.
+Support and communication channels help consumers find help regarding their use of the data contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Channel URL</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Invitation URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>slackname</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>http://find.me.here</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>slack</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="n"/>
+      <c r="B6" s="41" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="n"/>
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="n"/>
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="41" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="n"/>
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="41" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="41" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="41" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="n"/>
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="41" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="41" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="41" t="n"/>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="41" t="n"/>
+      <c r="E17" s="41" t="n"/>
+      <c r="F17" s="41" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="41" t="n"/>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="41" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="41" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="41" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="41" t="n"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="41" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5513,39 +4831,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.6640625" customWidth="1" style="2" min="4" max="6"/>
-    <col width="8.83203125" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.7109375" customWidth="1" style="2" min="4" max="7"/>
+    <col width="8.85546875" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Support and Communication Channels</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Support and communication channels help consumers find help regarding their use of the data contract.
-Support and communication channels help consumers find help regarding their use of the data contract.</t>
+          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract. In v2.x, this section was called stakeholders.
+</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Username</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Channel URL</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -5555,175 +4873,209 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Date In</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Invitation URL</t>
+          <t>Date Out</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Replaced By Username</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>slackname</t>
-        </is>
-      </c>
-      <c r="B5" s="36" t="inlineStr">
-        <is>
-          <t>http://find.me.here</t>
-        </is>
-      </c>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
-        <is>
-          <t>slack</t>
-        </is>
-      </c>
-      <c r="E5" s="36" t="inlineStr">
-        <is>
-          <t>interactive</t>
-        </is>
-      </c>
-      <c r="F5" s="36" t="n"/>
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>vimportant</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="41" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>nimportant</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="inlineStr">
+        <is>
+          <t>reader</t>
+        </is>
+      </c>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F6" s="41" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="G6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
+      <c r="A7" s="41" t="n"/>
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
+      <c r="A8" s="41" t="n"/>
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="41" t="n"/>
+      <c r="G8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
+      <c r="A9" s="41" t="n"/>
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="41" t="n"/>
+      <c r="G10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="G12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
+      <c r="A14" s="41" t="n"/>
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="41" t="n"/>
+      <c r="G14" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
+      <c r="G15" s="41" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="41" t="n"/>
+      <c r="G16" s="41" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="41" t="n"/>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="41" t="n"/>
+      <c r="E17" s="41" t="n"/>
+      <c r="F17" s="41" t="n"/>
+      <c r="G17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="41" t="n"/>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="41" t="n"/>
+      <c r="G18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="41" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="41" t="n"/>
+      <c r="G19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="41" t="n"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="41" t="n"/>
+      <c r="G20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+      <c r="G21" s="41" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B5:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5735,26 +5087,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.6640625" customWidth="1" style="2" min="4" max="7"/>
-    <col width="8.83203125" customWidth="1" style="2" min="8" max="16384"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.85546875" customWidth="1" style="2" min="4" max="4"/>
+    <col width="34.7109375" customWidth="1" style="2" min="5" max="5"/>
+    <col width="8.85546875" customWidth="1" style="2" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract. In v2.x, this section was called stakeholders.
+          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
+This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
 </t>
         </is>
       </c>
@@ -5762,224 +5117,152 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>1st Level Approvers</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Date In</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Date Out</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Replaced By Username</t>
+          <t>2nd Level Approvers</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>vimportant</t>
-        </is>
-      </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
-        <is>
-          <t>administrator</t>
-        </is>
-      </c>
-      <c r="E5" s="36" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
+      <c r="A5" s="41" t="n"/>
+      <c r="B5" s="41" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>nimportant</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>reader</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="G6" s="36" t="n"/>
+      <c r="A6" s="41" t="n"/>
+      <c r="B6" s="41" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
+      <c r="A7" s="41" t="n"/>
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
+      <c r="A8" s="41" t="n"/>
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
+      <c r="A9" s="41" t="n"/>
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
+      <c r="A14" s="41" t="n"/>
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="41" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="41" t="n"/>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="41" t="n"/>
+      <c r="E17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="41" t="n"/>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="41" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="41" t="n"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B5:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5991,182 +5274,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="34.6640625" customWidth="1" style="2" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="2" min="6" max="16384"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.85546875" customWidth="1" style="2" min="4" max="5"/>
+    <col width="34.7109375" customWidth="1" style="2" min="6" max="6"/>
+    <col width="8.85546875" customWidth="1" style="2" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Service-Level Agreement (SLA)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
+          <t xml:space="preserve">This section describes the service-level agreements (SLA).
 This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
 </t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Access</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>1st Level Approvers</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>2nd Level Approvers</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="36" t="n"/>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>Default SLA element(s)</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Extended value</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
+      <c r="A8" s="41" t="n"/>
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
+      <c r="A9" s="41" t="n"/>
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="41" t="n"/>
+      <c r="F9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
+      <c r="A10" s="41" t="n"/>
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="41" t="n"/>
+      <c r="F10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="41" t="n"/>
+      <c r="F11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
+      <c r="A14" s="41" t="n"/>
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
+      <c r="A15" s="41" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="41" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="41" t="n"/>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="41" t="n"/>
+      <c r="E17" s="41" t="n"/>
+      <c r="F17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="41" t="n"/>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="41" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="41" t="n"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="n"/>
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="n"/>
+      <c r="B23" s="41" t="n"/>
+      <c r="C23" s="41" t="n"/>
+      <c r="D23" s="41" t="n"/>
+      <c r="E23" s="41" t="n"/>
+      <c r="F23" s="41" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6178,232 +5511,821 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:F80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" style="2" min="4" max="5"/>
-    <col width="34.6640625" customWidth="1" style="2" min="6" max="6"/>
-    <col width="8.83203125" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="6.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="33.140625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="36.140625" customWidth="1" style="2" min="3" max="6"/>
+    <col width="15" customWidth="1" style="2" min="7" max="22"/>
+    <col width="32.85546875" customWidth="1" style="2" min="23" max="30"/>
+    <col width="34.7109375" customWidth="1" style="2" min="31" max="31"/>
+    <col width="8.85546875" customWidth="1" style="2" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Service-Level Agreement (SLA)</t>
-        </is>
-      </c>
+          <t>Infrastructure and Servers</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section describes the service-level agreements (SLA).
-This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
+          <t xml:space="preserve">The servers element describes where the data protected by this data contract is physically located. </t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>Default SLA element(s)</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="n"/>
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="n"/>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="n"/>
+      <c r="E4" s="41" t="n"/>
+      <c r="F4" s="41" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Extended value</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
+      <c r="A7" s="39" t="n"/>
+      <c r="B7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>bigquery</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
+      <c r="A12" s="39" t="n"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
+      <c r="A13" s="39" t="n"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
+      <c r="A14" s="39" t="n"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
+      <c r="A15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>BigQuery</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
+      <c r="A17" s="39" t="n"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>acme_shipments_prod</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="n"/>
+      <c r="E17" s="41" t="n"/>
+      <c r="F17" s="41" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
+      <c r="A18" s="39" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>shipments_v1</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
+      <c r="A19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Databricks Server</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
+      <c r="A21" s="39" t="n"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
+      <c r="A22" s="39" t="n"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
+      <c r="A23" s="39" t="n"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="n"/>
+      <c r="D23" s="41" t="n"/>
+      <c r="E23" s="41" t="n"/>
+      <c r="F23" s="41" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>Amazon Glue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="n"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="41" t="n"/>
+      <c r="E26" s="41" t="n"/>
+      <c r="F26" s="41" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="n"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="41" t="n"/>
+      <c r="E27" s="41" t="n"/>
+      <c r="F27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="41" t="n"/>
+      <c r="E28" s="41" t="n"/>
+      <c r="F28" s="41" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="n"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="n"/>
+      <c r="D29" s="41" t="n"/>
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="41" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="41" t="n"/>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="41" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="41" t="n"/>
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="41" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="n"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="n"/>
+      <c r="D36" s="41" t="n"/>
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="41" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="n"/>
+      <c r="D37" s="41" t="n"/>
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="41" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="n"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="41" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="n"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="n"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="n"/>
+      <c r="D42" s="41" t="n"/>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="41" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="n"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="41" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="n"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="n"/>
+      <c r="D44" s="41" t="n"/>
+      <c r="E44" s="41" t="n"/>
+      <c r="F44" s="41" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="n"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="n"/>
+      <c r="D45" s="41" t="n"/>
+      <c r="E45" s="41" t="n"/>
+      <c r="F45" s="41" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="39" t="n"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="n"/>
+      <c r="D48" s="41" t="n"/>
+      <c r="E48" s="41" t="n"/>
+      <c r="F48" s="41" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="n"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="n"/>
+      <c r="D49" s="41" t="n"/>
+      <c r="E49" s="41" t="n"/>
+      <c r="F49" s="41" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="n"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="n"/>
+      <c r="D50" s="41" t="n"/>
+      <c r="E50" s="41" t="n"/>
+      <c r="F50" s="41" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="n"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C51" s="41" t="n"/>
+      <c r="D51" s="41" t="n"/>
+      <c r="E51" s="41" t="n"/>
+      <c r="F51" s="41" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="n"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C52" s="41" t="n"/>
+      <c r="D52" s="41" t="n"/>
+      <c r="E52" s="41" t="n"/>
+      <c r="F52" s="41" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="n"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C53" s="41" t="n"/>
+      <c r="D53" s="41" t="n"/>
+      <c r="E53" s="41" t="n"/>
+      <c r="F53" s="41" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="39" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="39" t="n"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="n"/>
+      <c r="D56" s="41" t="n"/>
+      <c r="E56" s="41" t="n"/>
+      <c r="F56" s="41" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="n"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C57" s="41" t="n"/>
+      <c r="D57" s="41" t="n"/>
+      <c r="E57" s="41" t="n"/>
+      <c r="F57" s="41" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="n"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C58" s="41" t="n"/>
+      <c r="D58" s="41" t="n"/>
+      <c r="E58" s="41" t="n"/>
+      <c r="F58" s="41" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="n"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C59" s="41" t="n"/>
+      <c r="D59" s="41" t="n"/>
+      <c r="E59" s="41" t="n"/>
+      <c r="F59" s="41" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="39" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="39" t="n"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="n"/>
+      <c r="D62" s="41" t="n"/>
+      <c r="E62" s="41" t="n"/>
+      <c r="F62" s="41" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="39" t="n"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="n"/>
+      <c r="D63" s="41" t="n"/>
+      <c r="E63" s="41" t="n"/>
+      <c r="F63" s="41" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="39" t="n"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C64" s="41" t="n"/>
+      <c r="D64" s="41" t="n"/>
+      <c r="E64" s="41" t="n"/>
+      <c r="F64" s="41" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="39" t="n"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C65" s="41" t="n"/>
+      <c r="D65" s="41" t="n"/>
+      <c r="E65" s="41" t="n"/>
+      <c r="F65" s="41" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="39" t="n"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C66" s="41" t="n"/>
+      <c r="D66" s="41" t="n"/>
+      <c r="E66" s="41" t="n"/>
+      <c r="F66" s="41" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="39" t="n"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="C67" s="41" t="n"/>
+      <c r="D67" s="41" t="n"/>
+      <c r="E67" s="41" t="n"/>
+      <c r="F67" s="41" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="39" t="n"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C68" s="41" t="n"/>
+      <c r="D68" s="41" t="n"/>
+      <c r="E68" s="41" t="n"/>
+      <c r="F68" s="41" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="39" t="n"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="n"/>
+      <c r="D69" s="41" t="n"/>
+      <c r="E69" s="41" t="n"/>
+      <c r="F69" s="41" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="39" t="n"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C70" s="41" t="n"/>
+      <c r="D70" s="41" t="n"/>
+      <c r="E70" s="41" t="n"/>
+      <c r="F70" s="41" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="n"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C71" s="41" t="n"/>
+      <c r="D71" s="41" t="n"/>
+      <c r="E71" s="41" t="n"/>
+      <c r="F71" s="41" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="39" t="n"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C72" s="41" t="n"/>
+      <c r="D72" s="41" t="n"/>
+      <c r="E72" s="41" t="n"/>
+      <c r="F72" s="41" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="n"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C73" s="41" t="n"/>
+      <c r="D73" s="41" t="n"/>
+      <c r="E73" s="41" t="n"/>
+      <c r="F73" s="41" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="39" t="n"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="C74" s="41" t="n"/>
+      <c r="D74" s="41" t="n"/>
+      <c r="E74" s="41" t="n"/>
+      <c r="F74" s="41" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="39" t="n"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Region Name</t>
+        </is>
+      </c>
+      <c r="C75" s="41" t="n"/>
+      <c r="D75" s="41" t="n"/>
+      <c r="E75" s="41" t="n"/>
+      <c r="F75" s="41" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="39" t="n"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C76" s="41" t="n"/>
+      <c r="D76" s="41" t="n"/>
+      <c r="E76" s="41" t="n"/>
+      <c r="F76" s="41" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="n"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Service Name</t>
+        </is>
+      </c>
+      <c r="C77" s="41" t="n"/>
+      <c r="D77" s="41" t="n"/>
+      <c r="E77" s="41" t="n"/>
+      <c r="F77" s="41" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="39" t="n"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Staging Directory</t>
+        </is>
+      </c>
+      <c r="C78" s="41" t="n"/>
+      <c r="D78" s="41" t="n"/>
+      <c r="E78" s="41" t="n"/>
+      <c r="F78" s="41" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="39" t="n"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="C79" s="41" t="n"/>
+      <c r="D79" s="41" t="n"/>
+      <c r="E79" s="41" t="n"/>
+      <c r="F79" s="41" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="39" t="n"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C80" s="41" t="n"/>
+      <c r="D80" s="41" t="n"/>
+      <c r="E80" s="41" t="n"/>
+      <c r="F80" s="41" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
+    <dataValidation sqref="C4:F7 C9:F45 C48:F53 C56:F59 C62:F80 G4:AE43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="C8:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"api,athena,azure,bigquery,clickhouse,databricks,db2,denodo,dremio,duckdb,glue,cloudsql,informix,kafka,kinesis,mysql,local,oracle,postgresql,presto,pubsub,redshift,s3,sftp,snowflake,sqlserver,synapse,trino,vertica,custom"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -3,20 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1620" yWindow="345" windowWidth="27360" windowHeight="14340" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Schema shipments" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Quality" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Support" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Team" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Roles" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SLA" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Servers" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Pricing" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Custom Properties" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Support" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Team" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Roles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SLA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Servers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
@@ -36,30 +37,31 @@
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
     <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
+    <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
     <definedName name="servers.azure.delimiter">Servers!$C$14</definedName>
     <definedName name="servers.azure.format">Servers!$C$13</definedName>
     <definedName name="servers.azure.location">Servers!$C$12</definedName>
     <definedName name="servers.bigquery.dataset">Servers!$C$18</definedName>
     <definedName name="servers.bigquery.project">Servers!$C$17</definedName>
-    <definedName name="servers.custom.account">Servers!$C$62</definedName>
-    <definedName name="servers.custom.catalog">Servers!$C$63</definedName>
-    <definedName name="servers.custom.database">Servers!$C$64</definedName>
-    <definedName name="servers.custom.dataset">Servers!$C$65</definedName>
-    <definedName name="servers.custom.delimiter">Servers!$C$66</definedName>
-    <definedName name="servers.custom.endpointUrl">Servers!$C$67</definedName>
-    <definedName name="servers.custom.format">Servers!$C$68</definedName>
-    <definedName name="servers.custom.host">Servers!$C$69</definedName>
-    <definedName name="servers.custom.location">Servers!$C$70</definedName>
-    <definedName name="servers.custom.path">Servers!$C$71</definedName>
-    <definedName name="servers.custom.port">Servers!$C$72</definedName>
-    <definedName name="servers.custom.project">Servers!$C$73</definedName>
-    <definedName name="servers.custom.region">Servers!$C$74</definedName>
-    <definedName name="servers.custom.regionName">Servers!$C$75</definedName>
-    <definedName name="servers.custom.schema">Servers!$C$76</definedName>
-    <definedName name="servers.custom.serviceName">Servers!$C$77</definedName>
-    <definedName name="servers.custom.stagingDir">Servers!$C$78</definedName>
-    <definedName name="servers.custom.stream">Servers!$C$79</definedName>
-    <definedName name="servers.custom.warehouse">Servers!$C$80</definedName>
+    <definedName name="servers.custom.account">Servers!$C$67</definedName>
+    <definedName name="servers.custom.catalog">Servers!$C$68</definedName>
+    <definedName name="servers.custom.database">Servers!$C$69</definedName>
+    <definedName name="servers.custom.dataset">Servers!$C$70</definedName>
+    <definedName name="servers.custom.delimiter">Servers!$C$71</definedName>
+    <definedName name="servers.custom.endpointUrl">Servers!$C$72</definedName>
+    <definedName name="servers.custom.format">Servers!$C$73</definedName>
+    <definedName name="servers.custom.host">Servers!$C$74</definedName>
+    <definedName name="servers.custom.location">Servers!$C$75</definedName>
+    <definedName name="servers.custom.path">Servers!$C$76</definedName>
+    <definedName name="servers.custom.port">Servers!$C$77</definedName>
+    <definedName name="servers.custom.project">Servers!$C$78</definedName>
+    <definedName name="servers.custom.region">Servers!$C$79</definedName>
+    <definedName name="servers.custom.regionName">Servers!$C$80</definedName>
+    <definedName name="servers.custom.schema">Servers!$C$81</definedName>
+    <definedName name="servers.custom.serviceName">Servers!$C$82</definedName>
+    <definedName name="servers.custom.stagingDir">Servers!$C$83</definedName>
+    <definedName name="servers.custom.stream">Servers!$C$84</definedName>
+    <definedName name="servers.custom.warehouse">Servers!$C$85</definedName>
     <definedName name="servers.databricks.catalog">Servers!$C$21</definedName>
     <definedName name="servers.databricks.host">Servers!$C$23</definedName>
     <definedName name="servers.databricks.schema">Servers!$C$22</definedName>
@@ -71,6 +73,9 @@
     <definedName name="servers.glue.location">Servers!$C$28</definedName>
     <definedName name="servers.kafka.format">Servers!$C$33</definedName>
     <definedName name="servers.kafka.host">Servers!$C$32</definedName>
+    <definedName name="servers.oracle.host">Servers!$C$62</definedName>
+    <definedName name="servers.oracle.port">Servers!$C$63</definedName>
+    <definedName name="servers.oracle.servicename">Servers!$C$64</definedName>
     <definedName name="servers.postgres.database">Servers!$C$38</definedName>
     <definedName name="servers.postgres.host">Servers!$C$36</definedName>
     <definedName name="servers.postgres.port">Servers!$C$37</definedName>
@@ -106,17 +111,17 @@
     <definedName name="schema.physicalType" localSheetId="2">'Schema shipments'!$B$6</definedName>
     <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$13:$L$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema shipments'!$B$11</definedName>
-    <definedName name="roles" localSheetId="6">Roles!$A$4:$E$1000</definedName>
-    <definedName name="slaProperties" localSheetId="7">SLA!$A$6:$F$1002</definedName>
+    <definedName name="roles" localSheetId="7">Roles!$A$4:$E$1000</definedName>
+    <definedName name="slaProperties" localSheetId="8">SLA!$A$6:$F$1002</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,25 +169,6 @@
     </font>
     <font>
       <name val="Aptos Mono"/>
-      <color theme="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Aptos Mono"/>
-      <family val="3"/>
       <color theme="1"/>
       <sz val="12"/>
     </font>
@@ -348,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -433,21 +419,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -473,7 +444,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -784,10 +762,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="8.85546875" customWidth="1" style="3" min="2" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="3" min="2" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -801,7 +779,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Use this Excel template to edit data contracts.</t>
@@ -812,14 +790,14 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Data Contract</t>
@@ -834,7 +812,7 @@
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="13" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">A data contract is a document that defines the structure, format, semantics, quality, and terms of use </t>
@@ -849,7 +827,7 @@
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="13" t="n"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">for exchanging data between a data provider and their consumers. </t>
@@ -864,7 +842,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="13" t="n"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>A data contract is usually defined in YAML, but you can use this Excel document for easier collaboration</t>
@@ -879,7 +857,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="13" t="n"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>with your stakeholders.</t>
@@ -894,7 +872,7 @@
       <c r="H11" s="13" t="n"/>
       <c r="I11" s="13" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="13" t="n"/>
       <c r="B12" s="13" t="n"/>
       <c r="C12" s="13" t="n"/>
@@ -905,7 +883,7 @@
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="13" t="n"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="13" t="n"/>
@@ -916,7 +894,7 @@
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="13" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Instructions</t>
@@ -931,7 +909,7 @@
       <c r="H14" s="13" t="n"/>
       <c r="I14" s="13" t="n"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>1. Fill in the 'Fundamentals' sheet with basic contract information</t>
@@ -946,7 +924,7 @@
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="13" t="n"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
           <t>2. For every table create a Sheet called "Schema &lt;tablename&gt;"</t>
@@ -961,7 +939,7 @@
       <c r="H16" s="13" t="n"/>
       <c r="I16" s="13" t="n"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">3. After completing the template, </t>
@@ -976,7 +954,7 @@
       <c r="H17" s="13" t="n"/>
       <c r="I17" s="13" t="n"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>a)</t>
@@ -995,7 +973,7 @@
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="13" t="n"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="23" t="n"/>
       <c r="B19" s="24" t="inlineStr">
         <is>
@@ -1010,7 +988,7 @@
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="13" t="n"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="13" t="n"/>
@@ -1021,7 +999,7 @@
       <c r="H20" s="13" t="n"/>
       <c r="I20" s="13" t="n"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="16" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
           <t>b)</t>
@@ -1029,7 +1007,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Or, if you use Data Mesh Manager, import the Excel directly.</t>
+          <t>Or, if you use Entropy Data, import the Excel directly.</t>
         </is>
       </c>
       <c r="C21" s="13" t="n"/>
@@ -1040,7 +1018,7 @@
       <c r="H21" s="13" t="n"/>
       <c r="I21" s="13" t="n"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="25" t="n"/>
       <c r="B22" s="13" t="inlineStr">
         <is>
@@ -1055,11 +1033,11 @@
       <c r="H22" s="13" t="n"/>
       <c r="I22" s="13" t="n"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="16" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Open Data Mesh Manager → Go to Data Contracts → Click Add Data Contract → Import from Excel</t>
+          <t>Open Entropy Data → Go to Data Contracts → Click Add Data Contract → Import from Excel</t>
         </is>
       </c>
       <c r="C23" s="13" t="n"/>
@@ -1070,13 +1048,9 @@
       <c r="H23" s="13" t="n"/>
       <c r="I23" s="13" t="n"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="16" customHeight="1">
       <c r="A24" s="13" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>http://localhost:8080/demo203502625092/datacontracts/import/excel</t>
-        </is>
-      </c>
+      <c r="B24" s="13" t="n"/>
       <c r="C24" s="13" t="n"/>
       <c r="D24" s="13" t="n"/>
       <c r="E24" s="13" t="n"/>
@@ -1085,7 +1059,7 @@
       <c r="H24" s="13" t="n"/>
       <c r="I24" s="13" t="n"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="16" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
@@ -1096,7 +1070,7 @@
       <c r="H25" s="13" t="n"/>
       <c r="I25" s="13" t="n"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Authors:</t>
@@ -1115,7 +1089,7 @@
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="n"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="16" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Version:</t>
@@ -1123,7 +1097,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -1134,7 +1108,7 @@
       <c r="H27" s="13" t="n"/>
       <c r="I27" s="13" t="n"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>License:</t>
@@ -1153,7 +1127,7 @@
       <c r="H28" s="13" t="n"/>
       <c r="I28" s="13" t="n"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="13" t="n"/>
       <c r="C29" s="13" t="n"/>
@@ -1164,7 +1138,7 @@
       <c r="H29" s="13" t="n"/>
       <c r="I29" s="13" t="n"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="16" customHeight="1">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="13" t="n"/>
       <c r="C30" s="13" t="n"/>
@@ -1175,7 +1149,7 @@
       <c r="H30" s="13" t="n"/>
       <c r="I30" s="13" t="n"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="13" t="n"/>
       <c r="C31" s="13" t="n"/>
@@ -1187,9 +1161,6 @@
       <c r="I31" s="13" t="n"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1200,70 +1171,866 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="26.140625" customWidth="1" style="22" min="1" max="1"/>
-    <col width="22.28515625" customWidth="1" style="22" min="2" max="2"/>
-    <col width="10.85546875" customWidth="1" style="22" min="3" max="16384"/>
+    <col width="6.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="33.1640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="36.1640625" customWidth="1" style="2" min="3" max="6"/>
+    <col width="15" customWidth="1" style="2" min="7" max="22"/>
+    <col width="32.83203125" customWidth="1" style="2" min="23" max="30"/>
+    <col width="34.6640625" customWidth="1" style="2" min="31" max="31"/>
+    <col width="8.83203125" customWidth="1" style="2" min="32" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customFormat="1" customHeight="1" s="2">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customFormat="1" customHeight="1" s="2">
+          <t>Infrastructure and Servers</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+    </row>
+    <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2"/>
-    <row r="4" ht="15.75" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>Price Amount</t>
-        </is>
-      </c>
-      <c r="B4" s="41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>Price Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>Price Unit</t>
-        </is>
-      </c>
-      <c r="B6" s="41" t="inlineStr">
-        <is>
-          <t>Per 1000 requests</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The servers element describes where the data protected by this data contract is physically located. </t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="n"/>
+      <c r="B7" s="34" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>bigquery</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="n"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="n"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>BigQuery</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>acme_shipments_prod</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>shipments_v1</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>Databricks Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="n"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="n"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="n"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>Amazon Glue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="n"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="n"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="36" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="36" t="n"/>
+      <c r="F32" s="36" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="36" t="n"/>
+      <c r="F33" s="36" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>PostgreSQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="n"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="36" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="n"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="36" t="n"/>
+      <c r="F38" s="36" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="n"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
+      <c r="F42" s="36" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="34" t="n"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="n"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="36" t="n"/>
+      <c r="F44" s="36" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="n"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="n"/>
+      <c r="D45" s="36" t="n"/>
+      <c r="E45" s="36" t="n"/>
+      <c r="F45" s="36" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="n"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="n"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="n"/>
+      <c r="D49" s="36" t="n"/>
+      <c r="E49" s="36" t="n"/>
+      <c r="F49" s="36" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="n"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="n"/>
+      <c r="D50" s="36" t="n"/>
+      <c r="E50" s="36" t="n"/>
+      <c r="F50" s="36" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="n"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="n"/>
+      <c r="D51" s="36" t="n"/>
+      <c r="E51" s="36" t="n"/>
+      <c r="F51" s="36" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="n"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C52" s="36" t="n"/>
+      <c r="D52" s="36" t="n"/>
+      <c r="E52" s="36" t="n"/>
+      <c r="F52" s="36" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="34" t="n"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C53" s="36" t="n"/>
+      <c r="D53" s="36" t="n"/>
+      <c r="E53" s="36" t="n"/>
+      <c r="F53" s="36" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="34" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="34" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="n"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="36" t="n"/>
+      <c r="F56" s="36" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="n"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="n"/>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
+      <c r="F57" s="36" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="n"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C58" s="36" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="36" t="n"/>
+      <c r="F58" s="36" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="n"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="n"/>
+      <c r="D59" s="36" t="n"/>
+      <c r="E59" s="36" t="n"/>
+      <c r="F59" s="36" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="34" t="n"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C62" s="36" t="n"/>
+      <c r="D62" s="36" t="n"/>
+      <c r="E62" s="36" t="n"/>
+      <c r="F62" s="36" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="34" t="n"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C63" s="36" t="n"/>
+      <c r="D63" s="36" t="n"/>
+      <c r="E63" s="36" t="n"/>
+      <c r="F63" s="36" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="34" t="n"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ServiceName</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="n"/>
+      <c r="D64" s="36" t="n"/>
+      <c r="E64" s="36" t="n"/>
+      <c r="F64" s="36" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="34" t="n"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="n"/>
+      <c r="D67" s="36" t="n"/>
+      <c r="E67" s="36" t="n"/>
+      <c r="F67" s="36" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="n"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="n"/>
+      <c r="D68" s="36" t="n"/>
+      <c r="E68" s="36" t="n"/>
+      <c r="F68" s="36" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="34" t="n"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="C69" s="36" t="n"/>
+      <c r="D69" s="36" t="n"/>
+      <c r="E69" s="36" t="n"/>
+      <c r="F69" s="36" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="34" t="n"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C70" s="36" t="n"/>
+      <c r="D70" s="36" t="n"/>
+      <c r="E70" s="36" t="n"/>
+      <c r="F70" s="36" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="34" t="n"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
+      <c r="F71" s="36" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="34" t="n"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="36" t="n"/>
+      <c r="F72" s="36" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="34" t="n"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="n"/>
+      <c r="D73" s="36" t="n"/>
+      <c r="E73" s="36" t="n"/>
+      <c r="F73" s="36" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="34" t="n"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C74" s="36" t="n"/>
+      <c r="D74" s="36" t="n"/>
+      <c r="E74" s="36" t="n"/>
+      <c r="F74" s="36" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="34" t="n"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C75" s="36" t="n"/>
+      <c r="D75" s="36" t="n"/>
+      <c r="E75" s="36" t="n"/>
+      <c r="F75" s="36" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="34" t="n"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C76" s="36" t="n"/>
+      <c r="D76" s="36" t="n"/>
+      <c r="E76" s="36" t="n"/>
+      <c r="F76" s="36" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="34" t="n"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C77" s="36" t="n"/>
+      <c r="D77" s="36" t="n"/>
+      <c r="E77" s="36" t="n"/>
+      <c r="F77" s="36" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="34" t="n"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="36" t="n"/>
+      <c r="F78" s="36" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="34" t="n"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="C79" s="36" t="n"/>
+      <c r="D79" s="36" t="n"/>
+      <c r="E79" s="36" t="n"/>
+      <c r="F79" s="36" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="34" t="n"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Region Name</t>
+        </is>
+      </c>
+      <c r="C80" s="36" t="n"/>
+      <c r="D80" s="36" t="n"/>
+      <c r="E80" s="36" t="n"/>
+      <c r="F80" s="36" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="34" t="n"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C81" s="36" t="n"/>
+      <c r="D81" s="36" t="n"/>
+      <c r="E81" s="36" t="n"/>
+      <c r="F81" s="36" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="34" t="n"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Service Name</t>
+        </is>
+      </c>
+      <c r="C82" s="36" t="n"/>
+      <c r="D82" s="36" t="n"/>
+      <c r="E82" s="36" t="n"/>
+      <c r="F82" s="36" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="34" t="n"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Staging Directory</t>
+        </is>
+      </c>
+      <c r="C83" s="36" t="n"/>
+      <c r="D83" s="36" t="n"/>
+      <c r="E83" s="36" t="n"/>
+      <c r="F83" s="36" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="34" t="n"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="34" t="n"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="C85" s="36" t="n"/>
+      <c r="D85" s="36" t="n"/>
+      <c r="E85" s="36" t="n"/>
+      <c r="F85" s="36" t="n"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="F4:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="C4:F7 C9:F45 C48:F53 C56:F59 C62:F64 C67:F85 G4:AE43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="C8:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"api,athena,azure,bigquery,clickhouse,databricks,db2,denodo,dremio,duckdb,glue,cloudsql,informix,kafka,kinesis,mysql,local,oracle,postgresql,presto,pubsub,redshift,s3,sftp,snowflake,sqlserver,synapse,trino,vertica,custom"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1276,12 +2043,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="26.1640625" customWidth="1" style="22" min="1" max="1"/>
+    <col width="22.33203125" customWidth="1" style="22" min="2" max="2"/>
+    <col width="10.83203125" customWidth="1" style="22" min="3" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customFormat="1" customHeight="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customFormat="1" customHeight="1" s="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customFormat="1" customHeight="1" s="2"/>
+    <row r="4" ht="16" customFormat="1" customHeight="1" s="2">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Price Amount</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customFormat="1" customHeight="1" s="2">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Price Currency</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customFormat="1" customHeight="1" s="2">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Price Unit</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>Per 1000 requests</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation sqref="F4:K6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
     <col width="90" customWidth="1" style="2" min="2" max="2"/>
-    <col width="8.85546875" customWidth="1" style="2" min="3" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="2" min="3" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1311,87 +2152,87 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="B5" s="41">
-        <f>IF(owner&lt;&gt;"",owner,"")</f>
+      <c r="B5" s="36">
+        <f>IF(owner &lt;&gt; "", owner, "")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>additionalField</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>We added an addition field - b</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="n"/>
-      <c r="B7" s="41" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n"/>
-      <c r="B8" s="41" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="n"/>
-      <c r="B9" s="41" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n"/>
-      <c r="B13" s="41" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="n"/>
-      <c r="B14" s="41" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="n"/>
-      <c r="B15" s="41" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="41" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="n"/>
-      <c r="B17" s="41" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="n"/>
-      <c r="B18" s="41" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="n"/>
-      <c r="B19" s="41" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="n"/>
-      <c r="B20" s="41" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="n"/>
-      <c r="B21" s="41" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1408,20 +2249,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="2.85546875" customWidth="1" style="2" min="1" max="1"/>
-    <col width="19.7109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="2.83203125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="19.6640625" customWidth="1" style="2" min="2" max="2"/>
     <col width="45" customWidth="1" style="2" min="3" max="3"/>
-    <col width="1.85546875" customWidth="1" style="2" min="4" max="4"/>
-    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14.28515625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="1.83203125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.1640625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="14.33203125" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
-    <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.28515625" customWidth="1" style="2" min="10" max="11"/>
-    <col width="23.42578125" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="24.140625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
-    <col width="8.85546875" customWidth="1" style="2" min="14" max="16384"/>
+    <col width="14.1640625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.33203125" customWidth="1" style="2" min="10" max="11"/>
+    <col width="23.5" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+    <col width="24.1640625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
+    <col width="8.83203125" customWidth="1" style="2" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1439,99 +2280,99 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="B4" s="39" t="n"/>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>DataContract</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>apiVersion</t>
         </is>
       </c>
-      <c r="B5" s="39" t="n"/>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>v3.0.0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="n"/>
-      <c r="B6" s="39" t="n"/>
+      <c r="A6" s="34" t="n"/>
+      <c r="B6" s="34" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n"/>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>fulfillment_shipments_v1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n"/>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n"/>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>1.0.2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B10" s="39" t="n"/>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="n"/>
-      <c r="B11" s="39" t="n"/>
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="B12" s="40" t="n"/>
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>fulfillment</t>
         </is>
@@ -1539,105 +2380,105 @@
       <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n"/>
-      <c r="B13" s="39" t="n"/>
+      <c r="A13" s="34" t="n"/>
+      <c r="B13" s="34" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n"/>
-      <c r="C14" s="41" t="n"/>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="36" t="n"/>
       <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Data Product</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n"/>
-      <c r="C15" s="41" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="36" t="n"/>
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Tenant</t>
         </is>
       </c>
-      <c r="B16" s="39" t="n"/>
-      <c r="C16" s="41" t="inlineStr">
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>company-A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="n"/>
-      <c r="B17" s="39" t="n"/>
+      <c r="A17" s="34" t="n"/>
+      <c r="B17" s="34" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B18" s="39" t="n"/>
+      <c r="B18" s="34" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n"/>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="A19" s="34" t="n"/>
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>This data can be used for analytical purposes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="n"/>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="A20" s="34" t="n"/>
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Limitations</t>
         </is>
       </c>
-      <c r="C20" s="41" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Not suitable for real-time use cases</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="n"/>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="A21" s="34" t="n"/>
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="C21" s="41" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Use this to analyze shipments</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="n"/>
-      <c r="B22" s="39" t="n"/>
+      <c r="A22" s="34" t="n"/>
+      <c r="B22" s="34" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B23" s="39" t="n"/>
-      <c r="C23" s="41" t="inlineStr">
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>datalocation:EU</t>
         </is>
@@ -1668,31 +2509,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AL49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="34.85546875" customWidth="1" style="2" min="1" max="1"/>
+    <col width="34.83203125" customWidth="1" style="2" min="1" max="1"/>
     <col width="24" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="12.42578125" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="17.42578125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="28.140625" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="35.7109375" customWidth="1" style="2" min="6" max="6"/>
+    <col width="12.5" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="17.5" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.1640625" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="35.6640625" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
-    <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.28515625" customWidth="1" style="2" min="10" max="10"/>
-    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
-    <col width="28.7109375" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="28.7109375" customWidth="1" style="2" min="13" max="13"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
+    <col width="14.1640625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.33203125" customWidth="1" style="2" min="10" max="10"/>
+    <col width="28.1640625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="28.6640625" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+    <col width="28.6640625" customWidth="1" style="2" min="13" max="13"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
     <col width="19" bestFit="1" customWidth="1" style="2" min="15" max="15"/>
     <col width="19" customWidth="1" style="2" min="16" max="20"/>
-    <col width="21.7109375" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
-    <col width="27.28515625" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
-    <col width="15.42578125" customWidth="1" style="2" min="23" max="37"/>
-    <col width="26.140625" customWidth="1" style="2" min="38" max="38"/>
-    <col width="10.140625" bestFit="1" customWidth="1" style="2" min="39" max="39"/>
-    <col width="11.140625" bestFit="1" customWidth="1" style="2" min="40" max="40"/>
-    <col width="8.85546875" customWidth="1" style="2" min="41" max="16384"/>
+    <col width="21.6640625" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
+    <col width="27.33203125" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
+    <col width="15.5" customWidth="1" style="2" min="23" max="37"/>
+    <col width="26.1640625" customWidth="1" style="2" min="38" max="38"/>
+    <col width="8.83203125" customWidth="1" style="2" min="39" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1717,109 +2556,109 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n"/>
-      <c r="E5" s="47" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="42" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="47" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>This table contains shipment data, including details about shipment IDs, associated orders, delivery dates, carriers, tracking numbers, statuses, and additional shipment information in JSON format.</t>
         </is>
       </c>
-      <c r="C7" s="46" t="n"/>
-      <c r="D7" s="46" t="n"/>
-      <c r="E7" s="47" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="42" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="46" t="n"/>
-      <c r="E8" s="47" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="42" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Physical Name</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>shipments_v1</t>
         </is>
       </c>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="47" t="n"/>
+      <c r="C9" s="41" t="n"/>
+      <c r="D9" s="41" t="n"/>
+      <c r="E9" s="42" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Data Granularity</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Not Aggregated</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="47" t="n"/>
+      <c r="C10" s="41" t="n"/>
+      <c r="D10" s="41" t="n"/>
+      <c r="E10" s="42" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>pii</t>
         </is>
       </c>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="47" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="42" t="n"/>
     </row>
     <row r="12">
       <c r="W12" s="19" t="inlineStr">
@@ -1841,12 +2680,6 @@
       <c r="AI12" s="20" t="n"/>
       <c r="AJ12" s="20" t="n"/>
       <c r="AK12" s="21" t="n"/>
-      <c r="AM12" s="19" t="inlineStr">
-        <is>
-          <t>Custom Properties</t>
-        </is>
-      </c>
-      <c r="AN12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2039,18 +2872,8 @@
           <t>Comments (internal)</t>
         </is>
       </c>
-      <c r="AM13" s="10" t="inlineStr">
-        <is>
-          <t>ScdType</t>
-        </is>
-      </c>
-      <c r="AN13" s="10" t="inlineStr">
-        <is>
-          <t>isMasked</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="63" customHeight="1">
+    </row>
+    <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>shipment_id</t>
@@ -2121,7 +2944,7 @@
       </c>
       <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
-      <c r="S14" s="15" t="n"/>
+      <c r="S14" s="15" t="inlineStr"/>
       <c r="T14" s="15" t="n"/>
       <c r="U14" s="15" t="n"/>
       <c r="V14" s="15" t="b">
@@ -2143,12 +2966,8 @@
       <c r="AJ14" s="15" t="n"/>
       <c r="AK14" s="15" t="n"/>
       <c r="AL14" s="28" t="n"/>
-      <c r="AM14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="47.25" customHeight="1">
+    </row>
+    <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
           <t>order_id</t>
@@ -2161,12 +2980,12 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15" s="16" t="n"/>
+      <c r="E15" s="16" t="inlineStr"/>
       <c r="F15" s="15" t="n"/>
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
+      <c r="J15" s="15" t="inlineStr"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
           <t>http://localhost:8080/demo203502625092/definitions/sales/order_id</t>
@@ -2191,7 +3010,7 @@
       </c>
       <c r="Q15" s="15" t="n"/>
       <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="n"/>
+      <c r="S15" s="15" t="inlineStr"/>
       <c r="T15" s="15" t="n"/>
       <c r="U15" s="15" t="n"/>
       <c r="V15" s="15" t="n"/>
@@ -2211,12 +3030,8 @@
       <c r="AJ15" s="15" t="n"/>
       <c r="AK15" s="15" t="n"/>
       <c r="AL15" s="28" t="n"/>
-      <c r="AM15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="15" t="n"/>
-    </row>
-    <row r="16" ht="31.5" customHeight="1">
+    </row>
+    <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
           <t>delivery_date</t>
@@ -2258,7 +3073,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J16" s="15" t="n"/>
+      <c r="J16" s="15" t="inlineStr"/>
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
@@ -2271,7 +3086,7 @@
       </c>
       <c r="Q16" s="15" t="n"/>
       <c r="R16" s="15" t="n"/>
-      <c r="S16" s="15" t="n"/>
+      <c r="S16" s="15" t="inlineStr"/>
       <c r="T16" s="15" t="n"/>
       <c r="U16" s="15" t="n"/>
       <c r="V16" s="15" t="b">
@@ -2293,12 +3108,8 @@
       <c r="AJ16" s="15" t="n"/>
       <c r="AK16" s="15" t="n"/>
       <c r="AL16" s="28" t="n"/>
-      <c r="AM16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="31.5" customHeight="1">
+    </row>
+    <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
           <t>carrier</t>
@@ -2340,7 +3151,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J17" s="15" t="n"/>
+      <c r="J17" s="15" t="inlineStr"/>
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
@@ -2353,7 +3164,7 @@
       </c>
       <c r="Q17" s="15" t="n"/>
       <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="n"/>
+      <c r="S17" s="15" t="inlineStr"/>
       <c r="T17" s="15" t="n"/>
       <c r="U17" s="15" t="n"/>
       <c r="V17" s="15" t="b">
@@ -2375,12 +3186,8 @@
       <c r="AJ17" s="15" t="n"/>
       <c r="AK17" s="15" t="n"/>
       <c r="AL17" s="28" t="n"/>
-      <c r="AM17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN17" s="15" t="n"/>
-    </row>
-    <row r="18" ht="31.5" customHeight="1">
+    </row>
+    <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
           <t>tracking_number</t>
@@ -2422,7 +3229,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J18" s="15" t="n"/>
+      <c r="J18" s="15" t="inlineStr"/>
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -2435,7 +3242,7 @@
       </c>
       <c r="Q18" s="15" t="n"/>
       <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="n"/>
+      <c r="S18" s="15" t="inlineStr"/>
       <c r="T18" s="15" t="n"/>
       <c r="U18" s="15" t="n"/>
       <c r="V18" s="15" t="b">
@@ -2457,10 +3264,6 @@
       <c r="AJ18" s="15" t="n"/>
       <c r="AK18" s="15" t="n"/>
       <c r="AL18" s="28" t="n"/>
-      <c r="AM18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
@@ -2504,7 +3307,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J19" s="15" t="n"/>
+      <c r="J19" s="15" t="inlineStr"/>
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
@@ -2517,7 +3320,7 @@
       </c>
       <c r="Q19" s="15" t="n"/>
       <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="n"/>
+      <c r="S19" s="15" t="inlineStr"/>
       <c r="T19" s="15" t="n"/>
       <c r="U19" s="15" t="n"/>
       <c r="V19" s="15" t="b">
@@ -2539,12 +3342,8 @@
       <c r="AJ19" s="15" t="n"/>
       <c r="AK19" s="15" t="n"/>
       <c r="AL19" s="28" t="n"/>
-      <c r="AM19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" s="15" t="n"/>
-    </row>
-    <row r="20" ht="31.5" customHeight="1">
+    </row>
+    <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>inline_object_definition</t>
@@ -2586,7 +3385,7 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="J20" s="15" t="n"/>
+      <c r="J20" s="15" t="inlineStr"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
@@ -2597,13 +3396,11 @@
       <c r="P20" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="Q20" s="15" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Q20" s="15" t="n">
+        <v>-1</v>
       </c>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="n"/>
+      <c r="S20" s="15" t="inlineStr"/>
       <c r="T20" s="15" t="n"/>
       <c r="U20" s="15" t="n"/>
       <c r="V20" s="15" t="b">
@@ -2625,10 +3422,6 @@
       <c r="AJ20" s="15" t="n"/>
       <c r="AK20" s="15" t="n"/>
       <c r="AL20" s="28" t="n"/>
-      <c r="AM20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
@@ -2651,7 +3444,7 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="16" t="inlineStr"/>
       <c r="F21" s="15" t="inlineStr">
         <is>
           <t>Shipping address details.</t>
@@ -2666,7 +3459,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J21" s="15" t="n"/>
+      <c r="J21" s="15" t="inlineStr"/>
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
@@ -2675,7 +3468,7 @@
       <c r="P21" s="15" t="n"/>
       <c r="Q21" s="15" t="n"/>
       <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="n"/>
+      <c r="S21" s="15" t="inlineStr"/>
       <c r="T21" s="15" t="n"/>
       <c r="U21" s="15" t="n"/>
       <c r="V21" s="15" t="n"/>
@@ -2695,14 +3488,6 @@
       <c r="AJ21" s="15" t="n"/>
       <c r="AK21" s="15" t="n"/>
       <c r="AL21" s="28" t="n"/>
-      <c r="AM21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN21" s="15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -2746,7 +3531,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J22" s="15" t="n"/>
+      <c r="J22" s="15" t="inlineStr"/>
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
@@ -2759,7 +3544,7 @@
       </c>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="n"/>
+      <c r="S22" s="15" t="inlineStr"/>
       <c r="T22" s="15" t="n"/>
       <c r="U22" s="15" t="n"/>
       <c r="V22" s="15" t="n"/>
@@ -2779,14 +3564,6 @@
       <c r="AJ22" s="15" t="n"/>
       <c r="AK22" s="15" t="n"/>
       <c r="AL22" s="28" t="n"/>
-      <c r="AM22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN22" s="15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
@@ -2830,7 +3607,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J23" s="15" t="n"/>
+      <c r="J23" s="15" t="inlineStr"/>
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
@@ -2843,7 +3620,7 @@
       </c>
       <c r="Q23" s="15" t="n"/>
       <c r="R23" s="15" t="n"/>
-      <c r="S23" s="15" t="n"/>
+      <c r="S23" s="15" t="inlineStr"/>
       <c r="T23" s="15" t="n"/>
       <c r="U23" s="15" t="n"/>
       <c r="V23" s="15" t="n"/>
@@ -2863,14 +3640,6 @@
       <c r="AJ23" s="15" t="n"/>
       <c r="AK23" s="15" t="n"/>
       <c r="AL23" s="28" t="n"/>
-      <c r="AM23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN23" s="15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
@@ -2912,7 +3681,7 @@
           <t>restricted</t>
         </is>
       </c>
-      <c r="J24" s="15" t="n"/>
+      <c r="J24" s="15" t="inlineStr"/>
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
@@ -2925,7 +3694,7 @@
       </c>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="n"/>
+      <c r="S24" s="15" t="inlineStr"/>
       <c r="T24" s="15" t="n"/>
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="15" t="n"/>
@@ -2945,14 +3714,6 @@
       <c r="AJ24" s="15" t="n"/>
       <c r="AK24" s="15" t="n"/>
       <c r="AL24" s="28" t="n"/>
-      <c r="AM24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN24" s="15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="n"/>
@@ -2993,8 +3754,6 @@
       <c r="AJ25" s="15" t="n"/>
       <c r="AK25" s="15" t="n"/>
       <c r="AL25" s="28" t="n"/>
-      <c r="AM25" s="15" t="n"/>
-      <c r="AN25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="n"/>
@@ -3035,8 +3794,6 @@
       <c r="AJ26" s="15" t="n"/>
       <c r="AK26" s="15" t="n"/>
       <c r="AL26" s="28" t="n"/>
-      <c r="AM26" s="15" t="n"/>
-      <c r="AN26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="n"/>
@@ -3077,8 +3834,6 @@
       <c r="AJ27" s="15" t="n"/>
       <c r="AK27" s="15" t="n"/>
       <c r="AL27" s="28" t="n"/>
-      <c r="AM27" s="15" t="n"/>
-      <c r="AN27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="n"/>
@@ -3119,8 +3874,6 @@
       <c r="AJ28" s="15" t="n"/>
       <c r="AK28" s="15" t="n"/>
       <c r="AL28" s="28" t="n"/>
-      <c r="AM28" s="15" t="n"/>
-      <c r="AN28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
@@ -3161,8 +3914,6 @@
       <c r="AJ29" s="15" t="n"/>
       <c r="AK29" s="15" t="n"/>
       <c r="AL29" s="28" t="n"/>
-      <c r="AM29" s="15" t="n"/>
-      <c r="AN29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n"/>
@@ -3203,8 +3954,6 @@
       <c r="AJ30" s="15" t="n"/>
       <c r="AK30" s="15" t="n"/>
       <c r="AL30" s="28" t="n"/>
-      <c r="AM30" s="15" t="n"/>
-      <c r="AN30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
@@ -3245,8 +3994,6 @@
       <c r="AJ31" s="15" t="n"/>
       <c r="AK31" s="15" t="n"/>
       <c r="AL31" s="28" t="n"/>
-      <c r="AM31" s="15" t="n"/>
-      <c r="AN31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n"/>
@@ -3287,8 +4034,6 @@
       <c r="AJ32" s="15" t="n"/>
       <c r="AK32" s="15" t="n"/>
       <c r="AL32" s="28" t="n"/>
-      <c r="AM32" s="15" t="n"/>
-      <c r="AN32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
@@ -3329,8 +4074,6 @@
       <c r="AJ33" s="15" t="n"/>
       <c r="AK33" s="15" t="n"/>
       <c r="AL33" s="28" t="n"/>
-      <c r="AM33" s="15" t="n"/>
-      <c r="AN33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n"/>
@@ -3371,8 +4114,6 @@
       <c r="AJ34" s="15" t="n"/>
       <c r="AK34" s="15" t="n"/>
       <c r="AL34" s="28" t="n"/>
-      <c r="AM34" s="15" t="n"/>
-      <c r="AN34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>
@@ -3413,8 +4154,6 @@
       <c r="AJ35" s="15" t="n"/>
       <c r="AK35" s="15" t="n"/>
       <c r="AL35" s="28" t="n"/>
-      <c r="AM35" s="15" t="n"/>
-      <c r="AN35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n"/>
@@ -3455,8 +4194,6 @@
       <c r="AJ36" s="15" t="n"/>
       <c r="AK36" s="15" t="n"/>
       <c r="AL36" s="28" t="n"/>
-      <c r="AM36" s="15" t="n"/>
-      <c r="AN36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n"/>
@@ -3497,8 +4234,6 @@
       <c r="AJ37" s="15" t="n"/>
       <c r="AK37" s="15" t="n"/>
       <c r="AL37" s="28" t="n"/>
-      <c r="AM37" s="15" t="n"/>
-      <c r="AN37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n"/>
@@ -3539,8 +4274,6 @@
       <c r="AJ38" s="15" t="n"/>
       <c r="AK38" s="15" t="n"/>
       <c r="AL38" s="28" t="n"/>
-      <c r="AM38" s="15" t="n"/>
-      <c r="AN38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n"/>
@@ -3581,8 +4314,6 @@
       <c r="AJ39" s="15" t="n"/>
       <c r="AK39" s="15" t="n"/>
       <c r="AL39" s="28" t="n"/>
-      <c r="AM39" s="15" t="n"/>
-      <c r="AN39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n"/>
@@ -3623,8 +4354,6 @@
       <c r="AJ40" s="15" t="n"/>
       <c r="AK40" s="15" t="n"/>
       <c r="AL40" s="28" t="n"/>
-      <c r="AM40" s="15" t="n"/>
-      <c r="AN40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n"/>
@@ -3665,8 +4394,6 @@
       <c r="AJ41" s="15" t="n"/>
       <c r="AK41" s="15" t="n"/>
       <c r="AL41" s="28" t="n"/>
-      <c r="AM41" s="15" t="n"/>
-      <c r="AN41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n"/>
@@ -3707,8 +4434,6 @@
       <c r="AJ42" s="15" t="n"/>
       <c r="AK42" s="15" t="n"/>
       <c r="AL42" s="28" t="n"/>
-      <c r="AM42" s="15" t="n"/>
-      <c r="AN42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n"/>
@@ -3749,8 +4474,6 @@
       <c r="AJ43" s="15" t="n"/>
       <c r="AK43" s="15" t="n"/>
       <c r="AL43" s="28" t="n"/>
-      <c r="AM43" s="15" t="n"/>
-      <c r="AN43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n"/>
@@ -3791,8 +4514,6 @@
       <c r="AJ44" s="15" t="n"/>
       <c r="AK44" s="15" t="n"/>
       <c r="AL44" s="28" t="n"/>
-      <c r="AM44" s="15" t="n"/>
-      <c r="AN44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
@@ -3833,8 +4554,6 @@
       <c r="AJ45" s="15" t="n"/>
       <c r="AK45" s="15" t="n"/>
       <c r="AL45" s="28" t="n"/>
-      <c r="AM45" s="15" t="n"/>
-      <c r="AN45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n"/>
@@ -3875,8 +4594,6 @@
       <c r="AJ46" s="15" t="n"/>
       <c r="AK46" s="15" t="n"/>
       <c r="AL46" s="28" t="n"/>
-      <c r="AM46" s="15" t="n"/>
-      <c r="AN46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n"/>
@@ -3917,8 +4634,6 @@
       <c r="AJ47" s="15" t="n"/>
       <c r="AK47" s="15" t="n"/>
       <c r="AL47" s="28" t="n"/>
-      <c r="AM47" s="15" t="n"/>
-      <c r="AN47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n"/>
@@ -3959,8 +4674,6 @@
       <c r="AJ48" s="15" t="n"/>
       <c r="AK48" s="15" t="n"/>
       <c r="AL48" s="28" t="n"/>
-      <c r="AM48" s="15" t="n"/>
-      <c r="AN48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n"/>
@@ -4001,8 +4714,6 @@
       <c r="AJ49" s="15" t="n"/>
       <c r="AK49" s="15" t="n"/>
       <c r="AL49" s="28" t="n"/>
-      <c r="AM49" s="15" t="n"/>
-      <c r="AN49" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4014,31 +4725,6 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="11">
-    <dataValidation sqref="H14:H49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Unique" prompt="A value must be unique within the dataset" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C14:C49" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"string,number,integer,boolean,array,object,timestamp,date,time"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B14:B49 J14:J49 M14:U49 W14:AL49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="G14:G49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" type="list">
-      <formula1>"true,false"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B5:E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Schema Name" prompt="The name of the schema (e.g., table) must match the Sheet name &quot;Schema &lt;schema_name&gt;&quot;"/>
-    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number."/>
-    <dataValidation sqref="L14:L49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" type="list">
-      <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I14:I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"confidential,restricted,public"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K14:K49" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_"/>
-    <dataValidation sqref="V14:V49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AL13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML."/>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4049,28 +4735,240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="17.42578125" customWidth="1" style="30" min="1" max="1"/>
-    <col width="22" customWidth="1" style="30" min="2" max="2"/>
-    <col width="14.28515625" customWidth="1" style="30" min="3" max="3"/>
-    <col width="40.7109375" bestFit="1" customWidth="1" style="30" min="4" max="4"/>
-    <col width="18.28515625" customWidth="1" style="30" min="5" max="5"/>
-    <col width="28.28515625" customWidth="1" style="30" min="6" max="6"/>
-    <col width="19" bestFit="1" customWidth="1" style="30" min="7" max="7"/>
-    <col width="16" bestFit="1" customWidth="1" style="30" min="8" max="8"/>
-    <col width="22.85546875" bestFit="1" customWidth="1" style="30" min="9" max="9"/>
-    <col width="23.42578125" bestFit="1" customWidth="1" style="30" min="10" max="10"/>
-    <col width="15.42578125" bestFit="1" customWidth="1" style="30" min="11" max="11"/>
-    <col width="17.85546875" bestFit="1" customWidth="1" style="30" min="12" max="12"/>
-    <col width="17.85546875" customWidth="1" style="30" min="13" max="13"/>
-    <col width="8.85546875" customWidth="1" style="30" min="14" max="16384"/>
+    <col width="8.33203125" customWidth="1" style="30" min="1" max="1"/>
+    <col width="13" customWidth="1" style="30" min="2" max="2"/>
+    <col width="48.5" customWidth="1" style="30" min="3" max="3"/>
+    <col width="42.83203125" customWidth="1" style="30" min="4" max="4"/>
+    <col width="25.83203125" customWidth="1" style="30" min="5" max="5"/>
+    <col width="8.83203125" customWidth="1" style="30" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="29" t="inlineStr">
         <is>
+          <t>Relationships</t>
+        </is>
+      </c>
+      <c r="B1" s="29" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>Define relationships between schemas by mapping properties from one schema to another (e.g., foreign keys).</t>
+        </is>
+      </c>
+      <c r="B2" s="31" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>Use schema.property dot syntax (e.g., orders.customer_id). Comma-separated for composite keys. Level: 'schema' or 'property'.</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E5:E21">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>C5="sql"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Description" prompt="A human-readable description of the relationship. Explain the business context or purpose of how the source and target are related."/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Type" prompt="Type of the relationship column(s)."/>
+    <dataValidation sqref="A4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="From" prompt="Source property or schema of the relationship. Use schema.property dot notation (e.g., orders.customer_id). For composite keys at schema level, use comma-separated values (e.g., orders.order_id, orders.line_id)."/>
+    <dataValidation sqref="C22:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="A5:A100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Level" prompt="Select if the relationship shall be defined on schema or property level. Use schema level for composite keys." type="list">
+      <formula1>"schema,property"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Type" prompt="Type of the relationship column(s)." type="list">
+      <formula1>"foreignKey,references,mapsTo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="To" prompt="Target property or schema the source maps to. Use schema.property dot notation (e.g., customers.id). For composite keys at schema level, use comma-separated values matching the order of the 'From' fields."/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="17.5" customWidth="1" style="30" min="1" max="1"/>
+    <col width="22" customWidth="1" style="30" min="2" max="2"/>
+    <col width="14.33203125" customWidth="1" style="30" min="3" max="3"/>
+    <col width="32.6640625" customWidth="1" style="30" min="4" max="4"/>
+    <col width="18.33203125" customWidth="1" style="30" min="5" max="5"/>
+    <col width="28.33203125" customWidth="1" style="30" min="6" max="6"/>
+    <col width="19" bestFit="1" customWidth="1" style="30" min="7" max="7"/>
+    <col width="16" bestFit="1" customWidth="1" style="30" min="8" max="8"/>
+    <col width="22.83203125" bestFit="1" customWidth="1" style="30" min="9" max="9"/>
+    <col width="23.5" bestFit="1" customWidth="1" style="30" min="10" max="10"/>
+    <col width="15.5" bestFit="1" customWidth="1" style="30" min="11" max="11"/>
+    <col width="17.83203125" bestFit="1" customWidth="1" style="30" min="12" max="12"/>
+    <col width="17.83203125" customWidth="1" style="30" min="13" max="13"/>
+    <col width="8.83203125" customWidth="1" style="30" min="14" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
           <t>Quality</t>
         </is>
       </c>
@@ -4089,7 +4987,7 @@
       <c r="B3" s="31" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
@@ -4155,25 +5053,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="31.5" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>sql</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>testscenario for mustBeGreaterOrEqualTo</t>
         </is>
       </c>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM shipments</t>
         </is>
@@ -4183,8 +5081,10 @@
           <t>mustBeGreaterOrEqualTo</t>
         </is>
       </c>
-      <c r="H5" s="36" t="n">
-        <v>1</v>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I5" s="15" t="n"/>
       <c r="J5" s="15" t="n"/>
@@ -4192,38 +5092,46 @@
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
     </row>
-    <row r="6" ht="31.5" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>inline_object_definition</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>{field} must contain the field "destination"</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>testscenario for mustBe (integer)</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM shipments</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>mustBe</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
     </row>
-    <row r="7" ht="31.5" customHeight="1">
+    <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
@@ -4235,15 +5143,15 @@
           <t>sql</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>testscenario for mustBe (integer)</t>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>testscenario for mustBe (float)</t>
         </is>
       </c>
       <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM shipments</t>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>SELECT AVG(duration) FROM shipments</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -4251,16 +5159,18 @@
           <t>mustBe</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="36" t="n"/>
-      <c r="K7" s="36" t="n"/>
-      <c r="L7" s="36" t="n"/>
-      <c r="M7" s="36" t="n"/>
-    </row>
-    <row r="8" ht="31.5" customHeight="1">
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="15" t="n"/>
+      <c r="M7" s="15" t="n"/>
+    </row>
+    <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
@@ -4272,63 +5182,65 @@
           <t>sql</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>testscenario for mustBe (float)</t>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>testscenario for mustBeLessThan (integer)</t>
         </is>
       </c>
       <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM shipments where carries='active'</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>mustBeLessThan</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>testscenario for mustBeLessThan (float)</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>SELECT AVG(duration) FROM shipments</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>mustBe</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="36" t="n"/>
-      <c r="K8" s="36" t="n"/>
-      <c r="L8" s="36" t="n"/>
-      <c r="M8" s="36" t="n"/>
-    </row>
-    <row r="9" ht="47.25" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="n"/>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeLessThan (integer)</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM shipments where carries='active'</t>
-        </is>
-      </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>mustBeLessThan</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="n">
-        <v>1</v>
+          <t>mustBeLessOrEqualTo</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
       </c>
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
@@ -4336,37 +5248,37 @@
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
     </row>
-    <row r="10" ht="31.5" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n"/>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>sql</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeLessThan (float)</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="inlineStr">
-        <is>
-          <t>SELECT AVG(duration) FROM shipments</t>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>testscenario for mustBeBetween</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>SELECT AVG(*) FROM shipments</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>mustBeLessOrEqualTo</t>
-        </is>
-      </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>6.8</t>
+          <t>mustBeBetween</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>[25.0, 75.0]</t>
         </is>
       </c>
       <c r="I10" s="15" t="n"/>
@@ -4375,39 +5287,31 @@
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
     </row>
-    <row r="11" ht="31.5" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n"/>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeBetween</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="inlineStr">
-        <is>
-          <t>SELECT AVG(*) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>mustBeBetween</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>[25,75]</t>
-        </is>
-      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>inline_object_definition</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>{field} must contain the field "destination"</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
       <c r="I11" s="15" t="n"/>
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
@@ -4418,7 +5322,7 @@
       <c r="A12" s="17" t="n"/>
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="15" t="n"/>
-      <c r="D12" s="17" t="n"/>
+      <c r="D12" s="15" t="n"/>
       <c r="E12" s="15" t="n"/>
       <c r="F12" s="27" t="n"/>
       <c r="G12" s="15" t="n"/>
@@ -4433,7 +5337,7 @@
       <c r="A13" s="17" t="n"/>
       <c r="B13" s="17" t="n"/>
       <c r="C13" s="15" t="n"/>
-      <c r="D13" s="17" t="n"/>
+      <c r="D13" s="15" t="n"/>
       <c r="E13" s="15" t="n"/>
       <c r="F13" s="27" t="n"/>
       <c r="G13" s="15" t="n"/>
@@ -4448,7 +5352,7 @@
       <c r="A14" s="17" t="n"/>
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="15" t="n"/>
-      <c r="D14" s="17" t="n"/>
+      <c r="D14" s="15" t="n"/>
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="27" t="n"/>
       <c r="G14" s="15" t="n"/>
@@ -4463,7 +5367,7 @@
       <c r="A15" s="17" t="n"/>
       <c r="B15" s="17" t="n"/>
       <c r="C15" s="15" t="n"/>
-      <c r="D15" s="17" t="n"/>
+      <c r="D15" s="15" t="n"/>
       <c r="E15" s="15" t="n"/>
       <c r="F15" s="27" t="n"/>
       <c r="G15" s="15" t="n"/>
@@ -4478,7 +5382,7 @@
       <c r="A16" s="17" t="n"/>
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="15" t="n"/>
-      <c r="D16" s="17" t="n"/>
+      <c r="D16" s="15" t="n"/>
       <c r="E16" s="15" t="n"/>
       <c r="F16" s="27" t="n"/>
       <c r="G16" s="15" t="n"/>
@@ -4493,7 +5397,7 @@
       <c r="A17" s="17" t="n"/>
       <c r="B17" s="17" t="n"/>
       <c r="C17" s="15" t="n"/>
-      <c r="D17" s="17" t="n"/>
+      <c r="D17" s="15" t="n"/>
       <c r="E17" s="15" t="n"/>
       <c r="F17" s="27" t="n"/>
       <c r="G17" s="15" t="n"/>
@@ -4508,7 +5412,7 @@
       <c r="A18" s="17" t="n"/>
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="15" t="n"/>
-      <c r="D18" s="17" t="n"/>
+      <c r="D18" s="15" t="n"/>
       <c r="E18" s="15" t="n"/>
       <c r="F18" s="27" t="n"/>
       <c r="G18" s="15" t="n"/>
@@ -4523,7 +5427,7 @@
       <c r="A19" s="17" t="n"/>
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="15" t="n"/>
-      <c r="D19" s="17" t="n"/>
+      <c r="D19" s="15" t="n"/>
       <c r="E19" s="15" t="n"/>
       <c r="F19" s="27" t="n"/>
       <c r="G19" s="15" t="n"/>
@@ -4538,7 +5442,7 @@
       <c r="A20" s="17" t="n"/>
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="15" t="n"/>
-      <c r="D20" s="17" t="n"/>
+      <c r="D20" s="15" t="n"/>
       <c r="E20" s="15" t="n"/>
       <c r="F20" s="27" t="n"/>
       <c r="G20" s="15" t="n"/>
@@ -4553,7 +5457,7 @@
       <c r="A21" s="17" t="n"/>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="15" t="n"/>
-      <c r="D21" s="17" t="n"/>
+      <c r="D21" s="15" t="n"/>
       <c r="E21" s="15" t="n"/>
       <c r="F21" s="27" t="n"/>
       <c r="G21" s="15" t="n"/>
@@ -4582,10 +5486,6 @@
     <dataValidation sqref="K5:K21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Severity" prompt="The severity of the data quality rule, such as error or warning."/>
     <dataValidation sqref="J5:J21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Implementation" prompt="The data quality check in the engine's specific format."/>
     <dataValidation sqref="I5:I21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Engine" prompt="Required for custom DQ rule: name of the third-party engine being used. Any value is authorized here but common values are soda, greatExpectations, montecarlo, etc."/>
-    <dataValidation sqref="A4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Schema" prompt="The schema name must match the name of the schema (table, ...) in the previous sheets."/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_"/>
-    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)"/>
-    <dataValidation sqref="D5:D21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description"/>
     <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Threshold Value" prompt="The acutal value for the treshold operator._x000a_For mustBeBetween adn mustNotBeBetween, use [lowerBoundry, upperBoundy] syntax, e.g. [0, 100]."/>
     <dataValidation sqref="G5:G21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality Operator" prompt="The comparation operator specifies the condition to validate the rule._x000a_Use it together with the threshold value, e.g. mustBe 0, or mustBeBetween [0,100]_x000a_This is applicable for quality type sql and some library rules." type="list">
       <formula1>"mustBe, mustNotBe, mustBeGreaterThan, mustBeGreaterOrEqualTo, mustBeLessThan, mustBeLessOrEqualTo, mustBeBetween, mustNotBeBetween"</formula1>
@@ -4597,231 +5497,13 @@
     <dataValidation sqref="C5:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"text,library,sql,custom"</formula1>
     </dataValidation>
+    <dataValidation sqref="D5:D21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description"/>
+    <dataValidation sqref="A4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Schema" prompt="The schema name must match the name of the schema (table, ...) in the previous sheets."/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_"/>
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.7109375" customWidth="1" style="2" min="4" max="6"/>
-    <col width="8.85546875" customWidth="1" style="2" min="7" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Support and Communication Channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Support and communication channels help consumers find help regarding their use of the data contract.
-Support and communication channels help consumers find help regarding their use of the data contract.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Channel URL</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Tool</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Invitation URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>slackname</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>http://find.me.here</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>slack</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="inlineStr">
-        <is>
-          <t>interactive</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="41" t="n"/>
-      <c r="B6" s="41" t="n"/>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="41" t="n"/>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="41" t="n"/>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="41" t="n"/>
-      <c r="F8" s="41" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="41" t="n"/>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="41" t="n"/>
-      <c r="F10" s="41" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="41" t="n"/>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="41" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="41" t="n"/>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="41" t="n"/>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="41" t="n"/>
-      <c r="F16" s="41" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="41" t="n"/>
-      <c r="B17" s="41" t="n"/>
-      <c r="C17" s="41" t="n"/>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="41" t="n"/>
-      <c r="B18" s="41" t="n"/>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="41" t="n"/>
-      <c r="B19" s="41" t="n"/>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="41" t="n"/>
-      <c r="B20" s="41" t="n"/>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="41" t="n"/>
-      <c r="F20" s="41" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="41" t="n"/>
-      <c r="B21" s="41" t="n"/>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -4831,39 +5513,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.7109375" customWidth="1" style="2" min="4" max="7"/>
-    <col width="8.85546875" customWidth="1" style="2" min="8" max="16384"/>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.6640625" customWidth="1" style="2" min="4" max="6"/>
+    <col width="8.83203125" customWidth="1" style="2" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Support and Communication Channels</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract. In v2.x, this section was called stakeholders.
-</t>
+          <t>Support and communication channels help consumers find help regarding their use of the data contract.
+Support and communication channels help consumers find help regarding their use of the data contract.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Channel URL</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -4873,209 +5555,175 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Date In</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Date Out</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Replaced By Username</t>
+          <t>Invitation URL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>vimportant</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="n"/>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>administrator</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>slackname</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>http://find.me.here</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>slack</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
-        <is>
-          <t>nimportant</t>
-        </is>
-      </c>
-      <c r="B6" s="41" t="n"/>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="inlineStr">
-        <is>
-          <t>reader</t>
-        </is>
-      </c>
-      <c r="E6" s="41" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="F6" s="41" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="n"/>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="n"/>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n"/>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="41" t="n"/>
-      <c r="F8" s="41" t="n"/>
-      <c r="G8" s="41" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="n"/>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="41" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="41" t="n"/>
-      <c r="F10" s="41" t="n"/>
-      <c r="G10" s="41" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n"/>
-      <c r="G11" s="41" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
-      <c r="G12" s="41" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n"/>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="41" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n"/>
-      <c r="G13" s="41" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="n"/>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
-      <c r="G14" s="41" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="n"/>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
-      <c r="G15" s="41" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="41" t="n"/>
-      <c r="F16" s="41" t="n"/>
-      <c r="G16" s="41" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="n"/>
-      <c r="B17" s="41" t="n"/>
-      <c r="C17" s="41" t="n"/>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
-      <c r="G17" s="41" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="n"/>
-      <c r="B18" s="41" t="n"/>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
-      <c r="G18" s="41" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="n"/>
-      <c r="B19" s="41" t="n"/>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n"/>
-      <c r="G19" s="41" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="n"/>
-      <c r="B20" s="41" t="n"/>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="41" t="n"/>
-      <c r="F20" s="41" t="n"/>
-      <c r="G20" s="41" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="n"/>
-      <c r="B21" s="41" t="n"/>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
-      <c r="G21" s="41" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B5:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5087,29 +5735,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.7109375" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.85546875" customWidth="1" style="2" min="4" max="4"/>
-    <col width="34.7109375" customWidth="1" style="2" min="5" max="5"/>
-    <col width="8.85546875" customWidth="1" style="2" min="6" max="16384"/>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.6640625" customWidth="1" style="2" min="4" max="7"/>
+    <col width="8.83203125" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
-This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
+          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract. In v2.x, this section was called stakeholders.
 </t>
         </is>
       </c>
@@ -5117,152 +5762,224 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Access</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>1st Level Approvers</t>
-        </is>
-      </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>2nd Level Approvers</t>
+          <t>Date In</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Date Out</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Replaced By Username</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="n"/>
-      <c r="B5" s="41" t="n"/>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>vimportant</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="n"/>
-      <c r="B6" s="41" t="n"/>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>nimportant</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>reader</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="n"/>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n"/>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="41" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="n"/>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="41" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="41" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="41" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n"/>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="41" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="41" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="n"/>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="n"/>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="41" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="n"/>
-      <c r="B17" s="41" t="n"/>
-      <c r="C17" s="41" t="n"/>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="41" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="n"/>
-      <c r="B18" s="41" t="n"/>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="n"/>
-      <c r="B19" s="41" t="n"/>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="n"/>
-      <c r="B20" s="41" t="n"/>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="41" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="n"/>
-      <c r="B21" s="41" t="n"/>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B5:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5274,232 +5991,182 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.7109375" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.85546875" customWidth="1" style="2" min="4" max="5"/>
-    <col width="34.7109375" customWidth="1" style="2" min="6" max="6"/>
-    <col width="8.85546875" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.83203125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="34.6640625" customWidth="1" style="2" min="5" max="5"/>
+    <col width="8.83203125" customWidth="1" style="2" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Service-Level Agreement (SLA)</t>
+          <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This section describes the service-level agreements (SLA).
+          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
 This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
 </t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-    </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>Default SLA element(s)</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="n"/>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1st Level Approvers</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>2nd Level Approvers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Extended value</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="n"/>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="41" t="n"/>
-      <c r="F8" s="41" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="n"/>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="41" t="n"/>
-      <c r="F9" s="41" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="n"/>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="41" t="n"/>
-      <c r="F10" s="41" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="n"/>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="41" t="n"/>
-      <c r="F11" s="41" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="n"/>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="n"/>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="41" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="n"/>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="n"/>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="n"/>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="41" t="n"/>
-      <c r="F16" s="41" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="n"/>
-      <c r="B17" s="41" t="n"/>
-      <c r="C17" s="41" t="n"/>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="n"/>
-      <c r="B18" s="41" t="n"/>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="n"/>
-      <c r="B19" s="41" t="n"/>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="n"/>
-      <c r="B20" s="41" t="n"/>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="41" t="n"/>
-      <c r="F20" s="41" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="n"/>
-      <c r="B21" s="41" t="n"/>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="41" t="n"/>
-      <c r="B22" s="41" t="n"/>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="41" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="41" t="n"/>
-      <c r="B23" s="41" t="n"/>
-      <c r="C23" s="41" t="n"/>
-      <c r="D23" s="41" t="n"/>
-      <c r="E23" s="41" t="n"/>
-      <c r="F23" s="41" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5511,821 +6178,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="6.140625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="33.140625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="36.140625" customWidth="1" style="2" min="3" max="6"/>
-    <col width="15" customWidth="1" style="2" min="7" max="22"/>
-    <col width="32.85546875" customWidth="1" style="2" min="23" max="30"/>
-    <col width="34.7109375" customWidth="1" style="2" min="31" max="31"/>
-    <col width="8.85546875" customWidth="1" style="2" min="32" max="16384"/>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.83203125" customWidth="1" style="2" min="4" max="5"/>
+    <col width="34.6640625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="8.83203125" customWidth="1" style="2" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure and Servers</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
+          <t>Service-Level Agreement (SLA)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The servers element describes where the data protected by this data contract is physically located. </t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
+          <t xml:space="preserve">This section describes the service-level agreements (SLA).
+This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="39" t="n"/>
-      <c r="C4" s="41" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="B5" s="39" t="n"/>
-      <c r="C5" s="41" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Default SLA element(s)</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="n"/>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Extended value</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="n"/>
-      <c r="B7" s="39" t="n"/>
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="n"/>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>bigquery</t>
-        </is>
-      </c>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="41" t="n"/>
-      <c r="F8" s="41" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="n"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C13" s="41" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="41" t="n"/>
-      <c r="F13" s="41" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="n"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
-        <is>
-          <t>BigQuery</t>
-        </is>
-      </c>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="n"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C17" s="41" t="inlineStr">
-        <is>
-          <t>acme_shipments_prod</t>
-        </is>
-      </c>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="n"/>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr">
-        <is>
-          <t>shipments_v1</t>
-        </is>
-      </c>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>Databricks Server</t>
-        </is>
-      </c>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="n"/>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="n"/>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="41" t="n"/>
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="n"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="n"/>
-      <c r="D23" s="41" t="n"/>
-      <c r="E23" s="41" t="n"/>
-      <c r="F23" s="41" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="39" t="inlineStr">
-        <is>
-          <t>Amazon Glue</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="39" t="n"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="41" t="n"/>
-      <c r="E26" s="41" t="n"/>
-      <c r="F26" s="41" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="39" t="n"/>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="41" t="n"/>
-      <c r="E27" s="41" t="n"/>
-      <c r="F27" s="41" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="39" t="n"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="41" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="39" t="n"/>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C29" s="41" t="n"/>
-      <c r="D29" s="41" t="n"/>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="41" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="39" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="39" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="39" t="n"/>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C32" s="41" t="n"/>
-      <c r="D32" s="41" t="n"/>
-      <c r="E32" s="41" t="n"/>
-      <c r="F32" s="41" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="39" t="n"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C33" s="41" t="n"/>
-      <c r="D33" s="41" t="n"/>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="41" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="39" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="39" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="n"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C36" s="41" t="n"/>
-      <c r="D36" s="41" t="n"/>
-      <c r="E36" s="41" t="n"/>
-      <c r="F36" s="41" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="39" t="n"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C37" s="41" t="n"/>
-      <c r="D37" s="41" t="n"/>
-      <c r="E37" s="41" t="n"/>
-      <c r="F37" s="41" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="39" t="n"/>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C38" s="41" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="41" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="39" t="n"/>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C39" s="41" t="n"/>
-      <c r="D39" s="41" t="n"/>
-      <c r="E39" s="41" t="n"/>
-      <c r="F39" s="41" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="39" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="39" t="n"/>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C42" s="41" t="n"/>
-      <c r="D42" s="41" t="n"/>
-      <c r="E42" s="41" t="n"/>
-      <c r="F42" s="41" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="39" t="n"/>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Endpoint URL</t>
-        </is>
-      </c>
-      <c r="C43" s="41" t="n"/>
-      <c r="D43" s="41" t="n"/>
-      <c r="E43" s="41" t="n"/>
-      <c r="F43" s="41" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="n"/>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C44" s="41" t="n"/>
-      <c r="D44" s="41" t="n"/>
-      <c r="E44" s="41" t="n"/>
-      <c r="F44" s="41" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="39" t="n"/>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C45" s="41" t="n"/>
-      <c r="D45" s="41" t="n"/>
-      <c r="E45" s="41" t="n"/>
-      <c r="F45" s="41" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="39" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="39" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="39" t="n"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C48" s="41" t="n"/>
-      <c r="D48" s="41" t="n"/>
-      <c r="E48" s="41" t="n"/>
-      <c r="F48" s="41" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="39" t="n"/>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C49" s="41" t="n"/>
-      <c r="D49" s="41" t="n"/>
-      <c r="E49" s="41" t="n"/>
-      <c r="F49" s="41" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="n"/>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C50" s="41" t="n"/>
-      <c r="D50" s="41" t="n"/>
-      <c r="E50" s="41" t="n"/>
-      <c r="F50" s="41" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="39" t="n"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C51" s="41" t="n"/>
-      <c r="D51" s="41" t="n"/>
-      <c r="E51" s="41" t="n"/>
-      <c r="F51" s="41" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="39" t="n"/>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C52" s="41" t="n"/>
-      <c r="D52" s="41" t="n"/>
-      <c r="E52" s="41" t="n"/>
-      <c r="F52" s="41" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="39" t="n"/>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C53" s="41" t="n"/>
-      <c r="D53" s="41" t="n"/>
-      <c r="E53" s="41" t="n"/>
-      <c r="F53" s="41" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="39" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="39" t="inlineStr">
-        <is>
-          <t>SQL Server</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="39" t="n"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C56" s="41" t="n"/>
-      <c r="D56" s="41" t="n"/>
-      <c r="E56" s="41" t="n"/>
-      <c r="F56" s="41" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="39" t="n"/>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C57" s="41" t="n"/>
-      <c r="D57" s="41" t="n"/>
-      <c r="E57" s="41" t="n"/>
-      <c r="F57" s="41" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="39" t="n"/>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C58" s="41" t="n"/>
-      <c r="D58" s="41" t="n"/>
-      <c r="E58" s="41" t="n"/>
-      <c r="F58" s="41" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="39" t="n"/>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C59" s="41" t="n"/>
-      <c r="D59" s="41" t="n"/>
-      <c r="E59" s="41" t="n"/>
-      <c r="F59" s="41" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="39" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="39" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="39" t="n"/>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C62" s="41" t="n"/>
-      <c r="D62" s="41" t="n"/>
-      <c r="E62" s="41" t="n"/>
-      <c r="F62" s="41" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="39" t="n"/>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="C63" s="41" t="n"/>
-      <c r="D63" s="41" t="n"/>
-      <c r="E63" s="41" t="n"/>
-      <c r="F63" s="41" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="39" t="n"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C64" s="41" t="n"/>
-      <c r="D64" s="41" t="n"/>
-      <c r="E64" s="41" t="n"/>
-      <c r="F64" s="41" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="39" t="n"/>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C65" s="41" t="n"/>
-      <c r="D65" s="41" t="n"/>
-      <c r="E65" s="41" t="n"/>
-      <c r="F65" s="41" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="39" t="n"/>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C66" s="41" t="n"/>
-      <c r="D66" s="41" t="n"/>
-      <c r="E66" s="41" t="n"/>
-      <c r="F66" s="41" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="39" t="n"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Endpoint URL</t>
-        </is>
-      </c>
-      <c r="C67" s="41" t="n"/>
-      <c r="D67" s="41" t="n"/>
-      <c r="E67" s="41" t="n"/>
-      <c r="F67" s="41" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="39" t="n"/>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C68" s="41" t="n"/>
-      <c r="D68" s="41" t="n"/>
-      <c r="E68" s="41" t="n"/>
-      <c r="F68" s="41" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="39" t="n"/>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C69" s="41" t="n"/>
-      <c r="D69" s="41" t="n"/>
-      <c r="E69" s="41" t="n"/>
-      <c r="F69" s="41" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="39" t="n"/>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C70" s="41" t="n"/>
-      <c r="D70" s="41" t="n"/>
-      <c r="E70" s="41" t="n"/>
-      <c r="F70" s="41" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="39" t="n"/>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="C71" s="41" t="n"/>
-      <c r="D71" s="41" t="n"/>
-      <c r="E71" s="41" t="n"/>
-      <c r="F71" s="41" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="39" t="n"/>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C72" s="41" t="n"/>
-      <c r="D72" s="41" t="n"/>
-      <c r="E72" s="41" t="n"/>
-      <c r="F72" s="41" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="39" t="n"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C73" s="41" t="n"/>
-      <c r="D73" s="41" t="n"/>
-      <c r="E73" s="41" t="n"/>
-      <c r="F73" s="41" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="39" t="n"/>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C74" s="41" t="n"/>
-      <c r="D74" s="41" t="n"/>
-      <c r="E74" s="41" t="n"/>
-      <c r="F74" s="41" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="39" t="n"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Region Name</t>
-        </is>
-      </c>
-      <c r="C75" s="41" t="n"/>
-      <c r="D75" s="41" t="n"/>
-      <c r="E75" s="41" t="n"/>
-      <c r="F75" s="41" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="39" t="n"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C76" s="41" t="n"/>
-      <c r="D76" s="41" t="n"/>
-      <c r="E76" s="41" t="n"/>
-      <c r="F76" s="41" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="39" t="n"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Service Name</t>
-        </is>
-      </c>
-      <c r="C77" s="41" t="n"/>
-      <c r="D77" s="41" t="n"/>
-      <c r="E77" s="41" t="n"/>
-      <c r="F77" s="41" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="39" t="n"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Staging Directory</t>
-        </is>
-      </c>
-      <c r="C78" s="41" t="n"/>
-      <c r="D78" s="41" t="n"/>
-      <c r="E78" s="41" t="n"/>
-      <c r="F78" s="41" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="39" t="n"/>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="C79" s="41" t="n"/>
-      <c r="D79" s="41" t="n"/>
-      <c r="E79" s="41" t="n"/>
-      <c r="F79" s="41" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="39" t="n"/>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C80" s="41" t="n"/>
-      <c r="D80" s="41" t="n"/>
-      <c r="E80" s="41" t="n"/>
-      <c r="F80" s="41" t="n"/>
+      <c r="A23" s="36" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C4:F7 C9:F45 C48:F53 C56:F59 C62:F80 G4:AE43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="C8:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"api,athena,azure,bigquery,clickhouse,databricks,db2,denodo,dremio,duckdb,glue,cloudsql,informix,kafka,kinesis,mysql,local,oracle,postgresql,presto,pubsub,redshift,s3,sftp,snowflake,sqlserver,synapse,trino,vertica,custom"</formula1>
-    </dataValidation>
+    <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>http://localhost:8080/demo203502625092/definitions/fulfillment/shipment_id</t>
+          <t>definitions/shipment_id.odcs.yaml</t>
         </is>
       </c>
       <c r="L14" s="15" t="inlineStr">
@@ -2988,7 +2988,7 @@
       <c r="J15" s="15" t="inlineStr"/>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>http://localhost:8080/demo203502625092/definitions/sales/order_id</t>
+          <t>definitions/order_id.odcs.yaml</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">

--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -10,18 +10,23 @@
     <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Schema shipments" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Support" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Team" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Roles" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SLA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Servers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Enum" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Synonyms" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Verified Statements" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Quality" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Support" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Team" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Roles" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SLA" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Servers" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Pricing" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Custom Properties" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Authoritative Definitions" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_ServerFields" sheetId="18" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
-    <definedName name="CustomProperties">'Custom Properties'!$A$5:$B$21</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
     <definedName name="dataProduct">Fundamentals!$C$15</definedName>
     <definedName name="description.limitations">Fundamentals!$C$20</definedName>
@@ -36,83 +41,68 @@
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
-    <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
-    <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="servers.azure.delimiter">Servers!$C$14</definedName>
-    <definedName name="servers.azure.format">Servers!$C$13</definedName>
-    <definedName name="servers.azure.location">Servers!$C$12</definedName>
-    <definedName name="servers.bigquery.dataset">Servers!$C$18</definedName>
-    <definedName name="servers.bigquery.project">Servers!$C$17</definedName>
-    <definedName name="servers.custom.account">Servers!$C$67</definedName>
-    <definedName name="servers.custom.catalog">Servers!$C$68</definedName>
-    <definedName name="servers.custom.database">Servers!$C$69</definedName>
-    <definedName name="servers.custom.dataset">Servers!$C$70</definedName>
-    <definedName name="servers.custom.delimiter">Servers!$C$71</definedName>
-    <definedName name="servers.custom.endpointUrl">Servers!$C$72</definedName>
-    <definedName name="servers.custom.format">Servers!$C$73</definedName>
-    <definedName name="servers.custom.host">Servers!$C$74</definedName>
-    <definedName name="servers.custom.location">Servers!$C$75</definedName>
-    <definedName name="servers.custom.path">Servers!$C$76</definedName>
-    <definedName name="servers.custom.port">Servers!$C$77</definedName>
-    <definedName name="servers.custom.project">Servers!$C$78</definedName>
-    <definedName name="servers.custom.region">Servers!$C$79</definedName>
-    <definedName name="servers.custom.regionName">Servers!$C$80</definedName>
-    <definedName name="servers.custom.schema">Servers!$C$81</definedName>
-    <definedName name="servers.custom.serviceName">Servers!$C$82</definedName>
-    <definedName name="servers.custom.stagingDir">Servers!$C$83</definedName>
-    <definedName name="servers.custom.stream">Servers!$C$84</definedName>
-    <definedName name="servers.custom.warehouse">Servers!$C$85</definedName>
-    <definedName name="servers.databricks.catalog">Servers!$C$21</definedName>
-    <definedName name="servers.databricks.host">Servers!$C$23</definedName>
-    <definedName name="servers.databricks.schema">Servers!$C$22</definedName>
     <definedName name="servers.description">Servers!$C$6</definedName>
     <definedName name="servers.environment">Servers!$C$5</definedName>
-    <definedName name="servers.glue.account">Servers!$C$26</definedName>
-    <definedName name="servers.glue.database">Servers!$C$27</definedName>
-    <definedName name="servers.glue.format">Servers!$C$29</definedName>
-    <definedName name="servers.glue.location">Servers!$C$28</definedName>
-    <definedName name="servers.kafka.format">Servers!$C$33</definedName>
-    <definedName name="servers.kafka.host">Servers!$C$32</definedName>
-    <definedName name="servers.oracle.host">Servers!$C$62</definedName>
-    <definedName name="servers.oracle.port">Servers!$C$63</definedName>
-    <definedName name="servers.oracle.servicename">Servers!$C$64</definedName>
-    <definedName name="servers.postgres.database">Servers!$C$38</definedName>
-    <definedName name="servers.postgres.host">Servers!$C$36</definedName>
-    <definedName name="servers.postgres.port">Servers!$C$37</definedName>
-    <definedName name="servers.postgres.schema">Servers!$C$39</definedName>
-    <definedName name="servers.s3.delimiter">Servers!$C$45</definedName>
-    <definedName name="servers.s3.endpointUrl">Servers!$C$43</definedName>
-    <definedName name="servers.s3.format">Servers!$C$44</definedName>
-    <definedName name="servers.s3.location">Servers!$C$42</definedName>
     <definedName name="servers.server">Servers!$C$4</definedName>
-    <definedName name="servers.snowflake.account">Servers!$C$50</definedName>
-    <definedName name="servers.snowflake.database">Servers!$C$51</definedName>
-    <definedName name="servers.snowflake.host">Servers!$C$48</definedName>
-    <definedName name="servers.snowflake.port">Servers!$C$49</definedName>
-    <definedName name="servers.snowflake.schema">Servers!$C$53</definedName>
-    <definedName name="servers.snowflake.warehouse">Servers!$C$52</definedName>
-    <definedName name="servers.sqlserver.database">Servers!$C$58</definedName>
-    <definedName name="servers.sqlserver.host">Servers!$C$56</definedName>
-    <definedName name="servers.sqlserver.port">Servers!$C$57</definedName>
-    <definedName name="servers.sqlserver.schema">Servers!$C$59</definedName>
     <definedName name="servers.type">Servers!$C$8</definedName>
     <definedName name="slaDefaultElement">SLA!$B$4</definedName>
     <definedName name="status">Fundamentals!$C$10</definedName>
-    <definedName name="support">Support!$A$4:$F$1000</definedName>
     <definedName name="tags">Fundamentals!$C$23</definedName>
-    <definedName name="team">Team!$A$4:$G$1000</definedName>
     <definedName name="tenant">Fundamentals!$C$16</definedName>
     <definedName name="version">Fundamentals!$C$9</definedName>
+    <definedName name="templateVersion">Instructions!$B$29</definedName>
+    <definedName name="context.instructions">Fundamentals!$C$25</definedName>
+    <definedName name="support">Support!$A$4:$Z$1000</definedName>
+    <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
+    <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
+    <definedName name="team.name">Team!$B$4</definedName>
+    <definedName name="team.description">Team!$B$5</definedName>
+    <definedName name="team.tags">Team!$B$6</definedName>
+    <definedName name="team.id">Team!$B$7</definedName>
+    <definedName name="team">Team!$A$9:$Z$1000</definedName>
+    <definedName name="servers.account">Servers!$C$11</definedName>
+    <definedName name="servers.catalog">Servers!$C$12</definedName>
+    <definedName name="servers.catalogUrl">Servers!$C$13</definedName>
+    <definedName name="servers.database">Servers!$C$14</definedName>
+    <definedName name="servers.dataset">Servers!$C$15</definedName>
+    <definedName name="servers.delimiter">Servers!$C$16</definedName>
+    <definedName name="servers.encoding">Servers!$C$17</definedName>
+    <definedName name="servers.endpointUrl">Servers!$C$18</definedName>
+    <definedName name="servers.format">Servers!$C$19</definedName>
+    <definedName name="servers.host">Servers!$C$20</definedName>
+    <definedName name="servers.location">Servers!$C$21</definedName>
+    <definedName name="servers.namespace">Servers!$C$22</definedName>
+    <definedName name="servers.path">Servers!$C$23</definedName>
+    <definedName name="servers.port">Servers!$C$24</definedName>
+    <definedName name="servers.project">Servers!$C$25</definedName>
+    <definedName name="servers.region">Servers!$C$26</definedName>
+    <definedName name="servers.regionName">Servers!$C$27</definedName>
+    <definedName name="servers.schema">Servers!$C$28</definedName>
+    <definedName name="servers.serviceName">Servers!$C$29</definedName>
+    <definedName name="servers.stagingDir">Servers!$C$30</definedName>
+    <definedName name="servers.stream">Servers!$C$31</definedName>
+    <definedName name="servers.warehouse">Servers!$C$32</definedName>
+    <definedName name="servers.workgroup">Servers!$C$33</definedName>
+    <definedName name="servers.id">Servers!$C$35</definedName>
+    <definedName name="CustomProperties">'Custom Properties'!$A$4:$H$1000</definedName>
+    <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$Z$1000</definedName>
+    <definedName name="enum">Enum!$A$4:$Z$1000</definedName>
+    <definedName name="synonyms">Synonyms!$A$4:$Z$1000</definedName>
+    <definedName name="verifiedStatements">'Verified Statements'!$A$4:$Z$1000</definedName>
+    <definedName name="constraints">Constraints!$A$4:$Z$1000</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema shipments'!$B$8</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema shipments'!$B$10</definedName>
     <definedName name="schema.description" localSheetId="2">'Schema shipments'!$B$7</definedName>
     <definedName name="schema.name" localSheetId="2">'Schema shipments'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema shipments'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema shipments'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$13:$L$981</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$18:$AZ$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema shipments'!$B$11</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$A$4:$E$1000</definedName>
-    <definedName name="slaProperties" localSheetId="8">SLA!$A$6:$F$1002</definedName>
+    <definedName name="schema.id" localSheetId="2">'Schema shipments'!$B$12</definedName>
+    <definedName name="schema.deprecated" localSheetId="2">'Schema shipments'!$B$13</definedName>
+    <definedName name="schema.context.instructions" localSheetId="2">'Schema shipments'!$B$14</definedName>
+    <definedName name="roles" localSheetId="11">Roles!$A$4:$Z$1000</definedName>
+    <definedName name="slaProperties" localSheetId="12">SLA!$A$6:$Z$1002</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +434,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -466,10 +456,66 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="00A6A6A6"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>7</col>
+      <colOff>307680</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>9</col>
+      <colOff>18329</colOff>
+      <row>4</row>
+      <rowOff>164631</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Graphic 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="5420412" y="0"/>
+          <a:ext cx="1059206" cy="1068033"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1097,7 +1143,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -1128,8 +1174,14 @@
       <c r="I28" s="13" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="13" t="n"/>
-      <c r="B29" s="13" t="n"/>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Template Version:</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="C29" s="13" t="n"/>
       <c r="D29" s="13" t="n"/>
       <c r="E29" s="13" t="n"/>
@@ -1162,6 +1214,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1171,7 +1224,1103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.6640625" customWidth="1" style="2" min="4" max="6"/>
+    <col width="22" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Support and Communication Channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Support and communication channels help consumers find help regarding their use of the data contract.
+Support and communication channels help consumers find help regarding their use of the data contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Channel URL</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Invitation URL</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>slackname</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>http://find.me.here</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>slack</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sup-slack</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>sla</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.6640625" customWidth="1" style="2" min="4" max="7"/>
+    <col width="22" customWidth="1" style="2" min="8" max="16384"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract. In v2.x, this section was called stakeholders.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Team Name</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>Fulfillment Data Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Team Description</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Owns the shipment data product</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Team Tags</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Team ID</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>team-fulfillment</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Date In</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Date Out</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Replaced By Username</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>vimportant</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>tm-vi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>onCall</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>nimportant</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>reader</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="36" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B10:G66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.83203125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="34.6640625" customWidth="1" style="2" min="5" max="5"/>
+    <col width="22" customWidth="1" style="2" min="6" max="16384"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
+This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1st Level Approvers</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>2nd Level Approvers</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Read access for analysts</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>data-owner</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>role-analyst</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ticketQueue</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.83203125" customWidth="1" style="2" min="4" max="5"/>
+    <col width="34.6640625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="22" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Service-Level Agreement (SLA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This section describes the service-level agreements (SLA).
+This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>Default SLA element(s)</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>shipments.delivery_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Extended value</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>sla-availability</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>measuredBy</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>statuspage</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.1640625" customWidth="1" style="2" min="1" max="1"/>
@@ -1199,6 +2348,7 @@
       </c>
       <c r="B2" s="4" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -1211,8 +2361,16 @@
           <t>production</t>
         </is>
       </c>
-      <c r="D4" s="36" t="n"/>
-      <c r="E4" s="36" t="n"/>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>lakehouse</t>
+        </is>
+      </c>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
       <c r="F4" s="36" t="n"/>
     </row>
     <row r="5">
@@ -1227,8 +2385,16 @@
           <t>production</t>
         </is>
       </c>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
       <c r="F5" s="36" t="n"/>
     </row>
     <row r="6">
@@ -1238,7 +2404,11 @@
         </is>
       </c>
       <c r="B6" s="34" t="n"/>
-      <c r="C6" s="36" t="n"/>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Production dataset</t>
+        </is>
+      </c>
       <c r="D6" s="36" t="n"/>
       <c r="E6" s="36" t="n"/>
       <c r="F6" s="36" t="n"/>
@@ -1259,785 +2429,893 @@
           <t>bigquery</t>
         </is>
       </c>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>trino</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="inlineStr">
+        <is>
+          <t>kafka</t>
+        </is>
+      </c>
       <c r="F8" s="36" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>Connection</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
+      <c r="L11" s="36" t="n"/>
+      <c r="M11" s="36" t="n"/>
+      <c r="N11" s="36" t="n"/>
+      <c r="O11" s="36" t="n"/>
+      <c r="P11" s="36" t="n"/>
+      <c r="Q11" s="36" t="n"/>
+      <c r="R11" s="36" t="n"/>
+      <c r="S11" s="36" t="n"/>
+      <c r="T11" s="36" t="n"/>
+      <c r="U11" s="36" t="n"/>
+      <c r="V11" s="36" t="n"/>
+      <c r="W11" s="36" t="n"/>
+      <c r="X11" s="36" t="n"/>
+      <c r="Y11" s="36" t="n"/>
+      <c r="Z11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="n"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Catalog</t>
         </is>
       </c>
       <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>iceberg</t>
+        </is>
+      </c>
       <c r="E12" s="36" t="n"/>
       <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
+      <c r="L12" s="36" t="n"/>
+      <c r="M12" s="36" t="n"/>
+      <c r="N12" s="36" t="n"/>
+      <c r="O12" s="36" t="n"/>
+      <c r="P12" s="36" t="n"/>
+      <c r="Q12" s="36" t="n"/>
+      <c r="R12" s="36" t="n"/>
+      <c r="S12" s="36" t="n"/>
+      <c r="T12" s="36" t="n"/>
+      <c r="U12" s="36" t="n"/>
+      <c r="V12" s="36" t="n"/>
+      <c r="W12" s="36" t="n"/>
+      <c r="X12" s="36" t="n"/>
+      <c r="Y12" s="36" t="n"/>
+      <c r="Z12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="n"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Catalog URL</t>
         </is>
       </c>
       <c r="C13" s="36" t="n"/>
       <c r="D13" s="36" t="n"/>
       <c r="E13" s="36" t="n"/>
       <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="36" t="n"/>
+      <c r="L13" s="36" t="n"/>
+      <c r="M13" s="36" t="n"/>
+      <c r="N13" s="36" t="n"/>
+      <c r="O13" s="36" t="n"/>
+      <c r="P13" s="36" t="n"/>
+      <c r="Q13" s="36" t="n"/>
+      <c r="R13" s="36" t="n"/>
+      <c r="S13" s="36" t="n"/>
+      <c r="T13" s="36" t="n"/>
+      <c r="U13" s="36" t="n"/>
+      <c r="V13" s="36" t="n"/>
+      <c r="W13" s="36" t="n"/>
+      <c r="X13" s="36" t="n"/>
+      <c r="Y13" s="36" t="n"/>
+      <c r="Z13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="n"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Delimiter</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="C14" s="36" t="n"/>
       <c r="D14" s="36" t="n"/>
       <c r="E14" s="36" t="n"/>
       <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="36" t="n"/>
+      <c r="N14" s="36" t="n"/>
+      <c r="O14" s="36" t="n"/>
+      <c r="P14" s="36" t="n"/>
+      <c r="Q14" s="36" t="n"/>
+      <c r="R14" s="36" t="n"/>
+      <c r="S14" s="36" t="n"/>
+      <c r="T14" s="36" t="n"/>
+      <c r="U14" s="36" t="n"/>
+      <c r="V14" s="36" t="n"/>
+      <c r="W14" s="36" t="n"/>
+      <c r="X14" s="36" t="n"/>
+      <c r="Y14" s="36" t="n"/>
+      <c r="Z14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="n"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>shipments_v1</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="36" t="n"/>
+      <c r="N15" s="36" t="n"/>
+      <c r="O15" s="36" t="n"/>
+      <c r="P15" s="36" t="n"/>
+      <c r="Q15" s="36" t="n"/>
+      <c r="R15" s="36" t="n"/>
+      <c r="S15" s="36" t="n"/>
+      <c r="T15" s="36" t="n"/>
+      <c r="U15" s="36" t="n"/>
+      <c r="V15" s="36" t="n"/>
+      <c r="W15" s="36" t="n"/>
+      <c r="X15" s="36" t="n"/>
+      <c r="Y15" s="36" t="n"/>
+      <c r="Z15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>BigQuery</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="36" t="n"/>
+      <c r="N16" s="36" t="n"/>
+      <c r="O16" s="36" t="n"/>
+      <c r="P16" s="36" t="n"/>
+      <c r="Q16" s="36" t="n"/>
+      <c r="R16" s="36" t="n"/>
+      <c r="S16" s="36" t="n"/>
+      <c r="T16" s="36" t="n"/>
+      <c r="U16" s="36" t="n"/>
+      <c r="V16" s="36" t="n"/>
+      <c r="W16" s="36" t="n"/>
+      <c r="X16" s="36" t="n"/>
+      <c r="Y16" s="36" t="n"/>
+      <c r="Z16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="n"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>acme_shipments_prod</t>
-        </is>
-      </c>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n"/>
       <c r="D17" s="36" t="n"/>
       <c r="E17" s="36" t="n"/>
       <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="36" t="n"/>
+      <c r="M17" s="36" t="n"/>
+      <c r="N17" s="36" t="n"/>
+      <c r="O17" s="36" t="n"/>
+      <c r="P17" s="36" t="n"/>
+      <c r="Q17" s="36" t="n"/>
+      <c r="R17" s="36" t="n"/>
+      <c r="S17" s="36" t="n"/>
+      <c r="T17" s="36" t="n"/>
+      <c r="U17" s="36" t="n"/>
+      <c r="V17" s="36" t="n"/>
+      <c r="W17" s="36" t="n"/>
+      <c r="X17" s="36" t="n"/>
+      <c r="Y17" s="36" t="n"/>
+      <c r="Z17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="n"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>shipments_v1</t>
-        </is>
-      </c>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n"/>
       <c r="D18" s="36" t="n"/>
       <c r="E18" s="36" t="n"/>
       <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="36" t="n"/>
+      <c r="N18" s="36" t="n"/>
+      <c r="O18" s="36" t="n"/>
+      <c r="P18" s="36" t="n"/>
+      <c r="Q18" s="36" t="n"/>
+      <c r="R18" s="36" t="n"/>
+      <c r="S18" s="36" t="n"/>
+      <c r="T18" s="36" t="n"/>
+      <c r="U18" s="36" t="n"/>
+      <c r="V18" s="36" t="n"/>
+      <c r="W18" s="36" t="n"/>
+      <c r="X18" s="36" t="n"/>
+      <c r="Y18" s="36" t="n"/>
+      <c r="Z18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="n"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>avro</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="36" t="n"/>
+      <c r="N19" s="36" t="n"/>
+      <c r="O19" s="36" t="n"/>
+      <c r="P19" s="36" t="n"/>
+      <c r="Q19" s="36" t="n"/>
+      <c r="R19" s="36" t="n"/>
+      <c r="S19" s="36" t="n"/>
+      <c r="T19" s="36" t="n"/>
+      <c r="U19" s="36" t="n"/>
+      <c r="V19" s="36" t="n"/>
+      <c r="W19" s="36" t="n"/>
+      <c r="X19" s="36" t="n"/>
+      <c r="Y19" s="36" t="n"/>
+      <c r="Z19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t>Databricks Server</t>
-        </is>
-      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="inlineStr">
+        <is>
+          <t>trino.example.com</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>kafka.example.com:9092</t>
+        </is>
+      </c>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="36" t="n"/>
+      <c r="N20" s="36" t="n"/>
+      <c r="O20" s="36" t="n"/>
+      <c r="P20" s="36" t="n"/>
+      <c r="Q20" s="36" t="n"/>
+      <c r="R20" s="36" t="n"/>
+      <c r="S20" s="36" t="n"/>
+      <c r="T20" s="36" t="n"/>
+      <c r="U20" s="36" t="n"/>
+      <c r="V20" s="36" t="n"/>
+      <c r="W20" s="36" t="n"/>
+      <c r="X20" s="36" t="n"/>
+      <c r="Y20" s="36" t="n"/>
+      <c r="Z20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="n"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Catalog</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C21" s="36" t="n"/>
       <c r="D21" s="36" t="n"/>
       <c r="E21" s="36" t="n"/>
       <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="M21" s="36" t="n"/>
+      <c r="N21" s="36" t="n"/>
+      <c r="O21" s="36" t="n"/>
+      <c r="P21" s="36" t="n"/>
+      <c r="Q21" s="36" t="n"/>
+      <c r="R21" s="36" t="n"/>
+      <c r="S21" s="36" t="n"/>
+      <c r="T21" s="36" t="n"/>
+      <c r="U21" s="36" t="n"/>
+      <c r="V21" s="36" t="n"/>
+      <c r="W21" s="36" t="n"/>
+      <c r="X21" s="36" t="n"/>
+      <c r="Y21" s="36" t="n"/>
+      <c r="Z21" s="36" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="n"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Schema</t>
+          <t>Namespace</t>
         </is>
       </c>
       <c r="C22" s="36" t="n"/>
       <c r="D22" s="36" t="n"/>
       <c r="E22" s="36" t="n"/>
       <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="36" t="n"/>
+      <c r="N22" s="36" t="n"/>
+      <c r="O22" s="36" t="n"/>
+      <c r="P22" s="36" t="n"/>
+      <c r="Q22" s="36" t="n"/>
+      <c r="R22" s="36" t="n"/>
+      <c r="S22" s="36" t="n"/>
+      <c r="T22" s="36" t="n"/>
+      <c r="U22" s="36" t="n"/>
+      <c r="V22" s="36" t="n"/>
+      <c r="W22" s="36" t="n"/>
+      <c r="X22" s="36" t="n"/>
+      <c r="Y22" s="36" t="n"/>
+      <c r="Z22" s="36" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="n"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Host</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="C23" s="36" t="n"/>
       <c r="D23" s="36" t="n"/>
       <c r="E23" s="36" t="n"/>
       <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="36" t="n"/>
+      <c r="N23" s="36" t="n"/>
+      <c r="O23" s="36" t="n"/>
+      <c r="P23" s="36" t="n"/>
+      <c r="Q23" s="36" t="n"/>
+      <c r="R23" s="36" t="n"/>
+      <c r="S23" s="36" t="n"/>
+      <c r="T23" s="36" t="n"/>
+      <c r="U23" s="36" t="n"/>
+      <c r="V23" s="36" t="n"/>
+      <c r="W23" s="36" t="n"/>
+      <c r="X23" s="36" t="n"/>
+      <c r="Y23" s="36" t="n"/>
+      <c r="Z23" s="36" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="n"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>${TRINO_PORT}</t>
+        </is>
+      </c>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="36" t="n"/>
+      <c r="N24" s="36" t="n"/>
+      <c r="O24" s="36" t="n"/>
+      <c r="P24" s="36" t="n"/>
+      <c r="Q24" s="36" t="n"/>
+      <c r="R24" s="36" t="n"/>
+      <c r="S24" s="36" t="n"/>
+      <c r="T24" s="36" t="n"/>
+      <c r="U24" s="36" t="n"/>
+      <c r="V24" s="36" t="n"/>
+      <c r="W24" s="36" t="n"/>
+      <c r="X24" s="36" t="n"/>
+      <c r="Y24" s="36" t="n"/>
+      <c r="Z24" s="36" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
-        <is>
-          <t>Amazon Glue</t>
-        </is>
-      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>acme_shipments_prod</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="36" t="n"/>
+      <c r="N25" s="36" t="n"/>
+      <c r="O25" s="36" t="n"/>
+      <c r="P25" s="36" t="n"/>
+      <c r="Q25" s="36" t="n"/>
+      <c r="R25" s="36" t="n"/>
+      <c r="S25" s="36" t="n"/>
+      <c r="T25" s="36" t="n"/>
+      <c r="U25" s="36" t="n"/>
+      <c r="V25" s="36" t="n"/>
+      <c r="W25" s="36" t="n"/>
+      <c r="X25" s="36" t="n"/>
+      <c r="Y25" s="36" t="n"/>
+      <c r="Z25" s="36" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="n"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="C26" s="36" t="n"/>
       <c r="D26" s="36" t="n"/>
       <c r="E26" s="36" t="n"/>
       <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="36" t="n"/>
+      <c r="O26" s="36" t="n"/>
+      <c r="P26" s="36" t="n"/>
+      <c r="Q26" s="36" t="n"/>
+      <c r="R26" s="36" t="n"/>
+      <c r="S26" s="36" t="n"/>
+      <c r="T26" s="36" t="n"/>
+      <c r="U26" s="36" t="n"/>
+      <c r="V26" s="36" t="n"/>
+      <c r="W26" s="36" t="n"/>
+      <c r="X26" s="36" t="n"/>
+      <c r="Y26" s="36" t="n"/>
+      <c r="Z26" s="36" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="n"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Region Name</t>
         </is>
       </c>
       <c r="C27" s="36" t="n"/>
       <c r="D27" s="36" t="n"/>
       <c r="E27" s="36" t="n"/>
       <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="36" t="n"/>
+      <c r="N27" s="36" t="n"/>
+      <c r="O27" s="36" t="n"/>
+      <c r="P27" s="36" t="n"/>
+      <c r="Q27" s="36" t="n"/>
+      <c r="R27" s="36" t="n"/>
+      <c r="S27" s="36" t="n"/>
+      <c r="T27" s="36" t="n"/>
+      <c r="U27" s="36" t="n"/>
+      <c r="V27" s="36" t="n"/>
+      <c r="W27" s="36" t="n"/>
+      <c r="X27" s="36" t="n"/>
+      <c r="Y27" s="36" t="n"/>
+      <c r="Z27" s="36" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="n"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Schema</t>
         </is>
       </c>
       <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
+      <c r="D28" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
       <c r="E28" s="36" t="n"/>
       <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="36" t="n"/>
+      <c r="I28" s="36" t="n"/>
+      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="36" t="n"/>
+      <c r="L28" s="36" t="n"/>
+      <c r="M28" s="36" t="n"/>
+      <c r="N28" s="36" t="n"/>
+      <c r="O28" s="36" t="n"/>
+      <c r="P28" s="36" t="n"/>
+      <c r="Q28" s="36" t="n"/>
+      <c r="R28" s="36" t="n"/>
+      <c r="S28" s="36" t="n"/>
+      <c r="T28" s="36" t="n"/>
+      <c r="U28" s="36" t="n"/>
+      <c r="V28" s="36" t="n"/>
+      <c r="W28" s="36" t="n"/>
+      <c r="X28" s="36" t="n"/>
+      <c r="Y28" s="36" t="n"/>
+      <c r="Z28" s="36" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="n"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Service Name</t>
         </is>
       </c>
       <c r="C29" s="36" t="n"/>
       <c r="D29" s="36" t="n"/>
       <c r="E29" s="36" t="n"/>
       <c r="F29" s="36" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="36" t="n"/>
+      <c r="J29" s="36" t="n"/>
+      <c r="K29" s="36" t="n"/>
+      <c r="L29" s="36" t="n"/>
+      <c r="M29" s="36" t="n"/>
+      <c r="N29" s="36" t="n"/>
+      <c r="O29" s="36" t="n"/>
+      <c r="P29" s="36" t="n"/>
+      <c r="Q29" s="36" t="n"/>
+      <c r="R29" s="36" t="n"/>
+      <c r="S29" s="36" t="n"/>
+      <c r="T29" s="36" t="n"/>
+      <c r="U29" s="36" t="n"/>
+      <c r="V29" s="36" t="n"/>
+      <c r="W29" s="36" t="n"/>
+      <c r="X29" s="36" t="n"/>
+      <c r="Y29" s="36" t="n"/>
+      <c r="Z29" s="36" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="n"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Staging Directory</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="36" t="n"/>
+      <c r="L30" s="36" t="n"/>
+      <c r="M30" s="36" t="n"/>
+      <c r="N30" s="36" t="n"/>
+      <c r="O30" s="36" t="n"/>
+      <c r="P30" s="36" t="n"/>
+      <c r="Q30" s="36" t="n"/>
+      <c r="R30" s="36" t="n"/>
+      <c r="S30" s="36" t="n"/>
+      <c r="T30" s="36" t="n"/>
+      <c r="U30" s="36" t="n"/>
+      <c r="V30" s="36" t="n"/>
+      <c r="W30" s="36" t="n"/>
+      <c r="X30" s="36" t="n"/>
+      <c r="Y30" s="36" t="n"/>
+      <c r="Z30" s="36" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+      <c r="I31" s="36" t="n"/>
+      <c r="J31" s="36" t="n"/>
+      <c r="K31" s="36" t="n"/>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="36" t="n"/>
+      <c r="N31" s="36" t="n"/>
+      <c r="O31" s="36" t="n"/>
+      <c r="P31" s="36" t="n"/>
+      <c r="Q31" s="36" t="n"/>
+      <c r="R31" s="36" t="n"/>
+      <c r="S31" s="36" t="n"/>
+      <c r="T31" s="36" t="n"/>
+      <c r="U31" s="36" t="n"/>
+      <c r="V31" s="36" t="n"/>
+      <c r="W31" s="36" t="n"/>
+      <c r="X31" s="36" t="n"/>
+      <c r="Y31" s="36" t="n"/>
+      <c r="Z31" s="36" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="34" t="n"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Host</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C32" s="36" t="n"/>
       <c r="D32" s="36" t="n"/>
       <c r="E32" s="36" t="n"/>
       <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+      <c r="I32" s="36" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
+      <c r="L32" s="36" t="n"/>
+      <c r="M32" s="36" t="n"/>
+      <c r="N32" s="36" t="n"/>
+      <c r="O32" s="36" t="n"/>
+      <c r="P32" s="36" t="n"/>
+      <c r="Q32" s="36" t="n"/>
+      <c r="R32" s="36" t="n"/>
+      <c r="S32" s="36" t="n"/>
+      <c r="T32" s="36" t="n"/>
+      <c r="U32" s="36" t="n"/>
+      <c r="V32" s="36" t="n"/>
+      <c r="W32" s="36" t="n"/>
+      <c r="X32" s="36" t="n"/>
+      <c r="Y32" s="36" t="n"/>
+      <c r="Z32" s="36" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="n"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Workgroup</t>
         </is>
       </c>
       <c r="C33" s="36" t="n"/>
       <c r="D33" s="36" t="n"/>
       <c r="E33" s="36" t="n"/>
       <c r="F33" s="36" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="34" t="n"/>
-    </row>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="36" t="n"/>
+      <c r="I33" s="36" t="n"/>
+      <c r="J33" s="36" t="n"/>
+      <c r="K33" s="36" t="n"/>
+      <c r="L33" s="36" t="n"/>
+      <c r="M33" s="36" t="n"/>
+      <c r="N33" s="36" t="n"/>
+      <c r="O33" s="36" t="n"/>
+      <c r="P33" s="36" t="n"/>
+      <c r="Q33" s="36" t="n"/>
+      <c r="R33" s="36" t="n"/>
+      <c r="S33" s="36" t="n"/>
+      <c r="T33" s="36" t="n"/>
+      <c r="U33" s="36" t="n"/>
+      <c r="V33" s="36" t="n"/>
+      <c r="W33" s="36" t="n"/>
+      <c r="X33" s="36" t="n"/>
+      <c r="Y33" s="36" t="n"/>
+      <c r="Z33" s="36" t="n"/>
+    </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>srv-prod</t>
+        </is>
+      </c>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="36" t="n"/>
+      <c r="K35" s="36" t="n"/>
+      <c r="L35" s="36" t="n"/>
+      <c r="M35" s="36" t="n"/>
+      <c r="N35" s="36" t="n"/>
+      <c r="O35" s="36" t="n"/>
+      <c r="P35" s="36" t="n"/>
+      <c r="Q35" s="36" t="n"/>
+      <c r="R35" s="36" t="n"/>
+      <c r="S35" s="36" t="n"/>
+      <c r="T35" s="36" t="n"/>
+      <c r="U35" s="36" t="n"/>
+      <c r="V35" s="36" t="n"/>
+      <c r="W35" s="36" t="n"/>
+      <c r="X35" s="36" t="n"/>
+      <c r="Y35" s="36" t="n"/>
+      <c r="Z35" s="36" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="34" t="n"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C36" s="36" t="n"/>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t>costCenter</t>
+        </is>
+      </c>
       <c r="D36" s="36" t="n"/>
       <c r="E36" s="36" t="n"/>
       <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
+      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
+      <c r="L36" s="36" t="n"/>
+      <c r="M36" s="36" t="n"/>
+      <c r="N36" s="36" t="n"/>
+      <c r="O36" s="36" t="n"/>
+      <c r="P36" s="36" t="n"/>
+      <c r="Q36" s="36" t="n"/>
+      <c r="R36" s="36" t="n"/>
+      <c r="S36" s="36" t="n"/>
+      <c r="T36" s="36" t="n"/>
+      <c r="U36" s="36" t="n"/>
+      <c r="V36" s="36" t="n"/>
+      <c r="W36" s="36" t="n"/>
+      <c r="X36" s="36" t="n"/>
+      <c r="Y36" s="36" t="n"/>
+      <c r="Z36" s="36" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="n"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C37" s="36" t="n"/>
+          <t>Custom Value</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>cc-42</t>
+        </is>
+      </c>
       <c r="D37" s="36" t="n"/>
       <c r="E37" s="36" t="n"/>
       <c r="F37" s="36" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="34" t="n"/>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="34" t="n"/>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="36" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="34" t="n"/>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
-      <c r="F42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="34" t="n"/>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Endpoint URL</t>
-        </is>
-      </c>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="n"/>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C44" s="36" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
-      <c r="F44" s="36" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="34" t="n"/>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
-      <c r="F45" s="36" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="34" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="34" t="n"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="34" t="n"/>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="34" t="n"/>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C50" s="36" t="n"/>
-      <c r="D50" s="36" t="n"/>
-      <c r="E50" s="36" t="n"/>
-      <c r="F50" s="36" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="34" t="n"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="n"/>
-      <c r="F51" s="36" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="34" t="n"/>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C52" s="36" t="n"/>
-      <c r="D52" s="36" t="n"/>
-      <c r="E52" s="36" t="n"/>
-      <c r="F52" s="36" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="34" t="n"/>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="36" t="n"/>
-      <c r="E53" s="36" t="n"/>
-      <c r="F53" s="36" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="34" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>SQL Server</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="n"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C56" s="36" t="n"/>
-      <c r="D56" s="36" t="n"/>
-      <c r="E56" s="36" t="n"/>
-      <c r="F56" s="36" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="n"/>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="36" t="n"/>
-      <c r="E57" s="36" t="n"/>
-      <c r="F57" s="36" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="34" t="n"/>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C58" s="36" t="n"/>
-      <c r="D58" s="36" t="n"/>
-      <c r="E58" s="36" t="n"/>
-      <c r="F58" s="36" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="34" t="n"/>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="36" t="n"/>
-      <c r="E59" s="36" t="n"/>
-      <c r="F59" s="36" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="34" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="34" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="34" t="n"/>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C62" s="36" t="n"/>
-      <c r="D62" s="36" t="n"/>
-      <c r="E62" s="36" t="n"/>
-      <c r="F62" s="36" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="34" t="n"/>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C63" s="36" t="n"/>
-      <c r="D63" s="36" t="n"/>
-      <c r="E63" s="36" t="n"/>
-      <c r="F63" s="36" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="34" t="n"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>ServiceName</t>
-        </is>
-      </c>
-      <c r="C64" s="36" t="n"/>
-      <c r="D64" s="36" t="n"/>
-      <c r="E64" s="36" t="n"/>
-      <c r="F64" s="36" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="34" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="34" t="inlineStr">
-        <is>
-          <t>Custom</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="34" t="n"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C67" s="36" t="n"/>
-      <c r="D67" s="36" t="n"/>
-      <c r="E67" s="36" t="n"/>
-      <c r="F67" s="36" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="n"/>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Catalog</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="n"/>
-      <c r="D68" s="36" t="n"/>
-      <c r="E68" s="36" t="n"/>
-      <c r="F68" s="36" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="34" t="n"/>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="C69" s="36" t="n"/>
-      <c r="D69" s="36" t="n"/>
-      <c r="E69" s="36" t="n"/>
-      <c r="F69" s="36" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="34" t="n"/>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C70" s="36" t="n"/>
-      <c r="D70" s="36" t="n"/>
-      <c r="E70" s="36" t="n"/>
-      <c r="F70" s="36" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="34" t="n"/>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Delimiter</t>
-        </is>
-      </c>
-      <c r="C71" s="36" t="n"/>
-      <c r="D71" s="36" t="n"/>
-      <c r="E71" s="36" t="n"/>
-      <c r="F71" s="36" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="34" t="n"/>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Endpoint URL</t>
-        </is>
-      </c>
-      <c r="C72" s="36" t="n"/>
-      <c r="D72" s="36" t="n"/>
-      <c r="E72" s="36" t="n"/>
-      <c r="F72" s="36" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="34" t="n"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="C73" s="36" t="n"/>
-      <c r="D73" s="36" t="n"/>
-      <c r="E73" s="36" t="n"/>
-      <c r="F73" s="36" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="34" t="n"/>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="C74" s="36" t="n"/>
-      <c r="D74" s="36" t="n"/>
-      <c r="E74" s="36" t="n"/>
-      <c r="F74" s="36" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="34" t="n"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C75" s="36" t="n"/>
-      <c r="D75" s="36" t="n"/>
-      <c r="E75" s="36" t="n"/>
-      <c r="F75" s="36" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="34" t="n"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="C76" s="36" t="n"/>
-      <c r="D76" s="36" t="n"/>
-      <c r="E76" s="36" t="n"/>
-      <c r="F76" s="36" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="34" t="n"/>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="C77" s="36" t="n"/>
-      <c r="D77" s="36" t="n"/>
-      <c r="E77" s="36" t="n"/>
-      <c r="F77" s="36" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="34" t="n"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C78" s="36" t="n"/>
-      <c r="D78" s="36" t="n"/>
-      <c r="E78" s="36" t="n"/>
-      <c r="F78" s="36" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="34" t="n"/>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C79" s="36" t="n"/>
-      <c r="D79" s="36" t="n"/>
-      <c r="E79" s="36" t="n"/>
-      <c r="F79" s="36" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="34" t="n"/>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Region Name</t>
-        </is>
-      </c>
-      <c r="C80" s="36" t="n"/>
-      <c r="D80" s="36" t="n"/>
-      <c r="E80" s="36" t="n"/>
-      <c r="F80" s="36" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="34" t="n"/>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-      <c r="C81" s="36" t="n"/>
-      <c r="D81" s="36" t="n"/>
-      <c r="E81" s="36" t="n"/>
-      <c r="F81" s="36" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="34" t="n"/>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Service Name</t>
-        </is>
-      </c>
-      <c r="C82" s="36" t="n"/>
-      <c r="D82" s="36" t="n"/>
-      <c r="E82" s="36" t="n"/>
-      <c r="F82" s="36" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="34" t="n"/>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Staging Directory</t>
-        </is>
-      </c>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="36" t="n"/>
-      <c r="E83" s="36" t="n"/>
-      <c r="F83" s="36" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="34" t="n"/>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="C84" s="36" t="n"/>
-      <c r="D84" s="36" t="n"/>
-      <c r="E84" s="36" t="n"/>
-      <c r="F84" s="36" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="34" t="n"/>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C85" s="36" t="n"/>
-      <c r="D85" s="36" t="n"/>
-      <c r="E85" s="36" t="n"/>
-      <c r="F85" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="36" t="n"/>
+      <c r="K37" s="36" t="n"/>
+      <c r="L37" s="36" t="n"/>
+      <c r="M37" s="36" t="n"/>
+      <c r="N37" s="36" t="n"/>
+      <c r="O37" s="36" t="n"/>
+      <c r="P37" s="36" t="n"/>
+      <c r="Q37" s="36" t="n"/>
+      <c r="R37" s="36" t="n"/>
+      <c r="S37" s="36" t="n"/>
+      <c r="T37" s="36" t="n"/>
+      <c r="U37" s="36" t="n"/>
+      <c r="V37" s="36" t="n"/>
+      <c r="W37" s="36" t="n"/>
+      <c r="X37" s="36" t="n"/>
+      <c r="Y37" s="36" t="n"/>
+      <c r="Z37" s="36" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C4:F7 C9:F45 C48:F53 C56:F59 C62:F64 C67:F85 G4:AE43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="C8:F8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"api,athena,azure,bigquery,clickhouse,databricks,db2,denodo,dremio,duckdb,glue,cloudsql,informix,kafka,kinesis,mysql,local,oracle,postgresql,presto,pubsub,redshift,s3,sftp,snowflake,sqlserver,synapse,trino,vertica,custom"</formula1>
+  <conditionalFormatting sqref="C11:Z33">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX('_ServerFields'!$B$2:$AS$24,MATCH($B11,'_ServerFields'!$A$2:$A$24,0),MATCH(C$8,'_ServerFields'!$B$1:$AS$1,0)),"")="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:Z8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_ServerFields'!$B$1:$AS$1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2111,18 +3389,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="90" customWidth="1" style="2" min="2" max="2"/>
-    <col width="8.83203125" customWidth="1" style="2" min="3" max="16384"/>
+    <col width="20" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20" customWidth="1" style="2" min="2" max="2"/>
+    <col width="20" customWidth="1" style="2" min="3" max="16384"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2142,103 +3425,1931 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
+          <t>Element Type</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Value</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>ID</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="B5" s="36">
-        <f>IF(owner &lt;&gt; "", owner, "")</f>
-        <v/>
-      </c>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr"/>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>additionalField</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>some value</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="n"/>
+      <c r="H5" s="36" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t>additionalField</t>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr"/>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>pii</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr"/>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>retentionDays</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr"/>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>sourceSystem</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>The system of record</t>
+        </is>
+      </c>
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>acme</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="inlineStr">
+        <is>
+          <t>cp-source-system</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr"/>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>dbtVersion</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr"/>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>["eu-west", "eu-central"]</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr"/>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>costCenter</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>{"id": 4711, "name": "Fulfillment"}</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr"/>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>github_link</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>https://github.example.com/shipment-specification.yaml</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>retention</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>P1Y</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>ISO 8601 retention period</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>shipments.shipment_id</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr"/>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>costCenter</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>42</v>
+      </c>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="inlineStr"/>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>slack</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>#fulfillment-data</t>
+        </is>
+      </c>
+      <c r="E16" s="36" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Contract,Description,Server,Schema,Property,Quality,Support,Team,Team Member,Role,SLA,Relationship,Enum Value,Synonym,Verified Statement,Constraint"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Text,JSON"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Authoritative Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Links to authoritative sources (business definitions, implementations, tutorials) for any element of the contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Element Type</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>https://example.com/definitions/shipments</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Property</t>
         </is>
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>We added an addition field - b</t>
-        </is>
-      </c>
+          <t>shipments.shipment_id</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>https://example.com/tutorials/shipment_id</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>How shipment ids are minted</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>SLA</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>https://example.com/sla</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>implementation</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr"/>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>https://example.com/guidelines</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr"/>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>https://example.com/data-guidelines.html</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>Company-wide data guidelines</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="36" t="n"/>
       <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="36" t="n"/>
       <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="36" t="n"/>
       <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="36" t="n"/>
       <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Contract,Description,Server,Schema,Property,Quality,Support,Team,Team Member,Role,SLA,Relationship,Enum Value,Synonym,Verified Statement,Constraint"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AS24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>athena</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>bigquery</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>btrieve</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>databricks</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>denodo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>dremio</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>duckdb</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>exasol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fastobjects</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>glue</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>hana</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>cloudsql</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>db2</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>hive</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>iceberg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>impala</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>informix</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ingres</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>kafka</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>kinesis</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>mysql</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>oracle</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>poet</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>postgresql</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>presto</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>pubsub</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>redshift</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>sftp</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>snowflake</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>sqlserver</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>teradata</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>trino</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>vectorwise</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>versant</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>vertica</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>zen</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Catalog URL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Delimiter</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Endpoint URL</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Namespace</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Region Name</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Service Name</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Staging Directory</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Workgroup</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2248,7 +5359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="2.83203125" customWidth="1" style="2" min="1" max="1"/>
@@ -2301,7 +5412,7 @@
       <c r="B5" s="34" t="n"/>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>v3.0.0</t>
+          <t>v3.2.0</t>
         </is>
       </c>
     </row>
@@ -2344,7 +5455,7 @@
       <c r="B9" s="34" t="n"/>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>1.0.2</t>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
@@ -2374,7 +5485,7 @@
       <c r="B12" s="40" t="n"/>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>fulfillment</t>
+          <t>controlling-team</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
@@ -2390,7 +5501,11 @@
         </is>
       </c>
       <c r="B14" s="34" t="n"/>
-      <c r="C14" s="36" t="n"/>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>sales-team</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
@@ -2400,7 +5515,11 @@
         </is>
       </c>
       <c r="B15" s="34" t="n"/>
-      <c r="C15" s="36" t="n"/>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
@@ -2481,6 +5600,18 @@
       <c r="C23" s="36" t="inlineStr">
         <is>
           <t>datalocation:EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>Context Instructions</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>Join on shipment_id only; delivery_date is in UTC.</t>
         </is>
       </c>
     </row>
@@ -2509,7 +5640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL49"/>
+  <dimension ref="A1:AQ54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="34.83203125" customWidth="1" style="2" min="1" max="1"/>
@@ -2530,8 +5661,12 @@
     <col width="21.6640625" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
     <col width="27.33203125" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
     <col width="15.5" customWidth="1" style="2" min="23" max="37"/>
-    <col width="26.1640625" customWidth="1" style="2" min="38" max="38"/>
-    <col width="8.83203125" customWidth="1" style="2" min="39" max="16384"/>
+    <col width="22" customWidth="1" style="2" min="38" max="38"/>
+    <col width="22" customWidth="1" style="2" min="39" max="16384"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
+    <col width="22" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2555,6 +5690,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
@@ -2593,7 +5729,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>This table contains shipment data, including details about shipment IDs, associated orders, delivery dates, carriers, tracking numbers, statuses, and additional shipment information in JSON format.</t>
+          <t>Shipment data with orders, delivery dates, carriers and statuses.</t>
         </is>
       </c>
       <c r="C7" s="41" t="n"/>
@@ -2661,619 +5797,319 @@
       <c r="E11" s="42" t="n"/>
     </row>
     <row r="12">
-      <c r="W12" s="19" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="42" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="42" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Context Instructions</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>Filter on status = 'Delivered' for fulfilment KPIs.</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="42" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>sourceTable</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="42" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>sap.vbak</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="42" t="n"/>
+    </row>
+    <row r="17">
+      <c r="W17" s="19" t="inlineStr">
         <is>
           <t>Logical Type Options</t>
         </is>
       </c>
-      <c r="X12" s="20" t="n"/>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="20" t="n"/>
-      <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="20" t="n"/>
-      <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="20" t="n"/>
-      <c r="AF12" s="20" t="n"/>
-      <c r="AG12" s="20" t="n"/>
-      <c r="AH12" s="20" t="n"/>
-      <c r="AI12" s="20" t="n"/>
-      <c r="AJ12" s="20" t="n"/>
-      <c r="AK12" s="21" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="X17" s="20" t="n"/>
+      <c r="Y17" s="20" t="n"/>
+      <c r="Z17" s="20" t="n"/>
+      <c r="AA17" s="20" t="n"/>
+      <c r="AB17" s="20" t="n"/>
+      <c r="AC17" s="20" t="n"/>
+      <c r="AD17" s="20" t="n"/>
+      <c r="AE17" s="20" t="n"/>
+      <c r="AF17" s="20" t="n"/>
+      <c r="AG17" s="20" t="n"/>
+      <c r="AH17" s="20" t="n"/>
+      <c r="AI17" s="20" t="n"/>
+      <c r="AJ17" s="20" t="n"/>
+      <c r="AK17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Logical Type</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Physical Type</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Example(s)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>Authoritative Definition URL</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="L18" s="10" t="inlineStr">
         <is>
           <t>Authoritative Definition Type</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>Physical Name</t>
         </is>
       </c>
-      <c r="N13" s="10" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>Primary Key</t>
         </is>
       </c>
-      <c r="O13" s="10" t="inlineStr">
+      <c r="O18" s="10" t="inlineStr">
         <is>
           <t>Primary Key Position</t>
         </is>
       </c>
-      <c r="P13" s="10" t="inlineStr">
+      <c r="P18" s="10" t="inlineStr">
         <is>
           <t>Partitioned</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="inlineStr">
+      <c r="Q18" s="10" t="inlineStr">
         <is>
           <t>Partition Key Position</t>
         </is>
       </c>
-      <c r="R13" s="10" t="inlineStr">
+      <c r="R18" s="10" t="inlineStr">
         <is>
           <t>Encrypted Name</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>Transform Sources</t>
         </is>
       </c>
-      <c r="T13" s="10" t="inlineStr">
+      <c r="T18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Transform Logic	</t>
         </is>
       </c>
-      <c r="U13" s="10" t="inlineStr">
+      <c r="U18" s="10" t="inlineStr">
         <is>
           <t>Transform Description</t>
         </is>
       </c>
-      <c r="V13" s="10" t="inlineStr">
+      <c r="V18" s="10" t="inlineStr">
         <is>
           <t>Critical Data Element Status</t>
         </is>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W18" s="10" t="inlineStr">
         <is>
           <t>Maximum Items</t>
         </is>
       </c>
-      <c r="X13" s="10" t="inlineStr">
+      <c r="X18" s="10" t="inlineStr">
         <is>
           <t>Minimum Items</t>
         </is>
       </c>
-      <c r="Y13" s="10" t="inlineStr">
+      <c r="Y18" s="10" t="inlineStr">
         <is>
           <t>Unique Items</t>
         </is>
       </c>
-      <c r="Z13" s="10" t="inlineStr">
+      <c r="Z18" s="10" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="AA13" s="10" t="inlineStr">
+      <c r="AA18" s="10" t="inlineStr">
         <is>
           <t>Minimum Length</t>
         </is>
       </c>
-      <c r="AB13" s="10" t="inlineStr">
+      <c r="AB18" s="10" t="inlineStr">
         <is>
           <t>Maximum Length</t>
         </is>
       </c>
-      <c r="AC13" s="10" t="inlineStr">
+      <c r="AC18" s="10" t="inlineStr">
         <is>
           <t>Exclusive Minimum</t>
         </is>
       </c>
-      <c r="AD13" s="10" t="inlineStr">
+      <c r="AD18" s="10" t="inlineStr">
         <is>
           <t>Minimum</t>
         </is>
       </c>
-      <c r="AE13" s="10" t="inlineStr">
+      <c r="AE18" s="10" t="inlineStr">
         <is>
           <t>Exclusive Maximum</t>
         </is>
       </c>
-      <c r="AF13" s="10" t="inlineStr">
+      <c r="AF18" s="10" t="inlineStr">
         <is>
           <t>Maximum</t>
         </is>
       </c>
-      <c r="AG13" s="10" t="inlineStr">
+      <c r="AG18" s="10" t="inlineStr">
         <is>
           <t>Multiple Of</t>
         </is>
       </c>
-      <c r="AH13" s="10" t="inlineStr">
+      <c r="AH18" s="10" t="inlineStr">
         <is>
           <t>Minimum Properties</t>
         </is>
       </c>
-      <c r="AI13" s="10" t="inlineStr">
+      <c r="AI18" s="10" t="inlineStr">
         <is>
           <t>Maximum Properties</t>
         </is>
       </c>
-      <c r="AJ13" s="10" t="inlineStr">
+      <c r="AJ18" s="10" t="inlineStr">
         <is>
           <t>Required Properties</t>
         </is>
       </c>
-      <c r="AK13" s="10" t="inlineStr">
+      <c r="AK18" s="10" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="AL13" s="10" t="inlineStr">
+      <c r="AL18" s="9" t="inlineStr">
+        <is>
+          <t>Semantic Type</t>
+        </is>
+      </c>
+      <c r="AM18" s="9" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="AN18" s="9" t="inlineStr">
         <is>
           <t>Comments (internal)</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>shipment_id</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Shipment ID</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>123e4567-e89b-12d3-a456-426614174000</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>Unique identifier for each shipment.</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>businesskey</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>definitions/shipment_id.odcs.yaml</t>
-        </is>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>businessDefinition</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
-        <is>
-          <t>sid</t>
-        </is>
-      </c>
-      <c r="N14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="15" t="n"/>
-      <c r="R14" s="15" t="n"/>
-      <c r="S14" s="15" t="inlineStr"/>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="15" t="n"/>
-      <c r="V14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="15" t="n"/>
-      <c r="X14" s="15" t="n"/>
-      <c r="Y14" s="15" t="n"/>
-      <c r="Z14" s="15" t="n"/>
-      <c r="AA14" s="15" t="n"/>
-      <c r="AB14" s="15" t="n"/>
-      <c r="AC14" s="15" t="n"/>
-      <c r="AD14" s="15" t="n"/>
-      <c r="AE14" s="15" t="n"/>
-      <c r="AF14" s="15" t="n"/>
-      <c r="AG14" s="15" t="n"/>
-      <c r="AH14" s="15" t="n"/>
-      <c r="AI14" s="15" t="n"/>
-      <c r="AJ14" s="15" t="n"/>
-      <c r="AK14" s="15" t="n"/>
-      <c r="AL14" s="28" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="inlineStr"/>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>definitions/order_id.odcs.yaml</t>
-        </is>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>businessDefinition</t>
-        </is>
-      </c>
-      <c r="M15" s="15" t="inlineStr">
-        <is>
-          <t>oid</t>
-        </is>
-      </c>
-      <c r="N15" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" s="15" t="n"/>
-      <c r="P15" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="15" t="n"/>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="inlineStr"/>
-      <c r="T15" s="15" t="n"/>
-      <c r="U15" s="15" t="n"/>
-      <c r="V15" s="15" t="n"/>
-      <c r="W15" s="15" t="n"/>
-      <c r="X15" s="15" t="n"/>
-      <c r="Y15" s="15" t="n"/>
-      <c r="Z15" s="15" t="n"/>
-      <c r="AA15" s="15" t="n"/>
-      <c r="AB15" s="15" t="n"/>
-      <c r="AC15" s="15" t="n"/>
-      <c r="AD15" s="15" t="n"/>
-      <c r="AE15" s="15" t="n"/>
-      <c r="AF15" s="15" t="n"/>
-      <c r="AG15" s="15" t="n"/>
-      <c r="AH15" s="15" t="n"/>
-      <c r="AI15" s="15" t="n"/>
-      <c r="AJ15" s="15" t="n"/>
-      <c r="AK15" s="15" t="n"/>
-      <c r="AL15" s="28" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>delivery_date</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>timestamp_tz</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>2023-10-01T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>The actual or expected delivery date of the shipment.</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="inlineStr"/>
-      <c r="K16" s="15" t="n"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="15" t="n"/>
-      <c r="R16" s="15" t="n"/>
-      <c r="S16" s="15" t="inlineStr"/>
-      <c r="T16" s="15" t="n"/>
-      <c r="U16" s="15" t="n"/>
-      <c r="V16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" s="15" t="n"/>
-      <c r="X16" s="15" t="n"/>
-      <c r="Y16" s="15" t="n"/>
-      <c r="Z16" s="15" t="n"/>
-      <c r="AA16" s="15" t="n"/>
-      <c r="AB16" s="15" t="n"/>
-      <c r="AC16" s="15" t="n"/>
-      <c r="AD16" s="15" t="n"/>
-      <c r="AE16" s="15" t="n"/>
-      <c r="AF16" s="15" t="n"/>
-      <c r="AG16" s="15" t="n"/>
-      <c r="AH16" s="15" t="n"/>
-      <c r="AI16" s="15" t="n"/>
-      <c r="AJ16" s="15" t="n"/>
-      <c r="AK16" s="15" t="n"/>
-      <c r="AL16" s="28" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Carrier</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>FedEx,UPS</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>The shipping carrier used for the delivery.</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="inlineStr"/>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="15" t="n"/>
-      <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="inlineStr"/>
-      <c r="T17" s="15" t="n"/>
-      <c r="U17" s="15" t="n"/>
-      <c r="V17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" s="15" t="n"/>
-      <c r="X17" s="15" t="n"/>
-      <c r="Y17" s="15" t="n"/>
-      <c r="Z17" s="15" t="n"/>
-      <c r="AA17" s="15" t="n"/>
-      <c r="AB17" s="15" t="n"/>
-      <c r="AC17" s="15" t="n"/>
-      <c r="AD17" s="15" t="n"/>
-      <c r="AE17" s="15" t="n"/>
-      <c r="AF17" s="15" t="n"/>
-      <c r="AG17" s="15" t="n"/>
-      <c r="AH17" s="15" t="n"/>
-      <c r="AI17" s="15" t="n"/>
-      <c r="AJ17" s="15" t="n"/>
-      <c r="AK17" s="15" t="n"/>
-      <c r="AL17" s="28" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>tracking_number</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Tracking Number</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>1Z999AA10123456784</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>Tracking number provided by the carrier.</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>restricted</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="inlineStr"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="15" t="n"/>
-      <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="inlineStr"/>
-      <c r="T18" s="15" t="n"/>
-      <c r="U18" s="15" t="n"/>
-      <c r="V18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="15" t="n"/>
-      <c r="X18" s="15" t="n"/>
-      <c r="Y18" s="15" t="n"/>
-      <c r="Z18" s="15" t="n"/>
-      <c r="AA18" s="15" t="n"/>
-      <c r="AB18" s="15" t="n"/>
-      <c r="AC18" s="15" t="n"/>
-      <c r="AD18" s="15" t="n"/>
-      <c r="AE18" s="15" t="n"/>
-      <c r="AF18" s="15" t="n"/>
-      <c r="AG18" s="15" t="n"/>
-      <c r="AH18" s="15" t="n"/>
-      <c r="AI18" s="15" t="n"/>
-      <c r="AJ18" s="15" t="n"/>
-      <c r="AK18" s="15" t="n"/>
-      <c r="AL18" s="28" t="n"/>
+      <c r="AO18" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="AP18" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="AQ18" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>shipment_id</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Shipment ID</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -3283,49 +6119,61 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>Delivered,In Transit</t>
+          <t>123e4567-e89b-12d3-a456-426614174000</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Current status of the shipment.</t>
+          <t>Unique identifier for each shipment.</t>
         </is>
       </c>
       <c r="G19" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
           <t>internal</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-      <c r="M19" s="15" t="n"/>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>businesskey</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>definitions/shipment_id.odcs.yaml</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>businessDefinition</t>
+        </is>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>sid</t>
+        </is>
+      </c>
       <c r="N19" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="P19" s="15" t="n"/>
       <c r="Q19" s="15" t="n"/>
       <c r="R19" s="15" t="n"/>
       <c r="S19" s="15" t="inlineStr"/>
       <c r="T19" s="15" t="n"/>
       <c r="U19" s="15" t="n"/>
-      <c r="V19" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="V19" s="15" t="n"/>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="15" t="n"/>
       <c r="Y19" s="15" t="n"/>
@@ -3341,45 +6189,62 @@
       <c r="AI19" s="15" t="n"/>
       <c r="AJ19" s="15" t="n"/>
       <c r="AK19" s="15" t="n"/>
-      <c r="AL19" s="28" t="n"/>
+      <c r="AL19" s="15" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="AM19" s="15" t="n"/>
+      <c r="AN19" s="15" t="n"/>
+      <c r="AO19" s="15" t="inlineStr">
+        <is>
+          <t>prop-shipment-id</t>
+        </is>
+      </c>
+      <c r="AP19" s="15" t="inlineStr">
+        <is>
+          <t>masked</t>
+        </is>
+      </c>
+      <c r="AQ19" s="15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>inline_object_definition</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Inline Object Definition</t>
+          <t>Order ID</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>{"destination": "New York"}</t>
+          <t>ORD12345</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>A JSON representation of additional shipment info</t>
+          <t>Identifier for the order associated with the shipment.</t>
         </is>
       </c>
       <c r="G20" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="15" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H20" s="15" t="n"/>
       <c r="I20" s="15" t="inlineStr">
         <is>
           <t>internal</t>
@@ -3388,30 +6253,30 @@
       <c r="J20" s="15" t="inlineStr"/>
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>oid</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="15" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
       <c r="S20" s="15" t="inlineStr"/>
       <c r="T20" s="15" t="n"/>
       <c r="U20" s="15" t="n"/>
-      <c r="V20" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="n"/>
       <c r="Z20" s="15" t="n"/>
-      <c r="AA20" s="15" t="n"/>
-      <c r="AB20" s="15" t="n"/>
+      <c r="AA20" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="15" t="n">
+        <v>10</v>
+      </c>
       <c r="AC20" s="15" t="n"/>
       <c r="AD20" s="15" t="n"/>
       <c r="AE20" s="15" t="n"/>
@@ -3421,44 +6286,47 @@
       <c r="AI20" s="15" t="n"/>
       <c r="AJ20" s="15" t="n"/>
       <c r="AK20" s="15" t="n"/>
-      <c r="AL20" s="28" t="n"/>
+      <c r="AL20" s="15" t="n"/>
+      <c r="AM20" s="15" t="n"/>
+      <c r="AN20" s="15" t="n"/>
+      <c r="AO20" s="15" t="n"/>
+      <c r="AP20" s="15" t="n"/>
+      <c r="AQ20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>address</t>
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>status</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Shipment Address</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>Delivered,In Transit</t>
+        </is>
+      </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Shipping address details.</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="b">
-        <v>1</v>
-      </c>
+          <t>Current status of the shipment.</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="n"/>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>restricted</t>
-        </is>
-      </c>
+      <c r="I21" s="15" t="n"/>
       <c r="J21" s="15" t="inlineStr"/>
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
@@ -3487,61 +6355,56 @@
       <c r="AI21" s="15" t="n"/>
       <c r="AJ21" s="15" t="n"/>
       <c r="AK21" s="15" t="n"/>
-      <c r="AL21" s="28" t="n"/>
+      <c r="AL21" s="15" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="AM21" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="15" t="n"/>
+      <c r="AO21" s="15" t="n"/>
+      <c r="AP21" s="15" t="n"/>
+      <c r="AQ21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>address.street</t>
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>weight_kg</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>Marienplatz 1</t>
-        </is>
-      </c>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr"/>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Street address.</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>restricted</t>
-        </is>
-      </c>
+          <t>Weight of the parcel.</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
       <c r="J22" s="15" t="inlineStr"/>
       <c r="K22" s="15" t="n"/>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
       <c r="S22" s="15" t="inlineStr"/>
@@ -3563,45 +6426,58 @@
       <c r="AI22" s="15" t="n"/>
       <c r="AJ22" s="15" t="n"/>
       <c r="AK22" s="15" t="n"/>
-      <c r="AL22" s="28" t="n"/>
+      <c r="AL22" s="15" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="AM22" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="15" t="n"/>
+      <c r="AO22" s="15" t="n"/>
+      <c r="AP22" s="15" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AQ22" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>address.city</t>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>address</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Shipment Address</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr"/>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>City of the shipping address.</t>
+          <t>Shipping address details.</t>
         </is>
       </c>
       <c r="G23" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="H23" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="H23" s="15" t="n"/>
       <c r="I23" s="15" t="inlineStr">
         <is>
           <t>restricted</t>
@@ -3611,13 +6487,9 @@
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
-      <c r="N23" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
-      <c r="P23" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="P23" s="15" t="n"/>
       <c r="Q23" s="15" t="n"/>
       <c r="R23" s="15" t="n"/>
       <c r="S23" s="15" t="inlineStr"/>
@@ -3639,19 +6511,20 @@
       <c r="AI23" s="15" t="n"/>
       <c r="AJ23" s="15" t="n"/>
       <c r="AK23" s="15" t="n"/>
-      <c r="AL23" s="28" t="n"/>
+      <c r="AL23" s="15" t="n"/>
+      <c r="AM23" s="15" t="n"/>
+      <c r="AN23" s="15" t="n"/>
+      <c r="AO23" s="15" t="n"/>
+      <c r="AP23" s="15" t="n"/>
+      <c r="AQ23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>address.country</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
+          <t>address.street</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n"/>
       <c r="C24" s="15" t="inlineStr">
         <is>
           <t>string</t>
@@ -3662,36 +6535,24 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
+      <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Country of the shipping address.</t>
+          <t>Street address.</t>
         </is>
       </c>
       <c r="G24" s="15" t="b">
         <v>1</v>
       </c>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>restricted</t>
-        </is>
-      </c>
+      <c r="I24" s="15" t="n"/>
       <c r="J24" s="15" t="inlineStr"/>
       <c r="K24" s="15" t="n"/>
       <c r="L24" s="15" t="n"/>
       <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
-      <c r="P24" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
       <c r="S24" s="15" t="inlineStr"/>
@@ -3713,19 +6574,42 @@
       <c r="AI24" s="15" t="n"/>
       <c r="AJ24" s="15" t="n"/>
       <c r="AK24" s="15" t="n"/>
-      <c r="AL24" s="28" t="n"/>
+      <c r="AL24" s="15" t="n"/>
+      <c r="AM24" s="15" t="n"/>
+      <c r="AN24" s="15" t="n"/>
+      <c r="AO24" s="15" t="n"/>
+      <c r="AP24" s="15" t="n"/>
+      <c r="AQ24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n"/>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>address.country</t>
+        </is>
+      </c>
       <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr"/>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Country of the shipping address.</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="b">
+        <v>1</v>
+      </c>
       <c r="H25" s="15" t="n"/>
       <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="n"/>
+      <c r="J25" s="15" t="inlineStr"/>
       <c r="K25" s="15" t="n"/>
       <c r="L25" s="15" t="n"/>
       <c r="M25" s="15" t="n"/>
@@ -3734,7 +6618,7 @@
       <c r="P25" s="15" t="n"/>
       <c r="Q25" s="15" t="n"/>
       <c r="R25" s="15" t="n"/>
-      <c r="S25" s="15" t="n"/>
+      <c r="S25" s="15" t="inlineStr"/>
       <c r="T25" s="15" t="n"/>
       <c r="U25" s="15" t="n"/>
       <c r="V25" s="15" t="n"/>
@@ -3753,19 +6637,40 @@
       <c r="AI25" s="15" t="n"/>
       <c r="AJ25" s="15" t="n"/>
       <c r="AK25" s="15" t="n"/>
-      <c r="AL25" s="28" t="n"/>
+      <c r="AL25" s="15" t="n"/>
+      <c r="AM25" s="15" t="n"/>
+      <c r="AN25" s="15" t="n"/>
+      <c r="AO25" s="15" t="n"/>
+      <c r="AP25" s="15" t="n"/>
+      <c r="AQ25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n"/>
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>items</t>
+        </is>
+      </c>
       <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="15" t="n"/>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr"/>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Line items of the shipment.</t>
+        </is>
+      </c>
       <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
       <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="n"/>
+      <c r="J26" s="15" t="inlineStr"/>
       <c r="K26" s="15" t="n"/>
       <c r="L26" s="15" t="n"/>
       <c r="M26" s="15" t="n"/>
@@ -3774,7 +6679,7 @@
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
-      <c r="S26" s="15" t="n"/>
+      <c r="S26" s="15" t="inlineStr"/>
       <c r="T26" s="15" t="n"/>
       <c r="U26" s="15" t="n"/>
       <c r="V26" s="15" t="n"/>
@@ -3793,19 +6698,36 @@
       <c r="AI26" s="15" t="n"/>
       <c r="AJ26" s="15" t="n"/>
       <c r="AK26" s="15" t="n"/>
-      <c r="AL26" s="28" t="n"/>
+      <c r="AL26" s="15" t="n"/>
+      <c r="AM26" s="15" t="n"/>
+      <c r="AN26" s="15" t="n"/>
+      <c r="AO26" s="15" t="n"/>
+      <c r="AP26" s="15" t="n"/>
+      <c r="AQ26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>items.items</t>
+        </is>
+      </c>
       <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="16" t="n"/>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr"/>
       <c r="F27" s="15" t="n"/>
       <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
       <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
+      <c r="J27" s="15" t="inlineStr"/>
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
@@ -3814,7 +6736,7 @@
       <c r="P27" s="15" t="n"/>
       <c r="Q27" s="15" t="n"/>
       <c r="R27" s="15" t="n"/>
-      <c r="S27" s="15" t="n"/>
+      <c r="S27" s="15" t="inlineStr"/>
       <c r="T27" s="15" t="n"/>
       <c r="U27" s="15" t="n"/>
       <c r="V27" s="15" t="n"/>
@@ -3833,19 +6755,36 @@
       <c r="AI27" s="15" t="n"/>
       <c r="AJ27" s="15" t="n"/>
       <c r="AK27" s="15" t="n"/>
-      <c r="AL27" s="28" t="n"/>
+      <c r="AL27" s="15" t="n"/>
+      <c r="AM27" s="15" t="n"/>
+      <c r="AN27" s="15" t="n"/>
+      <c r="AO27" s="15" t="n"/>
+      <c r="AP27" s="15" t="n"/>
+      <c r="AQ27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="n"/>
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>items.items.sku</t>
+        </is>
+      </c>
       <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="16" t="n"/>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr"/>
       <c r="F28" s="15" t="n"/>
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
+      <c r="J28" s="15" t="inlineStr"/>
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
@@ -3854,7 +6793,7 @@
       <c r="P28" s="15" t="n"/>
       <c r="Q28" s="15" t="n"/>
       <c r="R28" s="15" t="n"/>
-      <c r="S28" s="15" t="n"/>
+      <c r="S28" s="15" t="inlineStr"/>
       <c r="T28" s="15" t="n"/>
       <c r="U28" s="15" t="n"/>
       <c r="V28" s="15" t="n"/>
@@ -3873,7 +6812,20 @@
       <c r="AI28" s="15" t="n"/>
       <c r="AJ28" s="15" t="n"/>
       <c r="AK28" s="15" t="n"/>
-      <c r="AL28" s="28" t="n"/>
+      <c r="AL28" s="15" t="n"/>
+      <c r="AM28" s="15" t="n"/>
+      <c r="AN28" s="15" t="n"/>
+      <c r="AO28" s="15" t="n"/>
+      <c r="AP28" s="15" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="AQ28" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="n"/>
@@ -3913,7 +6865,12 @@
       <c r="AI29" s="15" t="n"/>
       <c r="AJ29" s="15" t="n"/>
       <c r="AK29" s="15" t="n"/>
-      <c r="AL29" s="28" t="n"/>
+      <c r="AL29" s="15" t="n"/>
+      <c r="AM29" s="15" t="n"/>
+      <c r="AN29" s="15" t="n"/>
+      <c r="AO29" s="15" t="n"/>
+      <c r="AP29" s="15" t="n"/>
+      <c r="AQ29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="n"/>
@@ -3953,7 +6910,12 @@
       <c r="AI30" s="15" t="n"/>
       <c r="AJ30" s="15" t="n"/>
       <c r="AK30" s="15" t="n"/>
-      <c r="AL30" s="28" t="n"/>
+      <c r="AL30" s="15" t="n"/>
+      <c r="AM30" s="15" t="n"/>
+      <c r="AN30" s="15" t="n"/>
+      <c r="AO30" s="15" t="n"/>
+      <c r="AP30" s="15" t="n"/>
+      <c r="AQ30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="n"/>
@@ -3993,7 +6955,12 @@
       <c r="AI31" s="15" t="n"/>
       <c r="AJ31" s="15" t="n"/>
       <c r="AK31" s="15" t="n"/>
-      <c r="AL31" s="28" t="n"/>
+      <c r="AL31" s="15" t="n"/>
+      <c r="AM31" s="15" t="n"/>
+      <c r="AN31" s="15" t="n"/>
+      <c r="AO31" s="15" t="n"/>
+      <c r="AP31" s="15" t="n"/>
+      <c r="AQ31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="n"/>
@@ -4033,7 +7000,12 @@
       <c r="AI32" s="15" t="n"/>
       <c r="AJ32" s="15" t="n"/>
       <c r="AK32" s="15" t="n"/>
-      <c r="AL32" s="28" t="n"/>
+      <c r="AL32" s="15" t="n"/>
+      <c r="AM32" s="15" t="n"/>
+      <c r="AN32" s="15" t="n"/>
+      <c r="AO32" s="15" t="n"/>
+      <c r="AP32" s="15" t="n"/>
+      <c r="AQ32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="n"/>
@@ -4073,7 +7045,12 @@
       <c r="AI33" s="15" t="n"/>
       <c r="AJ33" s="15" t="n"/>
       <c r="AK33" s="15" t="n"/>
-      <c r="AL33" s="28" t="n"/>
+      <c r="AL33" s="15" t="n"/>
+      <c r="AM33" s="15" t="n"/>
+      <c r="AN33" s="15" t="n"/>
+      <c r="AO33" s="15" t="n"/>
+      <c r="AP33" s="15" t="n"/>
+      <c r="AQ33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="n"/>
@@ -4113,7 +7090,12 @@
       <c r="AI34" s="15" t="n"/>
       <c r="AJ34" s="15" t="n"/>
       <c r="AK34" s="15" t="n"/>
-      <c r="AL34" s="28" t="n"/>
+      <c r="AL34" s="15" t="n"/>
+      <c r="AM34" s="15" t="n"/>
+      <c r="AN34" s="15" t="n"/>
+      <c r="AO34" s="15" t="n"/>
+      <c r="AP34" s="15" t="n"/>
+      <c r="AQ34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="n"/>
@@ -4153,7 +7135,12 @@
       <c r="AI35" s="15" t="n"/>
       <c r="AJ35" s="15" t="n"/>
       <c r="AK35" s="15" t="n"/>
-      <c r="AL35" s="28" t="n"/>
+      <c r="AL35" s="15" t="n"/>
+      <c r="AM35" s="15" t="n"/>
+      <c r="AN35" s="15" t="n"/>
+      <c r="AO35" s="15" t="n"/>
+      <c r="AP35" s="15" t="n"/>
+      <c r="AQ35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="n"/>
@@ -4193,7 +7180,12 @@
       <c r="AI36" s="15" t="n"/>
       <c r="AJ36" s="15" t="n"/>
       <c r="AK36" s="15" t="n"/>
-      <c r="AL36" s="28" t="n"/>
+      <c r="AL36" s="15" t="n"/>
+      <c r="AM36" s="15" t="n"/>
+      <c r="AN36" s="15" t="n"/>
+      <c r="AO36" s="15" t="n"/>
+      <c r="AP36" s="15" t="n"/>
+      <c r="AQ36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n"/>
@@ -4233,7 +7225,12 @@
       <c r="AI37" s="15" t="n"/>
       <c r="AJ37" s="15" t="n"/>
       <c r="AK37" s="15" t="n"/>
-      <c r="AL37" s="28" t="n"/>
+      <c r="AL37" s="15" t="n"/>
+      <c r="AM37" s="15" t="n"/>
+      <c r="AN37" s="15" t="n"/>
+      <c r="AO37" s="15" t="n"/>
+      <c r="AP37" s="15" t="n"/>
+      <c r="AQ37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n"/>
@@ -4273,7 +7270,12 @@
       <c r="AI38" s="15" t="n"/>
       <c r="AJ38" s="15" t="n"/>
       <c r="AK38" s="15" t="n"/>
-      <c r="AL38" s="28" t="n"/>
+      <c r="AL38" s="15" t="n"/>
+      <c r="AM38" s="15" t="n"/>
+      <c r="AN38" s="15" t="n"/>
+      <c r="AO38" s="15" t="n"/>
+      <c r="AP38" s="15" t="n"/>
+      <c r="AQ38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n"/>
@@ -4313,7 +7315,12 @@
       <c r="AI39" s="15" t="n"/>
       <c r="AJ39" s="15" t="n"/>
       <c r="AK39" s="15" t="n"/>
-      <c r="AL39" s="28" t="n"/>
+      <c r="AL39" s="15" t="n"/>
+      <c r="AM39" s="15" t="n"/>
+      <c r="AN39" s="15" t="n"/>
+      <c r="AO39" s="15" t="n"/>
+      <c r="AP39" s="15" t="n"/>
+      <c r="AQ39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="17" t="n"/>
@@ -4353,7 +7360,12 @@
       <c r="AI40" s="15" t="n"/>
       <c r="AJ40" s="15" t="n"/>
       <c r="AK40" s="15" t="n"/>
-      <c r="AL40" s="28" t="n"/>
+      <c r="AL40" s="15" t="n"/>
+      <c r="AM40" s="15" t="n"/>
+      <c r="AN40" s="15" t="n"/>
+      <c r="AO40" s="15" t="n"/>
+      <c r="AP40" s="15" t="n"/>
+      <c r="AQ40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="17" t="n"/>
@@ -4393,7 +7405,12 @@
       <c r="AI41" s="15" t="n"/>
       <c r="AJ41" s="15" t="n"/>
       <c r="AK41" s="15" t="n"/>
-      <c r="AL41" s="28" t="n"/>
+      <c r="AL41" s="15" t="n"/>
+      <c r="AM41" s="15" t="n"/>
+      <c r="AN41" s="15" t="n"/>
+      <c r="AO41" s="15" t="n"/>
+      <c r="AP41" s="15" t="n"/>
+      <c r="AQ41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="n"/>
@@ -4433,7 +7450,12 @@
       <c r="AI42" s="15" t="n"/>
       <c r="AJ42" s="15" t="n"/>
       <c r="AK42" s="15" t="n"/>
-      <c r="AL42" s="28" t="n"/>
+      <c r="AL42" s="15" t="n"/>
+      <c r="AM42" s="15" t="n"/>
+      <c r="AN42" s="15" t="n"/>
+      <c r="AO42" s="15" t="n"/>
+      <c r="AP42" s="15" t="n"/>
+      <c r="AQ42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="n"/>
@@ -4473,7 +7495,12 @@
       <c r="AI43" s="15" t="n"/>
       <c r="AJ43" s="15" t="n"/>
       <c r="AK43" s="15" t="n"/>
-      <c r="AL43" s="28" t="n"/>
+      <c r="AL43" s="15" t="n"/>
+      <c r="AM43" s="15" t="n"/>
+      <c r="AN43" s="15" t="n"/>
+      <c r="AO43" s="15" t="n"/>
+      <c r="AP43" s="15" t="n"/>
+      <c r="AQ43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="n"/>
@@ -4513,7 +7540,12 @@
       <c r="AI44" s="15" t="n"/>
       <c r="AJ44" s="15" t="n"/>
       <c r="AK44" s="15" t="n"/>
-      <c r="AL44" s="28" t="n"/>
+      <c r="AL44" s="15" t="n"/>
+      <c r="AM44" s="15" t="n"/>
+      <c r="AN44" s="15" t="n"/>
+      <c r="AO44" s="15" t="n"/>
+      <c r="AP44" s="15" t="n"/>
+      <c r="AQ44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="n"/>
@@ -4553,7 +7585,12 @@
       <c r="AI45" s="15" t="n"/>
       <c r="AJ45" s="15" t="n"/>
       <c r="AK45" s="15" t="n"/>
-      <c r="AL45" s="28" t="n"/>
+      <c r="AL45" s="15" t="n"/>
+      <c r="AM45" s="15" t="n"/>
+      <c r="AN45" s="15" t="n"/>
+      <c r="AO45" s="15" t="n"/>
+      <c r="AP45" s="15" t="n"/>
+      <c r="AQ45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="n"/>
@@ -4593,7 +7630,12 @@
       <c r="AI46" s="15" t="n"/>
       <c r="AJ46" s="15" t="n"/>
       <c r="AK46" s="15" t="n"/>
-      <c r="AL46" s="28" t="n"/>
+      <c r="AL46" s="15" t="n"/>
+      <c r="AM46" s="15" t="n"/>
+      <c r="AN46" s="15" t="n"/>
+      <c r="AO46" s="15" t="n"/>
+      <c r="AP46" s="15" t="n"/>
+      <c r="AQ46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="n"/>
@@ -4633,7 +7675,12 @@
       <c r="AI47" s="15" t="n"/>
       <c r="AJ47" s="15" t="n"/>
       <c r="AK47" s="15" t="n"/>
-      <c r="AL47" s="28" t="n"/>
+      <c r="AL47" s="15" t="n"/>
+      <c r="AM47" s="15" t="n"/>
+      <c r="AN47" s="15" t="n"/>
+      <c r="AO47" s="15" t="n"/>
+      <c r="AP47" s="15" t="n"/>
+      <c r="AQ47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="n"/>
@@ -4673,7 +7720,12 @@
       <c r="AI48" s="15" t="n"/>
       <c r="AJ48" s="15" t="n"/>
       <c r="AK48" s="15" t="n"/>
-      <c r="AL48" s="28" t="n"/>
+      <c r="AL48" s="15" t="n"/>
+      <c r="AM48" s="15" t="n"/>
+      <c r="AN48" s="15" t="n"/>
+      <c r="AO48" s="15" t="n"/>
+      <c r="AP48" s="15" t="n"/>
+      <c r="AQ48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="n"/>
@@ -4713,17 +7765,252 @@
       <c r="AI49" s="15" t="n"/>
       <c r="AJ49" s="15" t="n"/>
       <c r="AK49" s="15" t="n"/>
-      <c r="AL49" s="28" t="n"/>
+      <c r="AL49" s="15" t="n"/>
+      <c r="AM49" s="15" t="n"/>
+      <c r="AN49" s="15" t="n"/>
+      <c r="AO49" s="15" t="n"/>
+      <c r="AP49" s="15" t="n"/>
+      <c r="AQ49" s="15" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n"/>
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="15" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="15" t="n"/>
+      <c r="J50" s="15" t="n"/>
+      <c r="K50" s="15" t="n"/>
+      <c r="L50" s="15" t="n"/>
+      <c r="M50" s="15" t="n"/>
+      <c r="N50" s="15" t="n"/>
+      <c r="O50" s="15" t="n"/>
+      <c r="P50" s="15" t="n"/>
+      <c r="Q50" s="15" t="n"/>
+      <c r="R50" s="15" t="n"/>
+      <c r="S50" s="15" t="n"/>
+      <c r="T50" s="15" t="n"/>
+      <c r="U50" s="15" t="n"/>
+      <c r="V50" s="15" t="n"/>
+      <c r="W50" s="15" t="n"/>
+      <c r="X50" s="15" t="n"/>
+      <c r="Y50" s="15" t="n"/>
+      <c r="Z50" s="15" t="n"/>
+      <c r="AA50" s="15" t="n"/>
+      <c r="AB50" s="15" t="n"/>
+      <c r="AC50" s="15" t="n"/>
+      <c r="AD50" s="15" t="n"/>
+      <c r="AE50" s="15" t="n"/>
+      <c r="AF50" s="15" t="n"/>
+      <c r="AG50" s="15" t="n"/>
+      <c r="AH50" s="15" t="n"/>
+      <c r="AI50" s="15" t="n"/>
+      <c r="AJ50" s="15" t="n"/>
+      <c r="AK50" s="15" t="n"/>
+      <c r="AL50" s="15" t="n"/>
+      <c r="AM50" s="15" t="n"/>
+      <c r="AN50" s="15" t="n"/>
+      <c r="AO50" s="15" t="n"/>
+      <c r="AP50" s="15" t="n"/>
+      <c r="AQ50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="n"/>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="15" t="n"/>
+      <c r="J51" s="15" t="n"/>
+      <c r="K51" s="15" t="n"/>
+      <c r="L51" s="15" t="n"/>
+      <c r="M51" s="15" t="n"/>
+      <c r="N51" s="15" t="n"/>
+      <c r="O51" s="15" t="n"/>
+      <c r="P51" s="15" t="n"/>
+      <c r="Q51" s="15" t="n"/>
+      <c r="R51" s="15" t="n"/>
+      <c r="S51" s="15" t="n"/>
+      <c r="T51" s="15" t="n"/>
+      <c r="U51" s="15" t="n"/>
+      <c r="V51" s="15" t="n"/>
+      <c r="W51" s="15" t="n"/>
+      <c r="X51" s="15" t="n"/>
+      <c r="Y51" s="15" t="n"/>
+      <c r="Z51" s="15" t="n"/>
+      <c r="AA51" s="15" t="n"/>
+      <c r="AB51" s="15" t="n"/>
+      <c r="AC51" s="15" t="n"/>
+      <c r="AD51" s="15" t="n"/>
+      <c r="AE51" s="15" t="n"/>
+      <c r="AF51" s="15" t="n"/>
+      <c r="AG51" s="15" t="n"/>
+      <c r="AH51" s="15" t="n"/>
+      <c r="AI51" s="15" t="n"/>
+      <c r="AJ51" s="15" t="n"/>
+      <c r="AK51" s="15" t="n"/>
+      <c r="AL51" s="15" t="n"/>
+      <c r="AM51" s="15" t="n"/>
+      <c r="AN51" s="15" t="n"/>
+      <c r="AO51" s="15" t="n"/>
+      <c r="AP51" s="15" t="n"/>
+      <c r="AQ51" s="15" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="n"/>
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="15" t="n"/>
+      <c r="J52" s="15" t="n"/>
+      <c r="K52" s="15" t="n"/>
+      <c r="L52" s="15" t="n"/>
+      <c r="M52" s="15" t="n"/>
+      <c r="N52" s="15" t="n"/>
+      <c r="O52" s="15" t="n"/>
+      <c r="P52" s="15" t="n"/>
+      <c r="Q52" s="15" t="n"/>
+      <c r="R52" s="15" t="n"/>
+      <c r="S52" s="15" t="n"/>
+      <c r="T52" s="15" t="n"/>
+      <c r="U52" s="15" t="n"/>
+      <c r="V52" s="15" t="n"/>
+      <c r="W52" s="15" t="n"/>
+      <c r="X52" s="15" t="n"/>
+      <c r="Y52" s="15" t="n"/>
+      <c r="Z52" s="15" t="n"/>
+      <c r="AA52" s="15" t="n"/>
+      <c r="AB52" s="15" t="n"/>
+      <c r="AC52" s="15" t="n"/>
+      <c r="AD52" s="15" t="n"/>
+      <c r="AE52" s="15" t="n"/>
+      <c r="AF52" s="15" t="n"/>
+      <c r="AG52" s="15" t="n"/>
+      <c r="AH52" s="15" t="n"/>
+      <c r="AI52" s="15" t="n"/>
+      <c r="AJ52" s="15" t="n"/>
+      <c r="AK52" s="15" t="n"/>
+      <c r="AL52" s="15" t="n"/>
+      <c r="AM52" s="15" t="n"/>
+      <c r="AN52" s="15" t="n"/>
+      <c r="AO52" s="15" t="n"/>
+      <c r="AP52" s="15" t="n"/>
+      <c r="AQ52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="15" t="n"/>
+      <c r="J53" s="15" t="n"/>
+      <c r="K53" s="15" t="n"/>
+      <c r="L53" s="15" t="n"/>
+      <c r="M53" s="15" t="n"/>
+      <c r="N53" s="15" t="n"/>
+      <c r="O53" s="15" t="n"/>
+      <c r="P53" s="15" t="n"/>
+      <c r="Q53" s="15" t="n"/>
+      <c r="R53" s="15" t="n"/>
+      <c r="S53" s="15" t="n"/>
+      <c r="T53" s="15" t="n"/>
+      <c r="U53" s="15" t="n"/>
+      <c r="V53" s="15" t="n"/>
+      <c r="W53" s="15" t="n"/>
+      <c r="X53" s="15" t="n"/>
+      <c r="Y53" s="15" t="n"/>
+      <c r="Z53" s="15" t="n"/>
+      <c r="AA53" s="15" t="n"/>
+      <c r="AB53" s="15" t="n"/>
+      <c r="AC53" s="15" t="n"/>
+      <c r="AD53" s="15" t="n"/>
+      <c r="AE53" s="15" t="n"/>
+      <c r="AF53" s="15" t="n"/>
+      <c r="AG53" s="15" t="n"/>
+      <c r="AH53" s="15" t="n"/>
+      <c r="AI53" s="15" t="n"/>
+      <c r="AJ53" s="15" t="n"/>
+      <c r="AK53" s="15" t="n"/>
+      <c r="AL53" s="15" t="n"/>
+      <c r="AM53" s="15" t="n"/>
+      <c r="AN53" s="15" t="n"/>
+      <c r="AO53" s="15" t="n"/>
+      <c r="AP53" s="15" t="n"/>
+      <c r="AQ53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="n"/>
+      <c r="B54" s="15" t="n"/>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="15" t="n"/>
+      <c r="J54" s="15" t="n"/>
+      <c r="K54" s="15" t="n"/>
+      <c r="L54" s="15" t="n"/>
+      <c r="M54" s="15" t="n"/>
+      <c r="N54" s="15" t="n"/>
+      <c r="O54" s="15" t="n"/>
+      <c r="P54" s="15" t="n"/>
+      <c r="Q54" s="15" t="n"/>
+      <c r="R54" s="15" t="n"/>
+      <c r="S54" s="15" t="n"/>
+      <c r="T54" s="15" t="n"/>
+      <c r="U54" s="15" t="n"/>
+      <c r="V54" s="15" t="n"/>
+      <c r="W54" s="15" t="n"/>
+      <c r="X54" s="15" t="n"/>
+      <c r="Y54" s="15" t="n"/>
+      <c r="Z54" s="15" t="n"/>
+      <c r="AA54" s="15" t="n"/>
+      <c r="AB54" s="15" t="n"/>
+      <c r="AC54" s="15" t="n"/>
+      <c r="AD54" s="15" t="n"/>
+      <c r="AE54" s="15" t="n"/>
+      <c r="AF54" s="15" t="n"/>
+      <c r="AG54" s="15" t="n"/>
+      <c r="AH54" s="15" t="n"/>
+      <c r="AI54" s="15" t="n"/>
+      <c r="AJ54" s="15" t="n"/>
+      <c r="AK54" s="15" t="n"/>
+      <c r="AL54" s="15" t="n"/>
+      <c r="AM54" s="15" t="n"/>
+      <c r="AN54" s="15" t="n"/>
+      <c r="AO54" s="15" t="n"/>
+      <c r="AP54" s="15" t="n"/>
+      <c r="AQ54" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="12">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4735,15 +8022,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="8.33203125" customWidth="1" style="30" min="1" max="1"/>
     <col width="13" customWidth="1" style="30" min="2" max="2"/>
     <col width="48.5" customWidth="1" style="30" min="3" max="3"/>
     <col width="42.83203125" customWidth="1" style="30" min="4" max="4"/>
-    <col width="25.83203125" customWidth="1" style="30" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="30" min="6" max="16384"/>
+    <col width="22" customWidth="1" style="30" min="5" max="5"/>
+    <col width="22" customWidth="1" style="30" min="6" max="16384"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4791,25 +8079,75 @@
           <t>To</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>Description</t>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>foreignKey</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>shipments.order_id</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>orders.order_id</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>rel-orders</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>foreignKey</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>shipments.order_id</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>orders.order_id</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>rel-order</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n"/>
@@ -4947,7 +8285,1283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Enum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Allowed values of a property. Use schema.property dot syntax for the property (e.g. orders.status).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Delivered to the customer</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>The carrier confirmed the delivery.</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>enum-delivered</t>
+        </is>
+      </c>
+      <c r="H5" s="36" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>On its way</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>Numeric legacy code</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>address.country</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>address.country</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Alternative names for a schema or a property. Leave Property blank for a synonym of the schema itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Synonym</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Locale</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Sendungen</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>German name</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>business glossary</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>glossaryId</t>
+        </is>
+      </c>
+      <c r="J5" s="36" t="n">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Sendungsnummer</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Verified Statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Verified question/answer pairs that give consumers and AI agents context. Level: Contract or Schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Does this table contain cancelled shipments?</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>No, cancelled shipments are excluded before loading.</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>vs-cancelled</t>
+        </is>
+      </c>
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>verifiedBy</t>
+        </is>
+      </c>
+      <c r="H5" s="36" t="inlineStr">
+        <is>
+          <t>data-steward</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Is weight_kg always populated?</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>No, it is null for letters.</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>vs-weight</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Contract,Schema"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Constraints that consumers and AI agents must respect when using the data. Level: Contract or Schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Do not join to customer PII without a legal basis.</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>c-pii</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Never aggregate weight_kg across carriers.</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>c-weight</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Contract,Schema"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="17.5" customWidth="1" style="30" min="1" max="1"/>
@@ -4963,7 +9577,9 @@
     <col width="15.5" bestFit="1" customWidth="1" style="30" min="11" max="11"/>
     <col width="17.83203125" bestFit="1" customWidth="1" style="30" min="12" max="12"/>
     <col width="17.83203125" customWidth="1" style="30" min="13" max="13"/>
-    <col width="8.83203125" customWidth="1" style="30" min="14" max="16384"/>
+    <col width="22" customWidth="1" style="30" min="14" max="16384"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5052,6 +9668,21 @@
           <t>Schedule</t>
         </is>
       </c>
+      <c r="N4" s="32" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="O4" s="32" t="inlineStr">
+        <is>
+          <t>Custom Property</t>
+        </is>
+      </c>
+      <c r="P4" s="32" t="inlineStr">
+        <is>
+          <t>Custom Value</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -5067,7 +9698,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>testscenario for mustBeGreaterOrEqualTo</t>
+          <t>Table shall contain at least 1 row</t>
         </is>
       </c>
       <c r="E5" s="15" t="n"/>
@@ -5091,6 +9722,11 @@
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>q-rowcount</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -5098,72 +9734,55 @@
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>testscenario for mustBe (integer)</t>
+          <t>Status must be one of the known values</t>
         </is>
       </c>
       <c r="E6" s="15" t="n"/>
-      <c r="F6" s="27" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>mustBe</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>q-status-values</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>quality-team</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
+      <c r="A7" s="17" t="n"/>
       <c r="B7" s="17" t="n"/>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBe (float)</t>
-        </is>
-      </c>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
       <c r="E7" s="15" t="n"/>
-      <c r="F7" s="27" t="inlineStr">
-        <is>
-          <t>SELECT AVG(duration) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>mustBe</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
       <c r="I7" s="15" t="n"/>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
@@ -5171,38 +9790,14 @@
       <c r="M7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
+      <c r="A8" s="17" t="n"/>
       <c r="B8" s="17" t="n"/>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeLessThan (integer)</t>
-        </is>
-      </c>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
       <c r="E8" s="15" t="n"/>
-      <c r="F8" s="27" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM shipments where carries='active'</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>mustBeLessThan</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
       <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
@@ -5210,38 +9805,14 @@
       <c r="M8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
+      <c r="A9" s="17" t="n"/>
       <c r="B9" s="17" t="n"/>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeLessThan (float)</t>
-        </is>
-      </c>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
       <c r="E9" s="15" t="n"/>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>SELECT AVG(duration) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>mustBeLessOrEqualTo</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
       <c r="I9" s="15" t="n"/>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
@@ -5249,38 +9820,14 @@
       <c r="M9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
+      <c r="A10" s="17" t="n"/>
       <c r="B10" s="17" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>testscenario for mustBeBetween</t>
-        </is>
-      </c>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
       <c r="E10" s="15" t="n"/>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>SELECT AVG(*) FROM shipments</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>mustBeBetween</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>[25.0, 75.0]</t>
-        </is>
-      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
       <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
@@ -5288,26 +9835,10 @@
       <c r="M10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>shipments</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>inline_object_definition</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>{field} must contain the field "destination"</t>
-        </is>
-      </c>
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
       <c r="E11" s="15" t="n"/>
       <c r="F11" s="27" t="n"/>
       <c r="G11" s="15" t="n"/>
@@ -5505,906 +10036,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.6640625" customWidth="1" style="2" min="4" max="6"/>
-    <col width="8.83203125" customWidth="1" style="2" min="7" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Support and Communication Channels</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Support and communication channels help consumers find help regarding their use of the data contract.
-Support and communication channels help consumers find help regarding their use of the data contract.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Channel URL</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Tool</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Invitation URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>slackname</t>
-        </is>
-      </c>
-      <c r="B5" s="36" t="inlineStr">
-        <is>
-          <t>http://find.me.here</t>
-        </is>
-      </c>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
-        <is>
-          <t>slack</t>
-        </is>
-      </c>
-      <c r="E5" s="36" t="inlineStr">
-        <is>
-          <t>interactive</t>
-        </is>
-      </c>
-      <c r="F5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.6640625" customWidth="1" style="2" min="4" max="7"/>
-    <col width="8.83203125" customWidth="1" style="2" min="8" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract. In v2.x, this section was called stakeholders.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Username</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Date In</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Date Out</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>Replaced By Username</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>vimportant</t>
-        </is>
-      </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
-        <is>
-          <t>administrator</t>
-        </is>
-      </c>
-      <c r="E5" s="36" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>nimportant</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="inlineStr">
-        <is>
-          <t>reader</t>
-        </is>
-      </c>
-      <c r="E6" s="36" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="F6" s="36" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="G6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="34.6640625" customWidth="1" style="2" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="2" min="6" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Roles</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
-This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Access</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>1st Level Approvers</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>2nd Level Approvers</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="36" t="n"/>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" style="2" min="4" max="5"/>
-    <col width="34.6640625" customWidth="1" style="2" min="6" max="6"/>
-    <col width="8.83203125" customWidth="1" style="2" min="7" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Service-Level Agreement (SLA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This section describes the service-level agreements (SLA).
-This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>Default SLA element(s)</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Extended value</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="36" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,13 +26,21 @@
     <sheet name="_ServerFields" sheetId="18" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
+    <definedName name="_ServerFieldLabels">_ServerFields!$A$2:$A$24</definedName>
+    <definedName name="_ServerFieldMatrix">_ServerFields!$B$2:$AS$24</definedName>
+    <definedName name="_ServerTypes">_ServerFields!$B$1:$AS$1</definedName>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
+    <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$Z$1000</definedName>
+    <definedName name="constraints">Constraints!$A$4:$Z$1000</definedName>
+    <definedName name="context.instructions">Fundamentals!$C$25</definedName>
+    <definedName name="CustomProperties">'Custom Properties'!$A$4:$H$1000</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
     <definedName name="dataProduct">Fundamentals!$C$15</definedName>
     <definedName name="description.limitations">Fundamentals!$C$20</definedName>
     <definedName name="description.purpose">Fundamentals!$C$19</definedName>
     <definedName name="description.usage">Fundamentals!$C$21</definedName>
     <definedName name="domain">Fundamentals!$C$14</definedName>
+    <definedName name="enum">Enum!$A$4:$Z$1000</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
@@ -41,35 +49,21 @@
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
-    <definedName name="servers.description">Servers!$C$6</definedName>
-    <definedName name="servers.environment">Servers!$C$5</definedName>
-    <definedName name="servers.server">Servers!$C$4</definedName>
-    <definedName name="servers.type">Servers!$C$8</definedName>
-    <definedName name="slaDefaultElement">SLA!$B$4</definedName>
-    <definedName name="status">Fundamentals!$C$10</definedName>
-    <definedName name="tags">Fundamentals!$C$23</definedName>
-    <definedName name="tenant">Fundamentals!$C$16</definedName>
-    <definedName name="version">Fundamentals!$C$9</definedName>
-    <definedName name="templateVersion">Instructions!$B$29</definedName>
-    <definedName name="context.instructions">Fundamentals!$C$25</definedName>
-    <definedName name="support">Support!$A$4:$Z$1000</definedName>
     <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="team.name">Team!$B$4</definedName>
-    <definedName name="team.description">Team!$B$5</definedName>
-    <definedName name="team.tags">Team!$B$6</definedName>
-    <definedName name="team.id">Team!$B$7</definedName>
-    <definedName name="team">Team!$A$9:$Z$1000</definedName>
     <definedName name="servers.account">Servers!$C$11</definedName>
     <definedName name="servers.catalog">Servers!$C$12</definedName>
     <definedName name="servers.catalogUrl">Servers!$C$13</definedName>
     <definedName name="servers.database">Servers!$C$14</definedName>
     <definedName name="servers.dataset">Servers!$C$15</definedName>
     <definedName name="servers.delimiter">Servers!$C$16</definedName>
+    <definedName name="servers.description">Servers!$C$6</definedName>
     <definedName name="servers.encoding">Servers!$C$17</definedName>
     <definedName name="servers.endpointUrl">Servers!$C$18</definedName>
+    <definedName name="servers.environment">Servers!$C$5</definedName>
     <definedName name="servers.format">Servers!$C$19</definedName>
     <definedName name="servers.host">Servers!$C$20</definedName>
+    <definedName name="servers.id">Servers!$C$35</definedName>
     <definedName name="servers.location">Servers!$C$21</definedName>
     <definedName name="servers.namespace">Servers!$C$22</definedName>
     <definedName name="servers.path">Servers!$C$23</definedName>
@@ -78,33 +72,42 @@
     <definedName name="servers.region">Servers!$C$26</definedName>
     <definedName name="servers.regionName">Servers!$C$27</definedName>
     <definedName name="servers.schema">Servers!$C$28</definedName>
+    <definedName name="servers.server">Servers!$C$4</definedName>
     <definedName name="servers.serviceName">Servers!$C$29</definedName>
     <definedName name="servers.stagingDir">Servers!$C$30</definedName>
     <definedName name="servers.stream">Servers!$C$31</definedName>
+    <definedName name="servers.type">Servers!$C$8</definedName>
     <definedName name="servers.warehouse">Servers!$C$32</definedName>
     <definedName name="servers.workgroup">Servers!$C$33</definedName>
-    <definedName name="servers.id">Servers!$C$35</definedName>
-    <definedName name="CustomProperties">'Custom Properties'!$A$4:$H$1000</definedName>
-    <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$Z$1000</definedName>
-    <definedName name="enum">Enum!$A$4:$Z$1000</definedName>
+    <definedName name="slaDefaultElement">SLA!$B$4</definedName>
+    <definedName name="status">Fundamentals!$C$10</definedName>
+    <definedName name="support">Support!$A$4:$Z$1000</definedName>
     <definedName name="synonyms">Synonyms!$A$4:$Z$1000</definedName>
+    <definedName name="tags">Fundamentals!$C$23</definedName>
+    <definedName name="team">Team!$A$9:$Z$1000</definedName>
+    <definedName name="team.description">Team!$B$5</definedName>
+    <definedName name="team.id">Team!$B$7</definedName>
+    <definedName name="team.name">Team!$B$4</definedName>
+    <definedName name="team.tags">Team!$B$6</definedName>
+    <definedName name="templateVersion">Instructions!$B$29</definedName>
+    <definedName name="tenant">Fundamentals!$C$16</definedName>
     <definedName name="verifiedStatements">'Verified Statements'!$A$4:$Z$1000</definedName>
-    <definedName name="constraints">Constraints!$A$4:$Z$1000</definedName>
+    <definedName name="version">Fundamentals!$C$9</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema shipments'!$B$8</definedName>
+    <definedName name="schema.context.instructions" localSheetId="2">'Schema shipments'!$B$14</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema shipments'!$B$10</definedName>
+    <definedName name="schema.deprecated" localSheetId="2">'Schema shipments'!$B$13</definedName>
     <definedName name="schema.description" localSheetId="2">'Schema shipments'!$B$7</definedName>
+    <definedName name="schema.id" localSheetId="2">'Schema shipments'!$B$12</definedName>
     <definedName name="schema.name" localSheetId="2">'Schema shipments'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema shipments'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema shipments'!$B$6</definedName>
     <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$18:$AZ$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema shipments'!$B$11</definedName>
-    <definedName name="schema.id" localSheetId="2">'Schema shipments'!$B$12</definedName>
-    <definedName name="schema.deprecated" localSheetId="2">'Schema shipments'!$B$13</definedName>
-    <definedName name="schema.context.instructions" localSheetId="2">'Schema shipments'!$B$14</definedName>
     <definedName name="roles" localSheetId="11">Roles!$A$4:$Z$1000</definedName>
     <definedName name="slaProperties" localSheetId="12">SLA!$A$6:$Z$1002</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -163,7 +166,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -197,12 +200,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCBD5E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBEB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -391,9 +388,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -427,14 +421,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -453,16 +461,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF3F4F6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="00A6A6A6"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00EDEDED"/>
         </patternFill>
       </fill>
     </dxf>
@@ -808,10 +806,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="8.83203125" customWidth="1" style="3" min="2" max="16384"/>
+    <col width="8.85546875" customWidth="1" style="3" min="2" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -825,7 +823,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="15.95" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Use this Excel template to edit data contracts.</t>
@@ -836,14 +834,14 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="15.95" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="15.95" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Data Contract</t>
@@ -858,7 +856,7 @@
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="13" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="15.95" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">A data contract is a document that defines the structure, format, semantics, quality, and terms of use </t>
@@ -873,7 +871,7 @@
       <c r="H8" s="13" t="n"/>
       <c r="I8" s="13" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="15.95" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">for exchanging data between a data provider and their consumers. </t>
@@ -888,7 +886,7 @@
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="13" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="15.95" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>A data contract is usually defined in YAML, but you can use this Excel document for easier collaboration</t>
@@ -903,7 +901,7 @@
       <c r="H10" s="13" t="n"/>
       <c r="I10" s="13" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="15.95" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>with your stakeholders.</t>
@@ -918,7 +916,7 @@
       <c r="H11" s="13" t="n"/>
       <c r="I11" s="13" t="n"/>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" ht="15.95" customHeight="1">
       <c r="A12" s="13" t="n"/>
       <c r="B12" s="13" t="n"/>
       <c r="C12" s="13" t="n"/>
@@ -929,7 +927,7 @@
       <c r="H12" s="13" t="n"/>
       <c r="I12" s="13" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" ht="15.95" customHeight="1">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="13" t="n"/>
       <c r="C13" s="13" t="n"/>
@@ -940,7 +938,7 @@
       <c r="H13" s="13" t="n"/>
       <c r="I13" s="13" t="n"/>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" ht="15.95" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Instructions</t>
@@ -955,7 +953,7 @@
       <c r="H14" s="13" t="n"/>
       <c r="I14" s="13" t="n"/>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="15.95" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>1. Fill in the 'Fundamentals' sheet with basic contract information</t>
@@ -970,7 +968,7 @@
       <c r="H15" s="13" t="n"/>
       <c r="I15" s="13" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16" ht="15.95" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
           <t>2. For every table create a Sheet called "Schema &lt;tablename&gt;"</t>
@@ -985,7 +983,7 @@
       <c r="H16" s="13" t="n"/>
       <c r="I16" s="13" t="n"/>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="15.95" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">3. After completing the template, </t>
@@ -1000,7 +998,7 @@
       <c r="H17" s="13" t="n"/>
       <c r="I17" s="13" t="n"/>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" ht="15.95" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>a)</t>
@@ -1019,7 +1017,7 @@
       <c r="H18" s="13" t="n"/>
       <c r="I18" s="13" t="n"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" ht="15.95" customHeight="1">
       <c r="A19" s="23" t="n"/>
       <c r="B19" s="24" t="inlineStr">
         <is>
@@ -1034,7 +1032,7 @@
       <c r="H19" s="13" t="n"/>
       <c r="I19" s="13" t="n"/>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20" ht="15.95" customHeight="1">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="13" t="n"/>
@@ -1045,7 +1043,7 @@
       <c r="H20" s="13" t="n"/>
       <c r="I20" s="13" t="n"/>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="15.95" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
           <t>b)</t>
@@ -1064,7 +1062,7 @@
       <c r="H21" s="13" t="n"/>
       <c r="I21" s="13" t="n"/>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" ht="15.95" customHeight="1">
       <c r="A22" s="25" t="n"/>
       <c r="B22" s="13" t="inlineStr">
         <is>
@@ -1079,7 +1077,7 @@
       <c r="H22" s="13" t="n"/>
       <c r="I22" s="13" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23" ht="15.95" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -1094,7 +1092,7 @@
       <c r="H23" s="13" t="n"/>
       <c r="I23" s="13" t="n"/>
     </row>
-    <row r="24" ht="16" customHeight="1">
+    <row r="24" ht="15.95" customHeight="1">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="13" t="n"/>
       <c r="C24" s="13" t="n"/>
@@ -1105,7 +1103,7 @@
       <c r="H24" s="13" t="n"/>
       <c r="I24" s="13" t="n"/>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25" ht="15.95" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
@@ -1116,7 +1114,7 @@
       <c r="H25" s="13" t="n"/>
       <c r="I25" s="13" t="n"/>
     </row>
-    <row r="26" ht="16" customHeight="1">
+    <row r="26" ht="15.95" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Authors:</t>
@@ -1135,13 +1133,13 @@
       <c r="H26" s="13" t="n"/>
       <c r="I26" s="13" t="n"/>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27" ht="15.95" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Version:</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -1154,7 +1152,7 @@
       <c r="H27" s="13" t="n"/>
       <c r="I27" s="13" t="n"/>
     </row>
-    <row r="28" ht="16" customHeight="1">
+    <row r="28" ht="15.95" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
           <t>License:</t>
@@ -1173,7 +1171,7 @@
       <c r="H28" s="13" t="n"/>
       <c r="I28" s="13" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" ht="15.95" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Template Version:</t>
@@ -1190,7 +1188,7 @@
       <c r="H29" s="13" t="n"/>
       <c r="I29" s="13" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30" ht="15.95" customHeight="1">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="13" t="n"/>
       <c r="C30" s="13" t="n"/>
@@ -1201,7 +1199,7 @@
       <c r="H30" s="13" t="n"/>
       <c r="I30" s="13" t="n"/>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="15.95" customHeight="1">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="13" t="n"/>
       <c r="C31" s="13" t="n"/>
@@ -1225,14 +1223,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.6640625" customWidth="1" style="2" min="4" max="6"/>
-    <col width="22" customWidth="1" style="2" min="7" max="16384"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.7109375" customWidth="1" style="2" min="4" max="6"/>
+    <col width="28.5703125" customWidth="1" style="2" min="7" max="9"/>
+    <col width="8.85546875" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1250,7 +1247,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Channel</t>
@@ -1298,28 +1295,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>slackname</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>http://find.me.here</t>
         </is>
       </c>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="C5" s="35" t="n"/>
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>slack</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>interactive</t>
         </is>
       </c>
-      <c r="F5" s="36" t="n"/>
+      <c r="F5" s="35" t="n"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>sup-slack</t>
@@ -1337,132 +1334,132 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
+      <c r="A6" s="35" t="n"/>
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1479,14 +1476,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="3"/>
-    <col width="23.6640625" customWidth="1" style="2" min="4" max="7"/>
-    <col width="22" customWidth="1" style="2" min="8" max="16384"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
+    <col width="23.7109375" customWidth="1" style="2" min="4" max="7"/>
+    <col width="28.5703125" customWidth="1" style="2" min="8" max="10"/>
+    <col width="8.85546875" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1504,55 +1500,55 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Team Name</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Fulfillment Data Team</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Team Description</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Owns the shipment data product</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Team Tags</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Team ID</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>team-fulfillment</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Username</t>
@@ -1605,25 +1601,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>vimportant</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>administrator</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>tm-vi</t>
@@ -1639,164 +1635,164 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>nimportant</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>reader</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="F11" s="36" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>2024-10-10</t>
         </is>
       </c>
-      <c r="G11" s="36" t="n"/>
+      <c r="G11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
+      <c r="A22" s="35" t="n"/>
+      <c r="B22" s="35" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-      <c r="G23" s="36" t="n"/>
+      <c r="A23" s="35" t="n"/>
+      <c r="B23" s="35" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
+      <c r="A24" s="35" t="n"/>
+      <c r="B24" s="35" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="n"/>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
+      <c r="A25" s="35" t="n"/>
+      <c r="B25" s="35" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
+      <c r="A26" s="35" t="n"/>
+      <c r="B26" s="35" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1813,16 +1809,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="34.6640625" customWidth="1" style="2" min="5" max="5"/>
-    <col width="22" customWidth="1" style="2" min="6" max="16384"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.85546875" customWidth="1" style="2" min="4" max="4"/>
+    <col width="34.7109375" customWidth="1" style="2" min="5" max="5"/>
+    <col width="28.5703125" customWidth="1" style="2" min="6" max="8"/>
+    <col width="8.85546875" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1841,7 +1836,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Role</t>
@@ -1884,27 +1879,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>analyst</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Read access for analysts</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>data-owner</t>
         </is>
       </c>
-      <c r="E5" s="36" t="n"/>
+      <c r="E5" s="35" t="n"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>role-analyst</t>
@@ -1922,116 +1917,116 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n"/>
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
+      <c r="A6" s="35" t="n"/>
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2048,16 +2043,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="33.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="59.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="39.33203125" customWidth="1" style="2" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" style="2" min="4" max="5"/>
-    <col width="34.6640625" customWidth="1" style="2" min="6" max="6"/>
-    <col width="22" customWidth="1" style="2" min="7" max="16384"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="59.7109375" customWidth="1" style="2" min="2" max="2"/>
+    <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
+    <col width="32.85546875" customWidth="1" style="2" min="4" max="5"/>
+    <col width="34.7109375" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.5703125" customWidth="1" style="2" min="7" max="9"/>
+    <col width="8.85546875" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2080,7 +2074,7 @@
       <c r="A3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Default SLA element(s)</t>
         </is>
@@ -2091,7 +2085,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Property</t>
@@ -2139,24 +2133,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="inlineStr">
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
@@ -2178,132 +2172,132 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
+      <c r="A22" s="35" t="n"/>
+      <c r="B22" s="35" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
+      <c r="A23" s="35" t="n"/>
+      <c r="B23" s="35" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -2321,15 +2315,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="6.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="33.1640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="36.1640625" customWidth="1" style="2" min="3" max="6"/>
+    <col width="6.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="33.140625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="36.140625" customWidth="1" style="2" min="3" max="6"/>
     <col width="15" customWidth="1" style="2" min="7" max="22"/>
-    <col width="32.83203125" customWidth="1" style="2" min="23" max="30"/>
-    <col width="34.6640625" customWidth="1" style="2" min="31" max="31"/>
-    <col width="8.83203125" customWidth="1" style="2" min="32" max="16384"/>
+    <col width="32.85546875" customWidth="1" style="2" min="23" max="30"/>
+    <col width="34.7109375" customWidth="1" style="2" min="31" max="31"/>
+    <col width="8.85546875" customWidth="1" style="2" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2350,965 +2344,1014 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Server</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>lakehouse</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="F4" s="36" t="n"/>
+      <c r="F4" s="35" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>dev</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="F5" s="36" t="n"/>
+      <c r="F5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n"/>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Production dataset</t>
         </is>
       </c>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="n"/>
-      <c r="B7" s="34" t="n"/>
+      <c r="A7" s="33" t="n"/>
+      <c r="B7" s="33" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>bigquery</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>trino</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>kafka</t>
         </is>
       </c>
-      <c r="F8" s="36" t="n"/>
+      <c r="F8" s="35" t="n"/>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Connection</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="n"/>
-      <c r="K11" s="36" t="n"/>
-      <c r="L11" s="36" t="n"/>
-      <c r="M11" s="36" t="n"/>
-      <c r="N11" s="36" t="n"/>
-      <c r="O11" s="36" t="n"/>
-      <c r="P11" s="36" t="n"/>
-      <c r="Q11" s="36" t="n"/>
-      <c r="R11" s="36" t="n"/>
-      <c r="S11" s="36" t="n"/>
-      <c r="T11" s="36" t="n"/>
-      <c r="U11" s="36" t="n"/>
-      <c r="V11" s="36" t="n"/>
-      <c r="W11" s="36" t="n"/>
-      <c r="X11" s="36" t="n"/>
-      <c r="Y11" s="36" t="n"/>
-      <c r="Z11" s="36" t="n"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+      <c r="K11" s="35" t="n"/>
+      <c r="L11" s="35" t="n"/>
+      <c r="M11" s="35" t="n"/>
+      <c r="N11" s="35" t="n"/>
+      <c r="O11" s="35" t="n"/>
+      <c r="P11" s="35" t="n"/>
+      <c r="Q11" s="35" t="n"/>
+      <c r="R11" s="35" t="n"/>
+      <c r="S11" s="35" t="n"/>
+      <c r="T11" s="35" t="n"/>
+      <c r="U11" s="35" t="n"/>
+      <c r="V11" s="35" t="n"/>
+      <c r="W11" s="35" t="n"/>
+      <c r="X11" s="35" t="n"/>
+      <c r="Y11" s="35" t="n"/>
+      <c r="Z11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Catalog</t>
         </is>
       </c>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>iceberg</t>
         </is>
       </c>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="36" t="n"/>
-      <c r="K12" s="36" t="n"/>
-      <c r="L12" s="36" t="n"/>
-      <c r="M12" s="36" t="n"/>
-      <c r="N12" s="36" t="n"/>
-      <c r="O12" s="36" t="n"/>
-      <c r="P12" s="36" t="n"/>
-      <c r="Q12" s="36" t="n"/>
-      <c r="R12" s="36" t="n"/>
-      <c r="S12" s="36" t="n"/>
-      <c r="T12" s="36" t="n"/>
-      <c r="U12" s="36" t="n"/>
-      <c r="V12" s="36" t="n"/>
-      <c r="W12" s="36" t="n"/>
-      <c r="X12" s="36" t="n"/>
-      <c r="Y12" s="36" t="n"/>
-      <c r="Z12" s="36" t="n"/>
-    </row>
-    <row r="13">
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="35" t="n"/>
+      <c r="L12" s="35" t="n"/>
+      <c r="M12" s="35" t="n"/>
+      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="35" t="n"/>
+      <c r="P12" s="35" t="n"/>
+      <c r="Q12" s="35" t="n"/>
+      <c r="R12" s="35" t="n"/>
+      <c r="S12" s="35" t="n"/>
+      <c r="T12" s="35" t="n"/>
+      <c r="U12" s="35" t="n"/>
+      <c r="V12" s="35" t="n"/>
+      <c r="W12" s="35" t="n"/>
+      <c r="X12" s="35" t="n"/>
+      <c r="Y12" s="35" t="n"/>
+      <c r="Z12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Catalog URL</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-      <c r="I13" s="36" t="n"/>
-      <c r="J13" s="36" t="n"/>
-      <c r="K13" s="36" t="n"/>
-      <c r="L13" s="36" t="n"/>
-      <c r="M13" s="36" t="n"/>
-      <c r="N13" s="36" t="n"/>
-      <c r="O13" s="36" t="n"/>
-      <c r="P13" s="36" t="n"/>
-      <c r="Q13" s="36" t="n"/>
-      <c r="R13" s="36" t="n"/>
-      <c r="S13" s="36" t="n"/>
-      <c r="T13" s="36" t="n"/>
-      <c r="U13" s="36" t="n"/>
-      <c r="V13" s="36" t="n"/>
-      <c r="W13" s="36" t="n"/>
-      <c r="X13" s="36" t="n"/>
-      <c r="Y13" s="36" t="n"/>
-      <c r="Z13" s="36" t="n"/>
-    </row>
-    <row r="14">
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="35" t="n"/>
+      <c r="K13" s="35" t="n"/>
+      <c r="L13" s="35" t="n"/>
+      <c r="M13" s="35" t="n"/>
+      <c r="N13" s="35" t="n"/>
+      <c r="O13" s="35" t="n"/>
+      <c r="P13" s="35" t="n"/>
+      <c r="Q13" s="35" t="n"/>
+      <c r="R13" s="35" t="n"/>
+      <c r="S13" s="35" t="n"/>
+      <c r="T13" s="35" t="n"/>
+      <c r="U13" s="35" t="n"/>
+      <c r="V13" s="35" t="n"/>
+      <c r="W13" s="35" t="n"/>
+      <c r="X13" s="35" t="n"/>
+      <c r="Y13" s="35" t="n"/>
+      <c r="Z13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-      <c r="I14" s="36" t="n"/>
-      <c r="J14" s="36" t="n"/>
-      <c r="K14" s="36" t="n"/>
-      <c r="L14" s="36" t="n"/>
-      <c r="M14" s="36" t="n"/>
-      <c r="N14" s="36" t="n"/>
-      <c r="O14" s="36" t="n"/>
-      <c r="P14" s="36" t="n"/>
-      <c r="Q14" s="36" t="n"/>
-      <c r="R14" s="36" t="n"/>
-      <c r="S14" s="36" t="n"/>
-      <c r="T14" s="36" t="n"/>
-      <c r="U14" s="36" t="n"/>
-      <c r="V14" s="36" t="n"/>
-      <c r="W14" s="36" t="n"/>
-      <c r="X14" s="36" t="n"/>
-      <c r="Y14" s="36" t="n"/>
-      <c r="Z14" s="36" t="n"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="35" t="n"/>
+      <c r="K14" s="35" t="n"/>
+      <c r="L14" s="35" t="n"/>
+      <c r="M14" s="35" t="n"/>
+      <c r="N14" s="35" t="n"/>
+      <c r="O14" s="35" t="n"/>
+      <c r="P14" s="35" t="n"/>
+      <c r="Q14" s="35" t="n"/>
+      <c r="R14" s="35" t="n"/>
+      <c r="S14" s="35" t="n"/>
+      <c r="T14" s="35" t="n"/>
+      <c r="U14" s="35" t="n"/>
+      <c r="V14" s="35" t="n"/>
+      <c r="W14" s="35" t="n"/>
+      <c r="X14" s="35" t="n"/>
+      <c r="Y14" s="35" t="n"/>
+      <c r="Z14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>shipments_v1</t>
         </is>
       </c>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="36" t="n"/>
-      <c r="K15" s="36" t="n"/>
-      <c r="L15" s="36" t="n"/>
-      <c r="M15" s="36" t="n"/>
-      <c r="N15" s="36" t="n"/>
-      <c r="O15" s="36" t="n"/>
-      <c r="P15" s="36" t="n"/>
-      <c r="Q15" s="36" t="n"/>
-      <c r="R15" s="36" t="n"/>
-      <c r="S15" s="36" t="n"/>
-      <c r="T15" s="36" t="n"/>
-      <c r="U15" s="36" t="n"/>
-      <c r="V15" s="36" t="n"/>
-      <c r="W15" s="36" t="n"/>
-      <c r="X15" s="36" t="n"/>
-      <c r="Y15" s="36" t="n"/>
-      <c r="Z15" s="36" t="n"/>
-    </row>
-    <row r="16">
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="35" t="n"/>
+      <c r="M15" s="35" t="n"/>
+      <c r="N15" s="35" t="n"/>
+      <c r="O15" s="35" t="n"/>
+      <c r="P15" s="35" t="n"/>
+      <c r="Q15" s="35" t="n"/>
+      <c r="R15" s="35" t="n"/>
+      <c r="S15" s="35" t="n"/>
+      <c r="T15" s="35" t="n"/>
+      <c r="U15" s="35" t="n"/>
+      <c r="V15" s="35" t="n"/>
+      <c r="W15" s="35" t="n"/>
+      <c r="X15" s="35" t="n"/>
+      <c r="Y15" s="35" t="n"/>
+      <c r="Z15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Delimiter</t>
         </is>
       </c>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
-      <c r="J16" s="36" t="n"/>
-      <c r="K16" s="36" t="n"/>
-      <c r="L16" s="36" t="n"/>
-      <c r="M16" s="36" t="n"/>
-      <c r="N16" s="36" t="n"/>
-      <c r="O16" s="36" t="n"/>
-      <c r="P16" s="36" t="n"/>
-      <c r="Q16" s="36" t="n"/>
-      <c r="R16" s="36" t="n"/>
-      <c r="S16" s="36" t="n"/>
-      <c r="T16" s="36" t="n"/>
-      <c r="U16" s="36" t="n"/>
-      <c r="V16" s="36" t="n"/>
-      <c r="W16" s="36" t="n"/>
-      <c r="X16" s="36" t="n"/>
-      <c r="Y16" s="36" t="n"/>
-      <c r="Z16" s="36" t="n"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="35" t="n"/>
+      <c r="O16" s="35" t="n"/>
+      <c r="P16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="35" t="n"/>
+      <c r="T16" s="35" t="n"/>
+      <c r="U16" s="35" t="n"/>
+      <c r="V16" s="35" t="n"/>
+      <c r="W16" s="35" t="n"/>
+      <c r="X16" s="35" t="n"/>
+      <c r="Y16" s="35" t="n"/>
+      <c r="Z16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Encoding</t>
         </is>
       </c>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="36" t="n"/>
-      <c r="K17" s="36" t="n"/>
-      <c r="L17" s="36" t="n"/>
-      <c r="M17" s="36" t="n"/>
-      <c r="N17" s="36" t="n"/>
-      <c r="O17" s="36" t="n"/>
-      <c r="P17" s="36" t="n"/>
-      <c r="Q17" s="36" t="n"/>
-      <c r="R17" s="36" t="n"/>
-      <c r="S17" s="36" t="n"/>
-      <c r="T17" s="36" t="n"/>
-      <c r="U17" s="36" t="n"/>
-      <c r="V17" s="36" t="n"/>
-      <c r="W17" s="36" t="n"/>
-      <c r="X17" s="36" t="n"/>
-      <c r="Y17" s="36" t="n"/>
-      <c r="Z17" s="36" t="n"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="35" t="n"/>
+      <c r="L17" s="35" t="n"/>
+      <c r="M17" s="35" t="n"/>
+      <c r="N17" s="35" t="n"/>
+      <c r="O17" s="35" t="n"/>
+      <c r="P17" s="35" t="n"/>
+      <c r="Q17" s="35" t="n"/>
+      <c r="R17" s="35" t="n"/>
+      <c r="S17" s="35" t="n"/>
+      <c r="T17" s="35" t="n"/>
+      <c r="U17" s="35" t="n"/>
+      <c r="V17" s="35" t="n"/>
+      <c r="W17" s="35" t="n"/>
+      <c r="X17" s="35" t="n"/>
+      <c r="Y17" s="35" t="n"/>
+      <c r="Z17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Endpoint URL</t>
         </is>
       </c>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="36" t="n"/>
-      <c r="K18" s="36" t="n"/>
-      <c r="L18" s="36" t="n"/>
-      <c r="M18" s="36" t="n"/>
-      <c r="N18" s="36" t="n"/>
-      <c r="O18" s="36" t="n"/>
-      <c r="P18" s="36" t="n"/>
-      <c r="Q18" s="36" t="n"/>
-      <c r="R18" s="36" t="n"/>
-      <c r="S18" s="36" t="n"/>
-      <c r="T18" s="36" t="n"/>
-      <c r="U18" s="36" t="n"/>
-      <c r="V18" s="36" t="n"/>
-      <c r="W18" s="36" t="n"/>
-      <c r="X18" s="36" t="n"/>
-      <c r="Y18" s="36" t="n"/>
-      <c r="Z18" s="36" t="n"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="35" t="n"/>
+      <c r="K18" s="35" t="n"/>
+      <c r="L18" s="35" t="n"/>
+      <c r="M18" s="35" t="n"/>
+      <c r="N18" s="35" t="n"/>
+      <c r="O18" s="35" t="n"/>
+      <c r="P18" s="35" t="n"/>
+      <c r="Q18" s="35" t="n"/>
+      <c r="R18" s="35" t="n"/>
+      <c r="S18" s="35" t="n"/>
+      <c r="T18" s="35" t="n"/>
+      <c r="U18" s="35" t="n"/>
+      <c r="V18" s="35" t="n"/>
+      <c r="W18" s="35" t="n"/>
+      <c r="X18" s="35" t="n"/>
+      <c r="Y18" s="35" t="n"/>
+      <c r="Z18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>avro</t>
         </is>
       </c>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
-      <c r="K19" s="36" t="n"/>
-      <c r="L19" s="36" t="n"/>
-      <c r="M19" s="36" t="n"/>
-      <c r="N19" s="36" t="n"/>
-      <c r="O19" s="36" t="n"/>
-      <c r="P19" s="36" t="n"/>
-      <c r="Q19" s="36" t="n"/>
-      <c r="R19" s="36" t="n"/>
-      <c r="S19" s="36" t="n"/>
-      <c r="T19" s="36" t="n"/>
-      <c r="U19" s="36" t="n"/>
-      <c r="V19" s="36" t="n"/>
-      <c r="W19" s="36" t="n"/>
-      <c r="X19" s="36" t="n"/>
-      <c r="Y19" s="36" t="n"/>
-      <c r="Z19" s="36" t="n"/>
-    </row>
-    <row r="20">
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+      <c r="I19" s="35" t="n"/>
+      <c r="J19" s="35" t="n"/>
+      <c r="K19" s="35" t="n"/>
+      <c r="L19" s="35" t="n"/>
+      <c r="M19" s="35" t="n"/>
+      <c r="N19" s="35" t="n"/>
+      <c r="O19" s="35" t="n"/>
+      <c r="P19" s="35" t="n"/>
+      <c r="Q19" s="35" t="n"/>
+      <c r="R19" s="35" t="n"/>
+      <c r="S19" s="35" t="n"/>
+      <c r="T19" s="35" t="n"/>
+      <c r="U19" s="35" t="n"/>
+      <c r="V19" s="35" t="n"/>
+      <c r="W19" s="35" t="n"/>
+      <c r="X19" s="35" t="n"/>
+      <c r="Y19" s="35" t="n"/>
+      <c r="Z19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Host</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>trino.example.com</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>kafka.example.com:9092</t>
         </is>
       </c>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="36" t="n"/>
-      <c r="P20" s="36" t="n"/>
-      <c r="Q20" s="36" t="n"/>
-      <c r="R20" s="36" t="n"/>
-      <c r="S20" s="36" t="n"/>
-      <c r="T20" s="36" t="n"/>
-      <c r="U20" s="36" t="n"/>
-      <c r="V20" s="36" t="n"/>
-      <c r="W20" s="36" t="n"/>
-      <c r="X20" s="36" t="n"/>
-      <c r="Y20" s="36" t="n"/>
-      <c r="Z20" s="36" t="n"/>
-    </row>
-    <row r="21">
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" s="35" t="n"/>
+      <c r="K20" s="35" t="n"/>
+      <c r="L20" s="35" t="n"/>
+      <c r="M20" s="35" t="n"/>
+      <c r="N20" s="35" t="n"/>
+      <c r="O20" s="35" t="n"/>
+      <c r="P20" s="35" t="n"/>
+      <c r="Q20" s="35" t="n"/>
+      <c r="R20" s="35" t="n"/>
+      <c r="S20" s="35" t="n"/>
+      <c r="T20" s="35" t="n"/>
+      <c r="U20" s="35" t="n"/>
+      <c r="V20" s="35" t="n"/>
+      <c r="W20" s="35" t="n"/>
+      <c r="X20" s="35" t="n"/>
+      <c r="Y20" s="35" t="n"/>
+      <c r="Z20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
-      <c r="K21" s="36" t="n"/>
-      <c r="L21" s="36" t="n"/>
-      <c r="M21" s="36" t="n"/>
-      <c r="N21" s="36" t="n"/>
-      <c r="O21" s="36" t="n"/>
-      <c r="P21" s="36" t="n"/>
-      <c r="Q21" s="36" t="n"/>
-      <c r="R21" s="36" t="n"/>
-      <c r="S21" s="36" t="n"/>
-      <c r="T21" s="36" t="n"/>
-      <c r="U21" s="36" t="n"/>
-      <c r="V21" s="36" t="n"/>
-      <c r="W21" s="36" t="n"/>
-      <c r="X21" s="36" t="n"/>
-      <c r="Y21" s="36" t="n"/>
-      <c r="Z21" s="36" t="n"/>
-    </row>
-    <row r="22">
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="35" t="n"/>
+      <c r="K21" s="35" t="n"/>
+      <c r="L21" s="35" t="n"/>
+      <c r="M21" s="35" t="n"/>
+      <c r="N21" s="35" t="n"/>
+      <c r="O21" s="35" t="n"/>
+      <c r="P21" s="35" t="n"/>
+      <c r="Q21" s="35" t="n"/>
+      <c r="R21" s="35" t="n"/>
+      <c r="S21" s="35" t="n"/>
+      <c r="T21" s="35" t="n"/>
+      <c r="U21" s="35" t="n"/>
+      <c r="V21" s="35" t="n"/>
+      <c r="W21" s="35" t="n"/>
+      <c r="X21" s="35" t="n"/>
+      <c r="Y21" s="35" t="n"/>
+      <c r="Z21" s="35" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Namespace</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="36" t="n"/>
-      <c r="O22" s="36" t="n"/>
-      <c r="P22" s="36" t="n"/>
-      <c r="Q22" s="36" t="n"/>
-      <c r="R22" s="36" t="n"/>
-      <c r="S22" s="36" t="n"/>
-      <c r="T22" s="36" t="n"/>
-      <c r="U22" s="36" t="n"/>
-      <c r="V22" s="36" t="n"/>
-      <c r="W22" s="36" t="n"/>
-      <c r="X22" s="36" t="n"/>
-      <c r="Y22" s="36" t="n"/>
-      <c r="Z22" s="36" t="n"/>
-    </row>
-    <row r="23">
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+      <c r="I22" s="35" t="n"/>
+      <c r="J22" s="35" t="n"/>
+      <c r="K22" s="35" t="n"/>
+      <c r="L22" s="35" t="n"/>
+      <c r="M22" s="35" t="n"/>
+      <c r="N22" s="35" t="n"/>
+      <c r="O22" s="35" t="n"/>
+      <c r="P22" s="35" t="n"/>
+      <c r="Q22" s="35" t="n"/>
+      <c r="R22" s="35" t="n"/>
+      <c r="S22" s="35" t="n"/>
+      <c r="T22" s="35" t="n"/>
+      <c r="U22" s="35" t="n"/>
+      <c r="V22" s="35" t="n"/>
+      <c r="W22" s="35" t="n"/>
+      <c r="X22" s="35" t="n"/>
+      <c r="Y22" s="35" t="n"/>
+      <c r="Z22" s="35" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
-      <c r="F23" s="36" t="n"/>
-      <c r="G23" s="36" t="n"/>
-      <c r="H23" s="36" t="n"/>
-      <c r="I23" s="36" t="n"/>
-      <c r="J23" s="36" t="n"/>
-      <c r="K23" s="36" t="n"/>
-      <c r="L23" s="36" t="n"/>
-      <c r="M23" s="36" t="n"/>
-      <c r="N23" s="36" t="n"/>
-      <c r="O23" s="36" t="n"/>
-      <c r="P23" s="36" t="n"/>
-      <c r="Q23" s="36" t="n"/>
-      <c r="R23" s="36" t="n"/>
-      <c r="S23" s="36" t="n"/>
-      <c r="T23" s="36" t="n"/>
-      <c r="U23" s="36" t="n"/>
-      <c r="V23" s="36" t="n"/>
-      <c r="W23" s="36" t="n"/>
-      <c r="X23" s="36" t="n"/>
-      <c r="Y23" s="36" t="n"/>
-      <c r="Z23" s="36" t="n"/>
-    </row>
-    <row r="24">
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="35" t="n"/>
+      <c r="J23" s="35" t="n"/>
+      <c r="K23" s="35" t="n"/>
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="35" t="n"/>
+      <c r="N23" s="35" t="n"/>
+      <c r="O23" s="35" t="n"/>
+      <c r="P23" s="35" t="n"/>
+      <c r="Q23" s="35" t="n"/>
+      <c r="R23" s="35" t="n"/>
+      <c r="S23" s="35" t="n"/>
+      <c r="T23" s="35" t="n"/>
+      <c r="U23" s="35" t="n"/>
+      <c r="V23" s="35" t="n"/>
+      <c r="W23" s="35" t="n"/>
+      <c r="X23" s="35" t="n"/>
+      <c r="Y23" s="35" t="n"/>
+      <c r="Z23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Port</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>${TRINO_PORT}</t>
         </is>
       </c>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="36" t="n"/>
-      <c r="O24" s="36" t="n"/>
-      <c r="P24" s="36" t="n"/>
-      <c r="Q24" s="36" t="n"/>
-      <c r="R24" s="36" t="n"/>
-      <c r="S24" s="36" t="n"/>
-      <c r="T24" s="36" t="n"/>
-      <c r="U24" s="36" t="n"/>
-      <c r="V24" s="36" t="n"/>
-      <c r="W24" s="36" t="n"/>
-      <c r="X24" s="36" t="n"/>
-      <c r="Y24" s="36" t="n"/>
-      <c r="Z24" s="36" t="n"/>
-    </row>
-    <row r="25">
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="35" t="n"/>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="35" t="n"/>
+      <c r="N24" s="35" t="n"/>
+      <c r="O24" s="35" t="n"/>
+      <c r="P24" s="35" t="n"/>
+      <c r="Q24" s="35" t="n"/>
+      <c r="R24" s="35" t="n"/>
+      <c r="S24" s="35" t="n"/>
+      <c r="T24" s="35" t="n"/>
+      <c r="U24" s="35" t="n"/>
+      <c r="V24" s="35" t="n"/>
+      <c r="W24" s="35" t="n"/>
+      <c r="X24" s="35" t="n"/>
+      <c r="Y24" s="35" t="n"/>
+      <c r="Z24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>acme_shipments_prod</t>
         </is>
       </c>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
-      <c r="H25" s="36" t="n"/>
-      <c r="I25" s="36" t="n"/>
-      <c r="J25" s="36" t="n"/>
-      <c r="K25" s="36" t="n"/>
-      <c r="L25" s="36" t="n"/>
-      <c r="M25" s="36" t="n"/>
-      <c r="N25" s="36" t="n"/>
-      <c r="O25" s="36" t="n"/>
-      <c r="P25" s="36" t="n"/>
-      <c r="Q25" s="36" t="n"/>
-      <c r="R25" s="36" t="n"/>
-      <c r="S25" s="36" t="n"/>
-      <c r="T25" s="36" t="n"/>
-      <c r="U25" s="36" t="n"/>
-      <c r="V25" s="36" t="n"/>
-      <c r="W25" s="36" t="n"/>
-      <c r="X25" s="36" t="n"/>
-      <c r="Y25" s="36" t="n"/>
-      <c r="Z25" s="36" t="n"/>
-    </row>
-    <row r="26">
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="35" t="n"/>
+      <c r="J25" s="35" t="n"/>
+      <c r="K25" s="35" t="n"/>
+      <c r="L25" s="35" t="n"/>
+      <c r="M25" s="35" t="n"/>
+      <c r="N25" s="35" t="n"/>
+      <c r="O25" s="35" t="n"/>
+      <c r="P25" s="35" t="n"/>
+      <c r="Q25" s="35" t="n"/>
+      <c r="R25" s="35" t="n"/>
+      <c r="S25" s="35" t="n"/>
+      <c r="T25" s="35" t="n"/>
+      <c r="U25" s="35" t="n"/>
+      <c r="V25" s="35" t="n"/>
+      <c r="W25" s="35" t="n"/>
+      <c r="X25" s="35" t="n"/>
+      <c r="Y25" s="35" t="n"/>
+      <c r="Z25" s="35" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="36" t="n"/>
-      <c r="M26" s="36" t="n"/>
-      <c r="N26" s="36" t="n"/>
-      <c r="O26" s="36" t="n"/>
-      <c r="P26" s="36" t="n"/>
-      <c r="Q26" s="36" t="n"/>
-      <c r="R26" s="36" t="n"/>
-      <c r="S26" s="36" t="n"/>
-      <c r="T26" s="36" t="n"/>
-      <c r="U26" s="36" t="n"/>
-      <c r="V26" s="36" t="n"/>
-      <c r="W26" s="36" t="n"/>
-      <c r="X26" s="36" t="n"/>
-      <c r="Y26" s="36" t="n"/>
-      <c r="Z26" s="36" t="n"/>
-    </row>
-    <row r="27">
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="35" t="n"/>
+      <c r="K26" s="35" t="n"/>
+      <c r="L26" s="35" t="n"/>
+      <c r="M26" s="35" t="n"/>
+      <c r="N26" s="35" t="n"/>
+      <c r="O26" s="35" t="n"/>
+      <c r="P26" s="35" t="n"/>
+      <c r="Q26" s="35" t="n"/>
+      <c r="R26" s="35" t="n"/>
+      <c r="S26" s="35" t="n"/>
+      <c r="T26" s="35" t="n"/>
+      <c r="U26" s="35" t="n"/>
+      <c r="V26" s="35" t="n"/>
+      <c r="W26" s="35" t="n"/>
+      <c r="X26" s="35" t="n"/>
+      <c r="Y26" s="35" t="n"/>
+      <c r="Z26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Region Name</t>
         </is>
       </c>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="36" t="n"/>
-      <c r="E27" s="36" t="n"/>
-      <c r="F27" s="36" t="n"/>
-      <c r="G27" s="36" t="n"/>
-      <c r="H27" s="36" t="n"/>
-      <c r="I27" s="36" t="n"/>
-      <c r="J27" s="36" t="n"/>
-      <c r="K27" s="36" t="n"/>
-      <c r="L27" s="36" t="n"/>
-      <c r="M27" s="36" t="n"/>
-      <c r="N27" s="36" t="n"/>
-      <c r="O27" s="36" t="n"/>
-      <c r="P27" s="36" t="n"/>
-      <c r="Q27" s="36" t="n"/>
-      <c r="R27" s="36" t="n"/>
-      <c r="S27" s="36" t="n"/>
-      <c r="T27" s="36" t="n"/>
-      <c r="U27" s="36" t="n"/>
-      <c r="V27" s="36" t="n"/>
-      <c r="W27" s="36" t="n"/>
-      <c r="X27" s="36" t="n"/>
-      <c r="Y27" s="36" t="n"/>
-      <c r="Z27" s="36" t="n"/>
-    </row>
-    <row r="28">
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="35" t="n"/>
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="35" t="n"/>
+      <c r="L27" s="35" t="n"/>
+      <c r="M27" s="35" t="n"/>
+      <c r="N27" s="35" t="n"/>
+      <c r="O27" s="35" t="n"/>
+      <c r="P27" s="35" t="n"/>
+      <c r="Q27" s="35" t="n"/>
+      <c r="R27" s="35" t="n"/>
+      <c r="S27" s="35" t="n"/>
+      <c r="T27" s="35" t="n"/>
+      <c r="U27" s="35" t="n"/>
+      <c r="V27" s="35" t="n"/>
+      <c r="W27" s="35" t="n"/>
+      <c r="X27" s="35" t="n"/>
+      <c r="Y27" s="35" t="n"/>
+      <c r="Z27" s="35" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="36" t="n"/>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="36" t="n"/>
-      <c r="O28" s="36" t="n"/>
-      <c r="P28" s="36" t="n"/>
-      <c r="Q28" s="36" t="n"/>
-      <c r="R28" s="36" t="n"/>
-      <c r="S28" s="36" t="n"/>
-      <c r="T28" s="36" t="n"/>
-      <c r="U28" s="36" t="n"/>
-      <c r="V28" s="36" t="n"/>
-      <c r="W28" s="36" t="n"/>
-      <c r="X28" s="36" t="n"/>
-      <c r="Y28" s="36" t="n"/>
-      <c r="Z28" s="36" t="n"/>
-    </row>
-    <row r="29">
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="35" t="n"/>
+      <c r="I28" s="35" t="n"/>
+      <c r="J28" s="35" t="n"/>
+      <c r="K28" s="35" t="n"/>
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="35" t="n"/>
+      <c r="N28" s="35" t="n"/>
+      <c r="O28" s="35" t="n"/>
+      <c r="P28" s="35" t="n"/>
+      <c r="Q28" s="35" t="n"/>
+      <c r="R28" s="35" t="n"/>
+      <c r="S28" s="35" t="n"/>
+      <c r="T28" s="35" t="n"/>
+      <c r="U28" s="35" t="n"/>
+      <c r="V28" s="35" t="n"/>
+      <c r="W28" s="35" t="n"/>
+      <c r="X28" s="35" t="n"/>
+      <c r="Y28" s="35" t="n"/>
+      <c r="Z28" s="35" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Service Name</t>
         </is>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="36" t="n"/>
-      <c r="K29" s="36" t="n"/>
-      <c r="L29" s="36" t="n"/>
-      <c r="M29" s="36" t="n"/>
-      <c r="N29" s="36" t="n"/>
-      <c r="O29" s="36" t="n"/>
-      <c r="P29" s="36" t="n"/>
-      <c r="Q29" s="36" t="n"/>
-      <c r="R29" s="36" t="n"/>
-      <c r="S29" s="36" t="n"/>
-      <c r="T29" s="36" t="n"/>
-      <c r="U29" s="36" t="n"/>
-      <c r="V29" s="36" t="n"/>
-      <c r="W29" s="36" t="n"/>
-      <c r="X29" s="36" t="n"/>
-      <c r="Y29" s="36" t="n"/>
-      <c r="Z29" s="36" t="n"/>
-    </row>
-    <row r="30">
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="35" t="n"/>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="35" t="n"/>
+      <c r="G29" s="35" t="n"/>
+      <c r="H29" s="35" t="n"/>
+      <c r="I29" s="35" t="n"/>
+      <c r="J29" s="35" t="n"/>
+      <c r="K29" s="35" t="n"/>
+      <c r="L29" s="35" t="n"/>
+      <c r="M29" s="35" t="n"/>
+      <c r="N29" s="35" t="n"/>
+      <c r="O29" s="35" t="n"/>
+      <c r="P29" s="35" t="n"/>
+      <c r="Q29" s="35" t="n"/>
+      <c r="R29" s="35" t="n"/>
+      <c r="S29" s="35" t="n"/>
+      <c r="T29" s="35" t="n"/>
+      <c r="U29" s="35" t="n"/>
+      <c r="V29" s="35" t="n"/>
+      <c r="W29" s="35" t="n"/>
+      <c r="X29" s="35" t="n"/>
+      <c r="Y29" s="35" t="n"/>
+      <c r="Z29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Staging Directory</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="36" t="n"/>
-      <c r="O30" s="36" t="n"/>
-      <c r="P30" s="36" t="n"/>
-      <c r="Q30" s="36" t="n"/>
-      <c r="R30" s="36" t="n"/>
-      <c r="S30" s="36" t="n"/>
-      <c r="T30" s="36" t="n"/>
-      <c r="U30" s="36" t="n"/>
-      <c r="V30" s="36" t="n"/>
-      <c r="W30" s="36" t="n"/>
-      <c r="X30" s="36" t="n"/>
-      <c r="Y30" s="36" t="n"/>
-      <c r="Z30" s="36" t="n"/>
-    </row>
-    <row r="31">
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+      <c r="G30" s="35" t="n"/>
+      <c r="H30" s="35" t="n"/>
+      <c r="I30" s="35" t="n"/>
+      <c r="J30" s="35" t="n"/>
+      <c r="K30" s="35" t="n"/>
+      <c r="L30" s="35" t="n"/>
+      <c r="M30" s="35" t="n"/>
+      <c r="N30" s="35" t="n"/>
+      <c r="O30" s="35" t="n"/>
+      <c r="P30" s="35" t="n"/>
+      <c r="Q30" s="35" t="n"/>
+      <c r="R30" s="35" t="n"/>
+      <c r="S30" s="35" t="n"/>
+      <c r="T30" s="35" t="n"/>
+      <c r="U30" s="35" t="n"/>
+      <c r="V30" s="35" t="n"/>
+      <c r="W30" s="35" t="n"/>
+      <c r="X30" s="35" t="n"/>
+      <c r="Y30" s="35" t="n"/>
+      <c r="Z30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="H31" s="36" t="n"/>
-      <c r="I31" s="36" t="n"/>
-      <c r="J31" s="36" t="n"/>
-      <c r="K31" s="36" t="n"/>
-      <c r="L31" s="36" t="n"/>
-      <c r="M31" s="36" t="n"/>
-      <c r="N31" s="36" t="n"/>
-      <c r="O31" s="36" t="n"/>
-      <c r="P31" s="36" t="n"/>
-      <c r="Q31" s="36" t="n"/>
-      <c r="R31" s="36" t="n"/>
-      <c r="S31" s="36" t="n"/>
-      <c r="T31" s="36" t="n"/>
-      <c r="U31" s="36" t="n"/>
-      <c r="V31" s="36" t="n"/>
-      <c r="W31" s="36" t="n"/>
-      <c r="X31" s="36" t="n"/>
-      <c r="Y31" s="36" t="n"/>
-      <c r="Z31" s="36" t="n"/>
-    </row>
-    <row r="32">
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="35" t="n"/>
+      <c r="E31" s="35" t="n"/>
+      <c r="F31" s="35" t="n"/>
+      <c r="G31" s="35" t="n"/>
+      <c r="H31" s="35" t="n"/>
+      <c r="I31" s="35" t="n"/>
+      <c r="J31" s="35" t="n"/>
+      <c r="K31" s="35" t="n"/>
+      <c r="L31" s="35" t="n"/>
+      <c r="M31" s="35" t="n"/>
+      <c r="N31" s="35" t="n"/>
+      <c r="O31" s="35" t="n"/>
+      <c r="P31" s="35" t="n"/>
+      <c r="Q31" s="35" t="n"/>
+      <c r="R31" s="35" t="n"/>
+      <c r="S31" s="35" t="n"/>
+      <c r="T31" s="35" t="n"/>
+      <c r="U31" s="35" t="n"/>
+      <c r="V31" s="35" t="n"/>
+      <c r="W31" s="35" t="n"/>
+      <c r="X31" s="35" t="n"/>
+      <c r="Y31" s="35" t="n"/>
+      <c r="Z31" s="35" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="36" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="36" t="n"/>
-      <c r="O32" s="36" t="n"/>
-      <c r="P32" s="36" t="n"/>
-      <c r="Q32" s="36" t="n"/>
-      <c r="R32" s="36" t="n"/>
-      <c r="S32" s="36" t="n"/>
-      <c r="T32" s="36" t="n"/>
-      <c r="U32" s="36" t="n"/>
-      <c r="V32" s="36" t="n"/>
-      <c r="W32" s="36" t="n"/>
-      <c r="X32" s="36" t="n"/>
-      <c r="Y32" s="36" t="n"/>
-      <c r="Z32" s="36" t="n"/>
-    </row>
-    <row r="33">
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="35" t="n"/>
+      <c r="H32" s="35" t="n"/>
+      <c r="I32" s="35" t="n"/>
+      <c r="J32" s="35" t="n"/>
+      <c r="K32" s="35" t="n"/>
+      <c r="L32" s="35" t="n"/>
+      <c r="M32" s="35" t="n"/>
+      <c r="N32" s="35" t="n"/>
+      <c r="O32" s="35" t="n"/>
+      <c r="P32" s="35" t="n"/>
+      <c r="Q32" s="35" t="n"/>
+      <c r="R32" s="35" t="n"/>
+      <c r="S32" s="35" t="n"/>
+      <c r="T32" s="35" t="n"/>
+      <c r="U32" s="35" t="n"/>
+      <c r="V32" s="35" t="n"/>
+      <c r="W32" s="35" t="n"/>
+      <c r="X32" s="35" t="n"/>
+      <c r="Y32" s="35" t="n"/>
+      <c r="Z32" s="35" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Workgroup</t>
         </is>
       </c>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="36" t="n"/>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="36" t="n"/>
-      <c r="H33" s="36" t="n"/>
-      <c r="I33" s="36" t="n"/>
-      <c r="J33" s="36" t="n"/>
-      <c r="K33" s="36" t="n"/>
-      <c r="L33" s="36" t="n"/>
-      <c r="M33" s="36" t="n"/>
-      <c r="N33" s="36" t="n"/>
-      <c r="O33" s="36" t="n"/>
-      <c r="P33" s="36" t="n"/>
-      <c r="Q33" s="36" t="n"/>
-      <c r="R33" s="36" t="n"/>
-      <c r="S33" s="36" t="n"/>
-      <c r="T33" s="36" t="n"/>
-      <c r="U33" s="36" t="n"/>
-      <c r="V33" s="36" t="n"/>
-      <c r="W33" s="36" t="n"/>
-      <c r="X33" s="36" t="n"/>
-      <c r="Y33" s="36" t="n"/>
-      <c r="Z33" s="36" t="n"/>
-    </row>
-    <row r="34"/>
-    <row r="35">
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="G33" s="35" t="n"/>
+      <c r="H33" s="35" t="n"/>
+      <c r="I33" s="35" t="n"/>
+      <c r="J33" s="35" t="n"/>
+      <c r="K33" s="35" t="n"/>
+      <c r="L33" s="35" t="n"/>
+      <c r="M33" s="35" t="n"/>
+      <c r="N33" s="35" t="n"/>
+      <c r="O33" s="35" t="n"/>
+      <c r="P33" s="35" t="n"/>
+      <c r="Q33" s="35" t="n"/>
+      <c r="R33" s="35" t="n"/>
+      <c r="S33" s="35" t="n"/>
+      <c r="T33" s="35" t="n"/>
+      <c r="U33" s="35" t="n"/>
+      <c r="V33" s="35" t="n"/>
+      <c r="W33" s="35" t="n"/>
+      <c r="X33" s="35" t="n"/>
+      <c r="Y33" s="35" t="n"/>
+      <c r="Z33" s="35" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C35" s="36" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>srv-prod</t>
         </is>
       </c>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="36" t="n"/>
-      <c r="H35" s="36" t="n"/>
-      <c r="I35" s="36" t="n"/>
-      <c r="J35" s="36" t="n"/>
-      <c r="K35" s="36" t="n"/>
-      <c r="L35" s="36" t="n"/>
-      <c r="M35" s="36" t="n"/>
-      <c r="N35" s="36" t="n"/>
-      <c r="O35" s="36" t="n"/>
-      <c r="P35" s="36" t="n"/>
-      <c r="Q35" s="36" t="n"/>
-      <c r="R35" s="36" t="n"/>
-      <c r="S35" s="36" t="n"/>
-      <c r="T35" s="36" t="n"/>
-      <c r="U35" s="36" t="n"/>
-      <c r="V35" s="36" t="n"/>
-      <c r="W35" s="36" t="n"/>
-      <c r="X35" s="36" t="n"/>
-      <c r="Y35" s="36" t="n"/>
-      <c r="Z35" s="36" t="n"/>
-    </row>
-    <row r="36">
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="35" t="n"/>
+      <c r="G35" s="35" t="n"/>
+      <c r="H35" s="35" t="n"/>
+      <c r="I35" s="35" t="n"/>
+      <c r="J35" s="35" t="n"/>
+      <c r="K35" s="35" t="n"/>
+      <c r="L35" s="35" t="n"/>
+      <c r="M35" s="35" t="n"/>
+      <c r="N35" s="35" t="n"/>
+      <c r="O35" s="35" t="n"/>
+      <c r="P35" s="35" t="n"/>
+      <c r="Q35" s="35" t="n"/>
+      <c r="R35" s="35" t="n"/>
+      <c r="S35" s="35" t="n"/>
+      <c r="T35" s="35" t="n"/>
+      <c r="U35" s="35" t="n"/>
+      <c r="V35" s="35" t="n"/>
+      <c r="W35" s="35" t="n"/>
+      <c r="X35" s="35" t="n"/>
+      <c r="Y35" s="35" t="n"/>
+      <c r="Z35" s="35" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Custom Property</t>
         </is>
       </c>
-      <c r="C36" s="36" t="inlineStr">
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>costCenter</t>
         </is>
       </c>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="n"/>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="36" t="n"/>
-      <c r="M36" s="36" t="n"/>
-      <c r="N36" s="36" t="n"/>
-      <c r="O36" s="36" t="n"/>
-      <c r="P36" s="36" t="n"/>
-      <c r="Q36" s="36" t="n"/>
-      <c r="R36" s="36" t="n"/>
-      <c r="S36" s="36" t="n"/>
-      <c r="T36" s="36" t="n"/>
-      <c r="U36" s="36" t="n"/>
-      <c r="V36" s="36" t="n"/>
-      <c r="W36" s="36" t="n"/>
-      <c r="X36" s="36" t="n"/>
-      <c r="Y36" s="36" t="n"/>
-      <c r="Z36" s="36" t="n"/>
-    </row>
-    <row r="37">
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="35" t="n"/>
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="35" t="n"/>
+      <c r="H36" s="35" t="n"/>
+      <c r="I36" s="35" t="n"/>
+      <c r="J36" s="35" t="n"/>
+      <c r="K36" s="35" t="n"/>
+      <c r="L36" s="35" t="n"/>
+      <c r="M36" s="35" t="n"/>
+      <c r="N36" s="35" t="n"/>
+      <c r="O36" s="35" t="n"/>
+      <c r="P36" s="35" t="n"/>
+      <c r="Q36" s="35" t="n"/>
+      <c r="R36" s="35" t="n"/>
+      <c r="S36" s="35" t="n"/>
+      <c r="T36" s="35" t="n"/>
+      <c r="U36" s="35" t="n"/>
+      <c r="V36" s="35" t="n"/>
+      <c r="W36" s="35" t="n"/>
+      <c r="X36" s="35" t="n"/>
+      <c r="Y36" s="35" t="n"/>
+      <c r="Z36" s="35" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Custom Value</t>
         </is>
       </c>
-      <c r="C37" s="36" t="inlineStr">
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>cc-42</t>
         </is>
       </c>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="36" t="n"/>
-      <c r="G37" s="36" t="n"/>
-      <c r="H37" s="36" t="n"/>
-      <c r="I37" s="36" t="n"/>
-      <c r="J37" s="36" t="n"/>
-      <c r="K37" s="36" t="n"/>
-      <c r="L37" s="36" t="n"/>
-      <c r="M37" s="36" t="n"/>
-      <c r="N37" s="36" t="n"/>
-      <c r="O37" s="36" t="n"/>
-      <c r="P37" s="36" t="n"/>
-      <c r="Q37" s="36" t="n"/>
-      <c r="R37" s="36" t="n"/>
-      <c r="S37" s="36" t="n"/>
-      <c r="T37" s="36" t="n"/>
-      <c r="U37" s="36" t="n"/>
-      <c r="V37" s="36" t="n"/>
-      <c r="W37" s="36" t="n"/>
-      <c r="X37" s="36" t="n"/>
-      <c r="Y37" s="36" t="n"/>
-      <c r="Z37" s="36" t="n"/>
-    </row>
+      <c r="D37" s="35" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="35" t="n"/>
+      <c r="G37" s="35" t="n"/>
+      <c r="H37" s="35" t="n"/>
+      <c r="I37" s="35" t="n"/>
+      <c r="J37" s="35" t="n"/>
+      <c r="K37" s="35" t="n"/>
+      <c r="L37" s="35" t="n"/>
+      <c r="M37" s="35" t="n"/>
+      <c r="N37" s="35" t="n"/>
+      <c r="O37" s="35" t="n"/>
+      <c r="P37" s="35" t="n"/>
+      <c r="Q37" s="35" t="n"/>
+      <c r="R37" s="35" t="n"/>
+      <c r="S37" s="35" t="n"/>
+      <c r="T37" s="35" t="n"/>
+      <c r="U37" s="35" t="n"/>
+      <c r="V37" s="35" t="n"/>
+      <c r="W37" s="35" t="n"/>
+      <c r="X37" s="35" t="n"/>
+      <c r="Y37" s="35" t="n"/>
+      <c r="Z37" s="35" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="C11:Z33">
-    <cfRule type="expression" priority="1" dxfId="3">
-      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX('_ServerFields'!$B$2:$AS$24,MATCH($B11,'_ServerFields'!$A$2:$A$24,0),MATCH(C$8,'_ServerFields'!$B$1:$AS$1,0)),"")="")</formula>
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B11,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="C8:Z8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='_ServerFields'!$B$1:$AS$1</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="AA4:AE9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
+    <dataValidation sqref="C8:Z8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>_ServerTypes</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3322,11 +3365,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col width="26.1640625" customWidth="1" style="22" min="1" max="1"/>
-    <col width="22.33203125" customWidth="1" style="22" min="2" max="2"/>
-    <col width="10.83203125" customWidth="1" style="22" min="3" max="16384"/>
+    <col width="26.140625" customWidth="1" style="22" min="1" max="1"/>
+    <col width="22.28515625" customWidth="1" style="22" min="2" max="2"/>
+    <col width="10.85546875" customWidth="1" style="22" min="3" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="2">
@@ -3336,7 +3379,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customFormat="1" customHeight="1" s="2">
+    <row r="2" ht="15.95" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
@@ -3344,36 +3387,36 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customFormat="1" customHeight="1" s="2"/>
-    <row r="4" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="3" ht="15.95" customFormat="1" customHeight="1" s="2"/>
+    <row r="4" ht="15.95" customFormat="1" customHeight="1" s="2">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Price Amount</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
+      <c r="B4" s="35" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5" ht="15.95" customFormat="1" customHeight="1" s="2">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Price Currency</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6" ht="15.95" customFormat="1" customHeight="1" s="2">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Price Unit</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Per 1000 requests</t>
         </is>
@@ -3396,16 +3439,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="20" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20" customWidth="1" style="2" min="2" max="2"/>
-    <col width="20" customWidth="1" style="2" min="3" max="16384"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="28.5703125" customWidth="1" style="2" min="1" max="3"/>
+    <col width="57.140625" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.5703125" customWidth="1" style="2" min="5" max="5"/>
+    <col width="47.5703125" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.5703125" customWidth="1" style="2" min="7" max="8"/>
+    <col width="8.85546875" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3422,7 +3463,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Element Type</t>
@@ -3465,363 +3506,363 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>additionalField</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>some value</t>
         </is>
       </c>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
-      <c r="H5" s="36" t="n"/>
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr"/>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr"/>
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>pii</t>
         </is>
       </c>
-      <c r="D6" s="36" t="b">
+      <c r="D6" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr"/>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr"/>
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>retentionDays</t>
         </is>
       </c>
-      <c r="D7" s="36" t="n">
+      <c r="D7" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr"/>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr"/>
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>sourceSystem</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="inlineStr">
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>The system of record</t>
         </is>
       </c>
-      <c r="G8" s="36" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>acme</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>cp-source-system</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr"/>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr"/>
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>dbtVersion</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr"/>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr"/>
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>regions</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>["eu-west", "eu-central"]</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr"/>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr"/>
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>costCenter</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>{"id": 4711, "name": "Fulfillment"}</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr"/>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr"/>
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>github_link</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>https://github.example.com/shipment-specification.yaml</t>
         </is>
       </c>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>retention</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>P1Y</t>
         </is>
       </c>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>ISO 8601 retention period</t>
         </is>
       </c>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>shipments.shipment_id</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr"/>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr"/>
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>costCenter</t>
         </is>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="35" t="n">
         <v>42</v>
       </c>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr"/>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr"/>
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>slack</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>#fulfillment-data</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Contract,Description,Server,Schema,Property,Quality,Support,Team,Team Member,Role,SLA,Relationship,Enum Value,Synonym,Verified Statement,Constraint"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Text,JSON"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3838,12 +3879,11 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="28.5703125" customWidth="1" min="1" max="2"/>
+    <col width="57.140625" customWidth="1" min="3" max="3"/>
+    <col width="28.5703125" customWidth="1" min="4" max="4"/>
+    <col width="47.5703125" customWidth="1" min="5" max="5"/>
+    <col width="28.5703125" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3853,14 +3893,14 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Links to authoritative sources (business definitions, implementations, tutorials) for any element of the contract.</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Element Type</t>
@@ -3892,232 +3932,232 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>https://example.com/definitions/shipments</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>implementation</t>
         </is>
       </c>
-      <c r="E5" s="36" t="n"/>
-      <c r="F5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>shipments.shipment_id</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>https://example.com/tutorials/shipment_id</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>tutorial</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>How shipment ids are minted</t>
         </is>
       </c>
-      <c r="F6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="F6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>https://example.com/sla</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>implementation</t>
         </is>
       </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr"/>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr"/>
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>https://example.com/guidelines</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>tutorial</t>
         </is>
       </c>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr"/>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr"/>
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>https://example.com/data-guidelines.html</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>tutorial</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Company-wide data guidelines</t>
         </is>
       </c>
-      <c r="F9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
+      <c r="F9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Contract,Description,Server,Schema,Property,Quality,Support,Team,Team Member,Role,SLA,Relationship,Enum Value,Synonym,Verified Statement,Constraint"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5349,7 +5389,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5360,20 +5400,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="2.83203125" customWidth="1" style="2" min="1" max="1"/>
-    <col width="19.6640625" customWidth="1" style="2" min="2" max="2"/>
+    <col width="2.85546875" customWidth="1" style="2" min="1" max="1"/>
+    <col width="19.7109375" customWidth="1" style="2" min="2" max="2"/>
     <col width="45" customWidth="1" style="2" min="3" max="3"/>
-    <col width="1.83203125" customWidth="1" style="2" min="4" max="4"/>
-    <col width="28.1640625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14.33203125" customWidth="1" style="2" min="6" max="6"/>
+    <col width="1.85546875" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="14.28515625" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
-    <col width="14.1640625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.33203125" customWidth="1" style="2" min="10" max="11"/>
-    <col width="23.5" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="24.1640625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
-    <col width="8.83203125" customWidth="1" style="2" min="14" max="16384"/>
+    <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.28515625" customWidth="1" style="2" min="10" max="11"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+    <col width="24.140625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
+    <col width="8.85546875" customWidth="1" style="2" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5391,99 +5431,99 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>DataContract</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>apiVersion</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>v3.2.0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="n"/>
-      <c r="B6" s="34" t="n"/>
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="33" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n"/>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="B7" s="33" t="n"/>
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>fulfillment_shipments_v1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n"/>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="B9" s="33" t="n"/>
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="B10" s="33" t="n"/>
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="n"/>
-      <c r="B11" s="34" t="n"/>
+      <c r="A11" s="33" t="n"/>
+      <c r="B11" s="33" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>controlling-team</t>
         </is>
@@ -5491,17 +5531,17 @@
       <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="n"/>
-      <c r="B13" s="34" t="n"/>
+      <c r="A13" s="33" t="n"/>
+      <c r="B13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>sales-team</t>
         </is>
@@ -5509,13 +5549,13 @@
       <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>Data Product</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
@@ -5523,93 +5563,93 @@
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Tenant</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>company-A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="n"/>
-      <c r="B17" s="34" t="n"/>
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="33" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n"/>
+      <c r="B18" s="33" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="n"/>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>This data can be used for analytical purposes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="n"/>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Limitations</t>
         </is>
       </c>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Not suitable for real-time use cases</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="n"/>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="C21" s="36" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Use this to analyze shipments</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="n"/>
-      <c r="B22" s="34" t="n"/>
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="33" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B23" s="34" t="n"/>
-      <c r="C23" s="36" t="inlineStr">
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>datalocation:EU</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>Context Instructions</t>
         </is>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Join on shipment_id only; delivery_date is in UTC.</t>
         </is>
@@ -5641,32 +5681,28 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AQ54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="34.83203125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="34.85546875" customWidth="1" style="2" min="1" max="1"/>
     <col width="24" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="12.5" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="17.5" customWidth="1" style="2" min="4" max="4"/>
-    <col width="28.1640625" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="35.6640625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="17.42578125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="35.7109375" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
-    <col width="14.1640625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.33203125" customWidth="1" style="2" min="10" max="10"/>
-    <col width="28.1640625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
-    <col width="28.6640625" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="28.6640625" customWidth="1" style="2" min="13" max="13"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
+    <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.28515625" customWidth="1" style="2" min="10" max="10"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="28.7109375" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
+    <col width="28.7109375" customWidth="1" style="2" min="13" max="13"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
     <col width="19" bestFit="1" customWidth="1" style="2" min="15" max="15"/>
     <col width="19" customWidth="1" style="2" min="16" max="20"/>
-    <col width="21.6640625" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
-    <col width="27.33203125" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
-    <col width="15.5" customWidth="1" style="2" min="23" max="37"/>
-    <col width="22" customWidth="1" style="2" min="38" max="38"/>
-    <col width="22" customWidth="1" style="2" min="39" max="16384"/>
-    <col width="22" customWidth="1" min="40" max="40"/>
-    <col width="22" customWidth="1" min="41" max="41"/>
-    <col width="22" customWidth="1" min="42" max="42"/>
-    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="21.7109375" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
+    <col width="27.28515625" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
+    <col width="15.42578125" customWidth="1" style="2" min="23" max="37"/>
+    <col width="28.5703125" customWidth="1" style="2" min="38" max="43"/>
+    <col width="8.85546875" customWidth="1" style="2" min="44" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5692,12 +5728,12 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
@@ -5707,12 +5743,12 @@
       <c r="E5" s="42" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>table</t>
         </is>
@@ -5722,12 +5758,12 @@
       <c r="E6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Shipment data with orders, delivery dates, carriers and statuses.</t>
         </is>
@@ -5737,12 +5773,12 @@
       <c r="E7" s="42" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
@@ -5752,12 +5788,12 @@
       <c r="E8" s="42" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Physical Name</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>shipments_v1</t>
         </is>
@@ -5767,12 +5803,12 @@
       <c r="E9" s="42" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Data Granularity</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Not Aggregated</t>
         </is>
@@ -5781,13 +5817,13 @@
       <c r="D10" s="41" t="n"/>
       <c r="E10" s="42" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>pii</t>
         </is>
@@ -5796,35 +5832,35 @@
       <c r="D11" s="41" t="n"/>
       <c r="E11" s="42" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n"/>
+      <c r="B12" s="44" t="n"/>
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
       <c r="E12" s="42" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n"/>
+      <c r="B13" s="44" t="n"/>
       <c r="C13" s="41" t="n"/>
       <c r="D13" s="41" t="n"/>
       <c r="E13" s="42" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>Context Instructions</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>Filter on status = 'Delivered' for fulfilment KPIs.</t>
         </is>
@@ -5833,13 +5869,13 @@
       <c r="D14" s="41" t="n"/>
       <c r="E14" s="42" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>Custom Property</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>sourceTable</t>
         </is>
@@ -5848,13 +5884,13 @@
       <c r="D15" s="41" t="n"/>
       <c r="E15" s="42" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Custom Value</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>sap.vbak</t>
         </is>
@@ -5863,7 +5899,7 @@
       <c r="D16" s="41" t="n"/>
       <c r="E16" s="42" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="W17" s="19" t="inlineStr">
         <is>
           <t>Logical Type Options</t>
@@ -5884,7 +5920,7 @@
       <c r="AJ17" s="20" t="n"/>
       <c r="AK17" s="21" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Property</t>
@@ -6101,7 +6137,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
         <is>
           <t>shipment_id</t>
@@ -6210,7 +6246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>order_id</t>
@@ -6293,7 +6329,7 @@
       <c r="AP20" s="15" t="n"/>
       <c r="AQ20" s="15" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="17" t="inlineStr">
         <is>
           <t>status</t>
@@ -6368,7 +6404,7 @@
       <c r="AP21" s="15" t="n"/>
       <c r="AQ21" s="15" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
           <t>weight_kg</t>
@@ -6447,7 +6483,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
         <is>
           <t>address</t>
@@ -6518,7 +6554,7 @@
       <c r="AP23" s="15" t="n"/>
       <c r="AQ23" s="15" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>address.street</t>
@@ -6581,7 +6617,7 @@
       <c r="AP24" s="15" t="n"/>
       <c r="AQ24" s="15" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
           <t>address.country</t>
@@ -6644,7 +6680,7 @@
       <c r="AP25" s="15" t="n"/>
       <c r="AQ25" s="15" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
         <is>
           <t>items</t>
@@ -6705,7 +6741,7 @@
       <c r="AP26" s="15" t="n"/>
       <c r="AQ26" s="15" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>items.items</t>
@@ -6762,7 +6798,7 @@
       <c r="AP27" s="15" t="n"/>
       <c r="AQ27" s="15" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
           <t>items.items.sku</t>
@@ -6827,7 +6863,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="17" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="15" t="n"/>
@@ -6872,7 +6908,7 @@
       <c r="AP29" s="15" t="n"/>
       <c r="AQ29" s="15" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="17" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="15" t="n"/>
@@ -6917,7 +6953,7 @@
       <c r="AP30" s="15" t="n"/>
       <c r="AQ30" s="15" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="17" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="15" t="n"/>
@@ -6962,7 +6998,7 @@
       <c r="AP31" s="15" t="n"/>
       <c r="AQ31" s="15" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="17" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="15" t="n"/>
@@ -7007,7 +7043,7 @@
       <c r="AP32" s="15" t="n"/>
       <c r="AQ32" s="15" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="17" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="15" t="n"/>
@@ -7052,7 +7088,7 @@
       <c r="AP33" s="15" t="n"/>
       <c r="AQ33" s="15" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="17" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="15" t="n"/>
@@ -7097,7 +7133,7 @@
       <c r="AP34" s="15" t="n"/>
       <c r="AQ34" s="15" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="17" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="15" t="n"/>
@@ -7142,7 +7178,7 @@
       <c r="AP35" s="15" t="n"/>
       <c r="AQ35" s="15" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="17" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="15" t="n"/>
@@ -7187,7 +7223,7 @@
       <c r="AP36" s="15" t="n"/>
       <c r="AQ36" s="15" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="17" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="15" t="n"/>
@@ -7232,7 +7268,7 @@
       <c r="AP37" s="15" t="n"/>
       <c r="AQ37" s="15" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="17" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="15" t="n"/>
@@ -7277,7 +7313,7 @@
       <c r="AP38" s="15" t="n"/>
       <c r="AQ38" s="15" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="17" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="15" t="n"/>
@@ -7322,7 +7358,7 @@
       <c r="AP39" s="15" t="n"/>
       <c r="AQ39" s="15" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="17" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="15" t="n"/>
@@ -7367,7 +7403,7 @@
       <c r="AP40" s="15" t="n"/>
       <c r="AQ40" s="15" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="17" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="15" t="n"/>
@@ -7412,7 +7448,7 @@
       <c r="AP41" s="15" t="n"/>
       <c r="AQ41" s="15" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="17" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="15" t="n"/>
@@ -7457,7 +7493,7 @@
       <c r="AP42" s="15" t="n"/>
       <c r="AQ42" s="15" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="17" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="15" t="n"/>
@@ -7502,7 +7538,7 @@
       <c r="AP43" s="15" t="n"/>
       <c r="AQ43" s="15" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="17" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="15" t="n"/>
@@ -7547,7 +7583,7 @@
       <c r="AP44" s="15" t="n"/>
       <c r="AQ44" s="15" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="17" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="15" t="n"/>
@@ -7592,7 +7628,7 @@
       <c r="AP45" s="15" t="n"/>
       <c r="AQ45" s="15" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="17" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="15" t="n"/>
@@ -7637,7 +7673,7 @@
       <c r="AP46" s="15" t="n"/>
       <c r="AQ46" s="15" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="17" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="15" t="n"/>
@@ -7682,7 +7718,7 @@
       <c r="AP47" s="15" t="n"/>
       <c r="AQ47" s="15" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="17" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="15" t="n"/>
@@ -7727,7 +7763,7 @@
       <c r="AP48" s="15" t="n"/>
       <c r="AQ48" s="15" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="17" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="15" t="n"/>
@@ -7772,7 +7808,7 @@
       <c r="AP49" s="15" t="n"/>
       <c r="AQ49" s="15" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="17" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="15" t="n"/>
@@ -7817,7 +7853,7 @@
       <c r="AP50" s="15" t="n"/>
       <c r="AQ50" s="15" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="17" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="15" t="n"/>
@@ -7862,7 +7898,7 @@
       <c r="AP51" s="15" t="n"/>
       <c r="AQ51" s="15" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="17" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="15" t="n"/>
@@ -7907,7 +7943,7 @@
       <c r="AP52" s="15" t="n"/>
       <c r="AQ52" s="15" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="17" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="15" t="n"/>
@@ -7952,7 +7988,7 @@
       <c r="AP53" s="15" t="n"/>
       <c r="AQ53" s="15" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="17" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="15" t="n"/>
@@ -8023,73 +8059,72 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="8.33203125" customWidth="1" style="30" min="1" max="1"/>
-    <col width="13" customWidth="1" style="30" min="2" max="2"/>
-    <col width="48.5" customWidth="1" style="30" min="3" max="3"/>
-    <col width="42.83203125" customWidth="1" style="30" min="4" max="4"/>
-    <col width="22" customWidth="1" style="30" min="5" max="5"/>
-    <col width="22" customWidth="1" style="30" min="6" max="16384"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="8.28515625" customWidth="1" style="29" min="1" max="1"/>
+    <col width="13" customWidth="1" style="29" min="2" max="2"/>
+    <col width="48.42578125" customWidth="1" style="29" min="3" max="3"/>
+    <col width="42.85546875" customWidth="1" style="29" min="4" max="4"/>
+    <col width="28.5703125" customWidth="1" style="29" min="5" max="7"/>
+    <col width="8.85546875" customWidth="1" style="29" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Relationships</t>
         </is>
       </c>
-      <c r="B1" s="29" t="n"/>
+      <c r="B1" s="28" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Define relationships between schemas by mapping properties from one schema to another (e.g., foreign keys).</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n"/>
+      <c r="B2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Use schema.property dot syntax (e.g., orders.customer_id). Comma-separated for composite keys. Level: 'schema' or 'property'.</t>
         </is>
       </c>
-      <c r="B3" s="31" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="B3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="31" t="inlineStr">
         <is>
           <t>Custom Property</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>Custom Value</t>
         </is>
@@ -8256,7 +8291,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
       <formula>C5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8288,15 +8323,9 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="28.5703125" customWidth="1" min="1" max="4"/>
+    <col width="47.5703125" customWidth="1" min="5" max="5"/>
+    <col width="28.5703125" customWidth="1" min="6" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8306,14 +8335,14 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Allowed values of a property. Use schema.property dot syntax for the property (e.g. orders.status).</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Schema</t>
@@ -8360,289 +8389,289 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Delivered to the customer</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>The carrier confirmed the delivery.</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>final</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>enum-delivered</t>
         </is>
       </c>
-      <c r="H5" s="36" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>color</t>
         </is>
       </c>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>In Transit</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>On its way</t>
         </is>
       </c>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
+      <c r="I6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>Lost</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>Numeric legacy code</t>
         </is>
       </c>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
-      <c r="I7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>address.country</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-      <c r="I8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>address.country</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="n"/>
-      <c r="I9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-      <c r="I10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-      <c r="I13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-      <c r="I14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
-      <c r="I15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
+      <c r="I13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+      <c r="I17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
+      <c r="I18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+      <c r="I19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+      <c r="I20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8655,16 +8684,9 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="28.5703125" customWidth="1" min="1" max="3"/>
+    <col width="47.5703125" customWidth="1" min="4" max="4"/>
+    <col width="28.5703125" customWidth="1" min="5" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8674,14 +8696,14 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Alternative names for a schema or a property. Leave Property blank for a synonym of the schema itself.</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Schema</t>
@@ -8733,258 +8755,258 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Sendungen</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>German name</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>de-DE</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>business glossary</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H5" s="36" t="n"/>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="H5" s="35" t="n"/>
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>glossaryId</t>
         </is>
       </c>
-      <c r="J5" s="36" t="n">
+      <c r="J5" s="35" t="n">
         <v>4711</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Sendungsnummer</t>
         </is>
       </c>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>de-DE</t>
         </is>
       </c>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-      <c r="J6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="n"/>
-      <c r="I9" s="36" t="n"/>
-      <c r="J9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-      <c r="I10" s="36" t="n"/>
-      <c r="J10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-      <c r="I11" s="36" t="n"/>
-      <c r="J11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-      <c r="I13" s="36" t="n"/>
-      <c r="J13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-      <c r="I14" s="36" t="n"/>
-      <c r="J14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
-      <c r="I15" s="36" t="n"/>
-      <c r="J15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
-      <c r="J16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-      <c r="I17" s="36" t="n"/>
-      <c r="J17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
-      <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
+      <c r="I6" s="35" t="n"/>
+      <c r="J6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
+      <c r="I7" s="35" t="n"/>
+      <c r="J7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="35" t="n"/>
+      <c r="J8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="35" t="n"/>
+      <c r="J9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+      <c r="I10" s="35" t="n"/>
+      <c r="J10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
+      <c r="I13" s="35" t="n"/>
+      <c r="J13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+      <c r="I14" s="35" t="n"/>
+      <c r="J14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="35" t="n"/>
+      <c r="J15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+      <c r="I17" s="35" t="n"/>
+      <c r="J17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+      <c r="I19" s="35" t="n"/>
+      <c r="J19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="35" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8997,14 +9019,9 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="28.5703125" customWidth="1" min="1" max="2"/>
+    <col width="57.140625" customWidth="1" min="3" max="4"/>
+    <col width="28.5703125" customWidth="1" min="5" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -9014,14 +9031,14 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Verified question/answer pairs that give consumers and AI agents context. Level: Contract or Schema.</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Level</t>
@@ -9063,231 +9080,231 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Does this table contain cancelled shipments?</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>No, cancelled shipments are excluded before loading.</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>completeness</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>vs-cancelled</t>
         </is>
       </c>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>verifiedBy</t>
         </is>
       </c>
-      <c r="H5" s="36" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>data-steward</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Is weight_kg always populated?</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>No, it is null for letters.</t>
         </is>
       </c>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="E6" s="35" t="n"/>
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>vs-weight</t>
         </is>
       </c>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-      <c r="H9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-      <c r="H15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-      <c r="H17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+      <c r="H17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Contract,Schema"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9300,13 +9317,9 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="28.5703125" customWidth="1" min="1" max="2"/>
+    <col width="66.7109375" customWidth="1" min="3" max="3"/>
+    <col width="28.5703125" customWidth="1" min="4" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -9316,14 +9329,14 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Constraints that consumers and AI agents must respect when using the data. Level: Contract or Schema.</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Level</t>
@@ -9360,198 +9373,198 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n"/>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Do not join to customer PII without a legal basis.</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>privacy</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>c-pii</t>
         </is>
       </c>
-      <c r="F5" s="36" t="n"/>
-      <c r="G5" s="36" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Never aggregate weight_kg across carriers.</t>
         </is>
       </c>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>c-weight</t>
         </is>
       </c>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="n"/>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
-      <c r="G7" s="36" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="n"/>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
-      <c r="G9" s="36" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="36" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="36" t="n"/>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
-      <c r="F17" s="36" t="n"/>
-      <c r="G17" s="36" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
-      <c r="F21" s="36" t="n"/>
-      <c r="G21" s="36" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="35" t="n"/>
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n"/>
+      <c r="E7" s="35" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="35" t="n"/>
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n"/>
+      <c r="G8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="35" t="n"/>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="35" t="n"/>
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="35" t="n"/>
+      <c r="G11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="35" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="35" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Contract,Schema"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9562,123 +9575,122 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col width="17.5" customWidth="1" style="30" min="1" max="1"/>
-    <col width="22" customWidth="1" style="30" min="2" max="2"/>
-    <col width="14.33203125" customWidth="1" style="30" min="3" max="3"/>
-    <col width="32.6640625" customWidth="1" style="30" min="4" max="4"/>
-    <col width="18.33203125" customWidth="1" style="30" min="5" max="5"/>
-    <col width="28.33203125" customWidth="1" style="30" min="6" max="6"/>
-    <col width="19" bestFit="1" customWidth="1" style="30" min="7" max="7"/>
-    <col width="16" bestFit="1" customWidth="1" style="30" min="8" max="8"/>
-    <col width="22.83203125" bestFit="1" customWidth="1" style="30" min="9" max="9"/>
-    <col width="23.5" bestFit="1" customWidth="1" style="30" min="10" max="10"/>
-    <col width="15.5" bestFit="1" customWidth="1" style="30" min="11" max="11"/>
-    <col width="17.83203125" bestFit="1" customWidth="1" style="30" min="12" max="12"/>
-    <col width="17.83203125" customWidth="1" style="30" min="13" max="13"/>
-    <col width="22" customWidth="1" style="30" min="14" max="16384"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="17.42578125" customWidth="1" style="29" min="1" max="1"/>
+    <col width="22" customWidth="1" style="29" min="2" max="2"/>
+    <col width="14.28515625" customWidth="1" style="29" min="3" max="3"/>
+    <col width="32.7109375" customWidth="1" style="29" min="4" max="4"/>
+    <col width="18.28515625" customWidth="1" style="29" min="5" max="5"/>
+    <col width="28.28515625" customWidth="1" style="29" min="6" max="6"/>
+    <col width="19" bestFit="1" customWidth="1" style="29" min="7" max="7"/>
+    <col width="16" bestFit="1" customWidth="1" style="29" min="8" max="8"/>
+    <col width="22.85546875" bestFit="1" customWidth="1" style="29" min="9" max="9"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="29" min="10" max="10"/>
+    <col width="15.42578125" bestFit="1" customWidth="1" style="29" min="11" max="11"/>
+    <col width="17.85546875" bestFit="1" customWidth="1" style="29" min="12" max="12"/>
+    <col width="17.85546875" customWidth="1" style="29" min="13" max="13"/>
+    <col width="28.5703125" customWidth="1" style="29" min="14" max="16"/>
+    <col width="8.85546875" customWidth="1" style="29" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="B1" s="29" t="n"/>
+      <c r="B1" s="28" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>This section describes data quality rules &amp; parameters. They are tightly linked to the schema described in the previous sheet(s).</t>
         </is>
       </c>
-      <c r="B2" s="31" t="n"/>
+      <c r="B2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="n"/>
-      <c r="B3" s="31" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A3" s="30" t="n"/>
+      <c r="B3" s="30" t="n"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Quality Type</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Rule (Library)</t>
         </is>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>Query (SQL)</t>
         </is>
       </c>
-      <c r="G4" s="33" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>Threshold Operator</t>
         </is>
       </c>
-      <c r="H4" s="33" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>Threshold Value</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t>Quality Engine (Custom)</t>
         </is>
       </c>
-      <c r="J4" s="33" t="inlineStr">
+      <c r="J4" s="32" t="inlineStr">
         <is>
           <t>Implementation (Custom)</t>
         </is>
       </c>
-      <c r="K4" s="33" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="L4" s="33" t="inlineStr">
+      <c r="L4" s="32" t="inlineStr">
         <is>
           <t>Scheduler</t>
         </is>
       </c>
-      <c r="M4" s="33" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="N4" s="32" t="inlineStr">
+      <c r="N4" s="31" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="O4" s="32" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t>Custom Property</t>
         </is>
       </c>
-      <c r="P4" s="32" t="inlineStr">
+      <c r="P4" s="31" t="inlineStr">
         <is>
           <t>Custom Value</t>
         </is>
@@ -10001,12 +10013,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
       <formula>C5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F21">
-    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>C5="library"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tests/fixtures/excel/shipments-odcs.xlsx
+++ b/tests/fixtures/excel/shipments-odcs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Schema shipments" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Enum" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Enums" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Synonyms" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Verified Statements" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
@@ -40,7 +40,7 @@
     <definedName name="description.purpose">Fundamentals!$C$19</definedName>
     <definedName name="description.usage">Fundamentals!$C$21</definedName>
     <definedName name="domain">Fundamentals!$C$14</definedName>
-    <definedName name="enum">Enum!$A$4:$Z$1000</definedName>
+    <definedName name="enum">Enums!$A$4:$Z$1000</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
@@ -102,7 +102,7 @@
     <definedName name="schema.name" localSheetId="2">'Schema shipments'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema shipments'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema shipments'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$18:$AZ$981</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema shipments'!$A$16:$AZ$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema shipments'!$B$11</definedName>
     <definedName name="roles" localSheetId="11">Roles!$A$4:$Z$1000</definedName>
     <definedName name="slaProperties" localSheetId="12">SLA!$A$6:$Z$1002</definedName>
@@ -321,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -403,6 +403,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -421,7 +422,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,9 +453,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F4F6"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEDEDED"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1139,7 +1152,7 @@
           <t>Version:</t>
         </is>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -1222,14 +1235,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
     <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
     <col width="23.7109375" customWidth="1" style="2" min="4" max="6"/>
-    <col width="28.5703125" customWidth="1" style="2" min="7" max="9"/>
-    <col width="8.85546875" customWidth="1" style="2" min="10" max="16384"/>
+    <col width="28.5703125" customWidth="1" style="2" min="7" max="7"/>
+    <col width="26.7109375" customWidth="1" style="2" min="8" max="10"/>
+    <col width="8.85546875" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1239,7 +1253,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Support and communication channels help consumers find help regarding their use of the data contract.
@@ -1247,6 +1261,15 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="15.95" customHeight="1">
+      <c r="H3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="I3" s="44" t="n"/>
+      <c r="J3" s="44" t="n"/>
+    </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1285,183 +1308,244 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>sla</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>slackname</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>http://find.me.here</t>
         </is>
       </c>
-      <c r="C5" s="35" t="n"/>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>slack</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>interactive</t>
         </is>
       </c>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>sup-slack</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>sla</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H5" s="36" t="inlineStr">
         <is>
           <t>24h</t>
         </is>
       </c>
+      <c r="I5" s="36" t="n"/>
+      <c r="J5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
@@ -1475,14 +1559,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
     <col width="59.7109375" customWidth="1" style="2" min="2" max="3"/>
     <col width="23.7109375" customWidth="1" style="2" min="4" max="7"/>
-    <col width="28.5703125" customWidth="1" style="2" min="8" max="10"/>
-    <col width="8.85546875" customWidth="1" style="2" min="11" max="16384"/>
+    <col width="28.5703125" customWidth="1" style="2" min="8" max="8"/>
+    <col width="26.7109375" customWidth="1" style="2" min="9" max="11"/>
+    <col width="8.85546875" customWidth="1" style="2" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1501,52 +1586,61 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Team Name</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Fulfillment Data Team</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Team Description</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Owns the shipment data product</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Team Tags</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Team ID</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>team-fulfillment</t>
         </is>
       </c>
+    </row>
+    <row r="8" ht="15.95" customHeight="1">
+      <c r="I8" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="J8" s="44" t="n"/>
+      <c r="K8" s="44" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1591,210 +1685,271 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>onCall</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>vimportant</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>administrator</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" t="inlineStr">
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>tm-vi</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>onCall</t>
-        </is>
-      </c>
-      <c r="J10" t="b">
+      <c r="I10" s="36" t="b">
         <v>1</v>
       </c>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>nimportant</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>reader</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>2024-10-10</t>
         </is>
       </c>
-      <c r="G11" s="35" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
+      <c r="A23" s="36" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="n"/>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="n"/>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35" t="n"/>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
+      <c r="A25" s="36" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="n"/>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
+      <c r="A26" s="36" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I8:K8"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B10:G66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
@@ -1808,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
@@ -1816,8 +1971,9 @@
     <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
     <col width="32.85546875" customWidth="1" style="2" min="4" max="4"/>
     <col width="34.7109375" customWidth="1" style="2" min="5" max="5"/>
-    <col width="28.5703125" customWidth="1" style="2" min="6" max="8"/>
-    <col width="8.85546875" customWidth="1" style="2" min="9" max="16384"/>
+    <col width="28.5703125" customWidth="1" style="2" min="6" max="6"/>
+    <col width="26.7109375" customWidth="1" style="2" min="7" max="9"/>
+    <col width="8.85546875" customWidth="1" style="2" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1827,7 +1983,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
@@ -1836,6 +1992,15 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="15.95" customHeight="1">
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="H3" s="44" t="n"/>
+      <c r="I3" s="44" t="n"/>
+    </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1869,166 +2034,227 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>ticketQueue</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>analyst</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Read access for analysts</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>data-owner</t>
         </is>
       </c>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>role-analyst</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ticketQueue</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B5:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
   </dataValidations>
@@ -2042,7 +2268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="33.140625" customWidth="1" style="2" min="1" max="1"/>
@@ -2050,8 +2276,9 @@
     <col width="39.28515625" customWidth="1" style="2" min="3" max="3"/>
     <col width="32.85546875" customWidth="1" style="2" min="4" max="5"/>
     <col width="34.7109375" customWidth="1" style="2" min="6" max="6"/>
-    <col width="28.5703125" customWidth="1" style="2" min="7" max="9"/>
-    <col width="8.85546875" customWidth="1" style="2" min="10" max="16384"/>
+    <col width="28.5703125" customWidth="1" style="2" min="7" max="7"/>
+    <col width="26.7109375" customWidth="1" style="2" min="8" max="10"/>
+    <col width="8.85546875" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2073,8 +2300,8 @@
     <row r="3">
       <c r="A3" s="4" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Default SLA element(s)</t>
         </is>
@@ -2084,6 +2311,15 @@
           <t>shipments.delivery_date</t>
         </is>
       </c>
+    </row>
+    <row r="5" ht="15.95" customHeight="1">
+      <c r="H5" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="I5" s="44" t="n"/>
+      <c r="J5" s="44" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -2123,183 +2359,244 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>measuredBy</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>operational</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>sla-availability</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>measuredBy</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>statuspage</t>
         </is>
       </c>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n"/>
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
+      <c r="A23" s="36" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H5:J5"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B7:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1"/>
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1"/>
@@ -2314,7 +2611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="6.140625" customWidth="1" style="2" min="1" max="1"/>
@@ -2344,100 +2641,100 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Server</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n"/>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="D4" s="35" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>lakehouse</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="F4" s="35" t="n"/>
+      <c r="F4" s="36" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>dev</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="F5" s="35" t="n"/>
+      <c r="F5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Production dataset</t>
         </is>
       </c>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="33" t="n"/>
+      <c r="A7" s="34" t="n"/>
+      <c r="B7" s="34" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>bigquery</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>trino</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>kafka</t>
         </is>
       </c>
-      <c r="F8" s="35" t="n"/>
+      <c r="F8" s="36" t="n"/>
     </row>
     <row r="9"/>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Connection</t>
         </is>
@@ -2449,30 +2746,30 @@
           <t>Account</t>
         </is>
       </c>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n"/>
-      <c r="K11" s="35" t="n"/>
-      <c r="L11" s="35" t="n"/>
-      <c r="M11" s="35" t="n"/>
-      <c r="N11" s="35" t="n"/>
-      <c r="O11" s="35" t="n"/>
-      <c r="P11" s="35" t="n"/>
-      <c r="Q11" s="35" t="n"/>
-      <c r="R11" s="35" t="n"/>
-      <c r="S11" s="35" t="n"/>
-      <c r="T11" s="35" t="n"/>
-      <c r="U11" s="35" t="n"/>
-      <c r="V11" s="35" t="n"/>
-      <c r="W11" s="35" t="n"/>
-      <c r="X11" s="35" t="n"/>
-      <c r="Y11" s="35" t="n"/>
-      <c r="Z11" s="35" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
+      <c r="L11" s="36" t="n"/>
+      <c r="M11" s="36" t="n"/>
+      <c r="N11" s="36" t="n"/>
+      <c r="O11" s="36" t="n"/>
+      <c r="P11" s="36" t="n"/>
+      <c r="Q11" s="36" t="n"/>
+      <c r="R11" s="36" t="n"/>
+      <c r="S11" s="36" t="n"/>
+      <c r="T11" s="36" t="n"/>
+      <c r="U11" s="36" t="n"/>
+      <c r="V11" s="36" t="n"/>
+      <c r="W11" s="36" t="n"/>
+      <c r="X11" s="36" t="n"/>
+      <c r="Y11" s="36" t="n"/>
+      <c r="Z11" s="36" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
@@ -2480,34 +2777,34 @@
           <t>Catalog</t>
         </is>
       </c>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>iceberg</t>
         </is>
       </c>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
-      <c r="K12" s="35" t="n"/>
-      <c r="L12" s="35" t="n"/>
-      <c r="M12" s="35" t="n"/>
-      <c r="N12" s="35" t="n"/>
-      <c r="O12" s="35" t="n"/>
-      <c r="P12" s="35" t="n"/>
-      <c r="Q12" s="35" t="n"/>
-      <c r="R12" s="35" t="n"/>
-      <c r="S12" s="35" t="n"/>
-      <c r="T12" s="35" t="n"/>
-      <c r="U12" s="35" t="n"/>
-      <c r="V12" s="35" t="n"/>
-      <c r="W12" s="35" t="n"/>
-      <c r="X12" s="35" t="n"/>
-      <c r="Y12" s="35" t="n"/>
-      <c r="Z12" s="35" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
+      <c r="L12" s="36" t="n"/>
+      <c r="M12" s="36" t="n"/>
+      <c r="N12" s="36" t="n"/>
+      <c r="O12" s="36" t="n"/>
+      <c r="P12" s="36" t="n"/>
+      <c r="Q12" s="36" t="n"/>
+      <c r="R12" s="36" t="n"/>
+      <c r="S12" s="36" t="n"/>
+      <c r="T12" s="36" t="n"/>
+      <c r="U12" s="36" t="n"/>
+      <c r="V12" s="36" t="n"/>
+      <c r="W12" s="36" t="n"/>
+      <c r="X12" s="36" t="n"/>
+      <c r="Y12" s="36" t="n"/>
+      <c r="Z12" s="36" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
@@ -2515,30 +2812,30 @@
           <t>Catalog URL</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="35" t="n"/>
-      <c r="K13" s="35" t="n"/>
-      <c r="L13" s="35" t="n"/>
-      <c r="M13" s="35" t="n"/>
-      <c r="N13" s="35" t="n"/>
-      <c r="O13" s="35" t="n"/>
-      <c r="P13" s="35" t="n"/>
-      <c r="Q13" s="35" t="n"/>
-      <c r="R13" s="35" t="n"/>
-      <c r="S13" s="35" t="n"/>
-      <c r="T13" s="35" t="n"/>
-      <c r="U13" s="35" t="n"/>
-      <c r="V13" s="35" t="n"/>
-      <c r="W13" s="35" t="n"/>
-      <c r="X13" s="35" t="n"/>
-      <c r="Y13" s="35" t="n"/>
-      <c r="Z13" s="35" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="36" t="n"/>
+      <c r="L13" s="36" t="n"/>
+      <c r="M13" s="36" t="n"/>
+      <c r="N13" s="36" t="n"/>
+      <c r="O13" s="36" t="n"/>
+      <c r="P13" s="36" t="n"/>
+      <c r="Q13" s="36" t="n"/>
+      <c r="R13" s="36" t="n"/>
+      <c r="S13" s="36" t="n"/>
+      <c r="T13" s="36" t="n"/>
+      <c r="U13" s="36" t="n"/>
+      <c r="V13" s="36" t="n"/>
+      <c r="W13" s="36" t="n"/>
+      <c r="X13" s="36" t="n"/>
+      <c r="Y13" s="36" t="n"/>
+      <c r="Z13" s="36" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
@@ -2546,30 +2843,30 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
-      <c r="L14" s="35" t="n"/>
-      <c r="M14" s="35" t="n"/>
-      <c r="N14" s="35" t="n"/>
-      <c r="O14" s="35" t="n"/>
-      <c r="P14" s="35" t="n"/>
-      <c r="Q14" s="35" t="n"/>
-      <c r="R14" s="35" t="n"/>
-      <c r="S14" s="35" t="n"/>
-      <c r="T14" s="35" t="n"/>
-      <c r="U14" s="35" t="n"/>
-      <c r="V14" s="35" t="n"/>
-      <c r="W14" s="35" t="n"/>
-      <c r="X14" s="35" t="n"/>
-      <c r="Y14" s="35" t="n"/>
-      <c r="Z14" s="35" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="36" t="n"/>
+      <c r="N14" s="36" t="n"/>
+      <c r="O14" s="36" t="n"/>
+      <c r="P14" s="36" t="n"/>
+      <c r="Q14" s="36" t="n"/>
+      <c r="R14" s="36" t="n"/>
+      <c r="S14" s="36" t="n"/>
+      <c r="T14" s="36" t="n"/>
+      <c r="U14" s="36" t="n"/>
+      <c r="V14" s="36" t="n"/>
+      <c r="W14" s="36" t="n"/>
+      <c r="X14" s="36" t="n"/>
+      <c r="Y14" s="36" t="n"/>
+      <c r="Z14" s="36" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
@@ -2577,34 +2874,34 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>shipments_v1</t>
         </is>
       </c>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
-      <c r="J15" s="35" t="n"/>
-      <c r="K15" s="35" t="n"/>
-      <c r="L15" s="35" t="n"/>
-      <c r="M15" s="35" t="n"/>
-      <c r="N15" s="35" t="n"/>
-      <c r="O15" s="35" t="n"/>
-      <c r="P15" s="35" t="n"/>
-      <c r="Q15" s="35" t="n"/>
-      <c r="R15" s="35" t="n"/>
-      <c r="S15" s="35" t="n"/>
-      <c r="T15" s="35" t="n"/>
-      <c r="U15" s="35" t="n"/>
-      <c r="V15" s="35" t="n"/>
-      <c r="W15" s="35" t="n"/>
-      <c r="X15" s="35" t="n"/>
-      <c r="Y15" s="35" t="n"/>
-      <c r="Z15" s="35" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="36" t="n"/>
+      <c r="N15" s="36" t="n"/>
+      <c r="O15" s="36" t="n"/>
+      <c r="P15" s="36" t="n"/>
+      <c r="Q15" s="36" t="n"/>
+      <c r="R15" s="36" t="n"/>
+      <c r="S15" s="36" t="n"/>
+      <c r="T15" s="36" t="n"/>
+      <c r="U15" s="36" t="n"/>
+      <c r="V15" s="36" t="n"/>
+      <c r="W15" s="36" t="n"/>
+      <c r="X15" s="36" t="n"/>
+      <c r="Y15" s="36" t="n"/>
+      <c r="Z15" s="36" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
@@ -2612,30 +2909,30 @@
           <t>Delimiter</t>
         </is>
       </c>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="35" t="n"/>
-      <c r="K16" s="35" t="n"/>
-      <c r="L16" s="35" t="n"/>
-      <c r="M16" s="35" t="n"/>
-      <c r="N16" s="35" t="n"/>
-      <c r="O16" s="35" t="n"/>
-      <c r="P16" s="35" t="n"/>
-      <c r="Q16" s="35" t="n"/>
-      <c r="R16" s="35" t="n"/>
-      <c r="S16" s="35" t="n"/>
-      <c r="T16" s="35" t="n"/>
-      <c r="U16" s="35" t="n"/>
-      <c r="V16" s="35" t="n"/>
-      <c r="W16" s="35" t="n"/>
-      <c r="X16" s="35" t="n"/>
-      <c r="Y16" s="35" t="n"/>
-      <c r="Z16" s="35" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="36" t="n"/>
+      <c r="N16" s="36" t="n"/>
+      <c r="O16" s="36" t="n"/>
+      <c r="P16" s="36" t="n"/>
+      <c r="Q16" s="36" t="n"/>
+      <c r="R16" s="36" t="n"/>
+      <c r="S16" s="36" t="n"/>
+      <c r="T16" s="36" t="n"/>
+      <c r="U16" s="36" t="n"/>
+      <c r="V16" s="36" t="n"/>
+      <c r="W16" s="36" t="n"/>
+      <c r="X16" s="36" t="n"/>
+      <c r="Y16" s="36" t="n"/>
+      <c r="Z16" s="36" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
@@ -2643,30 +2940,30 @@
           <t>Encoding</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="35" t="n"/>
-      <c r="J17" s="35" t="n"/>
-      <c r="K17" s="35" t="n"/>
-      <c r="L17" s="35" t="n"/>
-      <c r="M17" s="35" t="n"/>
-      <c r="N17" s="35" t="n"/>
-      <c r="O17" s="35" t="n"/>
-      <c r="P17" s="35" t="n"/>
-      <c r="Q17" s="35" t="n"/>
-      <c r="R17" s="35" t="n"/>
-      <c r="S17" s="35" t="n"/>
-      <c r="T17" s="35" t="n"/>
-      <c r="U17" s="35" t="n"/>
-      <c r="V17" s="35" t="n"/>
-      <c r="W17" s="35" t="n"/>
-      <c r="X17" s="35" t="n"/>
-      <c r="Y17" s="35" t="n"/>
-      <c r="Z17" s="35" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="36" t="n"/>
+      <c r="M17" s="36" t="n"/>
+      <c r="N17" s="36" t="n"/>
+      <c r="O17" s="36" t="n"/>
+      <c r="P17" s="36" t="n"/>
+      <c r="Q17" s="36" t="n"/>
+      <c r="R17" s="36" t="n"/>
+      <c r="S17" s="36" t="n"/>
+      <c r="T17" s="36" t="n"/>
+      <c r="U17" s="36" t="n"/>
+      <c r="V17" s="36" t="n"/>
+      <c r="W17" s="36" t="n"/>
+      <c r="X17" s="36" t="n"/>
+      <c r="Y17" s="36" t="n"/>
+      <c r="Z17" s="36" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="B18" s="2" t="inlineStr">
@@ -2674,30 +2971,30 @@
           <t>Endpoint URL</t>
         </is>
       </c>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
-      <c r="K18" s="35" t="n"/>
-      <c r="L18" s="35" t="n"/>
-      <c r="M18" s="35" t="n"/>
-      <c r="N18" s="35" t="n"/>
-      <c r="O18" s="35" t="n"/>
-      <c r="P18" s="35" t="n"/>
-      <c r="Q18" s="35" t="n"/>
-      <c r="R18" s="35" t="n"/>
-      <c r="S18" s="35" t="n"/>
-      <c r="T18" s="35" t="n"/>
-      <c r="U18" s="35" t="n"/>
-      <c r="V18" s="35" t="n"/>
-      <c r="W18" s="35" t="n"/>
-      <c r="X18" s="35" t="n"/>
-      <c r="Y18" s="35" t="n"/>
-      <c r="Z18" s="35" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="36" t="n"/>
+      <c r="N18" s="36" t="n"/>
+      <c r="O18" s="36" t="n"/>
+      <c r="P18" s="36" t="n"/>
+      <c r="Q18" s="36" t="n"/>
+      <c r="R18" s="36" t="n"/>
+      <c r="S18" s="36" t="n"/>
+      <c r="T18" s="36" t="n"/>
+      <c r="U18" s="36" t="n"/>
+      <c r="V18" s="36" t="n"/>
+      <c r="W18" s="36" t="n"/>
+      <c r="X18" s="36" t="n"/>
+      <c r="Y18" s="36" t="n"/>
+      <c r="Z18" s="36" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="B19" s="2" t="inlineStr">
@@ -2705,34 +3002,34 @@
           <t>Format</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>avro</t>
         </is>
       </c>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
-      <c r="J19" s="35" t="n"/>
-      <c r="K19" s="35" t="n"/>
-      <c r="L19" s="35" t="n"/>
-      <c r="M19" s="35" t="n"/>
-      <c r="N19" s="35" t="n"/>
-      <c r="O19" s="35" t="n"/>
-      <c r="P19" s="35" t="n"/>
-      <c r="Q19" s="35" t="n"/>
-      <c r="R19" s="35" t="n"/>
-      <c r="S19" s="35" t="n"/>
-      <c r="T19" s="35" t="n"/>
-      <c r="U19" s="35" t="n"/>
-      <c r="V19" s="35" t="n"/>
-      <c r="W19" s="35" t="n"/>
-      <c r="X19" s="35" t="n"/>
-      <c r="Y19" s="35" t="n"/>
-      <c r="Z19" s="35" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="36" t="n"/>
+      <c r="N19" s="36" t="n"/>
+      <c r="O19" s="36" t="n"/>
+      <c r="P19" s="36" t="n"/>
+      <c r="Q19" s="36" t="n"/>
+      <c r="R19" s="36" t="n"/>
+      <c r="S19" s="36" t="n"/>
+      <c r="T19" s="36" t="n"/>
+      <c r="U19" s="36" t="n"/>
+      <c r="V19" s="36" t="n"/>
+      <c r="W19" s="36" t="n"/>
+      <c r="X19" s="36" t="n"/>
+      <c r="Y19" s="36" t="n"/>
+      <c r="Z19" s="36" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
@@ -2740,38 +3037,38 @@
           <t>Host</t>
         </is>
       </c>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>trino.example.com</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>kafka.example.com:9092</t>
         </is>
       </c>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="35" t="n"/>
-      <c r="K20" s="35" t="n"/>
-      <c r="L20" s="35" t="n"/>
-      <c r="M20" s="35" t="n"/>
-      <c r="N20" s="35" t="n"/>
-      <c r="O20" s="35" t="n"/>
-      <c r="P20" s="35" t="n"/>
-      <c r="Q20" s="35" t="n"/>
-      <c r="R20" s="35" t="n"/>
-      <c r="S20" s="35" t="n"/>
-      <c r="T20" s="35" t="n"/>
-      <c r="U20" s="35" t="n"/>
-      <c r="V20" s="35" t="n"/>
-      <c r="W20" s="35" t="n"/>
-      <c r="X20" s="35" t="n"/>
-      <c r="Y20" s="35" t="n"/>
-      <c r="Z20" s="35" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="36" t="n"/>
+      <c r="N20" s="36" t="n"/>
+      <c r="O20" s="36" t="n"/>
+      <c r="P20" s="36" t="n"/>
+      <c r="Q20" s="36" t="n"/>
+      <c r="R20" s="36" t="n"/>
+      <c r="S20" s="36" t="n"/>
+      <c r="T20" s="36" t="n"/>
+      <c r="U20" s="36" t="n"/>
+      <c r="V20" s="36" t="n"/>
+      <c r="W20" s="36" t="n"/>
+      <c r="X20" s="36" t="n"/>
+      <c r="Y20" s="36" t="n"/>
+      <c r="Z20" s="36" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="2" t="inlineStr">
@@ -2779,30 +3076,30 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="35" t="n"/>
-      <c r="K21" s="35" t="n"/>
-      <c r="L21" s="35" t="n"/>
-      <c r="M21" s="35" t="n"/>
-      <c r="N21" s="35" t="n"/>
-      <c r="O21" s="35" t="n"/>
-      <c r="P21" s="35" t="n"/>
-      <c r="Q21" s="35" t="n"/>
-      <c r="R21" s="35" t="n"/>
-      <c r="S21" s="35" t="n"/>
-      <c r="T21" s="35" t="n"/>
-      <c r="U21" s="35" t="n"/>
-      <c r="V21" s="35" t="n"/>
-      <c r="W21" s="35" t="n"/>
-      <c r="X21" s="35" t="n"/>
-      <c r="Y21" s="35" t="n"/>
-      <c r="Z21" s="35" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="M21" s="36" t="n"/>
+      <c r="N21" s="36" t="n"/>
+      <c r="O21" s="36" t="n"/>
+      <c r="P21" s="36" t="n"/>
+      <c r="Q21" s="36" t="n"/>
+      <c r="R21" s="36" t="n"/>
+      <c r="S21" s="36" t="n"/>
+      <c r="T21" s="36" t="n"/>
+      <c r="U21" s="36" t="n"/>
+      <c r="V21" s="36" t="n"/>
+      <c r="W21" s="36" t="n"/>
+      <c r="X21" s="36" t="n"/>
+      <c r="Y21" s="36" t="n"/>
+      <c r="Z21" s="36" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
@@ -2810,30 +3107,30 @@
           <t>Namespace</t>
         </is>
       </c>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="35" t="n"/>
-      <c r="J22" s="35" t="n"/>
-      <c r="K22" s="35" t="n"/>
-      <c r="L22" s="35" t="n"/>
-      <c r="M22" s="35" t="n"/>
-      <c r="N22" s="35" t="n"/>
-      <c r="O22" s="35" t="n"/>
-      <c r="P22" s="35" t="n"/>
-      <c r="Q22" s="35" t="n"/>
-      <c r="R22" s="35" t="n"/>
-      <c r="S22" s="35" t="n"/>
-      <c r="T22" s="35" t="n"/>
-      <c r="U22" s="35" t="n"/>
-      <c r="V22" s="35" t="n"/>
-      <c r="W22" s="35" t="n"/>
-      <c r="X22" s="35" t="n"/>
-      <c r="Y22" s="35" t="n"/>
-      <c r="Z22" s="35" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="36" t="n"/>
+      <c r="N22" s="36" t="n"/>
+      <c r="O22" s="36" t="n"/>
+      <c r="P22" s="36" t="n"/>
+      <c r="Q22" s="36" t="n"/>
+      <c r="R22" s="36" t="n"/>
+      <c r="S22" s="36" t="n"/>
+      <c r="T22" s="36" t="n"/>
+      <c r="U22" s="36" t="n"/>
+      <c r="V22" s="36" t="n"/>
+      <c r="W22" s="36" t="n"/>
+      <c r="X22" s="36" t="n"/>
+      <c r="Y22" s="36" t="n"/>
+      <c r="Z22" s="36" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="2" t="inlineStr">
@@ -2841,30 +3138,30 @@
           <t>Path</t>
         </is>
       </c>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
-      <c r="J23" s="35" t="n"/>
-      <c r="K23" s="35" t="n"/>
-      <c r="L23" s="35" t="n"/>
-      <c r="M23" s="35" t="n"/>
-      <c r="N23" s="35" t="n"/>
-      <c r="O23" s="35" t="n"/>
-      <c r="P23" s="35" t="n"/>
-      <c r="Q23" s="35" t="n"/>
-      <c r="R23" s="35" t="n"/>
-      <c r="S23" s="35" t="n"/>
-      <c r="T23" s="35" t="n"/>
-      <c r="U23" s="35" t="n"/>
-      <c r="V23" s="35" t="n"/>
-      <c r="W23" s="35" t="n"/>
-      <c r="X23" s="35" t="n"/>
-      <c r="Y23" s="35" t="n"/>
-      <c r="Z23" s="35" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="36" t="n"/>
+      <c r="N23" s="36" t="n"/>
+      <c r="O23" s="36" t="n"/>
+      <c r="P23" s="36" t="n"/>
+      <c r="Q23" s="36" t="n"/>
+      <c r="R23" s="36" t="n"/>
+      <c r="S23" s="36" t="n"/>
+      <c r="T23" s="36" t="n"/>
+      <c r="U23" s="36" t="n"/>
+      <c r="V23" s="36" t="n"/>
+      <c r="W23" s="36" t="n"/>
+      <c r="X23" s="36" t="n"/>
+      <c r="Y23" s="36" t="n"/>
+      <c r="Z23" s="36" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="2" t="inlineStr">
@@ -2872,34 +3169,34 @@
           <t>Port</t>
         </is>
       </c>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>${TRINO_PORT}</t>
         </is>
       </c>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="35" t="n"/>
-      <c r="K24" s="35" t="n"/>
-      <c r="L24" s="35" t="n"/>
-      <c r="M24" s="35" t="n"/>
-      <c r="N24" s="35" t="n"/>
-      <c r="O24" s="35" t="n"/>
-      <c r="P24" s="35" t="n"/>
-      <c r="Q24" s="35" t="n"/>
-      <c r="R24" s="35" t="n"/>
-      <c r="S24" s="35" t="n"/>
-      <c r="T24" s="35" t="n"/>
-      <c r="U24" s="35" t="n"/>
-      <c r="V24" s="35" t="n"/>
-      <c r="W24" s="35" t="n"/>
-      <c r="X24" s="35" t="n"/>
-      <c r="Y24" s="35" t="n"/>
-      <c r="Z24" s="35" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="36" t="n"/>
+      <c r="N24" s="36" t="n"/>
+      <c r="O24" s="36" t="n"/>
+      <c r="P24" s="36" t="n"/>
+      <c r="Q24" s="36" t="n"/>
+      <c r="R24" s="36" t="n"/>
+      <c r="S24" s="36" t="n"/>
+      <c r="T24" s="36" t="n"/>
+      <c r="U24" s="36" t="n"/>
+      <c r="V24" s="36" t="n"/>
+      <c r="W24" s="36" t="n"/>
+      <c r="X24" s="36" t="n"/>
+      <c r="Y24" s="36" t="n"/>
+      <c r="Z24" s="36" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="2" t="inlineStr">
@@ -2907,34 +3204,34 @@
           <t>Project</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>acme_shipments_prod</t>
         </is>
       </c>
-      <c r="D25" s="35" t="n"/>
-      <c r="E25" s="35" t="n"/>
-      <c r="F25" s="35" t="n"/>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="35" t="n"/>
-      <c r="K25" s="35" t="n"/>
-      <c r="L25" s="35" t="n"/>
-      <c r="M25" s="35" t="n"/>
-      <c r="N25" s="35" t="n"/>
-      <c r="O25" s="35" t="n"/>
-      <c r="P25" s="35" t="n"/>
-      <c r="Q25" s="35" t="n"/>
-      <c r="R25" s="35" t="n"/>
-      <c r="S25" s="35" t="n"/>
-      <c r="T25" s="35" t="n"/>
-      <c r="U25" s="35" t="n"/>
-      <c r="V25" s="35" t="n"/>
-      <c r="W25" s="35" t="n"/>
-      <c r="X25" s="35" t="n"/>
-      <c r="Y25" s="35" t="n"/>
-      <c r="Z25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="36" t="n"/>
+      <c r="N25" s="36" t="n"/>
+      <c r="O25" s="36" t="n"/>
+      <c r="P25" s="36" t="n"/>
+      <c r="Q25" s="36" t="n"/>
+      <c r="R25" s="36" t="n"/>
+      <c r="S25" s="36" t="n"/>
+      <c r="T25" s="36" t="n"/>
+      <c r="U25" s="36" t="n"/>
+      <c r="V25" s="36" t="n"/>
+      <c r="W25" s="36" t="n"/>
+      <c r="X25" s="36" t="n"/>
+      <c r="Y25" s="36" t="n"/>
+      <c r="Z25" s="36" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="B26" s="2" t="inlineStr">
@@ -2942,30 +3239,30 @@
           <t>Region</t>
         </is>
       </c>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="35" t="n"/>
-      <c r="K26" s="35" t="n"/>
-      <c r="L26" s="35" t="n"/>
-      <c r="M26" s="35" t="n"/>
-      <c r="N26" s="35" t="n"/>
-      <c r="O26" s="35" t="n"/>
-      <c r="P26" s="35" t="n"/>
-      <c r="Q26" s="35" t="n"/>
-      <c r="R26" s="35" t="n"/>
-      <c r="S26" s="35" t="n"/>
-      <c r="T26" s="35" t="n"/>
-      <c r="U26" s="35" t="n"/>
-      <c r="V26" s="35" t="n"/>
-      <c r="W26" s="35" t="n"/>
-      <c r="X26" s="35" t="n"/>
-      <c r="Y26" s="35" t="n"/>
-      <c r="Z26" s="35" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="36" t="n"/>
+      <c r="O26" s="36" t="n"/>
+      <c r="P26" s="36" t="n"/>
+      <c r="Q26" s="36" t="n"/>
+      <c r="R26" s="36" t="n"/>
+      <c r="S26" s="36" t="n"/>
+      <c r="T26" s="36" t="n"/>
+      <c r="U26" s="36" t="n"/>
+      <c r="V26" s="36" t="n"/>
+      <c r="W26" s="36" t="n"/>
+      <c r="X26" s="36" t="n"/>
+      <c r="Y26" s="36" t="n"/>
+      <c r="Z26" s="36" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
@@ -2973,30 +3270,30 @@
           <t>Region Name</t>
         </is>
       </c>
-      <c r="C27" s="35" t="n"/>
-      <c r="D27" s="35" t="n"/>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="35" t="n"/>
-      <c r="G27" s="35" t="n"/>
-      <c r="H27" s="35" t="n"/>
-      <c r="I27" s="35" t="n"/>
-      <c r="J27" s="35" t="n"/>
-      <c r="K27" s="35" t="n"/>
-      <c r="L27" s="35" t="n"/>
-      <c r="M27" s="35" t="n"/>
-      <c r="N27" s="35" t="n"/>
-      <c r="O27" s="35" t="n"/>
-      <c r="P27" s="35" t="n"/>
-      <c r="Q27" s="35" t="n"/>
-      <c r="R27" s="35" t="n"/>
-      <c r="S27" s="35" t="n"/>
-      <c r="T27" s="35" t="n"/>
-      <c r="U27" s="35" t="n"/>
-      <c r="V27" s="35" t="n"/>
-      <c r="W27" s="35" t="n"/>
-      <c r="X27" s="35" t="n"/>
-      <c r="Y27" s="35" t="n"/>
-      <c r="Z27" s="35" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="36" t="n"/>
+      <c r="N27" s="36" t="n"/>
+      <c r="O27" s="36" t="n"/>
+      <c r="P27" s="36" t="n"/>
+      <c r="Q27" s="36" t="n"/>
+      <c r="R27" s="36" t="n"/>
+      <c r="S27" s="36" t="n"/>
+      <c r="T27" s="36" t="n"/>
+      <c r="U27" s="36" t="n"/>
+      <c r="V27" s="36" t="n"/>
+      <c r="W27" s="36" t="n"/>
+      <c r="X27" s="36" t="n"/>
+      <c r="Y27" s="36" t="n"/>
+      <c r="Z27" s="36" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="2" t="inlineStr">
@@ -3004,34 +3301,34 @@
           <t>Schema</t>
         </is>
       </c>
-      <c r="C28" s="35" t="n"/>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="E28" s="35" t="n"/>
-      <c r="F28" s="35" t="n"/>
-      <c r="G28" s="35" t="n"/>
-      <c r="H28" s="35" t="n"/>
-      <c r="I28" s="35" t="n"/>
-      <c r="J28" s="35" t="n"/>
-      <c r="K28" s="35" t="n"/>
-      <c r="L28" s="35" t="n"/>
-      <c r="M28" s="35" t="n"/>
-      <c r="N28" s="35" t="n"/>
-      <c r="O28" s="35" t="n"/>
-      <c r="P28" s="35" t="n"/>
-      <c r="Q28" s="35" t="n"/>
-      <c r="R28" s="35" t="n"/>
-      <c r="S28" s="35" t="n"/>
-      <c r="T28" s="35" t="n"/>
-      <c r="U28" s="35" t="n"/>
-      <c r="V28" s="35" t="n"/>
-      <c r="W28" s="35" t="n"/>
-      <c r="X28" s="35" t="n"/>
-      <c r="Y28" s="35" t="n"/>
-      <c r="Z28" s="35" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="36" t="n"/>
+      <c r="I28" s="36" t="n"/>
+      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="36" t="n"/>
+      <c r="L28" s="36" t="n"/>
+      <c r="M28" s="36" t="n"/>
+      <c r="N28" s="36" t="n"/>
+      <c r="O28" s="36" t="n"/>
+      <c r="P28" s="36" t="n"/>
+      <c r="Q28" s="36" t="n"/>
+      <c r="R28" s="36" t="n"/>
+      <c r="S28" s="36" t="n"/>
+      <c r="T28" s="36" t="n"/>
+      <c r="U28" s="36" t="n"/>
+      <c r="V28" s="36" t="n"/>
+      <c r="W28" s="36" t="n"/>
+      <c r="X28" s="36" t="n"/>
+      <c r="Y28" s="36" t="n"/>
+      <c r="Z28" s="36" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="2" t="inlineStr">
@@ -3039,30 +3336,30 @@
           <t>Service Name</t>
         </is>
       </c>
-      <c r="C29" s="35" t="n"/>
-      <c r="D29" s="35" t="n"/>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="35" t="n"/>
-      <c r="G29" s="35" t="n"/>
-      <c r="H29" s="35" t="n"/>
-      <c r="I29" s="35" t="n"/>
-      <c r="J29" s="35" t="n"/>
-      <c r="K29" s="35" t="n"/>
-      <c r="L29" s="35" t="n"/>
-      <c r="M29" s="35" t="n"/>
-      <c r="N29" s="35" t="n"/>
-      <c r="O29" s="35" t="n"/>
-      <c r="P29" s="35" t="n"/>
-      <c r="Q29" s="35" t="n"/>
-      <c r="R29" s="35" t="n"/>
-      <c r="S29" s="35" t="n"/>
-      <c r="T29" s="35" t="n"/>
-      <c r="U29" s="35" t="n"/>
-      <c r="V29" s="35" t="n"/>
-      <c r="W29" s="35" t="n"/>
-      <c r="X29" s="35" t="n"/>
-      <c r="Y29" s="35" t="n"/>
-      <c r="Z29" s="35" t="n"/>
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="36" t="n"/>
+      <c r="J29" s="36" t="n"/>
+      <c r="K29" s="36" t="n"/>
+      <c r="L29" s="36" t="n"/>
+      <c r="M29" s="36" t="n"/>
+      <c r="N29" s="36" t="n"/>
+      <c r="O29" s="36" t="n"/>
+      <c r="P29" s="36" t="n"/>
+      <c r="Q29" s="36" t="n"/>
+      <c r="R29" s="36" t="n"/>
+      <c r="S29" s="36" t="n"/>
+      <c r="T29" s="36" t="n"/>
+      <c r="U29" s="36" t="n"/>
+      <c r="V29" s="36" t="n"/>
+      <c r="W29" s="36" t="n"/>
+      <c r="X29" s="36" t="n"/>
+      <c r="Y29" s="36" t="n"/>
+      <c r="Z29" s="36" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="2" t="inlineStr">
@@ -3070,30 +3367,30 @@
           <t>Staging Directory</t>
         </is>
       </c>
-      <c r="C30" s="35" t="n"/>
-      <c r="D30" s="35" t="n"/>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="35" t="n"/>
-      <c r="H30" s="35" t="n"/>
-      <c r="I30" s="35" t="n"/>
-      <c r="J30" s="35" t="n"/>
-      <c r="K30" s="35" t="n"/>
-      <c r="L30" s="35" t="n"/>
-      <c r="M30" s="35" t="n"/>
-      <c r="N30" s="35" t="n"/>
-      <c r="O30" s="35" t="n"/>
-      <c r="P30" s="35" t="n"/>
-      <c r="Q30" s="35" t="n"/>
-      <c r="R30" s="35" t="n"/>
-      <c r="S30" s="35" t="n"/>
-      <c r="T30" s="35" t="n"/>
-      <c r="U30" s="35" t="n"/>
-      <c r="V30" s="35" t="n"/>
-      <c r="W30" s="35" t="n"/>
-      <c r="X30" s="35" t="n"/>
-      <c r="Y30" s="35" t="n"/>
-      <c r="Z30" s="35" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
+      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="36" t="n"/>
+      <c r="L30" s="36" t="n"/>
+      <c r="M30" s="36" t="n"/>
+      <c r="N30" s="36" t="n"/>
+      <c r="O30" s="36" t="n"/>
+      <c r="P30" s="36" t="n"/>
+      <c r="Q30" s="36" t="n"/>
+      <c r="R30" s="36" t="n"/>
+      <c r="S30" s="36" t="n"/>
+      <c r="T30" s="36" t="n"/>
+      <c r="U30" s="36" t="n"/>
+      <c r="V30" s="36" t="n"/>
+      <c r="W30" s="36" t="n"/>
+      <c r="X30" s="36" t="n"/>
+      <c r="Y30" s="36" t="n"/>
+      <c r="Z30" s="36" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="2" t="inlineStr">
@@ -3101,30 +3398,30 @@
           <t>Stream</t>
         </is>
       </c>
-      <c r="C31" s="35" t="n"/>
-      <c r="D31" s="35" t="n"/>
-      <c r="E31" s="35" t="n"/>
-      <c r="F31" s="35" t="n"/>
-      <c r="G31" s="35" t="n"/>
-      <c r="H31" s="35" t="n"/>
-      <c r="I31" s="35" t="n"/>
-      <c r="J31" s="35" t="n"/>
-      <c r="K31" s="35" t="n"/>
-      <c r="L31" s="35" t="n"/>
-      <c r="M31" s="35" t="n"/>
-      <c r="N31" s="35" t="n"/>
-      <c r="O31" s="35" t="n"/>
-      <c r="P31" s="35" t="n"/>
-      <c r="Q31" s="35" t="n"/>
-      <c r="R31" s="35" t="n"/>
-      <c r="S31" s="35" t="n"/>
-      <c r="T31" s="35" t="n"/>
-      <c r="U31" s="35" t="n"/>
-      <c r="V31" s="35" t="n"/>
-      <c r="W31" s="35" t="n"/>
-      <c r="X31" s="35" t="n"/>
-      <c r="Y31" s="35" t="n"/>
-      <c r="Z31" s="35" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+      <c r="I31" s="36" t="n"/>
+      <c r="J31" s="36" t="n"/>
+      <c r="K31" s="36" t="n"/>
+      <c r="L31" s="36" t="n"/>
+      <c r="M31" s="36" t="n"/>
+      <c r="N31" s="36" t="n"/>
+      <c r="O31" s="36" t="n"/>
+      <c r="P31" s="36" t="n"/>
+      <c r="Q31" s="36" t="n"/>
+      <c r="R31" s="36" t="n"/>
+      <c r="S31" s="36" t="n"/>
+      <c r="T31" s="36" t="n"/>
+      <c r="U31" s="36" t="n"/>
+      <c r="V31" s="36" t="n"/>
+      <c r="W31" s="36" t="n"/>
+      <c r="X31" s="36" t="n"/>
+      <c r="Y31" s="36" t="n"/>
+      <c r="Z31" s="36" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="2" t="inlineStr">
@@ -3132,30 +3429,30 @@
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="C32" s="35" t="n"/>
-      <c r="D32" s="35" t="n"/>
-      <c r="E32" s="35" t="n"/>
-      <c r="F32" s="35" t="n"/>
-      <c r="G32" s="35" t="n"/>
-      <c r="H32" s="35" t="n"/>
-      <c r="I32" s="35" t="n"/>
-      <c r="J32" s="35" t="n"/>
-      <c r="K32" s="35" t="n"/>
-      <c r="L32" s="35" t="n"/>
-      <c r="M32" s="35" t="n"/>
-      <c r="N32" s="35" t="n"/>
-      <c r="O32" s="35" t="n"/>
-      <c r="P32" s="35" t="n"/>
-      <c r="Q32" s="35" t="n"/>
-      <c r="R32" s="35" t="n"/>
-      <c r="S32" s="35" t="n"/>
-      <c r="T32" s="35" t="n"/>
-      <c r="U32" s="35" t="n"/>
-      <c r="V32" s="35" t="n"/>
-      <c r="W32" s="35" t="n"/>
-      <c r="X32" s="35" t="n"/>
-      <c r="Y32" s="35" t="n"/>
-      <c r="Z32" s="35" t="n"/>
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="36" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="36" t="n"/>
+      <c r="I32" s="36" t="n"/>
+      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
+      <c r="L32" s="36" t="n"/>
+      <c r="M32" s="36" t="n"/>
+      <c r="N32" s="36" t="n"/>
+      <c r="O32" s="36" t="n"/>
+      <c r="P32" s="36" t="n"/>
+      <c r="Q32" s="36" t="n"/>
+      <c r="R32" s="36" t="n"/>
+      <c r="S32" s="36" t="n"/>
+      <c r="T32" s="36" t="n"/>
+      <c r="U32" s="36" t="n"/>
+      <c r="V32" s="36" t="n"/>
+      <c r="W32" s="36" t="n"/>
+      <c r="X32" s="36" t="n"/>
+      <c r="Y32" s="36" t="n"/>
+      <c r="Z32" s="36" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="2" t="inlineStr">
@@ -3163,30 +3460,30 @@
           <t>Workgroup</t>
         </is>
       </c>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="35" t="n"/>
-      <c r="E33" s="35" t="n"/>
-      <c r="F33" s="35" t="n"/>
-      <c r="G33" s="35" t="n"/>
-      <c r="H33" s="35" t="n"/>
-      <c r="I33" s="35" t="n"/>
-      <c r="J33" s="35" t="n"/>
-      <c r="K33" s="35" t="n"/>
-      <c r="L33" s="35" t="n"/>
-      <c r="M33" s="35" t="n"/>
-      <c r="N33" s="35" t="n"/>
-      <c r="O33" s="35" t="n"/>
-      <c r="P33" s="35" t="n"/>
-      <c r="Q33" s="35" t="n"/>
-      <c r="R33" s="35" t="n"/>
-      <c r="S33" s="35" t="n"/>
-      <c r="T33" s="35" t="n"/>
-      <c r="U33" s="35" t="n"/>
-      <c r="V33" s="35" t="n"/>
-      <c r="W33" s="35" t="n"/>
-      <c r="X33" s="35" t="n"/>
-      <c r="Y33" s="35" t="n"/>
-      <c r="Z33" s="35" t="n"/>
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="36" t="n"/>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="36" t="n"/>
+      <c r="I33" s="36" t="n"/>
+      <c r="J33" s="36" t="n"/>
+      <c r="K33" s="36" t="n"/>
+      <c r="L33" s="36" t="n"/>
+      <c r="M33" s="36" t="n"/>
+      <c r="N33" s="36" t="n"/>
+      <c r="O33" s="36" t="n"/>
+      <c r="P33" s="36" t="n"/>
+      <c r="Q33" s="36" t="n"/>
+      <c r="R33" s="36" t="n"/>
+      <c r="S33" s="36" t="n"/>
+      <c r="T33" s="36" t="n"/>
+      <c r="U33" s="36" t="n"/>
+      <c r="V33" s="36" t="n"/>
+      <c r="W33" s="36" t="n"/>
+      <c r="X33" s="36" t="n"/>
+      <c r="Y33" s="36" t="n"/>
+      <c r="Z33" s="36" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1">
@@ -3195,107 +3492,129 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>srv-prod</t>
         </is>
       </c>
-      <c r="D35" s="35" t="n"/>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="35" t="n"/>
-      <c r="G35" s="35" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="35" t="n"/>
-      <c r="J35" s="35" t="n"/>
-      <c r="K35" s="35" t="n"/>
-      <c r="L35" s="35" t="n"/>
-      <c r="M35" s="35" t="n"/>
-      <c r="N35" s="35" t="n"/>
-      <c r="O35" s="35" t="n"/>
-      <c r="P35" s="35" t="n"/>
-      <c r="Q35" s="35" t="n"/>
-      <c r="R35" s="35" t="n"/>
-      <c r="S35" s="35" t="n"/>
-      <c r="T35" s="35" t="n"/>
-      <c r="U35" s="35" t="n"/>
-      <c r="V35" s="35" t="n"/>
-      <c r="W35" s="35" t="n"/>
-      <c r="X35" s="35" t="n"/>
-      <c r="Y35" s="35" t="n"/>
-      <c r="Z35" s="35" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="36" t="n"/>
+      <c r="K35" s="36" t="n"/>
+      <c r="L35" s="36" t="n"/>
+      <c r="M35" s="36" t="n"/>
+      <c r="N35" s="36" t="n"/>
+      <c r="O35" s="36" t="n"/>
+      <c r="P35" s="36" t="n"/>
+      <c r="Q35" s="36" t="n"/>
+      <c r="R35" s="36" t="n"/>
+      <c r="S35" s="36" t="n"/>
+      <c r="T35" s="36" t="n"/>
+      <c r="U35" s="36" t="n"/>
+      <c r="V35" s="36" t="n"/>
+      <c r="W35" s="36" t="n"/>
+      <c r="X35" s="36" t="n"/>
+      <c r="Y35" s="36" t="n"/>
+      <c r="Z35" s="36" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="B37" t="inlineStr">
         <is>
           <t>costCenter</t>
         </is>
       </c>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="35" t="n"/>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="35" t="n"/>
-      <c r="H36" s="35" t="n"/>
-      <c r="I36" s="35" t="n"/>
-      <c r="J36" s="35" t="n"/>
-      <c r="K36" s="35" t="n"/>
-      <c r="L36" s="35" t="n"/>
-      <c r="M36" s="35" t="n"/>
-      <c r="N36" s="35" t="n"/>
-      <c r="O36" s="35" t="n"/>
-      <c r="P36" s="35" t="n"/>
-      <c r="Q36" s="35" t="n"/>
-      <c r="R36" s="35" t="n"/>
-      <c r="S36" s="35" t="n"/>
-      <c r="T36" s="35" t="n"/>
-      <c r="U36" s="35" t="n"/>
-      <c r="V36" s="35" t="n"/>
-      <c r="W36" s="35" t="n"/>
-      <c r="X36" s="35" t="n"/>
-      <c r="Y36" s="35" t="n"/>
-      <c r="Z36" s="35" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>cc-42</t>
         </is>
       </c>
-      <c r="D37" s="35" t="n"/>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="35" t="n"/>
-      <c r="G37" s="35" t="n"/>
-      <c r="H37" s="35" t="n"/>
-      <c r="I37" s="35" t="n"/>
-      <c r="J37" s="35" t="n"/>
-      <c r="K37" s="35" t="n"/>
-      <c r="L37" s="35" t="n"/>
-      <c r="M37" s="35" t="n"/>
-      <c r="N37" s="35" t="n"/>
-      <c r="O37" s="35" t="n"/>
-      <c r="P37" s="35" t="n"/>
-      <c r="Q37" s="35" t="n"/>
-      <c r="R37" s="35" t="n"/>
-      <c r="S37" s="35" t="n"/>
-      <c r="T37" s="35" t="n"/>
-      <c r="U37" s="35" t="n"/>
-      <c r="V37" s="35" t="n"/>
-      <c r="W37" s="35" t="n"/>
-      <c r="X37" s="35" t="n"/>
-      <c r="Y37" s="35" t="n"/>
-      <c r="Z37" s="35" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="36" t="n"/>
+      <c r="K37" s="36" t="n"/>
+      <c r="L37" s="36" t="n"/>
+      <c r="M37" s="36" t="n"/>
+      <c r="N37" s="36" t="n"/>
+      <c r="O37" s="36" t="n"/>
+      <c r="P37" s="36" t="n"/>
+      <c r="Q37" s="36" t="n"/>
+      <c r="R37" s="36" t="n"/>
+      <c r="S37" s="36" t="n"/>
+      <c r="T37" s="36" t="n"/>
+      <c r="U37" s="36" t="n"/>
+      <c r="V37" s="36" t="n"/>
+      <c r="W37" s="36" t="n"/>
+      <c r="X37" s="36" t="n"/>
+      <c r="Y37" s="36" t="n"/>
+      <c r="Z37" s="36" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="36" t="n"/>
+      <c r="F38" s="36" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="36" t="n"/>
+      <c r="I38" s="36" t="n"/>
+      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
+      <c r="L38" s="36" t="n"/>
+      <c r="M38" s="36" t="n"/>
+      <c r="N38" s="36" t="n"/>
+      <c r="O38" s="36" t="n"/>
+      <c r="P38" s="36" t="n"/>
+      <c r="Q38" s="36" t="n"/>
+      <c r="R38" s="36" t="n"/>
+      <c r="S38" s="36" t="n"/>
+      <c r="T38" s="36" t="n"/>
+      <c r="U38" s="36" t="n"/>
+      <c r="V38" s="36" t="n"/>
+      <c r="W38" s="36" t="n"/>
+      <c r="X38" s="36" t="n"/>
+      <c r="Y38" s="36" t="n"/>
+      <c r="Z38" s="36" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="36" t="n"/>
+      <c r="I39" s="36" t="n"/>
+      <c r="J39" s="36" t="n"/>
+      <c r="K39" s="36" t="n"/>
+      <c r="L39" s="36" t="n"/>
+      <c r="M39" s="36" t="n"/>
+      <c r="N39" s="36" t="n"/>
+      <c r="O39" s="36" t="n"/>
+      <c r="P39" s="36" t="n"/>
+      <c r="Q39" s="36" t="n"/>
+      <c r="R39" s="36" t="n"/>
+      <c r="S39" s="36" t="n"/>
+      <c r="T39" s="36" t="n"/>
+      <c r="U39" s="36" t="n"/>
+      <c r="V39" s="36" t="n"/>
+      <c r="W39" s="36" t="n"/>
+      <c r="X39" s="36" t="n"/>
+      <c r="Y39" s="36" t="n"/>
+      <c r="Z39" s="36" t="n"/>
+    </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
@@ -3344,8 +3663,13 @@
     <row r="85" ht="15.75" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="C11:Z33">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B11,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:Z39">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B11,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B37,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -3389,34 +3713,34 @@
     </row>
     <row r="3" ht="15.95" customFormat="1" customHeight="1" s="2"/>
     <row r="4" ht="15.95" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Price Amount</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="15.95" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Price Currency</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15.95" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Price Unit</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Per 1000 requests</t>
         </is>
@@ -3459,7 +3783,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>This section covers custom properties you may find in a data contract.</t>
+          <t>Store additional information about the contract or specific elements of it. This is more fine-grained than the columns for Custom Properties on other sheets.</t>
         </is>
       </c>
     </row>
@@ -3506,356 +3830,372 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr"/>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>additionalField</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>some value</t>
         </is>
       </c>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="n"/>
+      <c r="H5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr"/>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr"/>
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>pii</t>
         </is>
       </c>
-      <c r="D6" s="35" t="b">
+      <c r="D6" s="36" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr"/>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr"/>
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>retentionDays</t>
         </is>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr"/>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr"/>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>sourceSystem</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>The system of record</t>
         </is>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>acme</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>cp-source-system</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr"/>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr"/>
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>dbtVersion</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr"/>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr"/>
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>regions</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>["eu-west", "eu-central"]</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr"/>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr"/>
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>costCenter</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>{"id": 4711, "name": "Fulfillment"}</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr"/>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr"/>
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>github_link</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>https://github.example.com/shipment-specification.yaml</t>
         </is>
       </c>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>sourceTable</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>sap.vbak</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>shipments</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>retention</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>P1Y</t>
         </is>
       </c>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>ISO 8601 retention period</t>
         </is>
       </c>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>shipments.shipment_id</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>external</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr"/>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr"/>
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>costCenter</t>
         </is>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D16" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr"/>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr"/>
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>slack</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>#fulfillment-data</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -3933,220 +4273,220 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>https://example.com/definitions/shipments</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>implementation</t>
         </is>
       </c>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>shipments.shipment_id</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>https://example.com/tutorials/shipment_id</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>tutorial</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>How shipment ids are minted</t>
         </is>
       </c>
-      <c r="F6" s="35" t="n"/>
+      <c r="F6" s="36" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>https://example.com/sla</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>implementation</t>
         </is>
       </c>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr"/>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr"/>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>https://example.com/guidelines</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>tutorial</t>
         </is>
       </c>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr"/>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr"/>
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>https://example.com/data-guidelines.html</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>tutorial</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>Company-wide data guidelines</t>
         </is>
       </c>
-      <c r="F9" s="35" t="n"/>
+      <c r="F9" s="36" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -5431,99 +5771,99 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n"/>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>DataContract</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>apiVersion</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>v3.2.0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
+      <c r="A6" s="34" t="n"/>
+      <c r="B6" s="34" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>fulfillment_shipments_v1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="33" t="n"/>
+      <c r="A11" s="34" t="n"/>
+      <c r="B11" s="34" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B12" s="43" t="n"/>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="B12" s="46" t="n"/>
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>controlling-team</t>
         </is>
@@ -5531,17 +5871,17 @@
       <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="33" t="n"/>
+      <c r="A13" s="34" t="n"/>
+      <c r="B13" s="34" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n"/>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>sales-team</t>
         </is>
@@ -5549,13 +5889,13 @@
       <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Data Product</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
@@ -5563,93 +5903,93 @@
       <c r="E15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Tenant</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>company-A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n"/>
-      <c r="B17" s="33" t="n"/>
+      <c r="A17" s="34" t="n"/>
+      <c r="B17" s="34" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="n"/>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="n"/>
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>This data can be used for analytical purposes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="n"/>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="n"/>
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Limitations</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Not suitable for real-time use cases</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="n"/>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="A21" s="34" t="n"/>
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Usage</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Use this to analyze shipments</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="n"/>
-      <c r="B22" s="33" t="n"/>
+      <c r="A22" s="34" t="n"/>
+      <c r="B22" s="34" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B23" s="33" t="n"/>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>datalocation:EU</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>Context Instructions</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t>Context (Guidance for AI)</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>Join on shipment_id only; delivery_date is in UTC.</t>
         </is>
@@ -5680,8 +6020,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ54"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <dimension ref="A1:AR52"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="34.85546875" customWidth="1" style="2" min="1" max="1"/>
     <col width="24" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -5691,18 +6031,21 @@
     <col width="35.7109375" customWidth="1" style="2" min="6" max="6"/>
     <col width="10" customWidth="1" style="2" min="7" max="8"/>
     <col width="14.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14.28515625" customWidth="1" style="2" min="10" max="10"/>
-    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
-    <col width="28.7109375" bestFit="1" customWidth="1" style="2" min="12" max="12"/>
-    <col width="28.7109375" customWidth="1" style="2" min="13" max="13"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
-    <col width="19" bestFit="1" customWidth="1" style="2" min="15" max="15"/>
-    <col width="19" customWidth="1" style="2" min="16" max="20"/>
-    <col width="21.7109375" bestFit="1" customWidth="1" style="2" min="21" max="21"/>
-    <col width="27.28515625" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
-    <col width="15.42578125" customWidth="1" style="2" min="23" max="37"/>
-    <col width="28.5703125" customWidth="1" style="2" min="38" max="43"/>
-    <col width="8.85546875" customWidth="1" style="2" min="44" max="16384"/>
+    <col width="21" customWidth="1" style="2" min="10" max="11"/>
+    <col width="14.28515625" customWidth="1" style="2" min="12" max="12"/>
+    <col width="28.140625" bestFit="1" customWidth="1" style="2" min="13" max="13"/>
+    <col width="28.7109375" bestFit="1" customWidth="1" style="2" min="14" max="14"/>
+    <col width="28.7109375" customWidth="1" style="2" min="15" max="15"/>
+    <col width="11.7109375" bestFit="1" customWidth="1" style="2" min="16" max="16"/>
+    <col width="19" bestFit="1" customWidth="1" style="2" min="17" max="17"/>
+    <col width="19" customWidth="1" style="2" min="18" max="22"/>
+    <col width="21.7109375" bestFit="1" customWidth="1" style="2" min="23" max="23"/>
+    <col width="27.28515625" bestFit="1" customWidth="1" style="2" min="24" max="24"/>
+    <col width="15.42578125" customWidth="1" style="2" min="25" max="39"/>
+    <col width="21" customWidth="1" style="2" min="40" max="40"/>
+    <col width="28.5703125" customWidth="1" style="2" min="41" max="41"/>
+    <col width="26.7109375" customWidth="1" style="2" min="42" max="44"/>
+    <col width="8.85546875" customWidth="1" style="2" min="45" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5726,426 +6069,598 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="42" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="45" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="42" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="45" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Shipment data with orders, delivery dates, carriers and statuses.</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="42" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="45" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Shipments</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="42" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="45" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Physical Name</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>shipments_v1</t>
         </is>
       </c>
-      <c r="C9" s="41" t="n"/>
-      <c r="D9" s="41" t="n"/>
-      <c r="E9" s="42" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="45" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Data Granularity</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Not Aggregated</t>
         </is>
       </c>
-      <c r="C10" s="41" t="n"/>
-      <c r="D10" s="41" t="n"/>
-      <c r="E10" s="42" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="45" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>pii</t>
         </is>
       </c>
-      <c r="C11" s="41" t="n"/>
-      <c r="D11" s="41" t="n"/>
-      <c r="E11" s="42" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="45" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B12" s="44" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="42" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="B12" s="47" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="45" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Deprecated</t>
         </is>
       </c>
-      <c r="B13" s="44" t="n"/>
-      <c r="C13" s="41" t="n"/>
-      <c r="D13" s="41" t="n"/>
-      <c r="E13" s="42" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>Context Instructions</t>
-        </is>
-      </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="45" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Context (Guidance for AI)</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>Filter on status = 'Delivered' for fulfilment KPIs.</t>
         </is>
       </c>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="42" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
-        <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>sourceTable</t>
-        </is>
-      </c>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="42" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>sap.vbak</t>
-        </is>
-      </c>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="42" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="W17" s="19" t="inlineStr">
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="45" t="n"/>
+    </row>
+    <row r="15">
+      <c r="Y15" s="19" t="inlineStr">
         <is>
           <t>Logical Type Options</t>
         </is>
       </c>
-      <c r="X17" s="20" t="n"/>
-      <c r="Y17" s="20" t="n"/>
-      <c r="Z17" s="20" t="n"/>
-      <c r="AA17" s="20" t="n"/>
-      <c r="AB17" s="20" t="n"/>
-      <c r="AC17" s="20" t="n"/>
-      <c r="AD17" s="20" t="n"/>
-      <c r="AE17" s="20" t="n"/>
-      <c r="AF17" s="20" t="n"/>
-      <c r="AG17" s="20" t="n"/>
-      <c r="AH17" s="20" t="n"/>
-      <c r="AI17" s="20" t="n"/>
-      <c r="AJ17" s="20" t="n"/>
-      <c r="AK17" s="21" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="Z15" s="20" t="n"/>
+      <c r="AA15" s="20" t="n"/>
+      <c r="AB15" s="20" t="n"/>
+      <c r="AC15" s="20" t="n"/>
+      <c r="AD15" s="20" t="n"/>
+      <c r="AE15" s="20" t="n"/>
+      <c r="AF15" s="20" t="n"/>
+      <c r="AG15" s="20" t="n"/>
+      <c r="AH15" s="20" t="n"/>
+      <c r="AI15" s="20" t="n"/>
+      <c r="AJ15" s="20" t="n"/>
+      <c r="AK15" s="20" t="n"/>
+      <c r="AL15" s="20" t="n"/>
+      <c r="AM15" s="21" t="n"/>
+      <c r="AN15" s="40" t="n"/>
+      <c r="AP15" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="AQ15" s="44" t="n"/>
+      <c r="AR15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Logical Type</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Physical Type</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Example(s)</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Deprecated</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Semantic Type</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>Authoritative Definition URL</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>Authoritative Definition Type</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="O16" s="10" t="inlineStr">
         <is>
           <t>Physical Name</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr">
+      <c r="P16" s="10" t="inlineStr">
         <is>
           <t>Primary Key</t>
         </is>
       </c>
-      <c r="O18" s="10" t="inlineStr">
+      <c r="Q16" s="10" t="inlineStr">
         <is>
           <t>Primary Key Position</t>
         </is>
       </c>
-      <c r="P18" s="10" t="inlineStr">
+      <c r="R16" s="10" t="inlineStr">
         <is>
           <t>Partitioned</t>
         </is>
       </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>Partition Key Position</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr">
+      <c r="T16" s="10" t="inlineStr">
         <is>
           <t>Encrypted Name</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="U16" s="10" t="inlineStr">
         <is>
           <t>Transform Sources</t>
         </is>
       </c>
-      <c r="T18" s="10" t="inlineStr">
+      <c r="V16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Transform Logic	</t>
         </is>
       </c>
-      <c r="U18" s="10" t="inlineStr">
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>Transform Description</t>
         </is>
       </c>
-      <c r="V18" s="10" t="inlineStr">
+      <c r="X16" s="10" t="inlineStr">
         <is>
           <t>Critical Data Element Status</t>
         </is>
       </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="Y16" s="10" t="inlineStr">
         <is>
           <t>Maximum Items</t>
         </is>
       </c>
-      <c r="X18" s="10" t="inlineStr">
+      <c r="Z16" s="10" t="inlineStr">
         <is>
           <t>Minimum Items</t>
         </is>
       </c>
-      <c r="Y18" s="10" t="inlineStr">
+      <c r="AA16" s="10" t="inlineStr">
         <is>
           <t>Unique Items</t>
         </is>
       </c>
-      <c r="Z18" s="10" t="inlineStr">
+      <c r="AB16" s="10" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="AA18" s="10" t="inlineStr">
+      <c r="AC16" s="10" t="inlineStr">
         <is>
           <t>Minimum Length</t>
         </is>
       </c>
-      <c r="AB18" s="10" t="inlineStr">
+      <c r="AD16" s="10" t="inlineStr">
         <is>
           <t>Maximum Length</t>
         </is>
       </c>
-      <c r="AC18" s="10" t="inlineStr">
+      <c r="AE16" s="10" t="inlineStr">
         <is>
           <t>Exclusive Minimum</t>
         </is>
       </c>
-      <c r="AD18" s="10" t="inlineStr">
+      <c r="AF16" s="10" t="inlineStr">
         <is>
           <t>Minimum</t>
         </is>
       </c>
-      <c r="AE18" s="10" t="inlineStr">
+      <c r="AG16" s="10" t="inlineStr">
         <is>
           <t>Exclusive Maximum</t>
         </is>
       </c>
-      <c r="AF18" s="10" t="inlineStr">
+      <c r="AH16" s="10" t="inlineStr">
         <is>
           <t>Maximum</t>
         </is>
       </c>
-      <c r="AG18" s="10" t="inlineStr">
+      <c r="AI16" s="10" t="inlineStr">
         <is>
           <t>Multiple Of</t>
         </is>
       </c>
-      <c r="AH18" s="10" t="inlineStr">
+      <c r="AJ16" s="10" t="inlineStr">
         <is>
           <t>Minimum Properties</t>
         </is>
       </c>
-      <c r="AI18" s="10" t="inlineStr">
+      <c r="AK16" s="10" t="inlineStr">
         <is>
           <t>Maximum Properties</t>
         </is>
       </c>
-      <c r="AJ18" s="10" t="inlineStr">
+      <c r="AL16" s="10" t="inlineStr">
         <is>
           <t>Required Properties</t>
         </is>
       </c>
-      <c r="AK18" s="10" t="inlineStr">
+      <c r="AM16" s="10" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="AL18" s="9" t="inlineStr">
-        <is>
-          <t>Semantic Type</t>
-        </is>
-      </c>
-      <c r="AM18" s="9" t="inlineStr">
-        <is>
-          <t>Deprecated</t>
-        </is>
-      </c>
-      <c r="AN18" s="9" t="inlineStr">
+      <c r="AN16" s="9" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="AO16" s="9" t="inlineStr">
         <is>
           <t>Comments (internal)</t>
         </is>
       </c>
-      <c r="AO18" s="9" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="AP18" s="9" t="inlineStr">
-        <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="AQ18" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
+      <c r="AP16" s="9" t="inlineStr">
+        <is>
+          <t>masked</t>
+        </is>
+      </c>
+      <c r="AQ16" s="9" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AR16" s="9" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>shipment_id</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Shipment ID</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>123e4567-e89b-12d3-a456-426614174000</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Unique identifier for each shipment.</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>businesskey</t>
+        </is>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>definitions/shipment_id.odcs.yaml</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>businessDefinition</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="inlineStr">
+        <is>
+          <t>sid</t>
+        </is>
+      </c>
+      <c r="P17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="15" t="n"/>
+      <c r="S17" s="15" t="n"/>
+      <c r="T17" s="15" t="n"/>
+      <c r="U17" s="15" t="inlineStr"/>
+      <c r="V17" s="15" t="n"/>
+      <c r="W17" s="15" t="n"/>
+      <c r="X17" s="15" t="n"/>
+      <c r="Y17" s="15" t="n"/>
+      <c r="Z17" s="15" t="n"/>
+      <c r="AA17" s="15" t="n"/>
+      <c r="AB17" s="15" t="n"/>
+      <c r="AC17" s="15" t="n"/>
+      <c r="AD17" s="15" t="n"/>
+      <c r="AE17" s="15" t="n"/>
+      <c r="AF17" s="15" t="n"/>
+      <c r="AG17" s="15" t="n"/>
+      <c r="AH17" s="15" t="n"/>
+      <c r="AI17" s="15" t="n"/>
+      <c r="AJ17" s="15" t="n"/>
+      <c r="AK17" s="15" t="n"/>
+      <c r="AL17" s="15" t="n"/>
+      <c r="AM17" s="15" t="n"/>
+      <c r="AN17" s="15" t="inlineStr">
+        <is>
+          <t>prop-shipment-id</t>
+        </is>
+      </c>
+      <c r="AO17" s="15" t="n"/>
+      <c r="AP17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="15" t="n"/>
+      <c r="AR17" s="15" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Order ID</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>ORD12345</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Identifier for the order associated with the shipment.</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="inlineStr"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="inlineStr">
+        <is>
+          <t>oid</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="15" t="inlineStr"/>
+      <c r="V18" s="15" t="n"/>
+      <c r="W18" s="15" t="n"/>
+      <c r="X18" s="15" t="n"/>
+      <c r="Y18" s="15" t="n"/>
+      <c r="Z18" s="15" t="n"/>
+      <c r="AA18" s="15" t="n"/>
+      <c r="AB18" s="15" t="n"/>
+      <c r="AC18" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE18" s="15" t="n"/>
+      <c r="AF18" s="15" t="n"/>
+      <c r="AG18" s="15" t="n"/>
+      <c r="AH18" s="15" t="n"/>
+      <c r="AI18" s="15" t="n"/>
+      <c r="AJ18" s="15" t="n"/>
+      <c r="AK18" s="15" t="n"/>
+      <c r="AL18" s="15" t="n"/>
+      <c r="AM18" s="15" t="n"/>
+      <c r="AN18" s="15" t="n"/>
+      <c r="AO18" s="15" t="n"/>
+      <c r="AP18" s="15" t="n"/>
+      <c r="AQ18" s="15" t="n"/>
+      <c r="AR18" s="15" t="n"/>
+    </row>
+    <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>shipment_id</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Shipment ID</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -6155,60 +6670,40 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>123e4567-e89b-12d3-a456-426614174000</t>
+          <t>Delivered,In Transit</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Unique identifier for each shipment.</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
-        <is>
-          <t>businesskey</t>
-        </is>
+          <t>Current status of the shipment.</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>definitions/shipment_id.odcs.yaml</t>
-        </is>
-      </c>
-      <c r="L19" s="15" t="inlineStr">
-        <is>
-          <t>businessDefinition</t>
-        </is>
-      </c>
-      <c r="M19" s="15" t="inlineStr">
-        <is>
-          <t>sid</t>
-        </is>
-      </c>
-      <c r="N19" s="15" t="b">
-        <v>1</v>
-      </c>
+          <t>dimension</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="inlineStr"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
       <c r="P19" s="15" t="n"/>
       <c r="Q19" s="15" t="n"/>
       <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="inlineStr"/>
+      <c r="S19" s="15" t="n"/>
       <c r="T19" s="15" t="n"/>
-      <c r="U19" s="15" t="n"/>
+      <c r="U19" s="15" t="inlineStr"/>
       <c r="V19" s="15" t="n"/>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="15" t="n"/>
@@ -6225,94 +6720,69 @@
       <c r="AI19" s="15" t="n"/>
       <c r="AJ19" s="15" t="n"/>
       <c r="AK19" s="15" t="n"/>
-      <c r="AL19" s="15" t="inlineStr">
-        <is>
-          <t>dimension</t>
-        </is>
-      </c>
+      <c r="AL19" s="15" t="n"/>
       <c r="AM19" s="15" t="n"/>
       <c r="AN19" s="15" t="n"/>
-      <c r="AO19" s="15" t="inlineStr">
-        <is>
-          <t>prop-shipment-id</t>
-        </is>
-      </c>
-      <c r="AP19" s="15" t="inlineStr">
-        <is>
-          <t>masked</t>
-        </is>
-      </c>
-      <c r="AQ19" s="15" t="b">
+      <c r="AO19" s="15" t="n"/>
+      <c r="AP19" s="15" t="n"/>
+      <c r="AQ19" s="15" t="n"/>
+      <c r="AR19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>weight_kg</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr"/>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Weight of the parcel.</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Order ID</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>ORD12345</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>Identifier for the order associated with the shipment.</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>oid</t>
-        </is>
-      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr"/>
+      <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="15" t="n"/>
       <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="inlineStr"/>
+      <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n"/>
-      <c r="U20" s="15" t="n"/>
+      <c r="U20" s="15" t="inlineStr"/>
       <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="n"/>
       <c r="Z20" s="15" t="n"/>
-      <c r="AA20" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB20" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="AA20" s="15" t="n"/>
+      <c r="AB20" s="15" t="n"/>
       <c r="AC20" s="15" t="n"/>
       <c r="AD20" s="15" t="n"/>
       <c r="AE20" s="15" t="n"/>
@@ -6327,54 +6797,61 @@
       <c r="AN20" s="15" t="n"/>
       <c r="AO20" s="15" t="n"/>
       <c r="AP20" s="15" t="n"/>
-      <c r="AQ20" s="15" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="AQ20" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="AR20" s="15" t="n"/>
+    </row>
+    <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>address</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Shipment Address</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>Delivered,In Transit</t>
-        </is>
-      </c>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr"/>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Current status of the shipment.</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="n"/>
+          <t>Shipping address details.</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="b">
+        <v>1</v>
+      </c>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="inlineStr"/>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="n"/>
       <c r="K21" s="15" t="n"/>
-      <c r="L21" s="15" t="n"/>
+      <c r="L21" s="15" t="inlineStr"/>
       <c r="M21" s="15" t="n"/>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
       <c r="P21" s="15" t="n"/>
       <c r="Q21" s="15" t="n"/>
       <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="inlineStr"/>
+      <c r="S21" s="15" t="n"/>
       <c r="T21" s="15" t="n"/>
-      <c r="U21" s="15" t="n"/>
+      <c r="U21" s="15" t="inlineStr"/>
       <c r="V21" s="15" t="n"/>
       <c r="W21" s="15" t="n"/>
       <c r="X21" s="15" t="n"/>
@@ -6391,61 +6868,54 @@
       <c r="AI21" s="15" t="n"/>
       <c r="AJ21" s="15" t="n"/>
       <c r="AK21" s="15" t="n"/>
-      <c r="AL21" s="15" t="inlineStr">
-        <is>
-          <t>dimension</t>
-        </is>
-      </c>
-      <c r="AM21" s="15" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL21" s="15" t="n"/>
+      <c r="AM21" s="15" t="n"/>
       <c r="AN21" s="15" t="n"/>
       <c r="AO21" s="15" t="n"/>
       <c r="AP21" s="15" t="n"/>
       <c r="AQ21" s="15" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="AR21" s="15" t="n"/>
+    </row>
+    <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>weight_kg</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
+          <t>address.street</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr"/>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Weight of the parcel.</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="n"/>
+          <t>Street address.</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="b">
+        <v>1</v>
+      </c>
       <c r="H22" s="15" t="n"/>
       <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="inlineStr"/>
+      <c r="J22" s="15" t="n"/>
       <c r="K22" s="15" t="n"/>
-      <c r="L22" s="15" t="n"/>
+      <c r="L22" s="15" t="inlineStr"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
       <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="inlineStr"/>
+      <c r="S22" s="15" t="n"/>
       <c r="T22" s="15" t="n"/>
-      <c r="U22" s="15" t="n"/>
+      <c r="U22" s="15" t="inlineStr"/>
       <c r="V22" s="15" t="n"/>
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="15" t="n"/>
@@ -6462,75 +6932,54 @@
       <c r="AI22" s="15" t="n"/>
       <c r="AJ22" s="15" t="n"/>
       <c r="AK22" s="15" t="n"/>
-      <c r="AL22" s="15" t="inlineStr">
-        <is>
-          <t>measure</t>
-        </is>
-      </c>
-      <c r="AM22" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="AL22" s="15" t="n"/>
+      <c r="AM22" s="15" t="n"/>
       <c r="AN22" s="15" t="n"/>
       <c r="AO22" s="15" t="n"/>
-      <c r="AP22" s="15" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="AQ22" s="15" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="AP22" s="15" t="n"/>
+      <c r="AQ22" s="15" t="n"/>
+      <c r="AR22" s="15" t="n"/>
+    </row>
+    <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Shipment Address</t>
-        </is>
-      </c>
+          <t>address.country</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n"/>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr"/>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Shipping address details.</t>
+          <t>Country of the shipping address.</t>
         </is>
       </c>
       <c r="G23" s="15" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>restricted</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
       <c r="K23" s="15" t="n"/>
-      <c r="L23" s="15" t="n"/>
+      <c r="L23" s="15" t="inlineStr"/>
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
       <c r="P23" s="15" t="n"/>
       <c r="Q23" s="15" t="n"/>
       <c r="R23" s="15" t="n"/>
-      <c r="S23" s="15" t="inlineStr"/>
+      <c r="S23" s="15" t="n"/>
       <c r="T23" s="15" t="n"/>
-      <c r="U23" s="15" t="n"/>
+      <c r="U23" s="15" t="inlineStr"/>
       <c r="V23" s="15" t="n"/>
       <c r="W23" s="15" t="n"/>
       <c r="X23" s="15" t="n"/>
@@ -6553,47 +7002,46 @@
       <c r="AO23" s="15" t="n"/>
       <c r="AP23" s="15" t="n"/>
       <c r="AQ23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>address.street</t>
+      <c r="AR23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>items</t>
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr"/>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Street address.</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="b">
-        <v>1</v>
-      </c>
+          <t>Line items of the shipment.</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="15" t="n"/>
-      <c r="J24" s="15" t="inlineStr"/>
+      <c r="J24" s="15" t="n"/>
       <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
+      <c r="L24" s="15" t="inlineStr"/>
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="15" t="n"/>
       <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
-      <c r="S24" s="15" t="inlineStr"/>
+      <c r="S24" s="15" t="n"/>
       <c r="T24" s="15" t="n"/>
-      <c r="U24" s="15" t="n"/>
+      <c r="U24" s="15" t="inlineStr"/>
       <c r="V24" s="15" t="n"/>
       <c r="W24" s="15" t="n"/>
       <c r="X24" s="15" t="n"/>
@@ -6616,47 +7064,42 @@
       <c r="AO24" s="15" t="n"/>
       <c r="AP24" s="15" t="n"/>
       <c r="AQ24" s="15" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>address.country</t>
+      <c r="AR24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>items.items</t>
         </is>
       </c>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>json</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>Country of the shipping address.</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
       <c r="H25" s="15" t="n"/>
       <c r="I25" s="15" t="n"/>
-      <c r="J25" s="15" t="inlineStr"/>
+      <c r="J25" s="15" t="n"/>
       <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="n"/>
+      <c r="L25" s="15" t="inlineStr"/>
       <c r="M25" s="15" t="n"/>
       <c r="N25" s="15" t="n"/>
       <c r="O25" s="15" t="n"/>
       <c r="P25" s="15" t="n"/>
       <c r="Q25" s="15" t="n"/>
       <c r="R25" s="15" t="n"/>
-      <c r="S25" s="15" t="inlineStr"/>
+      <c r="S25" s="15" t="n"/>
       <c r="T25" s="15" t="n"/>
-      <c r="U25" s="15" t="n"/>
+      <c r="U25" s="15" t="inlineStr"/>
       <c r="V25" s="15" t="n"/>
       <c r="W25" s="15" t="n"/>
       <c r="X25" s="15" t="n"/>
@@ -6679,45 +7122,42 @@
       <c r="AO25" s="15" t="n"/>
       <c r="AP25" s="15" t="n"/>
       <c r="AQ25" s="15" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="AR25" s="15" t="n"/>
+    </row>
+    <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>items</t>
+          <t>items.items.sku</t>
         </is>
       </c>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr"/>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>Line items of the shipment.</t>
-        </is>
-      </c>
+      <c r="F26" s="15" t="n"/>
       <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
       <c r="I26" s="15" t="n"/>
-      <c r="J26" s="15" t="inlineStr"/>
+      <c r="J26" s="15" t="n"/>
       <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n"/>
+      <c r="L26" s="15" t="inlineStr"/>
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="15" t="n"/>
       <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
-      <c r="S26" s="15" t="inlineStr"/>
+      <c r="S26" s="15" t="n"/>
       <c r="T26" s="15" t="n"/>
-      <c r="U26" s="15" t="n"/>
+      <c r="U26" s="15" t="inlineStr"/>
       <c r="V26" s="15" t="n"/>
       <c r="W26" s="15" t="n"/>
       <c r="X26" s="15" t="n"/>
@@ -6740,30 +7180,23 @@
       <c r="AO26" s="15" t="n"/>
       <c r="AP26" s="15" t="n"/>
       <c r="AQ26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>items.items</t>
-        </is>
-      </c>
+      <c r="AR26" s="15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
       <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="16" t="n"/>
       <c r="F27" s="15" t="n"/>
       <c r="G27" s="15" t="n"/>
       <c r="H27" s="15" t="n"/>
       <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="inlineStr"/>
+      <c r="J27" s="15" t="n"/>
       <c r="K27" s="15" t="n"/>
       <c r="L27" s="15" t="n"/>
       <c r="M27" s="15" t="n"/>
@@ -6772,7 +7205,7 @@
       <c r="P27" s="15" t="n"/>
       <c r="Q27" s="15" t="n"/>
       <c r="R27" s="15" t="n"/>
-      <c r="S27" s="15" t="inlineStr"/>
+      <c r="S27" s="15" t="n"/>
       <c r="T27" s="15" t="n"/>
       <c r="U27" s="15" t="n"/>
       <c r="V27" s="15" t="n"/>
@@ -6797,30 +7230,19 @@
       <c r="AO27" s="15" t="n"/>
       <c r="AP27" s="15" t="n"/>
       <c r="AQ27" s="15" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>items.items.sku</t>
-        </is>
-      </c>
+      <c r="AR27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
       <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="16" t="n"/>
       <c r="F28" s="15" t="n"/>
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
       <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="inlineStr"/>
+      <c r="J28" s="15" t="n"/>
       <c r="K28" s="15" t="n"/>
       <c r="L28" s="15" t="n"/>
       <c r="M28" s="15" t="n"/>
@@ -6829,7 +7251,7 @@
       <c r="P28" s="15" t="n"/>
       <c r="Q28" s="15" t="n"/>
       <c r="R28" s="15" t="n"/>
-      <c r="S28" s="15" t="inlineStr"/>
+      <c r="S28" s="15" t="n"/>
       <c r="T28" s="15" t="n"/>
       <c r="U28" s="15" t="n"/>
       <c r="V28" s="15" t="n"/>
@@ -6852,18 +7274,11 @@
       <c r="AM28" s="15" t="n"/>
       <c r="AN28" s="15" t="n"/>
       <c r="AO28" s="15" t="n"/>
-      <c r="AP28" s="15" t="inlineStr">
-        <is>
-          <t>catalog</t>
-        </is>
-      </c>
-      <c r="AQ28" s="15" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+      <c r="AP28" s="15" t="n"/>
+      <c r="AQ28" s="15" t="n"/>
+      <c r="AR28" s="15" t="n"/>
+    </row>
+    <row r="29">
       <c r="A29" s="17" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="15" t="n"/>
@@ -6907,8 +7322,9 @@
       <c r="AO29" s="15" t="n"/>
       <c r="AP29" s="15" t="n"/>
       <c r="AQ29" s="15" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+      <c r="AR29" s="15" t="n"/>
+    </row>
+    <row r="30">
       <c r="A30" s="17" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="15" t="n"/>
@@ -6952,8 +7368,9 @@
       <c r="AO30" s="15" t="n"/>
       <c r="AP30" s="15" t="n"/>
       <c r="AQ30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+      <c r="AR30" s="15" t="n"/>
+    </row>
+    <row r="31">
       <c r="A31" s="17" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="15" t="n"/>
@@ -6997,8 +7414,9 @@
       <c r="AO31" s="15" t="n"/>
       <c r="AP31" s="15" t="n"/>
       <c r="AQ31" s="15" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
+      <c r="AR31" s="15" t="n"/>
+    </row>
+    <row r="32">
       <c r="A32" s="17" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="15" t="n"/>
@@ -7042,8 +7460,9 @@
       <c r="AO32" s="15" t="n"/>
       <c r="AP32" s="15" t="n"/>
       <c r="AQ32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
+      <c r="AR32" s="15" t="n"/>
+    </row>
+    <row r="33">
       <c r="A33" s="17" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="15" t="n"/>
@@ -7087,8 +7506,9 @@
       <c r="AO33" s="15" t="n"/>
       <c r="AP33" s="15" t="n"/>
       <c r="AQ33" s="15" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+      <c r="AR33" s="15" t="n"/>
+    </row>
+    <row r="34">
       <c r="A34" s="17" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="15" t="n"/>
@@ -7132,8 +7552,9 @@
       <c r="AO34" s="15" t="n"/>
       <c r="AP34" s="15" t="n"/>
       <c r="AQ34" s="15" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
+      <c r="AR34" s="15" t="n"/>
+    </row>
+    <row r="35">
       <c r="A35" s="17" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="15" t="n"/>
@@ -7177,8 +7598,9 @@
       <c r="AO35" s="15" t="n"/>
       <c r="AP35" s="15" t="n"/>
       <c r="AQ35" s="15" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
+      <c r="AR35" s="15" t="n"/>
+    </row>
+    <row r="36">
       <c r="A36" s="17" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="15" t="n"/>
@@ -7222,8 +7644,9 @@
       <c r="AO36" s="15" t="n"/>
       <c r="AP36" s="15" t="n"/>
       <c r="AQ36" s="15" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
+      <c r="AR36" s="15" t="n"/>
+    </row>
+    <row r="37">
       <c r="A37" s="17" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="15" t="n"/>
@@ -7267,8 +7690,9 @@
       <c r="AO37" s="15" t="n"/>
       <c r="AP37" s="15" t="n"/>
       <c r="AQ37" s="15" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
+      <c r="AR37" s="15" t="n"/>
+    </row>
+    <row r="38">
       <c r="A38" s="17" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="15" t="n"/>
@@ -7312,8 +7736,9 @@
       <c r="AO38" s="15" t="n"/>
       <c r="AP38" s="15" t="n"/>
       <c r="AQ38" s="15" t="n"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
+      <c r="AR38" s="15" t="n"/>
+    </row>
+    <row r="39">
       <c r="A39" s="17" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="15" t="n"/>
@@ -7357,8 +7782,9 @@
       <c r="AO39" s="15" t="n"/>
       <c r="AP39" s="15" t="n"/>
       <c r="AQ39" s="15" t="n"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+      <c r="AR39" s="15" t="n"/>
+    </row>
+    <row r="40">
       <c r="A40" s="17" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="15" t="n"/>
@@ -7402,8 +7828,9 @@
       <c r="AO40" s="15" t="n"/>
       <c r="AP40" s="15" t="n"/>
       <c r="AQ40" s="15" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
+      <c r="AR40" s="15" t="n"/>
+    </row>
+    <row r="41">
       <c r="A41" s="17" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="15" t="n"/>
@@ -7447,8 +7874,9 @@
       <c r="AO41" s="15" t="n"/>
       <c r="AP41" s="15" t="n"/>
       <c r="AQ41" s="15" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+      <c r="AR41" s="15" t="n"/>
+    </row>
+    <row r="42">
       <c r="A42" s="17" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="15" t="n"/>
@@ -7492,8 +7920,9 @@
       <c r="AO42" s="15" t="n"/>
       <c r="AP42" s="15" t="n"/>
       <c r="AQ42" s="15" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
+      <c r="AR42" s="15" t="n"/>
+    </row>
+    <row r="43">
       <c r="A43" s="17" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="15" t="n"/>
@@ -7537,8 +7966,9 @@
       <c r="AO43" s="15" t="n"/>
       <c r="AP43" s="15" t="n"/>
       <c r="AQ43" s="15" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+      <c r="AR43" s="15" t="n"/>
+    </row>
+    <row r="44">
       <c r="A44" s="17" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="15" t="n"/>
@@ -7582,8 +8012,9 @@
       <c r="AO44" s="15" t="n"/>
       <c r="AP44" s="15" t="n"/>
       <c r="AQ44" s="15" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+      <c r="AR44" s="15" t="n"/>
+    </row>
+    <row r="45">
       <c r="A45" s="17" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="15" t="n"/>
@@ -7627,8 +8058,9 @@
       <c r="AO45" s="15" t="n"/>
       <c r="AP45" s="15" t="n"/>
       <c r="AQ45" s="15" t="n"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
+      <c r="AR45" s="15" t="n"/>
+    </row>
+    <row r="46">
       <c r="A46" s="17" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="15" t="n"/>
@@ -7672,8 +8104,9 @@
       <c r="AO46" s="15" t="n"/>
       <c r="AP46" s="15" t="n"/>
       <c r="AQ46" s="15" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+      <c r="AR46" s="15" t="n"/>
+    </row>
+    <row r="47">
       <c r="A47" s="17" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="15" t="n"/>
@@ -7717,8 +8150,9 @@
       <c r="AO47" s="15" t="n"/>
       <c r="AP47" s="15" t="n"/>
       <c r="AQ47" s="15" t="n"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
+      <c r="AR47" s="15" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="17" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="15" t="n"/>
@@ -7762,8 +8196,9 @@
       <c r="AO48" s="15" t="n"/>
       <c r="AP48" s="15" t="n"/>
       <c r="AQ48" s="15" t="n"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
+      <c r="AR48" s="15" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="17" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="15" t="n"/>
@@ -7807,8 +8242,9 @@
       <c r="AO49" s="15" t="n"/>
       <c r="AP49" s="15" t="n"/>
       <c r="AQ49" s="15" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+      <c r="AR49" s="15" t="n"/>
+    </row>
+    <row r="50">
       <c r="A50" s="17" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="15" t="n"/>
@@ -7852,8 +8288,9 @@
       <c r="AO50" s="15" t="n"/>
       <c r="AP50" s="15" t="n"/>
       <c r="AQ50" s="15" t="n"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
+      <c r="AR50" s="15" t="n"/>
+    </row>
+    <row r="51">
       <c r="A51" s="17" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="15" t="n"/>
@@ -7897,8 +8334,9 @@
       <c r="AO51" s="15" t="n"/>
       <c r="AP51" s="15" t="n"/>
       <c r="AQ51" s="15" t="n"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
+      <c r="AR51" s="15" t="n"/>
+    </row>
+    <row r="52">
       <c r="A52" s="17" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="15" t="n"/>
@@ -7942,106 +8380,16 @@
       <c r="AO52" s="15" t="n"/>
       <c r="AP52" s="15" t="n"/>
       <c r="AQ52" s="15" t="n"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="15" t="n"/>
-      <c r="D53" s="15" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
-      <c r="H53" s="15" t="n"/>
-      <c r="I53" s="15" t="n"/>
-      <c r="J53" s="15" t="n"/>
-      <c r="K53" s="15" t="n"/>
-      <c r="L53" s="15" t="n"/>
-      <c r="M53" s="15" t="n"/>
-      <c r="N53" s="15" t="n"/>
-      <c r="O53" s="15" t="n"/>
-      <c r="P53" s="15" t="n"/>
-      <c r="Q53" s="15" t="n"/>
-      <c r="R53" s="15" t="n"/>
-      <c r="S53" s="15" t="n"/>
-      <c r="T53" s="15" t="n"/>
-      <c r="U53" s="15" t="n"/>
-      <c r="V53" s="15" t="n"/>
-      <c r="W53" s="15" t="n"/>
-      <c r="X53" s="15" t="n"/>
-      <c r="Y53" s="15" t="n"/>
-      <c r="Z53" s="15" t="n"/>
-      <c r="AA53" s="15" t="n"/>
-      <c r="AB53" s="15" t="n"/>
-      <c r="AC53" s="15" t="n"/>
-      <c r="AD53" s="15" t="n"/>
-      <c r="AE53" s="15" t="n"/>
-      <c r="AF53" s="15" t="n"/>
-      <c r="AG53" s="15" t="n"/>
-      <c r="AH53" s="15" t="n"/>
-      <c r="AI53" s="15" t="n"/>
-      <c r="AJ53" s="15" t="n"/>
-      <c r="AK53" s="15" t="n"/>
-      <c r="AL53" s="15" t="n"/>
-      <c r="AM53" s="15" t="n"/>
-      <c r="AN53" s="15" t="n"/>
-      <c r="AO53" s="15" t="n"/>
-      <c r="AP53" s="15" t="n"/>
-      <c r="AQ53" s="15" t="n"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="15" t="n"/>
-      <c r="D54" s="15" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="15" t="n"/>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="15" t="n"/>
-      <c r="K54" s="15" t="n"/>
-      <c r="L54" s="15" t="n"/>
-      <c r="M54" s="15" t="n"/>
-      <c r="N54" s="15" t="n"/>
-      <c r="O54" s="15" t="n"/>
-      <c r="P54" s="15" t="n"/>
-      <c r="Q54" s="15" t="n"/>
-      <c r="R54" s="15" t="n"/>
-      <c r="S54" s="15" t="n"/>
-      <c r="T54" s="15" t="n"/>
-      <c r="U54" s="15" t="n"/>
-      <c r="V54" s="15" t="n"/>
-      <c r="W54" s="15" t="n"/>
-      <c r="X54" s="15" t="n"/>
-      <c r="Y54" s="15" t="n"/>
-      <c r="Z54" s="15" t="n"/>
-      <c r="AA54" s="15" t="n"/>
-      <c r="AB54" s="15" t="n"/>
-      <c r="AC54" s="15" t="n"/>
-      <c r="AD54" s="15" t="n"/>
-      <c r="AE54" s="15" t="n"/>
-      <c r="AF54" s="15" t="n"/>
-      <c r="AG54" s="15" t="n"/>
-      <c r="AH54" s="15" t="n"/>
-      <c r="AI54" s="15" t="n"/>
-      <c r="AJ54" s="15" t="n"/>
-      <c r="AK54" s="15" t="n"/>
-      <c r="AL54" s="15" t="n"/>
-      <c r="AM54" s="15" t="n"/>
-      <c r="AN54" s="15" t="n"/>
-      <c r="AO54" s="15" t="n"/>
-      <c r="AP54" s="15" t="n"/>
-      <c r="AQ54" s="15" t="n"/>
+      <c r="AR52" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B5:E5"/>
@@ -8058,15 +8406,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="8.28515625" customWidth="1" style="29" min="1" max="1"/>
     <col width="13" customWidth="1" style="29" min="2" max="2"/>
     <col width="48.42578125" customWidth="1" style="29" min="3" max="3"/>
     <col width="42.85546875" customWidth="1" style="29" min="4" max="4"/>
-    <col width="28.5703125" customWidth="1" style="29" min="5" max="7"/>
-    <col width="8.85546875" customWidth="1" style="29" min="8" max="16384"/>
+    <col width="28.5703125" customWidth="1" style="29" min="5" max="5"/>
+    <col width="26.7109375" customWidth="1" style="29" min="6" max="8"/>
+    <col width="8.85546875" customWidth="1" style="29" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8077,7 +8426,7 @@
       </c>
       <c r="B1" s="28" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Define relationships between schemas by mapping properties from one schema to another (e.g., foreign keys).</t>
@@ -8085,13 +8434,20 @@
       </c>
       <c r="B2" s="30" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Use schema.property dot syntax (e.g., orders.customer_id). Comma-separated for composite keys. Level: 'schema' or 'property'.</t>
         </is>
       </c>
       <c r="B3" s="30" t="n"/>
+      <c r="F3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="G3" s="44" t="n"/>
+      <c r="H3" s="44" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -8119,18 +8475,11 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="31" t="n"/>
+      <c r="H4" s="31" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>schema</t>
@@ -8151,13 +8500,16 @@
           <t>orders.order_id</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>rel-orders</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="17" t="n"/>
+      <c r="H5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
           <t>property</t>
@@ -8178,123 +8530,169 @@
           <t>orders.order_id</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>rel-order</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="17" t="n"/>
       <c r="B7" s="17" t="n"/>
       <c r="C7" s="15" t="n"/>
       <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-    </row>
-    <row r="8">
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="17" t="n"/>
       <c r="B8" s="17" t="n"/>
       <c r="C8" s="15" t="n"/>
       <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-    </row>
-    <row r="9">
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="17" t="n"/>
       <c r="B9" s="17" t="n"/>
       <c r="C9" s="15" t="n"/>
       <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-    </row>
-    <row r="10">
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="17" t="n"/>
       <c r="B10" s="17" t="n"/>
       <c r="C10" s="15" t="n"/>
       <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-    </row>
-    <row r="11">
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="17" t="n"/>
       <c r="B11" s="17" t="n"/>
       <c r="C11" s="15" t="n"/>
       <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-    </row>
-    <row r="12">
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="17" t="n"/>
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="15" t="n"/>
       <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-    </row>
-    <row r="13">
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="17" t="n"/>
       <c r="B13" s="17" t="n"/>
       <c r="C13" s="15" t="n"/>
       <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-    </row>
-    <row r="14">
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="17" t="n"/>
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="15" t="n"/>
       <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-    </row>
-    <row r="15">
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="17" t="n"/>
       <c r="B15" s="17" t="n"/>
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-    </row>
-    <row r="16">
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="17" t="n"/>
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="15" t="n"/>
       <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-    </row>
-    <row r="17">
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="17" t="n"/>
       <c r="B17" s="17" t="n"/>
       <c r="C17" s="15" t="n"/>
       <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-    </row>
-    <row r="18">
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="17" t="n"/>
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="15" t="n"/>
       <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-    </row>
-    <row r="19">
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="17" t="n"/>
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="15" t="n"/>
       <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-    </row>
-    <row r="20">
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="17" t="n"/>
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-    </row>
-    <row r="21">
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="17" t="n"/>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="15" t="n"/>
       <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
-      <formula>C5="sql"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <mergeCells count="1">
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
   <dataValidations count="8">
     <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Description" prompt="A human-readable description of the relationship. Explain the business context or purpose of how the source and target are related."/>
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Type" prompt="Type of the relationship column(s)."/>
@@ -8320,27 +8718,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.5703125" customWidth="1" min="1" max="4"/>
     <col width="47.5703125" customWidth="1" min="5" max="5"/>
-    <col width="28.5703125" customWidth="1" min="6" max="9"/>
+    <col width="28.5703125" customWidth="1" min="6" max="7"/>
+    <col width="26.7109375" customWidth="1" min="8" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Enum</t>
+          <t>Enums</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Allowed values of a property. Use schema.property dot syntax for the property (e.g. orders.status).</t>
-        </is>
-      </c>
+          <t>Restrict the allowed values of a property. Use one row per accepted value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="H3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="I3" s="44" t="n"/>
+      <c r="J3" s="44" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -8380,297 +8788,310 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Delivered</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>Delivered to the customer</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>The carrier confirmed the delivery.</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>final</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>enum-delivered</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
-        <is>
-          <t>color</t>
-        </is>
-      </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="H5" s="36" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
+      <c r="I5" s="36" t="n"/>
+      <c r="J5" s="36" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>In Transit</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>On its way</t>
         </is>
       </c>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
-      <c r="I6" s="35" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Lost</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>Numeric legacy code</t>
         </is>
       </c>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>address.country</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>address.country</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8681,12 +9102,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.5703125" customWidth="1" min="1" max="3"/>
     <col width="47.5703125" customWidth="1" min="4" max="4"/>
-    <col width="28.5703125" customWidth="1" min="5" max="10"/>
+    <col width="28.5703125" customWidth="1" min="5" max="8"/>
+    <col width="26.7109375" customWidth="1" min="9" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -8703,6 +9125,15 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="I3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="J3" s="44" t="n"/>
+      <c r="K3" s="44" t="n"/>
+    </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -8746,266 +9177,279 @@
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>glossaryId</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Sendungen</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>German name</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>de-DE</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>business glossary</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="H5" s="35" t="n"/>
-      <c r="I5" s="35" t="inlineStr">
-        <is>
-          <t>glossaryId</t>
-        </is>
-      </c>
-      <c r="J5" s="35" t="n">
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="36" t="n">
         <v>4711</v>
       </c>
+      <c r="J5" s="36" t="n"/>
+      <c r="K5" s="36" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Sendungsnummer</t>
         </is>
       </c>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>de-DE</t>
         </is>
       </c>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
-      <c r="I6" s="35" t="n"/>
-      <c r="J6" s="35" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
+      <c r="J6" s="36" t="n"/>
+      <c r="K6" s="36" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
-      <c r="I7" s="35" t="n"/>
-      <c r="J7" s="35" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
+      <c r="J7" s="36" t="n"/>
+      <c r="K7" s="36" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="35" t="n"/>
-      <c r="J8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="35" t="n"/>
-      <c r="J9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
+      <c r="K9" s="36" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="35" t="n"/>
-      <c r="J11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="36" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="35" t="n"/>
-      <c r="J15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="35" t="n"/>
-      <c r="J17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
-      <c r="J19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I3:K3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9016,12 +9460,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.5703125" customWidth="1" min="1" max="2"/>
     <col width="57.140625" customWidth="1" min="3" max="4"/>
-    <col width="28.5703125" customWidth="1" min="5" max="8"/>
+    <col width="28.5703125" customWidth="1" min="5" max="6"/>
+    <col width="26.7109375" customWidth="1" min="7" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -9038,6 +9483,15 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="H3" s="44" t="n"/>
+      <c r="I3" s="44" t="n"/>
+    </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -9071,234 +9525,247 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>verifiedBy</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Does this table contain cancelled shipments?</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>No, cancelled shipments are excluded before loading.</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>completeness</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>vs-cancelled</t>
         </is>
       </c>
-      <c r="G5" s="35" t="inlineStr">
-        <is>
-          <t>verifiedBy</t>
-        </is>
-      </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>data-steward</t>
         </is>
       </c>
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="36" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Is weight_kg always populated?</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>No, it is null for letters.</t>
         </is>
       </c>
-      <c r="E6" s="35" t="n"/>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>vs-weight</t>
         </is>
       </c>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="35" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="36" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
-      <c r="H8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
-      <c r="H16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Contract,Schema"</formula1>
@@ -9314,12 +9781,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.5703125" customWidth="1" min="1" max="2"/>
     <col width="66.7109375" customWidth="1" min="3" max="3"/>
-    <col width="28.5703125" customWidth="1" min="4" max="7"/>
+    <col width="28.5703125" customWidth="1" min="4" max="5"/>
+    <col width="26.7109375" customWidth="1" min="6" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -9336,6 +9804,15 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="F3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="G3" s="44" t="n"/>
+      <c r="H3" s="44" t="n"/>
+    </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -9362,203 +9839,216 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n"/>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Do not join to customer PII without a legal basis.</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>privacy</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>c-pii</t>
         </is>
       </c>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="n"/>
+      <c r="H5" s="36" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>shipments</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Never aggregate weight_kg across carriers.</t>
         </is>
       </c>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>c-weight</t>
         </is>
       </c>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="35" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="35" t="n"/>
-      <c r="C7" s="35" t="n"/>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="35" t="n"/>
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="35" t="n"/>
-      <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="35" t="n"/>
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
-      <c r="C9" s="35" t="n"/>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
+      <c r="A15" s="36" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="35" t="n"/>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="35" t="n"/>
-      <c r="G20" s="35" t="n"/>
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="A5:A1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Contract,Schema"</formula1>
@@ -9574,7 +10064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col width="17.42578125" customWidth="1" style="29" min="1" max="1"/>
@@ -9590,8 +10080,9 @@
     <col width="15.42578125" bestFit="1" customWidth="1" style="29" min="11" max="11"/>
     <col width="17.85546875" bestFit="1" customWidth="1" style="29" min="12" max="12"/>
     <col width="17.85546875" customWidth="1" style="29" min="13" max="13"/>
-    <col width="28.5703125" customWidth="1" style="29" min="14" max="16"/>
-    <col width="8.85546875" customWidth="1" style="29" min="17" max="16384"/>
+    <col width="28.5703125" customWidth="1" style="29" min="14" max="14"/>
+    <col width="26.7109375" customWidth="1" style="29" min="15" max="17"/>
+    <col width="8.85546875" customWidth="1" style="29" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -9602,17 +10093,24 @@
       </c>
       <c r="B1" s="28" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>This section describes data quality rules &amp; parameters. They are tightly linked to the schema described in the previous sheet(s).</t>
+          <t>Add quality rules to the schemas of the contract or their properties.</t>
         </is>
       </c>
       <c r="B2" s="30" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="30" t="n"/>
       <c r="B3" s="30" t="n"/>
+      <c r="O3" s="41" t="inlineStr">
+        <is>
+          <t>Custom Properties (add as needed)</t>
+        </is>
+      </c>
+      <c r="P3" s="44" t="n"/>
+      <c r="Q3" s="44" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -9687,14 +10185,11 @@
       </c>
       <c r="O4" s="31" t="inlineStr">
         <is>
-          <t>Custom Property</t>
-        </is>
-      </c>
-      <c r="P4" s="31" t="inlineStr">
-        <is>
-          <t>Custom Value</t>
-        </is>
-      </c>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="P4" s="31" t="n"/>
+      <c r="Q4" s="31" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -9734,11 +10229,14 @@
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
       <c r="M5" s="15" t="n"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t>q-rowcount</t>
         </is>
       </c>
+      <c r="O5" s="17" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -9770,21 +10268,18 @@
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="15" t="n"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>q-status-values</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>quality-team</t>
         </is>
       </c>
+      <c r="P6" s="17" t="n"/>
+      <c r="Q6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n"/>
@@ -9800,6 +10295,10 @@
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
       <c r="M7" s="15" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n"/>
@@ -9815,6 +10314,10 @@
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
       <c r="M8" s="15" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="17" t="n"/>
+      <c r="P8" s="17" t="n"/>
+      <c r="Q8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="n"/>
@@ -9830,6 +10333,10 @@
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="15" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="n"/>
+      <c r="P9" s="17" t="n"/>
+      <c r="Q9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="n"/>
@@ -9845,6 +10352,10 @@
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
       <c r="M10" s="15" t="n"/>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="17" t="n"/>
+      <c r="Q10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="n"/>
@@ -9860,6 +10371,10 @@
       <c r="K11" s="15" t="n"/>
       <c r="L11" s="15" t="n"/>
       <c r="M11" s="15" t="n"/>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="17" t="n"/>
+      <c r="P11" s="17" t="n"/>
+      <c r="Q11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="n"/>
@@ -9875,6 +10390,10 @@
       <c r="K12" s="15" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="17" t="n"/>
+      <c r="P12" s="17" t="n"/>
+      <c r="Q12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="n"/>
@@ -9890,6 +10409,10 @@
       <c r="K13" s="15" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="17" t="n"/>
+      <c r="P13" s="17" t="n"/>
+      <c r="Q13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="n"/>
@@ -9905,6 +10428,10 @@
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="17" t="n"/>
+      <c r="P14" s="17" t="n"/>
+      <c r="Q14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="n"/>
@@ -9920,6 +10447,10 @@
       <c r="K15" s="15" t="n"/>
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="15" t="n"/>
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="17" t="n"/>
+      <c r="P15" s="17" t="n"/>
+      <c r="Q15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n"/>
@@ -9935,6 +10466,10 @@
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
       <c r="M16" s="15" t="n"/>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="17" t="n"/>
+      <c r="P16" s="17" t="n"/>
+      <c r="Q16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="n"/>
@@ -9950,6 +10485,10 @@
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
+      <c r="N17" s="17" t="n"/>
+      <c r="O17" s="17" t="n"/>
+      <c r="P17" s="17" t="n"/>
+      <c r="Q17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="n"/>
@@ -9965,6 +10504,10 @@
       <c r="K18" s="15" t="n"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
+      <c r="N18" s="17" t="n"/>
+      <c r="O18" s="17" t="n"/>
+      <c r="P18" s="17" t="n"/>
+      <c r="Q18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="n"/>
@@ -9980,6 +10523,10 @@
       <c r="K19" s="15" t="n"/>
       <c r="L19" s="15" t="n"/>
       <c r="M19" s="15" t="n"/>
+      <c r="N19" s="17" t="n"/>
+      <c r="O19" s="17" t="n"/>
+      <c r="P19" s="17" t="n"/>
+      <c r="Q19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="n"/>
@@ -9995,6 +10542,10 @@
       <c r="K20" s="15" t="n"/>
       <c r="L20" s="15" t="n"/>
       <c r="M20" s="15" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="17" t="n"/>
+      <c r="P20" s="17" t="n"/>
+      <c r="Q20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="n"/>
@@ -10010,15 +10561,22 @@
       <c r="K21" s="15" t="n"/>
       <c r="L21" s="15" t="n"/>
       <c r="M21" s="15" t="n"/>
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="17" t="n"/>
+      <c r="P21" s="17" t="n"/>
+      <c r="Q21" s="17" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="O3:Q3"/>
+  </mergeCells>
   <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="1" dxfId="2" stopIfTrue="1">
       <formula>C5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F21">
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="2" dxfId="2" stopIfTrue="1">
       <formula>C5="library"</formula>
     </cfRule>
   </conditionalFormatting>
